--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,135 +613,125 @@
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>bcb_sgs_cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -835,32 +825,30 @@
         <v>5.1216</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -877,8 +865,6 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -996,78 +982,72 @@
         <v>5.1433</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1187,78 +1167,72 @@
         <v>5.4394</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.757676</v>
+        <v>2.329166</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1378,78 +1352,72 @@
         <v>5.643</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1569,78 +1537,72 @@
         <v>5.6199</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="AN6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="AO6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="AP6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="AU6" t="n">
-        <v>367772</v>
+        <v>1.599501</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.599501</v>
+        <v>1.372425</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.372425</v>
+        <v>-0.409357</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.409357</v>
+        <v>1.896096</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1760,78 +1722,72 @@
         <v>5.5805</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
+        <v>1.856332</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.701155</v>
+        <v>2.135418</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1951,78 +1907,72 @@
         <v>5.3574</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="AW8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
+        <v>-0.015397</v>
       </c>
       <c r="AY8" t="n">
-        <v>-3.99828</v>
+        <v>-1.385541</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2142,78 +2092,72 @@
         <v>5.1394</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
+        <v>0.975774</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.069594</v>
+        <v>1.257759</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2333,78 +2277,72 @@
         <v>4.7378</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
+        <v>1.412174</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.815054</v>
+        <v>1.146068</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2524,78 +2462,72 @@
         <v>4.9191</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
+        <v>0.816526</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.827155</v>
+        <v>0.461006</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2715,78 +2647,72 @@
         <v>4.7289</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="AN12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="AO12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="AP12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
+        <v>1.151595</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.867033</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2906,84 +2832,78 @@
         <v>5.238</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="AN13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="AO13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="AP13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>1.558597</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>1.928912</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>-1.286607</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>11.88673</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>10.700862</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3103,84 +3023,78 @@
         <v>5.1884</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="AN14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="AO14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="AP14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>0.677481</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>-0.269467</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>1.299867</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>10.069235</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>10.074751</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3300,84 +3214,78 @@
         <v>5.179</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="AN15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="AO15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="AP15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>1.469562</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>0.837552</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3497,84 +3405,78 @@
         <v>5.4066</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="AN16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="AO16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="AP16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>1.814888</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>2.210221</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3694,84 +3596,78 @@
         <v>5.257</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="AN17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="AO17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="AP17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>0.991621</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>-0.187221</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3891,84 +3787,78 @@
         <v>5.2941</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="AN18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="AO18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="AP18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>1.335643</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>1.161333</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4088,84 +3978,78 @@
         <v>5.2177</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="AN19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="AO19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="AP19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>1.521325</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>2.249624</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="BG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH19" t="n">
         <v>0</v>
       </c>
-      <c r="BH19" t="n">
-        <v>-0</v>
-      </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4285,84 +4169,78 @@
         <v>5.0993</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="AN20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="AO20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="AP20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="AW20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>0.133468</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>-1.232052</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4482,84 +4360,78 @@
         <v>5.2078</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="AN21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="AO21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="AP21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>-0.042451</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>-0.710886</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4679,84 +4551,78 @@
         <v>5.0804</v>
       </c>
       <c r="AM22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="AN22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="AO22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="AP22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>1.002821</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>0.879872</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4876,84 +4742,78 @@
         <v>5.0007</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="AN23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="AO23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="AP23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>0.027577</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>-0.459418</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5073,84 +4933,78 @@
         <v>5.0959</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="AN24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="AO24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="AP24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>0.504966</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>0.024709</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5270,84 +5124,78 @@
         <v>4.8192</v>
       </c>
       <c r="AM25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="AN25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="AO25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="AP25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="AU25" t="n">
-        <v>343620</v>
+        <v>-0.06297</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.06297</v>
+        <v>-0.424293</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.424293</v>
+        <v>-5.429855</v>
       </c>
       <c r="AX25" t="n">
-        <v>-5.429855</v>
+        <v>0.472174</v>
       </c>
       <c r="AY25" t="n">
-        <v>-5.430495</v>
+        <v>1.122473</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="BE25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5467,84 +5315,78 @@
         <v>4.7415</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="AN26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="AO26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="AP26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>0.098769</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>-0.740777</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5664,84 +5506,78 @@
         <v>4.9219</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="AN27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="AO27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="AP27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>1.352666</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>0.887701</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BI27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5861,84 +5697,78 @@
         <v>5.0076</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="AN28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="AO28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="AP28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="AW28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>1.203116</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>1.956912</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6058,84 +5888,78 @@
         <v>5.0575</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="AN29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="AO29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>0.495259</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>-0.467999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BI29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6255,84 +6079,78 @@
         <v>4.9355</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="AN30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="AO30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="AP30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>1.013388</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>0.723782</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BI30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6452,84 +6270,78 @@
         <v>4.8413</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="AN31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="AO31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="AP31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>1.646862</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>2.824206</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6649,84 +6461,78 @@
         <v>4.9535</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="AN32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="AO32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="AP32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="AW32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>-0.180012</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>-2.151229</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6846,84 +6652,78 @@
         <v>4.9833</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="AN33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="AO33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="AP33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>0.366662</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>0.04207</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BI33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7043,84 +6843,78 @@
         <v>4.9962</v>
       </c>
       <c r="AM34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="AN34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="AO34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="AP34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>1.440658</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>2.257995</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7240,84 +7034,78 @@
         <v>5.1718</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="AN35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="AO35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="AP35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>0.267741</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7437,84 +7225,78 @@
         <v>5.2416</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="AN36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="AO36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="AP36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>0.64951</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>0.415624</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BI36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7634,84 +7416,78 @@
         <v>5.5589</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="AN37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="AO37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="AP37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>1.476967</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>2.569845</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7831,84 +7607,78 @@
         <v>5.6621</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="AN38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="AO38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="AP38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>0.451961</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>-0.577528</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8028,84 +7798,78 @@
         <v>5.6562</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="AN39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="AO39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="AP39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>1.088989</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>0.905369</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8225,84 +7989,78 @@
         <v>5.4481</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="AN40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="AO40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="AP40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>1.323978</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>1.72458</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8422,84 +8180,78 @@
         <v>5.7779</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="AN41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="AO41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="AP41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>0.532743</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8619,84 +8371,78 @@
         <v>6.0535</v>
       </c>
       <c r="AM42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="AN42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="AO42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="AP42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>1.443368</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>1.605359</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8816,84 +8562,78 @@
         <v>6.1923</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="AN43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="AO43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="AP43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>1.55383</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>2.592546</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9013,84 +8753,78 @@
         <v>5.8301</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="AN44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="AO44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="AP44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="AW44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>0.006404</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>-1.889422</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9210,84 +8944,78 @@
         <v>5.8488</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="AN45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="AO45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="AP45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>1.027506</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9407,84 +9135,78 @@
         <v>5.7422</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="AN46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="AO46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="AP46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>0.99855</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>0.852229</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9604,84 +9326,78 @@
         <v>5.6608</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="AN47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="AO47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="AP47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>0.722029</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>0.566954</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9801,84 +9517,78 @@
         <v>5.7087</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="AN48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="AO48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="AP48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.639181</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>0.807268</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9998,84 +9708,78 @@
         <v>5.4571</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="AN49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="AO49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="AP49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>0.591659</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10195,84 +9899,78 @@
         <v>5.6021</v>
       </c>
       <c r="AM50" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="AN50" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="AO50" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="AP50" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="AT50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="AU50" t="n">
-        <v>345111</v>
+        <v>-0.410362</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.410362</v>
+        <v>5.358126</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.358126</v>
+        <v>2.657089</v>
       </c>
       <c r="AX50" t="n">
-        <v>2.657089</v>
+        <v>0.440744</v>
       </c>
       <c r="AY50" t="n">
-        <v>2.657381</v>
+        <v>-0.129254</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="BA50" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="BB50" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="BC50" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="BH50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10392,84 +10090,78 @@
         <v>5.4264</v>
       </c>
       <c r="AM51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="AN51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="AO51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="AP51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>0.612293</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>0.073298</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10589,84 +10281,78 @@
         <v>5.3186</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="AN52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="AO52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="AP52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>1.155358</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>1.710427</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10786,84 +10472,78 @@
         <v>5.3843</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="AN53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="AO53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="AP53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="AU53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.235287</v>
+        <v>1.038729</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.235427</v>
+        <v>0.301682</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10983,84 +10663,78 @@
         <v>5.3338</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="AN54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="AO54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="AP54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="AW54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>1.146567</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>0.715383</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>1.405488</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>0.973109</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>4.461836</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="BI54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11180,84 +10854,78 @@
         <v>5.5024</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="AN55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="AO55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="AP55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>1.90144</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>3.24641</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>1.099346</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>-0.650067</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>4.264385</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>0</v>
       </c>
-      <c r="BI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11377,84 +11045,78 @@
         <v>5.2301</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="AN56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="AO56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="AP56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="AW56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>-0.083179</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>-1.743482</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>0.927966</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>1.712009</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>4.441351</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11574,84 +11236,78 @@
         <v>5.1495</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="AN57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="AO57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="AP57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>0.371461</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>0.070797</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>0.549722</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>1.840727</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>3.812497</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11771,84 +11427,78 @@
         <v>5.2194</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="AN58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="AO58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="AP58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="AQ58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>1.12824</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>1.133877</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>1.124914</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>-2.444795</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>4.142847</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BI58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11968,84 +11618,78 @@
         <v>4.9886</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="AN59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="AO59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="AP59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>0.288267</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>-0.052977</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>0.489642</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>1.356622</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>4.39172</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BI59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12161,80 +11805,74 @@
         <v>5.0569</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="AN60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="AO60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="AP60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="AQ60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="AU60" t="n">
         <v>371137</v>
       </c>
+      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
+      <c r="AW60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>0.565068</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>0.742264</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>1.151227</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12345,139 +11983,133 @@
       <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AM61" t="n">
-        <v>5.176</v>
-      </c>
+      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="n">
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
+      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="n">
+      <c r="AW61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AY61" t="n">
-        <v>2.367344</v>
-      </c>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="inlineStr"/>
+      <c r="BA61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="BD61" t="inlineStr"/>
       <c r="BE61" t="n">
-        <v>3.177699</v>
-      </c>
-      <c r="BF61" t="inlineStr"/>
+        <v>-0.25</v>
+      </c>
+      <c r="BF61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="BG61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>170654</v>
+        <v>171260.59375</v>
       </c>
       <c r="C62" t="n">
-        <v>167.559998</v>
+        <v>168.350006</v>
       </c>
       <c r="D62" t="n">
-        <v>105.550003</v>
+        <v>105.809998</v>
       </c>
       <c r="E62" t="n">
-        <v>433.700012</v>
+        <v>435.450012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1431</v>
+        <v>5.1453</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8966</v>
+        <v>5.8964</v>
       </c>
       <c r="H62" t="n">
-        <v>7482.709961</v>
+        <v>7492.100098</v>
       </c>
       <c r="I62" t="n">
-        <v>25870.650391</v>
+        <v>25918.525391</v>
       </c>
       <c r="J62" t="n">
-        <v>52348.390625</v>
+        <v>52299.730469</v>
       </c>
       <c r="K62" t="n">
-        <v>4125.299805</v>
+        <v>4133.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>73.989998</v>
+        <v>73.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>78.650002</v>
+        <v>77.910004</v>
       </c>
       <c r="N62" t="n">
-        <v>1187.5</v>
+        <v>1185.5</v>
       </c>
       <c r="O62" t="n">
-        <v>451</v>
+        <v>451.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.796401</v>
+        <v>-0.443779</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.881399</v>
+        <v>-0.414077</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.250417</v>
+        <v>-2.009637</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.447603</v>
+        <v>-0.045904</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.7466</v>
+        <v>-0.704141</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.347468</v>
+        <v>-0.350845</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.222018</v>
+        <v>-0.096805</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.308743</v>
+        <v>-1.12611</v>
       </c>
       <c r="X62" t="n">
-        <v>0.055795</v>
+        <v>-0.037211</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.545425</v>
+        <v>2.754239</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.460429</v>
+        <v>5.223018</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.857931</v>
+        <v>6.843123</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.335348</v>
+        <v>6.156257</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.267111</v>
+        <v>9.388249999999999</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12496,9 +12128,7 @@
       <c r="AL62" t="n">
         <v>5.1552</v>
       </c>
-      <c r="AM62" t="n">
-        <v>5.1546</v>
-      </c>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12508,33 +12138,29 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="n">
+      <c r="AW62" t="n">
         <v>-0.413399</v>
       </c>
-      <c r="AY62" t="n">
-        <v>-0.413447</v>
-      </c>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,125 +613,135 @@
       </c>
       <c r="AM1" t="inlineStr">
         <is>
+          <t>bcb_sgs_cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_cambio_compra_usd</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -825,30 +835,32 @@
         <v>5.1216</v>
       </c>
       <c r="AM2" t="n">
+        <v>5.121</v>
+      </c>
+      <c r="AN2" t="n">
         <v>4271865</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>1833179</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>2438686</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>2.94</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>355671</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -865,6 +877,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -982,72 +996,78 @@
         <v>5.1433</v>
       </c>
       <c r="AM3" t="n">
+        <v>5.1427</v>
+      </c>
+      <c r="AN3" t="n">
         <v>4346060</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>1851006</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>2495054</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
+        <v>0.423745</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BA3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BB3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>1</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BI3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BJ3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BK3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BL3" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1167,72 +1187,78 @@
         <v>5.4394</v>
       </c>
       <c r="AM4" t="n">
+        <v>5.4388</v>
+      </c>
+      <c r="AN4" t="n">
         <v>4441056</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>1894119</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>2546936</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>2.34</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>368886</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
+        <v>5.757676</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BA4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BB4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>1</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BI4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BJ4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BK4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BL4" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1352,72 +1378,78 @@
         <v>5.643</v>
       </c>
       <c r="AM5" t="n">
+        <v>5.6424</v>
+      </c>
+      <c r="AN5" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>2.99</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>367927</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
+        <v>3.743473</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BB5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BI5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BJ5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BK5" t="n">
         <v>0</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1537,72 +1569,78 @@
         <v>5.6199</v>
       </c>
       <c r="AM6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="AN6" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>367772</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BA6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BB6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BI6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BK6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1722,72 +1760,78 @@
         <v>5.5805</v>
       </c>
       <c r="AM7" t="n">
+        <v>5.5799</v>
+      </c>
+      <c r="AN7" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>3.05</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>362204</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
+        <v>-0.701155</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BA7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BB7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BI7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BJ7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BK7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BL7" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1907,72 +1951,78 @@
         <v>5.3574</v>
       </c>
       <c r="AM8" t="n">
+        <v>5.3568</v>
+      </c>
+      <c r="AN8" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>3.26</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>358398</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
+        <v>-3.99828</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BA8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BB8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
         <v>0</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BI8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BJ8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BK8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>0.21</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2092,72 +2142,78 @@
         <v>5.1394</v>
       </c>
       <c r="AM9" t="n">
+        <v>5.1388</v>
+      </c>
+      <c r="AN9" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>3.38</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>357740</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
+        <v>-4.069594</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BA9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BB9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BI9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BJ9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BK9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
         <v>0.12</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2277,72 +2333,78 @@
         <v>4.7378</v>
       </c>
       <c r="AM10" t="n">
+        <v>4.7372</v>
+      </c>
+      <c r="AN10" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>353169</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
+        <v>-7.815054</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BB10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>1</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BI10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BK10" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2462,72 +2524,78 @@
         <v>4.9191</v>
       </c>
       <c r="AM11" t="n">
+        <v>4.9185</v>
+      </c>
+      <c r="AN11" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>3.54</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>345097</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
+        <v>3.827155</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BA11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BB11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BI11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BJ11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BK11" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2647,72 +2715,78 @@
         <v>4.7289</v>
       </c>
       <c r="AM12" t="n">
+        <v>4.7283</v>
+      </c>
+      <c r="AN12" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>346415</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
+        <v>-3.867033</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BA12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BB12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
         <v>1</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BI12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2832,78 +2906,84 @@
         <v>5.238</v>
       </c>
       <c r="AM13" t="n">
+        <v>5.2374</v>
+      </c>
+      <c r="AN13" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>3.57</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>341958</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
+        <v>10.767083</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BA13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BB13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BE13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BF13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BG13" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BI13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BJ13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3023,78 +3103,84 @@
         <v>5.1884</v>
       </c>
       <c r="AM14" t="n">
+        <v>5.1878</v>
+      </c>
+      <c r="AN14" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>346403</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
+        <v>-0.947035</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BA14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BB14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BD14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BE14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BF14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BI14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BJ14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BK14" t="n">
         <v>0.08</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>0.14</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3214,78 +3300,84 @@
         <v>5.179</v>
       </c>
       <c r="AM15" t="n">
+        <v>5.1784</v>
+      </c>
+      <c r="AN15" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>339664</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
+        <v>-0.181194</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BA15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BB15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BC15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BD15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BE15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BF15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BG15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BI15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BJ15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BK15" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3405,78 +3497,84 @@
         <v>5.4066</v>
       </c>
       <c r="AM16" t="n">
+        <v>5.406</v>
+      </c>
+      <c r="AN16" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AO16" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>327580</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
+        <v>4.39518</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BA16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BB16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BC16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BD16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BE16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BF16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BG16" t="n">
         <v>0</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BI16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3596,78 +3694,84 @@
         <v>5.257</v>
       </c>
       <c r="AM17" t="n">
+        <v>5.2564</v>
+      </c>
+      <c r="AN17" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>325546</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
+        <v>-2.767296</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BA17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BB17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BC17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BD17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BE17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BF17" t="n">
         <v>6.460076</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BK17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BL17" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3787,78 +3891,84 @@
         <v>5.2941</v>
       </c>
       <c r="AM18" t="n">
+        <v>5.2935</v>
+      </c>
+      <c r="AN18" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AS18" t="n">
         <v>3.92</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>331505</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
+        <v>0.705806</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BA18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BB18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BC18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BD18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BF18" t="n">
         <v>5.974439</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3978,78 +4088,84 @@
         <v>5.2177</v>
       </c>
       <c r="AM19" t="n">
+        <v>5.2171</v>
+      </c>
+      <c r="AN19" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>3.94</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>324703</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
+        <v>-1.443279</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BA19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BB19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BC19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BD19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BE19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BF19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BG19" t="n">
         <v>0</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BH19" t="n">
         <v>-0</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BI19" t="n">
         <v>-0</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BJ19" t="n">
         <v>0</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BK19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4169,78 +4285,84 @@
         <v>5.0993</v>
       </c>
       <c r="AM20" t="n">
+        <v>5.0987</v>
+      </c>
+      <c r="AN20" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>331122</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
+        <v>-2.26946</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BA20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BB20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BC20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BD20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BE20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BF20" t="n">
         <v>5.711379</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4360,78 +4482,84 @@
         <v>5.2078</v>
       </c>
       <c r="AM21" t="n">
+        <v>5.2072</v>
+      </c>
+      <c r="AN21" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AS21" t="n">
         <v>4.16</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>328098</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
+        <v>2.127993</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BA21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BB21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BC21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BD21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BE21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BF21" t="n">
         <v>5.47065</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BK21" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4551,78 +4679,84 @@
         <v>5.0804</v>
       </c>
       <c r="AM22" t="n">
+        <v>5.0798</v>
+      </c>
+      <c r="AN22" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>341158</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
+        <v>-2.446612</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BA22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BB22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BC22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BD22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BE22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BF22" t="n">
         <v>4.361088</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BK22" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4742,78 +4876,84 @@
         <v>5.0007</v>
       </c>
       <c r="AM23" t="n">
+        <v>5.0001</v>
+      </c>
+      <c r="AN23" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>4.26</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>345725</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
+        <v>-1.568959</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BB23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BC23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BD23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BE23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BF23" t="n">
         <v>3.834324</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BK23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>0.15</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4933,78 +5073,84 @@
         <v>5.0959</v>
       </c>
       <c r="AM24" t="n">
+        <v>5.0953</v>
+      </c>
+      <c r="AN24" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>4.35</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>343489</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AY24" t="n">
+        <v>1.903962</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BB24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BC24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BD24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BE24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BF24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BG24" t="n">
         <v>0</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BH24" t="n">
         <v>-0</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BI24" t="n">
         <v>-0</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BJ24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BK24" t="n">
         <v>0.13</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5124,78 +5270,84 @@
         <v>4.8192</v>
       </c>
       <c r="AM25" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="AN25" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>343620</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="BA25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BB25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BC25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BD25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BE25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BF25" t="n">
         <v>2.998957</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BK25" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5315,78 +5467,84 @@
         <v>4.7415</v>
       </c>
       <c r="AM26" t="n">
+        <v>4.7409</v>
+      </c>
+      <c r="AN26" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>4.22</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>345476</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
+        <v>-1.612502</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BA26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BB26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BC26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BD26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BE26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BF26" t="n">
         <v>3.527423</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BK26" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5506,78 +5664,84 @@
         <v>4.9219</v>
       </c>
       <c r="AM27" t="n">
+        <v>4.9213</v>
+      </c>
+      <c r="AN27" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>4.12</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>344177</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AX27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AY27" t="n">
+        <v>3.805185</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="BA27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BB27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BC27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BD27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BE27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BF27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BG27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BI27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BK27" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5697,78 +5861,84 @@
         <v>5.0076</v>
       </c>
       <c r="AM28" t="n">
+        <v>5.007</v>
+      </c>
+      <c r="AN28" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>4</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>340324</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
+        <v>1.74141</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BB28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BC28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BD28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BE28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BF28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BI28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BH28" t="n">
+      <c r="BJ28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BK28" t="n">
         <v>0</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BL28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK28" t="n">
+      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5888,78 +6058,84 @@
         <v>5.0575</v>
       </c>
       <c r="AM29" t="n">
+        <v>5.0569</v>
+      </c>
+      <c r="AN29" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.97</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>340247</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AY29" t="n">
+        <v>0.996605</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BA29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BB29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BC29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BD29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BE29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BF29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BG29" t="n">
         <v>0</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BI29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BH29" t="n">
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BK29" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BL29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK29" t="n">
+      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6079,78 +6255,84 @@
         <v>4.9355</v>
       </c>
       <c r="AM30" t="n">
+        <v>4.9349</v>
+      </c>
+      <c r="AN30" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.88</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>348406</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AY30" t="n">
+        <v>-2.412545</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BA30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BB30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BC30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BD30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BE30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BF30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BG30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BI30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BH30" t="n">
+      <c r="BJ30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BK30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BL30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BK30" t="n">
+      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6270,78 +6452,84 @@
         <v>4.8413</v>
       </c>
       <c r="AM31" t="n">
+        <v>4.8407</v>
+      </c>
+      <c r="AN31" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>355034</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
+        <v>-1.908853</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BA31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BB31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BC31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BD31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BE31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BF31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BG31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BI31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BJ31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BK31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BL31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BK31" t="n">
+      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6461,78 +6649,84 @@
         <v>4.9535</v>
       </c>
       <c r="AM32" t="n">
+        <v>4.9529</v>
+      </c>
+      <c r="AN32" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>355066</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
+        <v>2.317847</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BA32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BB32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BC32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BD32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BE32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BF32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BG32" t="n">
         <v>0</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BI32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BH32" t="n">
+      <c r="BJ32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BK32" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BL32" t="n">
         <v>0.01</v>
       </c>
-      <c r="BK32" t="n">
+      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6652,78 +6846,84 @@
         <v>4.9833</v>
       </c>
       <c r="AM33" t="n">
+        <v>4.9827</v>
+      </c>
+      <c r="AN33" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>352705</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AX33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
+        <v>0.601668</v>
+      </c>
+      <c r="AZ33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BA33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BB33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BC33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BD33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BE33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BF33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BG33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BI33" t="n">
         <v>-0.001782</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6843,78 +7043,84 @@
         <v>4.9962</v>
       </c>
       <c r="AM34" t="n">
+        <v>4.9956</v>
+      </c>
+      <c r="AN34" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>355008</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
+        <v>0.258896</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="BA34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BB34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BC34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BD34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BE34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BF34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BG34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BI34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7034,78 +7240,84 @@
         <v>5.1718</v>
       </c>
       <c r="AM35" t="n">
+        <v>5.1712</v>
+      </c>
+      <c r="AN35" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>351599</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AX35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AY35" t="n">
+        <v>3.515093</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="BA35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BB35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BC35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BD35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BE35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BF35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BG35" t="n">
         <v>0</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BI35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7225,78 +7437,84 @@
         <v>5.2416</v>
       </c>
       <c r="AM36" t="n">
+        <v>5.241</v>
+      </c>
+      <c r="AN36" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>355560</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AX36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AY36" t="n">
+        <v>1.349783</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BA36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BB36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BC36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BD36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BE36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BF36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BG36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BI36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BH36" t="n">
+      <c r="BJ36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI36" t="n">
+      <c r="BK36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BL36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK36" t="n">
+      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7416,78 +7634,84 @@
         <v>5.5589</v>
       </c>
       <c r="AM37" t="n">
+        <v>5.5583</v>
+      </c>
+      <c r="AN37" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>357827</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AX37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AY37" t="n">
+        <v>6.054188</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="BA37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BB37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BC37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BD37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BE37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BF37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BG37" t="n">
         <v>0</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BI37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BH37" t="n">
+      <c r="BJ37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BI37" t="n">
+      <c r="BK37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BL37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7607,78 +7831,84 @@
         <v>5.6621</v>
       </c>
       <c r="AM38" t="n">
+        <v>5.6615</v>
+      </c>
+      <c r="AN38" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>363282</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AY38" t="n">
+        <v>1.856683</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="BA38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BB38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BC38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BD38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BE38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BF38" t="n">
         <v>4.060953</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI38" t="n">
+      <c r="BK38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BL38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK38" t="n">
+      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7798,78 +8028,84 @@
         <v>5.6562</v>
       </c>
       <c r="AM39" t="n">
+        <v>5.6556</v>
+      </c>
+      <c r="AN39" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>369214</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
+        <v>-0.104213</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="BA39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BB39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BC39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BD39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BE39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BF39" t="n">
         <v>3.707852</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI39" t="n">
+      <c r="BK39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ39" t="n">
+      <c r="BL39" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK39" t="n">
+      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7989,78 +8225,84 @@
         <v>5.4481</v>
       </c>
       <c r="AM40" t="n">
+        <v>5.4475</v>
+      </c>
+      <c r="AN40" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>3.83</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>372016</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AY40" t="n">
+        <v>-3.679539</v>
+      </c>
+      <c r="AZ40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BA40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BB40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BC40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BD40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BE40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BF40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BG40" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="BG40" t="n">
+      <c r="BI40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8180,78 +8422,84 @@
         <v>5.7779</v>
       </c>
       <c r="AM41" t="n">
+        <v>5.7773</v>
+      </c>
+      <c r="AN41" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>3.79</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AT41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AU41" t="n">
         <v>366096</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AW41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AX41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AY41" t="n">
+        <v>6.054153</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="BA41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BB41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BC41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BD41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BE41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BF41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BG41" t="n">
         <v>0</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BI41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8371,78 +8619,84 @@
         <v>6.0535</v>
       </c>
       <c r="AM42" t="n">
+        <v>6.0529</v>
+      </c>
+      <c r="AN42" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AT42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AU42" t="n">
         <v>363003</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AW42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AX42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AY42" t="n">
+        <v>4.770394</v>
+      </c>
+      <c r="AZ42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="BA42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BB42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BC42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BD42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BE42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BF42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BG42" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BI42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BH42" t="n">
+      <c r="BJ42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI42" t="n">
+      <c r="BK42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BL42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BK42" t="n">
+      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8562,78 +8816,84 @@
         <v>6.1923</v>
       </c>
       <c r="AM43" t="n">
+        <v>6.1917</v>
+      </c>
+      <c r="AN43" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>3.63</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>329730</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AY43" t="n">
+        <v>2.293116</v>
+      </c>
+      <c r="AZ43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="BA43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BB43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BC43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BD43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BE43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BF43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BG43" t="n">
         <v>1</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BI43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BH43" t="n">
+      <c r="BJ43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BK43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BL43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8753,78 +9013,84 @@
         <v>5.8301</v>
       </c>
       <c r="AM44" t="n">
+        <v>5.8295</v>
+      </c>
+      <c r="AN44" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>328303</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AY44" t="n">
+        <v>-5.849767</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="BA44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BB44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BC44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BD44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BE44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BF44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BG44" t="n">
         <v>1</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BI44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8944,78 +9210,84 @@
         <v>5.8488</v>
       </c>
       <c r="AM45" t="n">
+        <v>5.8482</v>
+      </c>
+      <c r="AN45" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>3.96</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AT45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AU45" t="n">
         <v>332508</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AW45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AX45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AY45" t="n">
+        <v>0.320782</v>
+      </c>
+      <c r="AZ45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="BA45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BB45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BC45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BD45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BE45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BF45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BG45" t="n">
         <v>0</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BI45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9135,78 +9407,84 @@
         <v>5.7422</v>
       </c>
       <c r="AM46" t="n">
+        <v>5.7416</v>
+      </c>
+      <c r="AN46" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4.03</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AU46" t="n">
         <v>336157</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AW46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AY46" t="n">
+        <v>-1.822783</v>
+      </c>
+      <c r="AZ46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BA46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BB46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BC46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BD46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BE46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BF46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BG46" t="n">
         <v>1</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BI46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BH46" t="n">
+      <c r="BJ46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI46" t="n">
+      <c r="BK46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BL46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK46" t="n">
+      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9326,78 +9604,84 @@
         <v>5.6608</v>
       </c>
       <c r="AM47" t="n">
+        <v>5.6602</v>
+      </c>
+      <c r="AN47" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AT47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AU47" t="n">
         <v>340789</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AW47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AY47" t="n">
+        <v>-1.417723</v>
+      </c>
+      <c r="AZ47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="BA47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BB47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BC47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BD47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BE47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BF47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BG47" t="n">
         <v>0</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BI47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BH47" t="n">
+      <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BK47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BL47" t="n">
         <v>0.22</v>
       </c>
-      <c r="BK47" t="n">
+      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9517,78 +9801,84 @@
         <v>5.7087</v>
       </c>
       <c r="AM48" t="n">
+        <v>5.7081</v>
+      </c>
+      <c r="AN48" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>4.36</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AT48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AU48" t="n">
         <v>341459</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AW48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AX48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
+        <v>0.84626</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BA48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BB48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BC48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BD48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BE48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BF48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BG48" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BI48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BH48" t="n">
+      <c r="BJ48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BK48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BL48" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9708,78 +9998,84 @@
         <v>5.4571</v>
       </c>
       <c r="AM49" t="n">
+        <v>5.4565</v>
+      </c>
+      <c r="AN49" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>4.41</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>344440</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AW49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
+        <v>-4.407771</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="BA49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BB49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BC49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BD49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BE49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BF49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BG49" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BI49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BH49" t="n">
+      <c r="BJ49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BK49" t="n">
         <v>0</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BL49" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9899,78 +10195,84 @@
         <v>5.6021</v>
       </c>
       <c r="AM50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="AN50" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>4.66</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>345111</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AX50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AY50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="AZ50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="BA50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BB50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BC50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BD50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BE50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BF50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BG50" t="n">
         <v>0</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BI50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BH50" t="n">
+      <c r="BJ50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BK50" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BL50" t="n">
         <v>0.25</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10090,78 +10392,84 @@
         <v>5.4264</v>
       </c>
       <c r="AM51" t="n">
+        <v>5.4258</v>
+      </c>
+      <c r="AN51" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>4.92</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AT51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AU51" t="n">
         <v>350767</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AY51" t="n">
+        <v>-3.13666</v>
+      </c>
+      <c r="AZ51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="BA51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BB51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BC51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BD51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BE51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BF51" t="n">
         <v>5.054283</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BK51" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BL51" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10281,78 +10589,84 @@
         <v>5.3186</v>
       </c>
       <c r="AM52" t="n">
+        <v>5.318</v>
+      </c>
+      <c r="AN52" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>4.89</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AT52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AU52" t="n">
         <v>356582</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AW52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AY52" t="n">
+        <v>-1.986804</v>
+      </c>
+      <c r="AZ52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="BA52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BB52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BC52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BD52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BE52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BF52" t="n">
         <v>5.096104</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BI52" t="n">
+      <c r="BK52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ52" t="n">
+      <c r="BL52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK52" t="n">
+      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10472,78 +10786,84 @@
         <v>5.3843</v>
       </c>
       <c r="AM53" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="AN53" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>4.99</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AT53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AU53" t="n">
         <v>357103</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AW53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AX53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AY53" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="BA53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BB53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BC53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BD53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BE53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BF53" t="n">
         <v>4.490243</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI53" t="n">
+      <c r="BK53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BL53" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK53" t="n">
+      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10663,78 +10983,84 @@
         <v>5.3338</v>
       </c>
       <c r="AM54" t="n">
+        <v>5.3332</v>
+      </c>
+      <c r="AN54" t="n">
         <v>7003273</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2616213</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>4387061</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>4.23</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.74</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AT54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AU54" t="n">
         <v>360578</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AW54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AX54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AY54" t="n">
+        <v>-0.938017</v>
+      </c>
+      <c r="AZ54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="BA54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BB54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BC54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BD54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BE54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BF54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BG54" t="n">
         <v>0</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BH54" t="n">
         <v>-0</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BI54" t="n">
         <v>-0</v>
       </c>
-      <c r="BH54" t="n">
+      <c r="BJ54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI54" t="n">
+      <c r="BK54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BL54" t="n">
         <v>0.13</v>
       </c>
-      <c r="BK54" t="n">
+      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10854,78 +11180,84 @@
         <v>5.5024</v>
       </c>
       <c r="AM55" t="n">
+        <v>5.5018</v>
+      </c>
+      <c r="AN55" t="n">
         <v>7136436</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2701146</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>4435290</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.68</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AT55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AU55" t="n">
         <v>358234</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AW55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AY55" t="n">
+        <v>3.161329</v>
+      </c>
+      <c r="AZ55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="BA55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BB55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BC55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BD55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BE55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="BD55" t="n">
+      <c r="BF55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI55" t="n">
+      <c r="BK55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BL55" t="n">
         <v>0</v>
       </c>
-      <c r="BK55" t="n">
+      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11045,78 +11377,84 @@
         <v>5.2301</v>
       </c>
       <c r="AM56" t="n">
+        <v>5.2295</v>
+      </c>
+      <c r="AN56" t="n">
         <v>7130500</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2654052</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>4476448</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>4.45</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>5.38</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AT56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AU56" t="n">
         <v>364367</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AW56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AX56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AY56" t="n">
+        <v>-4.949289</v>
+      </c>
+      <c r="AZ56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="BA56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BB56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BC56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BD56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BE56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BF56" t="n">
         <v>4.303068</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BI56" t="n">
+      <c r="BK56" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BL56" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK56" t="n">
+      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11236,78 +11574,84 @@
         <v>5.1495</v>
       </c>
       <c r="AM57" t="n">
+        <v>5.1489</v>
+      </c>
+      <c r="AN57" t="n">
         <v>7156987</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2655931</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>4501056</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>5.56</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AT57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AU57" t="n">
         <v>371074</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AW57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AX57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AY57" t="n">
+        <v>-1.541256</v>
+      </c>
+      <c r="AZ57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="BA57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BB57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BC57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BD57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BE57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BF57" t="n">
         <v>3.357475</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI57" t="n">
+      <c r="BK57" t="n">
         <v>0.2</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BL57" t="n">
         <v>0.18</v>
       </c>
-      <c r="BK57" t="n">
+      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11427,78 +11771,84 @@
         <v>5.2194</v>
       </c>
       <c r="AM58" t="n">
+        <v>5.2188</v>
+      </c>
+      <c r="AN58" t="n">
         <v>7237735</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2686046</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>4551689</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>3.04</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AT58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AU58" t="n">
         <v>362002</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AW58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AX58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AY58" t="n">
+        <v>1.357572</v>
+      </c>
+      <c r="AZ58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="BA58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BB58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BC58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BD58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BE58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BF58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BG58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BI58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BH58" t="n">
+      <c r="BJ58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BI58" t="n">
+      <c r="BK58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ58" t="n">
+      <c r="BL58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BK58" t="n">
+      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11618,78 +11968,84 @@
         <v>4.9886</v>
       </c>
       <c r="AM59" t="n">
+        <v>4.988</v>
+      </c>
+      <c r="AN59" t="n">
         <v>7258599</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2684623</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>4573976</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>4.63</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AT59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AU59" t="n">
         <v>366913</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AW59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AX59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AY59" t="n">
+        <v>-4.422473</v>
+      </c>
+      <c r="AZ59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="BA59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BB59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BC59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BD59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BE59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BF59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BG59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BI59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI59" t="n">
-        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11805,74 +12161,80 @@
         <v>5.0569</v>
       </c>
       <c r="AM60" t="n">
+        <v>5.0563</v>
+      </c>
+      <c r="AN60" t="n">
         <v>7299615</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2704550</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>4595065</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>4.74</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>3.24</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>5.62</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AT60" t="n">
         <v>33.42</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="n">
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AY60" t="n">
+        <v>1.369286</v>
+      </c>
+      <c r="AZ60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="BA60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BB60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BC60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BD60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BE60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BF60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BG60" t="n">
         <v>0</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="BG60" t="n">
+      <c r="BI60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -11983,133 +12345,139 @@
       <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AM61" t="inlineStr"/>
+      <c r="AM61" t="n">
+        <v>5.176</v>
+      </c>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="n">
         <v>367558</v>
       </c>
-      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="n">
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
+      <c r="AY61" t="n">
+        <v>2.367344</v>
+      </c>
       <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="n">
-        <v>-0.964334</v>
-      </c>
+      <c r="BA61" t="inlineStr"/>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="n">
-        <v>3.177699</v>
+        <v>-0.964334</v>
       </c>
       <c r="BD61" t="inlineStr"/>
       <c r="BE61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BI61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BH61" t="inlineStr"/>
-      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>171260.59375</v>
+        <v>172742</v>
       </c>
       <c r="C62" t="n">
-        <v>168.350006</v>
+        <v>169.800003</v>
       </c>
       <c r="D62" t="n">
-        <v>105.809998</v>
+        <v>107.760002</v>
       </c>
       <c r="E62" t="n">
-        <v>435.450012</v>
+        <v>435.079987</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1453</v>
+        <v>5.1146</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8964</v>
+        <v>5.8474</v>
       </c>
       <c r="H62" t="n">
-        <v>7492.100098</v>
+        <v>7543.640137</v>
       </c>
       <c r="I62" t="n">
-        <v>25918.525391</v>
+        <v>26206.890625</v>
       </c>
       <c r="J62" t="n">
-        <v>52299.730469</v>
+        <v>52487.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4133.700195</v>
+        <v>4117.700195</v>
       </c>
       <c r="L62" t="n">
-        <v>73.129997</v>
+        <v>71.949997</v>
       </c>
       <c r="M62" t="n">
-        <v>77.910004</v>
+        <v>76.360001</v>
       </c>
       <c r="N62" t="n">
-        <v>1185.5</v>
+        <v>1180.25</v>
       </c>
       <c r="O62" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-0.443779</v>
+        <v>0.417384</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.414077</v>
+        <v>0.443656</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.009637</v>
+        <v>-0.203743</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.045904</v>
+        <v>-0.130841</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.704141</v>
+        <v>-1.296596</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.350845</v>
+        <v>-1.178941</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.096805</v>
+        <v>0.590454</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.12611</v>
+        <v>-0.026055</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.037211</v>
+        <v>0.321509</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.754239</v>
+        <v>2.356516</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.223018</v>
+        <v>3.525175</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.843123</v>
+        <v>4.717502</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.156257</v>
+        <v>5.686143</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.388249999999999</v>
+        <v>9.448819</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12126,9 +12494,11 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.1552</v>
-      </c>
-      <c r="AM62" t="inlineStr"/>
+        <v>5.1329</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>5.1323</v>
+      </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12138,29 +12508,33 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="n">
-        <v>-0.413399</v>
-      </c>
-      <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="n">
+        <v>-0.844183</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>-0.8442809999999999</v>
+      </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="n">
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
         <v>0</v>
       </c>
-      <c r="BF62" t="n">
+      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BI62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BH62" t="inlineStr"/>
-      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12335,11 +12335,15 @@
       <c r="AF61" t="n">
         <v>0.053028</v>
       </c>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AG61" t="n">
+        <v>0.16</v>
+      </c>
       <c r="AH61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AI61" t="inlineStr"/>
+      <c r="AI61" t="n">
+        <v>0.14</v>
+      </c>
       <c r="AJ61" t="inlineStr"/>
       <c r="AK61" t="inlineStr"/>
       <c r="AL61" t="n">
@@ -12372,11 +12376,15 @@
       <c r="BC61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="BD61" t="inlineStr"/>
+      <c r="BD61" t="n">
+        <v>4.641328</v>
+      </c>
       <c r="BE61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="BF61" t="inlineStr"/>
+      <c r="BF61" t="n">
+        <v>4.327084</v>
+      </c>
       <c r="BG61" t="n">
         <v>-0.25</v>
       </c>
@@ -12396,88 +12404,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>172742</v>
+        <v>177866</v>
       </c>
       <c r="C62" t="n">
-        <v>169.800003</v>
+        <v>175.009995</v>
       </c>
       <c r="D62" t="n">
-        <v>107.760002</v>
+        <v>111.080002</v>
       </c>
       <c r="E62" t="n">
-        <v>435.079987</v>
+        <v>436.290009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1146</v>
+        <v>5.1075</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8474</v>
+        <v>5.8296</v>
       </c>
       <c r="H62" t="n">
-        <v>7543.640137</v>
+        <v>7575.390137</v>
       </c>
       <c r="I62" t="n">
-        <v>26206.890625</v>
+        <v>26281.609375</v>
       </c>
       <c r="J62" t="n">
-        <v>52487.410156</v>
+        <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4117.700195</v>
+        <v>4104.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>71.949997</v>
+        <v>71.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>76.360001</v>
+        <v>76.010002</v>
       </c>
       <c r="N62" t="n">
-        <v>1180.25</v>
+        <v>1196.5</v>
       </c>
       <c r="O62" t="n">
-        <v>451.75</v>
+        <v>438</v>
       </c>
       <c r="P62" t="n">
-        <v>0.417384</v>
+        <v>3.396038</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.443656</v>
+        <v>3.525579</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.203743</v>
+        <v>2.870901</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.130841</v>
+        <v>0.14691</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.296596</v>
+        <v>-1.433616</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.178941</v>
+        <v>-1.479767</v>
       </c>
       <c r="V62" t="n">
-        <v>0.590454</v>
+        <v>1.013824</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.026055</v>
+        <v>0.258981</v>
       </c>
       <c r="X62" t="n">
-        <v>0.321509</v>
+        <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.356516</v>
+        <v>2.018449</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.525175</v>
+        <v>2.748207</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.717502</v>
+        <v>4.237526</v>
       </c>
       <c r="AB62" t="n">
-        <v>5.686143</v>
+        <v>7.141258</v>
       </c>
       <c r="AC62" t="n">
-        <v>9.448819</v>
+        <v>6.117505</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12494,10 +12502,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.1329</v>
+        <v>5.1088</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.1323</v>
+        <v>5.1082</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12510,10 +12518,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-0.844183</v>
+        <v>-1.30974</v>
       </c>
       <c r="AY62" t="n">
-        <v>-0.8442809999999999</v>
+        <v>-1.309892</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12431,7 +12431,7 @@
         <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4104.100098</v>
+        <v>4113.700195</v>
       </c>
       <c r="L62" t="n">
         <v>71.410004</v>
@@ -12440,10 +12440,10 @@
         <v>76.010002</v>
       </c>
       <c r="N62" t="n">
-        <v>1196.5</v>
+        <v>1190.75</v>
       </c>
       <c r="O62" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="P62" t="n">
         <v>3.396038</v>
@@ -12473,7 +12473,7 @@
         <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.018449</v>
+        <v>2.257086</v>
       </c>
       <c r="Z62" t="n">
         <v>2.748207</v>
@@ -12482,10 +12482,10 @@
         <v>4.237526</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.141258</v>
+        <v>6.626371</v>
       </c>
       <c r="AC62" t="n">
-        <v>6.117505</v>
+        <v>11.689885</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,160 +588,150 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>bcb_sgs_igp_m</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_igp_m_acum_12m</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -820,47 +810,45 @@
         <v>0.96</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.02</v>
+        <v>96.42256999999999</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96.42256999999999</v>
+        <v>99.83515</v>
       </c>
       <c r="AK2" t="n">
-        <v>99.83515</v>
+        <v>5.1216</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -877,8 +865,6 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -981,93 +967,89 @@
         <v>0.87</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.88</v>
+        <v>97.03115</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.03115</v>
+        <v>99.19471</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.19471</v>
+        <v>5.1433</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1172,93 +1154,89 @@
         <v>1.16</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>96.97727</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.97727</v>
+        <v>97.10229</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.10229</v>
+        <v>5.4394</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1363,93 +1341,89 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.16</v>
+        <v>97.49541000000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.49541000000001</v>
+        <v>96.53060000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.53060000000001</v>
+        <v>5.643</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1554,93 +1528,89 @@
         <v>0.95</v>
       </c>
       <c r="AH6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>99.05485</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>97.85541000000001</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5.6199</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>2664395</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>367772</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.599501</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.372425</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>-0.409357</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2.436662</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>-0.042128</v>
+      </c>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>99.05485</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>97.85541000000001</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>5.6199</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>5.6193</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>4597507</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1933111</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2664395</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>367772</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.599501</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.372425</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.03</v>
-      </c>
       <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1745,93 +1715,89 @@
         <v>0.73</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.87</v>
+        <v>0.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.73</v>
+        <v>99.30268</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.30268</v>
+        <v>99.31872</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.31872</v>
+        <v>5.5805</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1936,93 +1902,89 @@
         <v>0.54</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.67</v>
+        <v>97.42644</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.42644</v>
+        <v>91.67792</v>
       </c>
       <c r="AK8" t="n">
-        <v>91.67792</v>
+        <v>5.3574</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="AW8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="AY8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2127,93 +2089,89 @@
         <v>1.01</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>98.38327</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.38327</v>
+        <v>95.6409</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.6409</v>
+        <v>5.1394</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2318,93 +2276,89 @@
         <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.71</v>
+        <v>99.5587</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.5587</v>
+        <v>104.52811</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.52811</v>
+        <v>4.7378</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2509,93 +2463,89 @@
         <v>1.06</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>99.56286</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.56286</v>
+        <v>100.22885</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.22885</v>
+        <v>4.9191</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2700,93 +2650,89 @@
         <v>0.47</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.45</v>
+        <v>99.67480999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>99.67480999999999</v>
+        <v>99.74863999999999</v>
       </c>
       <c r="AK12" t="n">
-        <v>99.74863999999999</v>
+        <v>4.7289</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="AN12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="AO12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="AP12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2891,99 +2837,93 @@
         <v>0.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.62</v>
+        <v>99.51873000000001</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99.51873000000001</v>
+        <v>99.3134</v>
       </c>
       <c r="AK13" t="n">
-        <v>99.3134</v>
+        <v>5.238</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="AN13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="AO13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="AP13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3088,99 +3028,93 @@
         <v>-0.68</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.6</v>
+        <v>101.41705</v>
       </c>
       <c r="AJ14" t="n">
-        <v>101.41705</v>
+        <v>103.95829</v>
       </c>
       <c r="AK14" t="n">
-        <v>103.95829</v>
+        <v>5.1884</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="AN14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="AO14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="AP14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3285,99 +3219,93 @@
         <v>-0.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.31</v>
+        <v>101.1048</v>
       </c>
       <c r="AJ15" t="n">
-        <v>101.1048</v>
+        <v>104.51622</v>
       </c>
       <c r="AK15" t="n">
-        <v>104.51622</v>
+        <v>5.179</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="AN15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="AO15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="AP15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3482,99 +3410,93 @@
         <v>-0.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.32</v>
+        <v>101.15658</v>
       </c>
       <c r="AJ16" t="n">
-        <v>101.15658</v>
+        <v>101.18649</v>
       </c>
       <c r="AK16" t="n">
-        <v>101.18649</v>
+        <v>5.4066</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="AN16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="AO16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="AP16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3679,99 +3601,93 @@
         <v>0.59</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.47</v>
+        <v>101.44313</v>
       </c>
       <c r="AJ17" t="n">
-        <v>101.44313</v>
+        <v>100.08007</v>
       </c>
       <c r="AK17" t="n">
-        <v>100.08007</v>
+        <v>5.257</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="AN17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="AO17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="AP17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3876,99 +3792,93 @@
         <v>0.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.38</v>
+        <v>100.70751</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.70751</v>
+        <v>99.15338</v>
       </c>
       <c r="AK18" t="n">
-        <v>99.15338</v>
+        <v>5.2941</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="AN18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="AO18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="AP18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4073,99 +3983,93 @@
         <v>0.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.45671</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100.45671</v>
+        <v>99.96775</v>
       </c>
       <c r="AK19" t="n">
-        <v>99.96775</v>
+        <v>5.2177</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="AN19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="AO19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="AP19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="BG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH19" t="n">
         <v>0</v>
       </c>
-      <c r="BH19" t="n">
-        <v>-0</v>
-      </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4270,99 +4174,93 @@
         <v>0.53</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.46</v>
+        <v>100.1131</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100.1131</v>
+        <v>95.09765</v>
       </c>
       <c r="AK20" t="n">
-        <v>95.09765</v>
+        <v>5.0993</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="AN20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="AO20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="AP20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="AW20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4467,99 +4365,93 @@
         <v>0.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.77</v>
+        <v>102.99794</v>
       </c>
       <c r="AJ21" t="n">
-        <v>102.99794</v>
+        <v>98.65175000000001</v>
       </c>
       <c r="AK21" t="n">
-        <v>98.65175000000001</v>
+        <v>5.2078</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="AN21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="AO21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="AP21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4664,99 +4556,93 @@
         <v>0.71</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.64</v>
+        <v>103.10183</v>
       </c>
       <c r="AJ22" t="n">
-        <v>103.10183</v>
+        <v>110.6159</v>
       </c>
       <c r="AK22" t="n">
-        <v>110.6159</v>
+        <v>5.0804</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="AM22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="AN22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="AO22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="AP22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4861,99 +4747,93 @@
         <v>0.61</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.53</v>
+        <v>104.18587</v>
       </c>
       <c r="AJ23" t="n">
-        <v>104.18587</v>
+        <v>104.03928</v>
       </c>
       <c r="AK23" t="n">
-        <v>104.03928</v>
+        <v>5.0007</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="AN23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="AO23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="AP23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5058,99 +4938,93 @@
         <v>0.23</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.36</v>
+        <v>102.46133</v>
       </c>
       <c r="AJ24" t="n">
-        <v>102.46133</v>
+        <v>102.71672</v>
       </c>
       <c r="AK24" t="n">
-        <v>102.71672</v>
+        <v>5.0959</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="AN24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="AO24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="AP24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5255,99 +5129,93 @@
         <v>-0.08</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.1</v>
+        <v>102.39681</v>
       </c>
       <c r="AJ25" t="n">
-        <v>102.39681</v>
+        <v>102.2809</v>
       </c>
       <c r="AK25" t="n">
-        <v>102.2809</v>
+        <v>4.8192</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="AM25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="AN25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="AO25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="AP25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="AU25" t="n">
-        <v>343620</v>
+        <v>-0.06297</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.06297</v>
+        <v>-0.424293</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.424293</v>
+        <v>-5.429855</v>
       </c>
       <c r="AX25" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="AY25" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.472174</v>
+        <v>1.122473</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.122473</v>
+        <v>0.050421</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.050421</v>
+        <v>0.038138</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="BE25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5452,99 +5320,93 @@
         <v>0.12</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.09</v>
+        <v>102.86628</v>
       </c>
       <c r="AJ26" t="n">
-        <v>102.86628</v>
+        <v>105.34289</v>
       </c>
       <c r="AK26" t="n">
-        <v>105.34289</v>
+        <v>4.7415</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="AN26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="AO26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="AP26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5649,99 +5511,93 @@
         <v>0.23</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.2</v>
+        <v>102.48117</v>
       </c>
       <c r="AJ27" t="n">
-        <v>102.48117</v>
+        <v>106.05936</v>
       </c>
       <c r="AK27" t="n">
-        <v>106.05936</v>
+        <v>4.9219</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="AN27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="AO27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="AP27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BI27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5846,99 +5702,93 @@
         <v>0.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.11</v>
+        <v>102.49422</v>
       </c>
       <c r="AJ28" t="n">
-        <v>102.49422</v>
+        <v>101.75832</v>
       </c>
       <c r="AK28" t="n">
-        <v>101.75832</v>
+        <v>5.0076</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="AN28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="AO28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="AP28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="AW28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6043,99 +5893,93 @@
         <v>0.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.12</v>
+        <v>102.81544</v>
       </c>
       <c r="AJ29" t="n">
-        <v>102.81544</v>
+        <v>101.93091</v>
       </c>
       <c r="AK29" t="n">
-        <v>101.93091</v>
+        <v>5.0575</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="AN29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="AO29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BI29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6240,99 +6084,93 @@
         <v>0.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1</v>
+        <v>103.57529</v>
       </c>
       <c r="AJ30" t="n">
-        <v>103.57529</v>
+        <v>101.68306</v>
       </c>
       <c r="AK30" t="n">
-        <v>101.68306</v>
+        <v>4.9355</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="AN30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="AO30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="AP30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BI30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6437,99 +6275,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.55</v>
+        <v>104.68308</v>
       </c>
       <c r="AJ31" t="n">
-        <v>104.68308</v>
+        <v>101.68292</v>
       </c>
       <c r="AK31" t="n">
-        <v>101.68292</v>
+        <v>4.8413</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="AN31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="AO31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="AP31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6634,99 +6466,93 @@
         <v>0.42</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.57</v>
+        <v>104.47997</v>
       </c>
       <c r="AJ32" t="n">
-        <v>104.47997</v>
+        <v>99.29383</v>
       </c>
       <c r="AK32" t="n">
-        <v>99.29383</v>
+        <v>4.9535</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="AN32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="AO32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="AP32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="AW32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6831,99 +6657,93 @@
         <v>0.83</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.63436</v>
       </c>
       <c r="AJ33" t="n">
-        <v>104.63436</v>
+        <v>102.15169</v>
       </c>
       <c r="AK33" t="n">
-        <v>102.15169</v>
+        <v>4.9833</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="AN33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="AO33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="AP33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BI33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7028,99 +6848,93 @@
         <v>0.16</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.19</v>
+        <v>104.71934</v>
       </c>
       <c r="AJ34" t="n">
-        <v>104.71934</v>
+        <v>109.56886</v>
       </c>
       <c r="AK34" t="n">
-        <v>109.56886</v>
+        <v>4.9962</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="AM34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="AN34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="AO34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="AP34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7225,99 +7039,93 @@
         <v>0.38</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.37</v>
+        <v>104.96661</v>
       </c>
       <c r="AJ35" t="n">
-        <v>104.96661</v>
+        <v>109.2559</v>
       </c>
       <c r="AK35" t="n">
-        <v>109.2559</v>
+        <v>5.1718</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="AN35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="AO35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="AP35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7422,99 +7230,93 @@
         <v>0.46</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.46</v>
+        <v>105.66388</v>
       </c>
       <c r="AJ36" t="n">
-        <v>105.66388</v>
+        <v>104.71434</v>
       </c>
       <c r="AK36" t="n">
-        <v>104.71434</v>
+        <v>5.2416</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="AN36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="AO36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="AP36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BI36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7619,99 +7421,93 @@
         <v>0.21</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.25</v>
+        <v>106.57692</v>
       </c>
       <c r="AJ37" t="n">
-        <v>106.57692</v>
+        <v>105.86962</v>
       </c>
       <c r="AK37" t="n">
-        <v>105.86962</v>
+        <v>5.5589</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="AN37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="AO37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="AP37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7816,99 +7612,93 @@
         <v>0.38</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.26</v>
+        <v>106.95254</v>
       </c>
       <c r="AJ38" t="n">
-        <v>106.95254</v>
+        <v>111.51388</v>
       </c>
       <c r="AK38" t="n">
-        <v>111.51388</v>
+        <v>5.6621</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="AN38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="AO38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="AP38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8013,99 +7803,93 @@
         <v>-0.02</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.14</v>
+        <v>107.13607</v>
       </c>
       <c r="AJ39" t="n">
-        <v>107.13607</v>
+        <v>110.06483</v>
       </c>
       <c r="AK39" t="n">
-        <v>110.06483</v>
+        <v>5.6562</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="AN39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="AO39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="AP39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8210,99 +7994,93 @@
         <v>0.44</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.48</v>
+        <v>107.99994</v>
       </c>
       <c r="AJ40" t="n">
-        <v>107.99994</v>
+        <v>107.08167</v>
       </c>
       <c r="AK40" t="n">
-        <v>107.08167</v>
+        <v>5.4481</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="AN40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="AO40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="AP40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8407,99 +8185,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.61</v>
+        <v>108.20756</v>
       </c>
       <c r="AJ41" t="n">
-        <v>108.20756</v>
+        <v>109.18693</v>
       </c>
       <c r="AK41" t="n">
-        <v>109.18693</v>
+        <v>5.7779</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="AN41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="AO41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="AP41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8604,99 +8376,93 @@
         <v>0.39</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.33</v>
+        <v>107.96783</v>
       </c>
       <c r="AJ42" t="n">
-        <v>107.96783</v>
+        <v>105.49025</v>
       </c>
       <c r="AK42" t="n">
-        <v>105.49025</v>
+        <v>6.0535</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="AM42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="AN42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="AO42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="AP42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8801,99 +8567,93 @@
         <v>0.52</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.48</v>
+        <v>107.1418</v>
       </c>
       <c r="AJ43" t="n">
-        <v>107.1418</v>
+        <v>104.15997</v>
       </c>
       <c r="AK43" t="n">
-        <v>104.15997</v>
+        <v>6.1923</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="AN43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="AO43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="AP43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8998,99 +8758,93 @@
         <v>0.16</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>108.21392</v>
       </c>
       <c r="AJ44" t="n">
-        <v>108.21392</v>
+        <v>102.72834</v>
       </c>
       <c r="AK44" t="n">
-        <v>102.72834</v>
+        <v>5.8301</v>
       </c>
       <c r="AL44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="AN44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="AO44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="AP44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="AW44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9195,99 +8949,93 @@
         <v>1.31</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.48</v>
+        <v>108.74593</v>
       </c>
       <c r="AJ45" t="n">
-        <v>108.74593</v>
+        <v>106.92609</v>
       </c>
       <c r="AK45" t="n">
-        <v>106.92609</v>
+        <v>5.8488</v>
       </c>
       <c r="AL45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="AN45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="AO45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="AP45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9392,99 +9140,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.51</v>
+        <v>110.20451</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110.20451</v>
+        <v>114.11998</v>
       </c>
       <c r="AK46" t="n">
-        <v>114.11998</v>
+        <v>5.7422</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="AN46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="AO46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="AP46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9589,99 +9331,93 @@
         <v>0.43</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.48</v>
+        <v>110.0593</v>
       </c>
       <c r="AJ47" t="n">
-        <v>110.0593</v>
+        <v>112.69428</v>
       </c>
       <c r="AK47" t="n">
-        <v>112.69428</v>
+        <v>5.6608</v>
       </c>
       <c r="AL47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="AN47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="AO47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="AP47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9786,99 +9522,93 @@
         <v>0.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.35</v>
+        <v>109.08727</v>
       </c>
       <c r="AJ48" t="n">
-        <v>109.08727</v>
+        <v>108.65566</v>
       </c>
       <c r="AK48" t="n">
-        <v>108.65566</v>
+        <v>5.7087</v>
       </c>
       <c r="AL48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="AN48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="AO48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="AP48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9983,99 +9713,93 @@
         <v>0.24</v>
       </c>
       <c r="AH49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.23</v>
+        <v>108.85988</v>
       </c>
       <c r="AJ49" t="n">
-        <v>108.85988</v>
+        <v>107.4594</v>
       </c>
       <c r="AK49" t="n">
-        <v>107.4594</v>
+        <v>5.4571</v>
       </c>
       <c r="AL49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="AN49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="AO49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="AP49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10180,99 +9904,93 @@
         <v>0.26</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="AI50" t="n">
+        <v>108.41316</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>113.21721</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>-0.410362</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>5.358126</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AJ50" t="n">
-        <v>108.41316</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>113.21721</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>-0.410362</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>5.358126</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="BI50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10377,99 +10095,93 @@
         <v>-0.11</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.21</v>
+        <v>108.83964</v>
       </c>
       <c r="AJ51" t="n">
-        <v>108.83964</v>
+        <v>110.47825</v>
       </c>
       <c r="AK51" t="n">
-        <v>110.47825</v>
+        <v>5.4264</v>
       </c>
       <c r="AL51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="AM51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="AN51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="AO51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="AP51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10574,99 +10286,93 @@
         <v>0.48</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.52</v>
+        <v>108.76251</v>
       </c>
       <c r="AJ52" t="n">
-        <v>108.76251</v>
+        <v>109.57602</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.57602</v>
+        <v>5.3186</v>
       </c>
       <c r="AL52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="AN52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="AO52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="AP52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10771,99 +10477,93 @@
         <v>0.09</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.03</v>
+        <v>108.78795</v>
       </c>
       <c r="AJ53" t="n">
-        <v>108.78795</v>
+        <v>110.16742</v>
       </c>
       <c r="AK53" t="n">
-        <v>110.16742</v>
+        <v>5.3843</v>
       </c>
       <c r="AL53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="AN53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="AO53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="AP53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="AU53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10968,99 +10668,93 @@
         <v>0.18</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03</v>
+        <v>109.30007</v>
       </c>
       <c r="AJ54" t="n">
-        <v>109.30007</v>
+        <v>106.69062</v>
       </c>
       <c r="AK54" t="n">
-        <v>106.69062</v>
+        <v>5.3338</v>
       </c>
       <c r="AL54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="AN54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="AO54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="AP54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="AW54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="BI54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11165,99 +10859,93 @@
         <v>0.33</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.21</v>
+        <v>109.27117</v>
       </c>
       <c r="AJ55" t="n">
-        <v>109.27117</v>
+        <v>107.27827</v>
       </c>
       <c r="AK55" t="n">
-        <v>107.27827</v>
+        <v>5.5024</v>
       </c>
       <c r="AL55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="AN55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="AO55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="AP55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>0</v>
       </c>
-      <c r="BI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11362,99 +11050,93 @@
         <v>0.33</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.39</v>
+        <v>110.09703</v>
       </c>
       <c r="AJ56" t="n">
-        <v>110.09703</v>
+        <v>103.80093</v>
       </c>
       <c r="AK56" t="n">
-        <v>103.80093</v>
+        <v>5.2301</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="AN56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="AO56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="AP56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="AW56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11559,99 +11241,93 @@
         <v>0.7</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.78559</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110.78559</v>
+        <v>106.7205</v>
       </c>
       <c r="AK57" t="n">
-        <v>106.7205</v>
+        <v>5.1495</v>
       </c>
       <c r="AL57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="AN57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="AO57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="AP57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11756,99 +11432,93 @@
         <v>0.88</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.91</v>
+        <v>110.58589</v>
       </c>
       <c r="AJ58" t="n">
-        <v>110.58589</v>
+        <v>117.92682</v>
       </c>
       <c r="AK58" t="n">
-        <v>117.92682</v>
+        <v>5.2194</v>
       </c>
       <c r="AL58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="AN58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="AO58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="AP58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="AQ58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BI58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11953,99 +11623,93 @@
         <v>0.67</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.8100000000000001</v>
+        <v>111.15205</v>
       </c>
       <c r="AJ59" t="n">
-        <v>111.15205</v>
+        <v>113.72712</v>
       </c>
       <c r="AK59" t="n">
-        <v>113.72712</v>
+        <v>4.9886</v>
       </c>
       <c r="AL59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="AN59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="AO59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="AP59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BI59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12150,91 +11814,85 @@
         <v>0.58</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AI60" t="n">
         <v>0.65</v>
       </c>
+      <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
+      <c r="AK60" t="n">
+        <v>5.0569</v>
+      </c>
       <c r="AL60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="AN60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="AO60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="AP60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="AQ60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="AU60" t="n">
         <v>371137</v>
       </c>
+      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
+      <c r="AW60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12339,65 +11997,59 @@
         <v>0.16</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
+      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AK61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="AL61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
+      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="n">
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
+      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
+      <c r="AW61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="AX61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="inlineStr"/>
+      <c r="BB61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="BD61" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="BE61" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="BG61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -12416,10 +12068,10 @@
         <v>436.290009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1075</v>
+        <v>5.1165</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8296</v>
+        <v>5.8455</v>
       </c>
       <c r="H62" t="n">
         <v>7575.390137</v>
@@ -12431,19 +12083,19 @@
         <v>52637.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4113.700195</v>
+        <v>4067.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>71.410004</v>
+        <v>74.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>76.010002</v>
+        <v>78.879997</v>
       </c>
       <c r="N62" t="n">
-        <v>1190.75</v>
+        <v>1196.25</v>
       </c>
       <c r="O62" t="n">
-        <v>461</v>
+        <v>467.25</v>
       </c>
       <c r="P62" t="n">
         <v>3.396038</v>
@@ -12458,10 +12110,10 @@
         <v>0.14691</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.433616</v>
+        <v>-1.259934</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.479767</v>
+        <v>-1.211055</v>
       </c>
       <c r="V62" t="n">
         <v>1.013824</v>
@@ -12473,19 +12125,19 @@
         <v>0.607449</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.257086</v>
+        <v>1.118596</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.748207</v>
+        <v>6.661867</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.237526</v>
+        <v>8.17334</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.626371</v>
+        <v>7.118872</v>
       </c>
       <c r="AC62" t="n">
-        <v>11.689885</v>
+        <v>13.204119</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12500,13 +12152,13 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AK62" t="n">
+        <v>5.1088</v>
+      </c>
       <c r="AL62" t="n">
-        <v>5.1088</v>
-      </c>
-      <c r="AM62" t="n">
         <v>5.1082</v>
       </c>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12516,33 +12168,31 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
+      <c r="AW62" t="n">
+        <v>-1.30974</v>
+      </c>
       <c r="AX62" t="n">
-        <v>-1.30974</v>
-      </c>
-      <c r="AY62" t="n">
         <v>-1.309892</v>
       </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,150 +588,160 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
+          <t>bcb_sgs_igp_m</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_igp_m_acum_12m</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -810,45 +820,47 @@
         <v>0.96</v>
       </c>
       <c r="AH2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AI2" t="n">
         <v>1.02</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>96.42256999999999</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>99.83515</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>5.121</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>4271865</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>1833179</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>2438686</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>2.94</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>355671</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -865,6 +877,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -967,89 +981,93 @@
         <v>0.87</v>
       </c>
       <c r="AH3" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.88</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>97.03115</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>99.19471</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>4346060</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>1851006</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>2495054</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>1</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BI3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BJ3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BK3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BL3" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1154,89 +1172,93 @@
         <v>1.16</v>
       </c>
       <c r="AH4" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>96.97727</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>97.10229</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>4441056</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>1894119</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>2546936</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>2.34</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>368886</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>1</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BI4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BJ4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BK4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BL4" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1341,89 +1363,93 @@
         <v>1.25</v>
       </c>
       <c r="AH5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>97.49541000000001</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>96.53060000000001</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>5.643</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>2.99</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>367927</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BI5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BJ5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BK5" t="n">
         <v>0</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1528,89 +1554,93 @@
         <v>0.95</v>
       </c>
       <c r="AH6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.84</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>99.05485</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>97.85541000000001</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>367772</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BI6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BK6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1715,89 +1745,93 @@
         <v>0.73</v>
       </c>
       <c r="AH7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>99.30268</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>99.31872</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>3.05</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>362204</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BI7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BJ7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BK7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BL7" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1902,89 +1936,93 @@
         <v>0.54</v>
       </c>
       <c r="AH8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>97.42644</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>91.67792</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>3.26</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>358398</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
         <v>0</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BI8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BJ8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BK8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>0.21</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2089,89 +2127,93 @@
         <v>1.01</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>98.38327</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>95.6409</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>3.38</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>357740</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BI9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BJ9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BK9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
         <v>0.12</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2276,89 +2318,93 @@
         <v>1.62</v>
       </c>
       <c r="AH10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>99.5587</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>104.52811</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>353169</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>1</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BI10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BK10" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2463,89 +2509,93 @@
         <v>1.06</v>
       </c>
       <c r="AH11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>99.56286</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>100.22885</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>3.54</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>345097</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BI11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BJ11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BK11" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2650,89 +2700,93 @@
         <v>0.47</v>
       </c>
       <c r="AH12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AI12" t="n">
         <v>0.45</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>99.67480999999999</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>99.74863999999999</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>346415</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
         <v>1</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BI12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2837,93 +2891,99 @@
         <v>0.67</v>
       </c>
       <c r="AH13" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0.62</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>99.51873000000001</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>99.3134</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>5.238</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>3.57</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>341958</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
+        <v>10.700862</v>
+      </c>
+      <c r="BF13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BG13" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BI13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BJ13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3028,93 +3088,99 @@
         <v>-0.68</v>
       </c>
       <c r="AH14" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AI14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>101.41705</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>103.95829</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AL14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AN14" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>346403</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BA14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BB14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BC14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
+        <v>10.074751</v>
+      </c>
+      <c r="BF14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BI14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BJ14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BK14" t="n">
         <v>0.08</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>0.14</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3219,93 +3285,99 @@
         <v>-0.36</v>
       </c>
       <c r="AH15" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AI15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
         <v>101.1048</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
         <v>104.51622</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AL15" t="n">
         <v>5.179</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AM15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>339664</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AZ15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BA15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BD15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
+        <v>8.58755</v>
+      </c>
+      <c r="BF15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BG15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BI15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BJ15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BK15" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3410,93 +3482,99 @@
         <v>-0.29</v>
       </c>
       <c r="AH16" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AI16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
         <v>101.15658</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AK16" t="n">
         <v>101.18649</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AL16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
         <v>5.406</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AN16" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AO16" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>327580</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BA16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BC16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BE16" t="n">
+        <v>8.248760000000001</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BG16" t="n">
         <v>0</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BI16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3601,93 +3679,99 @@
         <v>0.59</v>
       </c>
       <c r="AH17" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0.47</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
         <v>101.44313</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AK17" t="n">
         <v>100.08007</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AL17" t="n">
         <v>5.257</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AM17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AN17" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>325546</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AZ17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BA17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BC17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
+        <v>6.517038</v>
+      </c>
+      <c r="BF17" t="n">
         <v>6.460076</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BK17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BL17" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3792,93 +3876,99 @@
         <v>0.41</v>
       </c>
       <c r="AH18" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="AI18" t="n">
         <v>0.38</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>100.70751</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AK18" t="n">
         <v>99.15338</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AL18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AN18" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AS18" t="n">
         <v>3.92</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>331505</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BA18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BB18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BD18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
+        <v>5.899363</v>
+      </c>
+      <c r="BF18" t="n">
         <v>5.974439</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3983,93 +4073,99 @@
         <v>0.62</v>
       </c>
       <c r="AH19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AI19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
         <v>100.45671</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AK19" t="n">
         <v>99.96775</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AM19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AN19" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>3.94</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>324703</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BA19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BC19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BD19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BE19" t="n">
+        <v>5.458422</v>
+      </c>
+      <c r="BF19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BG19" t="n">
         <v>0</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BH19" t="n">
         <v>-0</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BI19" t="n">
         <v>-0</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BJ19" t="n">
         <v>0</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BK19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4174,93 +4270,99 @@
         <v>0.53</v>
       </c>
       <c r="AH20" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AI20" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
         <v>100.1131</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>95.09765</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AL20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AN20" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>331122</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AZ20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BA20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BB20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BD20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
+        <v>3.79089</v>
+      </c>
+      <c r="BF20" t="n">
         <v>5.711379</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4365,93 +4467,99 @@
         <v>0.84</v>
       </c>
       <c r="AH21" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AI21" t="n">
         <v>0.77</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
         <v>102.99794</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AK21" t="n">
         <v>98.65175000000001</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AL21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AM21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AN21" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AS21" t="n">
         <v>4.16</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>328098</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BA21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BD21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
+        <v>1.864495</v>
+      </c>
+      <c r="BF21" t="n">
         <v>5.47065</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BK21" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4556,93 +4664,99 @@
         <v>0.71</v>
       </c>
       <c r="AH22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.64</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
         <v>103.10183</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AK22" t="n">
         <v>110.6159</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AL22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>341158</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BA22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BC22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BD22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BE22" t="n">
+        <v>0.172427</v>
+      </c>
+      <c r="BF22" t="n">
         <v>4.361088</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BK22" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4747,93 +4861,99 @@
         <v>0.61</v>
       </c>
       <c r="AH23" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="AI23" t="n">
         <v>0.53</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>104.18587</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>104.03928</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>4.26</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>345725</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BA23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BC23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BD23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BE23" t="n">
+        <v>-2.158772</v>
+      </c>
+      <c r="BF23" t="n">
         <v>3.834324</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BK23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>0.15</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4938,93 +5058,99 @@
         <v>0.23</v>
       </c>
       <c r="AH24" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0.36</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>102.46133</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>102.71672</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>4.35</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>343489</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AY24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BA24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BB24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BD24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
+        <v>-4.45588</v>
+      </c>
+      <c r="BF24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BG24" t="n">
         <v>0</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BH24" t="n">
         <v>-0</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BI24" t="n">
         <v>-0</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BJ24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BK24" t="n">
         <v>0.13</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5129,93 +5255,99 @@
         <v>-0.08</v>
       </c>
       <c r="AH25" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="AI25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>102.39681</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>102.2809</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>343620</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AZ25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BA25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BC25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BD25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BE25" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="BF25" t="n">
         <v>2.998957</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BK25" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5320,93 +5452,99 @@
         <v>0.12</v>
       </c>
       <c r="AH26" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="AI26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>102.86628</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>105.34289</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>4.22</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>345476</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="AZ26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BA26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BB26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BC26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BD26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BE26" t="n">
+        <v>-7.713954</v>
+      </c>
+      <c r="BF26" t="n">
         <v>3.527423</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BK26" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5511,93 +5649,99 @@
         <v>0.23</v>
       </c>
       <c r="AH27" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>102.48117</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>106.05936</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>4.12</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>344177</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AX27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AY27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AZ27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BA27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BB27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BC27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BD27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BE27" t="n">
+        <v>-7.193509</v>
+      </c>
+      <c r="BF27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BG27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BI27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BK27" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5702,93 +5846,99 @@
         <v>0.26</v>
       </c>
       <c r="AH28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AI28" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>102.49422</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>101.75832</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>5.007</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>4</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>340324</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="AZ28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BA28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BB28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BC28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BD28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BE28" t="n">
+        <v>-5.956714</v>
+      </c>
+      <c r="BF28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BI28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BH28" t="n">
+      <c r="BJ28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BK28" t="n">
         <v>0</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BL28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK28" t="n">
+      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5893,93 +6043,99 @@
         <v>0.24</v>
       </c>
       <c r="AH29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI29" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>102.81544</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>101.93091</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.97</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>340247</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AY29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AZ29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BA29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BB29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BC29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BD29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BE29" t="n">
+        <v>-4.560737</v>
+      </c>
+      <c r="BF29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BG29" t="n">
         <v>0</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BI29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BH29" t="n">
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BK29" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BL29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK29" t="n">
+      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6084,93 +6240,99 @@
         <v>0.28</v>
       </c>
       <c r="AH30" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>103.57529</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>101.68306</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.88</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>348406</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AY30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AZ30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BA30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BB30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BC30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BD30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BE30" t="n">
+        <v>-3.457004</v>
+      </c>
+      <c r="BF30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BG30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BI30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BH30" t="n">
+      <c r="BJ30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BK30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BL30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BK30" t="n">
+      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6275,93 +6437,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH31" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AI31" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>104.68308</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AK31" t="n">
         <v>101.68292</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>355034</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AZ31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BA31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BB31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BC31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BD31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BE31" t="n">
+        <v>-3.178284</v>
+      </c>
+      <c r="BF31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BG31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BI31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BJ31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BK31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BL31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BK31" t="n">
+      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6466,93 +6634,99 @@
         <v>0.42</v>
       </c>
       <c r="AH32" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AI32" t="n">
         <v>0.57</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>104.47997</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AK32" t="n">
         <v>99.29383</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>355066</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AZ32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BA32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BB32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BC32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BD32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BE32" t="n">
+        <v>-3.31355</v>
+      </c>
+      <c r="BF32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BG32" t="n">
         <v>0</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BI32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BH32" t="n">
+      <c r="BJ32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BK32" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BL32" t="n">
         <v>0.01</v>
       </c>
-      <c r="BK32" t="n">
+      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6657,93 +6831,99 @@
         <v>0.83</v>
       </c>
       <c r="AH33" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="AI33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
         <v>104.63436</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AK33" t="n">
         <v>102.15169</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>352705</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AX33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AZ33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BA33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BB33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BC33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BD33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BE33" t="n">
+        <v>-3.758575</v>
+      </c>
+      <c r="BF33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BG33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BI33" t="n">
         <v>-0.001782</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6848,93 +7028,99 @@
         <v>0.16</v>
       </c>
       <c r="AH34" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="AI34" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
         <v>104.71934</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>109.56886</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>355008</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AZ34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BA34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BB34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BC34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
+        <v>-4.25878</v>
+      </c>
+      <c r="BF34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BG34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BI34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7039,93 +7225,99 @@
         <v>0.38</v>
       </c>
       <c r="AH35" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0.37</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
         <v>104.96661</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>109.2559</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>351599</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AX35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AY35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AZ35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BA35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BB35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BC35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BD35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BE35" t="n">
+        <v>-3.040871</v>
+      </c>
+      <c r="BF35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BG35" t="n">
         <v>0</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BI35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7230,93 +7422,99 @@
         <v>0.46</v>
       </c>
       <c r="AH36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AI36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
         <v>105.66388</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AK36" t="n">
         <v>104.71434</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AL36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>5.241</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AN36" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>355560</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AX36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AY36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AZ36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BA36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BB36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BC36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BD36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BE36" t="n">
+        <v>-0.344269</v>
+      </c>
+      <c r="BF36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BG36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BI36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BH36" t="n">
+      <c r="BJ36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI36" t="n">
+      <c r="BK36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BL36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK36" t="n">
+      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7421,93 +7619,99 @@
         <v>0.21</v>
       </c>
       <c r="AH37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AI37" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
         <v>106.57692</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AK37" t="n">
         <v>105.86962</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AL37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AM37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AN37" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>357827</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AX37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AY37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AZ37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BA37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BB37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BC37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BD37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BE37" t="n">
+        <v>2.440035</v>
+      </c>
+      <c r="BF37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BG37" t="n">
         <v>0</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BI37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BH37" t="n">
+      <c r="BJ37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BI37" t="n">
+      <c r="BK37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BL37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7612,93 +7816,99 @@
         <v>0.38</v>
       </c>
       <c r="AH38" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
         <v>106.95254</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AK38" t="n">
         <v>111.51388</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AL38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AN38" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>363282</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AY38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="AZ38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BA38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BB38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BC38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BD38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BE38" t="n">
+        <v>3.812368</v>
+      </c>
+      <c r="BF38" t="n">
         <v>4.060953</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI38" t="n">
+      <c r="BK38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BL38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK38" t="n">
+      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7803,93 +8013,99 @@
         <v>-0.02</v>
       </c>
       <c r="AH39" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AI39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AJ39" t="n">
         <v>107.13607</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AK39" t="n">
         <v>110.06483</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AM39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>369214</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="AZ39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BA39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BB39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BC39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BD39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BE39" t="n">
+        <v>4.259387</v>
+      </c>
+      <c r="BF39" t="n">
         <v>3.707852</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI39" t="n">
+      <c r="BK39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ39" t="n">
+      <c r="BL39" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK39" t="n">
+      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7994,93 +8210,99 @@
         <v>0.44</v>
       </c>
       <c r="AH40" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AJ40" t="n">
         <v>107.99994</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AK40" t="n">
         <v>107.08167</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AL40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>3.83</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>372016</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AY40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="AZ40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BA40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BB40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BC40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BD40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BE40" t="n">
+        <v>4.519075</v>
+      </c>
+      <c r="BF40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BG40" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="BG40" t="n">
+      <c r="BI40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8185,93 +8407,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI41" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
         <v>108.20756</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AK41" t="n">
         <v>109.18693</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AL41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AM41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AN41" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>3.79</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AT41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AU41" t="n">
         <v>366096</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AW41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AX41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AY41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="AZ41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BA41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BB41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BC41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BD41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BE41" t="n">
+        <v>5.579866</v>
+      </c>
+      <c r="BF41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BG41" t="n">
         <v>0</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BI41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8376,93 +8604,99 @@
         <v>0.39</v>
       </c>
       <c r="AH42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI42" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
         <v>107.96783</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AK42" t="n">
         <v>105.49025</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AL42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AT42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AU42" t="n">
         <v>363003</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AW42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AX42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AY42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="AZ42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BA42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BB42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BC42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BD42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BE42" t="n">
+        <v>6.325086</v>
+      </c>
+      <c r="BF42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BG42" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BI42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BH42" t="n">
+      <c r="BJ42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI42" t="n">
+      <c r="BK42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BL42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BK42" t="n">
+      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8567,93 +8801,99 @@
         <v>0.52</v>
       </c>
       <c r="AH43" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AI43" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
         <v>107.1418</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AK43" t="n">
         <v>104.15997</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AL43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AM43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>3.63</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>329730</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AY43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="AZ43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BA43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BB43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BC43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BD43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
+        <v>6.536174</v>
+      </c>
+      <c r="BF43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BG43" t="n">
         <v>1</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BI43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BH43" t="n">
+      <c r="BJ43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BK43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BL43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8758,93 +8998,99 @@
         <v>0.16</v>
       </c>
       <c r="AH44" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AI44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
         <v>108.21392</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AK44" t="n">
         <v>102.72834</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AL44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AM44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>328303</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AY44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="AZ44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BA44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BB44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BC44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BD44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BE44" t="n">
+        <v>6.749097</v>
+      </c>
+      <c r="BF44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BG44" t="n">
         <v>1</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BI44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8949,93 +9195,99 @@
         <v>1.31</v>
       </c>
       <c r="AH45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
         <v>108.74593</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AK45" t="n">
         <v>106.92609</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AL45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AN45" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>3.96</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AT45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AU45" t="n">
         <v>332508</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AW45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AX45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AY45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="AZ45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BA45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BB45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BC45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BD45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BE45" t="n">
+        <v>8.444549</v>
+      </c>
+      <c r="BF45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BG45" t="n">
         <v>0</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BI45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9140,93 +9392,99 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AH46" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AI46" t="n">
         <v>0.51</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
         <v>110.20451</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AK46" t="n">
         <v>114.11998</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AL46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AM46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4.03</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AU46" t="n">
         <v>336157</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AW46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AY46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="AZ46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BA46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BB46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BC46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BD46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BE46" t="n">
+        <v>8.586193</v>
+      </c>
+      <c r="BF46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BG46" t="n">
         <v>1</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BI46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BH46" t="n">
+      <c r="BJ46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI46" t="n">
+      <c r="BK46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BL46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK46" t="n">
+      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9331,93 +9589,99 @@
         <v>0.43</v>
       </c>
       <c r="AH47" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AI47" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AJ47" t="n">
         <v>110.0593</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AK47" t="n">
         <v>112.69428</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AL47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AM47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AN47" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AT47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AU47" t="n">
         <v>340789</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AW47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AY47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="AZ47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BA47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BB47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BC47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BD47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BE47" t="n">
+        <v>8.510418</v>
+      </c>
+      <c r="BF47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BG47" t="n">
         <v>0</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BI47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BH47" t="n">
+      <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BK47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BL47" t="n">
         <v>0.22</v>
       </c>
-      <c r="BK47" t="n">
+      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9522,93 +9786,99 @@
         <v>0.26</v>
       </c>
       <c r="AH48" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="AI48" t="n">
         <v>0.35</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
         <v>109.08727</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AK48" t="n">
         <v>108.65566</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AL48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AM48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>4.36</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AT48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AU48" t="n">
         <v>341459</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AW48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AX48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="AZ48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BA48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BB48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BC48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BD48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BE48" t="n">
+        <v>7.026183</v>
+      </c>
+      <c r="BF48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BG48" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BI48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BH48" t="n">
+      <c r="BJ48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BK48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BL48" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9713,93 +9983,99 @@
         <v>0.24</v>
       </c>
       <c r="AH49" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AI49" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AJ49" t="n">
         <v>108.85988</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AK49" t="n">
         <v>107.4594</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AM49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>4.41</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>344440</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AW49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="AZ49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BA49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BB49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BC49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BD49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BE49" t="n">
+        <v>4.393261</v>
+      </c>
+      <c r="BF49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BG49" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BI49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BH49" t="n">
+      <c r="BJ49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BK49" t="n">
         <v>0</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BL49" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9904,93 +10180,99 @@
         <v>0.26</v>
       </c>
       <c r="AH50" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="AI50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
         <v>108.41316</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AK50" t="n">
         <v>113.21721</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>4.66</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>345111</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AX50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AY50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="AZ50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BA50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BB50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BC50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BD50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BE50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="BF50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BG50" t="n">
         <v>0</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BI50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BH50" t="n">
+      <c r="BJ50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BK50" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BL50" t="n">
         <v>0.25</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10095,93 +10377,99 @@
         <v>-0.11</v>
       </c>
       <c r="AH51" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
         <v>108.83964</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AK51" t="n">
         <v>110.47825</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AM51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>4.92</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AT51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AU51" t="n">
         <v>350767</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AY51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="AZ51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BA51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BB51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BC51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BD51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BE51" t="n">
+        <v>3.033233</v>
+      </c>
+      <c r="BF51" t="n">
         <v>5.054283</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BK51" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BL51" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10286,93 +10574,99 @@
         <v>0.48</v>
       </c>
       <c r="AH52" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AI52" t="n">
         <v>0.52</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
         <v>108.76251</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AK52" t="n">
         <v>109.57602</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AL52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AM52" t="n">
         <v>5.318</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AN52" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>4.89</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AT52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AU52" t="n">
         <v>356582</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AW52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AY52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="AZ52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BA52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BB52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BC52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BD52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BE52" t="n">
+        <v>2.828436</v>
+      </c>
+      <c r="BF52" t="n">
         <v>5.096104</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BI52" t="n">
+      <c r="BK52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ52" t="n">
+      <c r="BL52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK52" t="n">
+      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10477,93 +10771,99 @@
         <v>0.09</v>
       </c>
       <c r="AH53" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI53" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
         <v>108.78795</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AK53" t="n">
         <v>110.16742</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AL53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AM53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AN53" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>4.99</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AT53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AU53" t="n">
         <v>357103</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AW53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AX53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AY53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="AZ53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BA53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BB53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BC53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BD53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BE53" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="BF53" t="n">
         <v>4.490243</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI53" t="n">
+      <c r="BK53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BL53" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK53" t="n">
+      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10668,93 +10968,99 @@
         <v>0.18</v>
       </c>
       <c r="AH54" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AI54" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
         <v>109.30007</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AK54" t="n">
         <v>106.69062</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AL54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AM54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AN54" t="n">
         <v>7003273</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2616213</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>4387061</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>4.23</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.74</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AT54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AU54" t="n">
         <v>360578</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AW54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AX54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AY54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AZ54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BA54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BB54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BC54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BD54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BE54" t="n">
+        <v>-0.101973</v>
+      </c>
+      <c r="BF54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BG54" t="n">
         <v>0</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BH54" t="n">
         <v>-0</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BI54" t="n">
         <v>-0</v>
       </c>
-      <c r="BH54" t="n">
+      <c r="BJ54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI54" t="n">
+      <c r="BK54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BL54" t="n">
         <v>0.13</v>
       </c>
-      <c r="BK54" t="n">
+      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10859,93 +11165,99 @@
         <v>0.33</v>
       </c>
       <c r="AH55" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AI55" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
         <v>109.27117</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AK55" t="n">
         <v>107.27827</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AM55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AN55" t="n">
         <v>7136436</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2701146</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>4435290</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.68</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AT55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AU55" t="n">
         <v>358234</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AW55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AY55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="AZ55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BA55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BB55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BC55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BD55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="BD55" t="n">
+      <c r="BE55" t="n">
+        <v>-1.042167</v>
+      </c>
+      <c r="BF55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI55" t="n">
+      <c r="BK55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BL55" t="n">
         <v>0</v>
       </c>
-      <c r="BK55" t="n">
+      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11050,93 +11362,99 @@
         <v>0.33</v>
       </c>
       <c r="AH56" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AI56" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
         <v>110.09703</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AK56" t="n">
         <v>103.80093</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AM56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AN56" t="n">
         <v>7130500</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2654052</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>4476448</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>4.45</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>5.38</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AT56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AU56" t="n">
         <v>364367</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AW56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AX56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AY56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="AZ56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BA56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BB56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BC56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BD56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BE56" t="n">
+        <v>-0.903999</v>
+      </c>
+      <c r="BF56" t="n">
         <v>4.303068</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BI56" t="n">
+      <c r="BK56" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BL56" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK56" t="n">
+      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11241,93 +11559,99 @@
         <v>0.7</v>
       </c>
       <c r="AH57" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="AI57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
         <v>110.78559</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AK57" t="n">
         <v>106.7205</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AL57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AM57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AN57" t="n">
         <v>7156987</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2655931</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>4501056</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>5.56</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AT57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AU57" t="n">
         <v>371074</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AW57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AX57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AY57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="AZ57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BA57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BB57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BC57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BD57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BE57" t="n">
+        <v>-2.659212</v>
+      </c>
+      <c r="BF57" t="n">
         <v>3.357475</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI57" t="n">
+      <c r="BK57" t="n">
         <v>0.2</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BL57" t="n">
         <v>0.18</v>
       </c>
-      <c r="BK57" t="n">
+      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11432,93 +11756,99 @@
         <v>0.88</v>
       </c>
       <c r="AH58" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AI58" t="n">
         <v>0.91</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
         <v>110.58589</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AK58" t="n">
         <v>117.92682</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AL58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AM58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AN58" t="n">
         <v>7237735</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2686046</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>4551689</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>3.04</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AT58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AU58" t="n">
         <v>362002</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AW58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AX58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AY58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="AZ58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BA58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BB58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BC58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BD58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BE58" t="n">
+        <v>-1.819225</v>
+      </c>
+      <c r="BF58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BG58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BI58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BH58" t="n">
+      <c r="BJ58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BI58" t="n">
+      <c r="BK58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ58" t="n">
+      <c r="BL58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BK58" t="n">
+      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11623,93 +11953,99 @@
         <v>0.67</v>
       </c>
       <c r="AH59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AI59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AJ59" t="n">
         <v>111.15205</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AK59" t="n">
         <v>113.72712</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AL59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AM59" t="n">
         <v>4.988</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AN59" t="n">
         <v>7258599</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2684623</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>4573976</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>4.63</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AT59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AU59" t="n">
         <v>366913</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AW59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AX59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AY59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="AZ59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BA59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BB59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BC59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BD59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BE59" t="n">
+        <v>0.619623</v>
+      </c>
+      <c r="BF59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BG59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BI59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI59" t="n">
-        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11814,85 +12150,91 @@
         <v>0.58</v>
       </c>
       <c r="AH60" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI60" t="n">
         <v>0.65</v>
       </c>
-      <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="n">
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AM60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AN60" t="n">
         <v>7299615</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2704550</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>4595065</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>4.74</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>3.24</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>5.62</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AT60" t="n">
         <v>33.42</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="n">
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AY60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="AZ60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BA60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BB60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BC60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BD60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BE60" t="n">
+        <v>1.964454</v>
+      </c>
+      <c r="BF60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BG60" t="n">
         <v>0</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="BG60" t="n">
+      <c r="BI60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -11997,147 +12339,153 @@
         <v>0.16</v>
       </c>
       <c r="AH61" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="n">
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
-      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="n">
         <v>367558</v>
       </c>
-      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="n">
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AX61" t="n">
+      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="n">
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BD61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="BD61" t="n">
+      <c r="BE61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="BF61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="BE61" t="n">
+      <c r="BG61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BI61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BH61" t="inlineStr"/>
-      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>177866</v>
+        <v>175739</v>
       </c>
       <c r="C62" t="n">
-        <v>175.009995</v>
+        <v>172.25</v>
       </c>
       <c r="D62" t="n">
-        <v>111.080002</v>
+        <v>109.199997</v>
       </c>
       <c r="E62" t="n">
-        <v>436.290009</v>
+        <v>434.600006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1165</v>
+        <v>5.1318</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8455</v>
+        <v>5.8466</v>
       </c>
       <c r="H62" t="n">
-        <v>7575.390137</v>
+        <v>7515.339844</v>
       </c>
       <c r="I62" t="n">
-        <v>26281.609375</v>
+        <v>25873.179688</v>
       </c>
       <c r="J62" t="n">
-        <v>52637.011719</v>
+        <v>52498.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4067.899902</v>
+        <v>4029</v>
       </c>
       <c r="L62" t="n">
-        <v>74.129997</v>
+        <v>80.510002</v>
       </c>
       <c r="M62" t="n">
-        <v>78.879997</v>
+        <v>86.900002</v>
       </c>
       <c r="N62" t="n">
-        <v>1196.25</v>
+        <v>1187.5</v>
       </c>
       <c r="O62" t="n">
-        <v>467.25</v>
+        <v>457.5</v>
       </c>
       <c r="P62" t="n">
-        <v>3.396038</v>
+        <v>2.159582</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.525579</v>
+        <v>1.892929</v>
       </c>
       <c r="R62" t="n">
-        <v>2.870901</v>
+        <v>1.129833</v>
       </c>
       <c r="S62" t="n">
-        <v>0.14691</v>
+        <v>-0.241016</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.259934</v>
+        <v>-0.964664</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.211055</v>
+        <v>-1.192464</v>
       </c>
       <c r="V62" t="n">
-        <v>1.013824</v>
+        <v>0.213085</v>
       </c>
       <c r="W62" t="n">
-        <v>0.258981</v>
+        <v>-1.299095</v>
       </c>
       <c r="X62" t="n">
-        <v>0.607449</v>
+        <v>0.342974</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.118596</v>
+        <v>0.151634</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.661867</v>
+        <v>15.84173</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.17334</v>
+        <v>19.1717</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.118872</v>
+        <v>6.335348</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.204119</v>
+        <v>10.841914</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12152,13 +12500,13 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="n">
-        <v>5.1088</v>
-      </c>
+      <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.1082</v>
-      </c>
-      <c r="AM62" t="inlineStr"/>
+        <v>5.1183</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>5.1177</v>
+      </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12168,31 +12516,33 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="n">
-        <v>-1.30974</v>
-      </c>
+      <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.309892</v>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+        <v>-1.126222</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>-1.126352</v>
+      </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="n">
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
         <v>0</v>
       </c>
-      <c r="BF62" t="n">
+      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BI62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BH62" t="inlineStr"/>
-      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12407,19 +12407,19 @@
         <v>175739</v>
       </c>
       <c r="C62" t="n">
-        <v>172.25</v>
+        <v>173.600006</v>
       </c>
       <c r="D62" t="n">
-        <v>109.199997</v>
+        <v>110.400002</v>
       </c>
       <c r="E62" t="n">
-        <v>434.600006</v>
+        <v>432</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1318</v>
+        <v>5.0745</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8466</v>
+        <v>5.7922</v>
       </c>
       <c r="H62" t="n">
         <v>7515.339844</v>
@@ -12431,37 +12431,37 @@
         <v>52498.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4029</v>
+        <v>4035.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>80.510002</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>86.900002</v>
+        <v>85.260002</v>
       </c>
       <c r="N62" t="n">
-        <v>1187.5</v>
+        <v>1195.5</v>
       </c>
       <c r="O62" t="n">
-        <v>457.5</v>
+        <v>465</v>
       </c>
       <c r="P62" t="n">
         <v>2.159582</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.892929</v>
+        <v>2.691513</v>
       </c>
       <c r="R62" t="n">
-        <v>1.129833</v>
+        <v>2.241154</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.241016</v>
+        <v>-0.837827</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.964664</v>
+        <v>-2.070462</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.192464</v>
+        <v>-2.111823</v>
       </c>
       <c r="V62" t="n">
         <v>0.213085</v>
@@ -12473,19 +12473,19 @@
         <v>0.342974</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.151634</v>
+        <v>0.32315</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.84173</v>
+        <v>14.84892</v>
       </c>
       <c r="AA62" t="n">
-        <v>19.1717</v>
+        <v>16.922661</v>
       </c>
       <c r="AB62" t="n">
-        <v>6.335348</v>
+        <v>7.051713</v>
       </c>
       <c r="AC62" t="n">
-        <v>10.841914</v>
+        <v>12.658995</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12502,10 +12502,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.1183</v>
+        <v>5.0742</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.1177</v>
+        <v>5.0736</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12518,10 +12518,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.126222</v>
+        <v>-1.978132</v>
       </c>
       <c r="AY62" t="n">
-        <v>-1.126352</v>
+        <v>-1.978362</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,105 +643,95 @@
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>bcb_sgs_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pf</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -853,14 +843,12 @@
         <v>1.58</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -877,8 +865,6 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1014,60 +1000,54 @@
         <v>1.56</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>0.631159</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.631159</v>
+        <v>-0.641498</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.641498</v>
+        <v>0.423696</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1205,60 +1185,54 @@
         <v>1.43</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>-0.055529</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.055529</v>
+        <v>-2.109407</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.109407</v>
+        <v>5.757004</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>1</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1396,60 +1370,54 @@
         <v>1.43</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>0.53429</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53429</v>
+        <v>-0.58875</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.58875</v>
+        <v>3.74306</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1587,60 +1555,54 @@
         <v>1.46</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="AU6" t="n">
-        <v>367772</v>
+        <v>1.599501</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.599501</v>
+        <v>1.372425</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.372425</v>
+        <v>-0.409357</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1778,60 +1740,54 @@
         <v>1.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>0.250195</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.250195</v>
+        <v>1.49538</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.49538</v>
+        <v>-0.70108</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1969,60 +1925,54 @@
         <v>1.46</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-1.889415</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.889415</v>
+        <v>-7.693212</v>
       </c>
       <c r="AW8" t="n">
-        <v>-7.693212</v>
+        <v>-3.99785</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="AY8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2160,60 +2110,54 @@
         <v>1.44</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>0.982105</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.982105</v>
+        <v>4.32272</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.32272</v>
+        <v>-4.069138</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2351,60 +2295,54 @@
         <v>1.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>1.194746</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.194746</v>
+        <v>9.292268999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.292268999999999</v>
+        <v>-7.814142</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2542,60 +2480,54 @@
         <v>1.57</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>0.004178</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.004178</v>
+        <v>-4.113018</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.113018</v>
+        <v>3.826671</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2733,60 +2665,54 @@
         <v>1.57</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>0.112442</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.112442</v>
+        <v>-0.479114</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.479114</v>
+        <v>-3.866561</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>1</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2924,66 +2850,60 @@
         <v>1.52</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>-0.156589</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.156589</v>
+        <v>-0.436337</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.436337</v>
+        <v>10.765717</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>0.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3121,66 +3041,60 @@
         <v>1.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>1.9075</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.9075</v>
+        <v>4.677002</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.677002</v>
+        <v>-0.946926</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3318,66 +3232,60 @@
         <v>1.62</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>-0.307887</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.307887</v>
+        <v>0.536686</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.536686</v>
+        <v>-0.181173</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3515,66 +3423,60 @@
         <v>1.65</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>0.051214</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.051214</v>
+        <v>-3.18585</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.18585</v>
+        <v>4.394671</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3712,46 +3614,46 @@
         <v>1.77</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>0.283274</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.283274</v>
+        <v>-1.093446</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.093446</v>
+        <v>-2.766988</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>6.460076</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3760,18 +3662,12 @@
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3909,46 +3805,46 @@
         <v>1.81</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>-0.725155</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.725155</v>
+        <v>-0.925949</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.925949</v>
+        <v>0.705726</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>5.974439</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3957,18 +3853,12 @@
         <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4106,66 +3996,60 @@
         <v>1.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>-0.249038</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.249038</v>
+        <v>0.821323</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.821323</v>
+        <v>-1.443116</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>5.932356</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH19" t="n">
         <v>-0</v>
       </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4303,46 +4187,46 @@
         <v>1.94</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-0.342048</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.342048</v>
+        <v>-4.871671</v>
       </c>
       <c r="AW20" t="n">
-        <v>-4.871671</v>
+        <v>-2.269199</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>5.711379</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4351,18 +4235,12 @@
         <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4500,46 +4378,46 @@
         <v>2.17</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>2.881581</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.881581</v>
+        <v>3.737316</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.737316</v>
+        <v>2.127743</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>5.47065</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4548,18 +4426,12 @@
         <v>0</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4697,46 +4569,46 @@
         <v>2.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>0.100866</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.100866</v>
+        <v>12.127661</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.127661</v>
+        <v>-2.446331</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>4.361088</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4745,18 +4617,12 @@
         <v>0</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4894,46 +4760,46 @@
         <v>2.45</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>1.051427</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.051427</v>
+        <v>-5.945456</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.945456</v>
+        <v>-1.568774</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>3.834324</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -4942,18 +4808,12 @@
         <v>0</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5091,66 +4951,60 @@
         <v>2.58</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>-1.655253</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.655253</v>
+        <v>-1.271212</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.271212</v>
+        <v>1.903733</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>3.741292</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH24" t="n">
         <v>-0</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5288,46 +5142,46 @@
         <v>2.63</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="AU25" t="n">
-        <v>343620</v>
+        <v>-0.06297</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.06297</v>
+        <v>-0.424293</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.424293</v>
+        <v>-5.429855</v>
       </c>
       <c r="AX25" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="AY25" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.472174</v>
+        <v>1.122473</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.122473</v>
+        <v>0.050421</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.050421</v>
+        <v>0.038138</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.161501</v>
+        <v>-6.84947</v>
       </c>
       <c r="BE25" t="n">
-        <v>-6.84947</v>
+        <v>2.998957</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5336,18 +5190,12 @@
         <v>0</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.04</v>
+        <v>0.05</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5485,46 +5333,46 @@
         <v>2.73</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>0.458481</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.458481</v>
+        <v>2.993707</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.993707</v>
+        <v>-1.612301</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>3.527423</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5533,18 +5381,12 @@
         <v>0</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5682,66 +5524,60 @@
         <v>2.82</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>-0.374379</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.374379</v>
+        <v>0.680131</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.680131</v>
+        <v>3.804703</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>4.057054</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
       <c r="BI27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>0.09</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5879,66 +5715,60 @@
         <v>2.82</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>0.012734</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.012734</v>
+        <v>-4.055314</v>
       </c>
       <c r="AW28" t="n">
-        <v>-4.055314</v>
+        <v>1.741198</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>4.505936</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
       <c r="BI28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6076,66 +5906,60 @@
         <v>2.92</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.313403</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.313403</v>
+        <v>0.169608</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.169608</v>
+        <v>0.996485</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>4.141877</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
       <c r="BI29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6273,66 +6097,60 @@
         <v>2.99</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>0.739043</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.739043</v>
+        <v>-0.243155</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.243155</v>
+        <v>-2.412259</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>3.851383</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
       <c r="BI30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6470,66 +6288,60 @@
         <v>2.59</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>1.06955</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.06955</v>
+        <v>-0.000138</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.000138</v>
+        <v>-1.908621</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>3.706988</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.24</v>
+        <v>-0.4</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6667,66 +6479,60 @@
         <v>2.77</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>-0.194024</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.194024</v>
+        <v>-2.349549</v>
       </c>
       <c r="AW32" t="n">
-        <v>-2.349549</v>
+        <v>2.317559</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>3.820543</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6864,66 +6670,60 @@
         <v>2.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>0.14777</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.14777</v>
+        <v>2.878185</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.878185</v>
+        <v>0.601595</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>3.861754</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>-0.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
       <c r="BI33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BJ33" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7061,66 +6861,60 @@
         <v>2.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>0.081216</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.081216</v>
+        <v>7.260937</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.260937</v>
+        <v>0.258865</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>3.397348</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7258,66 +7052,60 @@
         <v>2.76</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>0.236126</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.236126</v>
+        <v>-0.285629</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.285629</v>
+        <v>3.514671</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>3.232784</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BJ35" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7455,66 +7243,60 @@
         <v>2.8</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>0.664278</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.664278</v>
+        <v>-4.15681</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.15681</v>
+        <v>1.349627</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>3.335647</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>-0.25</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
       <c r="BI36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7652,66 +7434,60 @@
         <v>2.64</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>0.864098</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.864098</v>
+        <v>1.103268</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.103268</v>
+        <v>6.053495</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>3.697684</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7849,46 +7625,46 @@
         <v>2.52</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>0.35244</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.35244</v>
+        <v>5.331331</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.331331</v>
+        <v>1.856482</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>4.060953</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -7897,18 +7673,12 @@
         <v>0</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8046,46 +7816,46 @@
         <v>2.55</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>0.171599</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.171599</v>
+        <v>-1.299435</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.299435</v>
+        <v>-0.104202</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>3.707852</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8094,18 +7864,12 @@
         <v>0</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8243,66 +8007,60 @@
         <v>2.56</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>0.80633</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.80633</v>
+        <v>-2.710366</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.710366</v>
+        <v>-3.679149</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>4.091149</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.25</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8440,66 +8198,60 @@
         <v>2.52</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>0.192241</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.192241</v>
+        <v>1.966032</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.966032</v>
+        <v>6.053487</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>4.600584</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8637,66 +8389,60 @@
         <v>2.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>-0.221546</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.221546</v>
+        <v>-3.385643</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.385643</v>
+        <v>4.769899</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>4.840925</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>0.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8834,66 +8580,60 @@
         <v>2.21</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>-0.76507</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.76507</v>
+        <v>-1.261045</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.261045</v>
+        <v>2.292888</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>4.767938</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>1</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BJ43" t="n">
-        <v>-0.19</v>
+        <v>-0.29</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9031,66 +8771,60 @@
         <v>2.43</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>1.000655</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.000655</v>
+        <v>-1.374453</v>
       </c>
       <c r="AW44" t="n">
-        <v>-1.374453</v>
+        <v>-5.8492</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>4.174145</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>1</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BJ44" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9228,66 +8962,60 @@
         <v>2.52</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>0.491628</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.491628</v>
+        <v>4.086263</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.086263</v>
+        <v>0.320749</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>4.866504</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9425,66 +9153,60 @@
         <v>2.49</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>1.341273</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.341273</v>
+        <v>6.727909</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.727909</v>
+        <v>-1.822596</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>5.201441</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>1</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9622,66 +9344,60 @@
         <v>2.72</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-0.131764</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.131764</v>
+        <v>-1.249299</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.249299</v>
+        <v>-1.417575</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>5.316736</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9819,66 +9535,60 @@
         <v>2.67</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>-0.883188</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.883188</v>
+        <v>-3.583696</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.583696</v>
+        <v>0.84617</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>5.201418</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -10016,66 +9726,60 @@
         <v>2.67</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-0.208448</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.208448</v>
+        <v>-1.100964</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.100964</v>
+        <v>-4.407308</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>5.18043</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.25</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10213,66 +9917,60 @@
         <v>2.79</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="AT50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="AU50" t="n">
-        <v>345111</v>
+        <v>-0.410362</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.410362</v>
+        <v>5.358126</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.358126</v>
+        <v>2.657089</v>
       </c>
       <c r="AX50" t="n">
-        <v>2.657089</v>
+        <v>2.657381</v>
       </c>
       <c r="AY50" t="n">
-        <v>2.657381</v>
+        <v>0.440744</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.440744</v>
+        <v>-0.129254</v>
       </c>
       <c r="BA50" t="n">
-        <v>-0.129254</v>
+        <v>0.79014</v>
       </c>
       <c r="BB50" t="n">
-        <v>0.79014</v>
+        <v>0.194809</v>
       </c>
       <c r="BC50" t="n">
-        <v>0.194809</v>
+        <v>5.225222</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.225222</v>
+        <v>2.961368</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.961368</v>
+        <v>5.127976</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.127976</v>
+        <v>0</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10410,46 +10108,46 @@
         <v>2.85</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>0.393384</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.393384</v>
+        <v>-2.419208</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.419208</v>
+        <v>-3.136324</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>5.054283</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10458,18 +10156,12 @@
         <v>0</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.18</v>
+        <v>0.06</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10607,46 +10299,46 @@
         <v>2.77</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-0.070866</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.070866</v>
+        <v>-0.816658</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.816658</v>
+        <v>-1.986584</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>5.096104</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10655,18 +10347,12 @@
         <v>0</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ52" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10804,46 +10490,46 @@
         <v>2.82</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="AU53" t="n">
-        <v>357103</v>
+        <v>0.02339</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.02339</v>
+        <v>0.539717</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.539717</v>
+        <v>1.235287</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>4.490243</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10852,18 +10538,12 @@
         <v>0</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -11001,66 +10681,60 @@
         <v>2.74</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>0.470751</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.470751</v>
+        <v>-3.155924</v>
       </c>
       <c r="AW54" t="n">
-        <v>-3.155924</v>
+        <v>-0.937912</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>4.177803</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH54" t="n">
         <v>-0</v>
       </c>
       <c r="BI54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11198,46 +10872,46 @@
         <v>2.68</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>-0.026441</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.026441</v>
+        <v>0.550798</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.550798</v>
+        <v>3.160973</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>3.897866</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11246,18 +10920,12 @@
         <v>0</v>
       </c>
       <c r="BI55" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ55" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11395,46 +11063,46 @@
         <v>2.87</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>0.755789</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.755789</v>
+        <v>-3.241421</v>
       </c>
       <c r="AW56" t="n">
-        <v>-3.241421</v>
+        <v>-4.94875</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>4.303068</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11443,18 +11111,12 @@
         <v>0</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11592,46 +11254,46 @@
         <v>3.07</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>0.625412</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.625412</v>
+        <v>2.812663</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.812663</v>
+        <v>-1.54108</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>3.357475</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11640,18 +11302,12 @@
         <v>0</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11789,66 +11445,60 @@
         <v>3.04</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>-0.180258</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.180258</v>
+        <v>10.500625</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.500625</v>
+        <v>1.357413</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>3.768807</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.25</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
       <c r="BI58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ58" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11986,66 +11636,60 @@
         <v>3.15</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>0.511964</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.511964</v>
+        <v>-3.561276</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.561276</v>
+        <v>-4.421964</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>4.109608</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>-0.25</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
       <c r="BI59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12179,62 +11823,56 @@
         <v>3.24</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="AU60" t="n">
         <v>371137</v>
       </c>
+      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
+      <c r="AW60" t="n">
+        <v>1.369122</v>
+      </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>4.420848</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BJ60" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12358,134 +11996,132 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="n">
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
+      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
+      <c r="AW61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="AX61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="inlineStr"/>
+      <c r="BB61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="BD61" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="BE61" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.327084</v>
+        <v>-0.25</v>
       </c>
       <c r="BG61" t="n">
-        <v>-0.25</v>
+        <v>-0.000372</v>
       </c>
       <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175739</v>
+        <v>175690.03125</v>
       </c>
       <c r="C62" t="n">
-        <v>173.600006</v>
+        <v>172.649994</v>
       </c>
       <c r="D62" t="n">
-        <v>110.400002</v>
+        <v>109.639999</v>
       </c>
       <c r="E62" t="n">
-        <v>432</v>
+        <v>432.140015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0745</v>
+        <v>5.0804</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7922</v>
+        <v>5.8103</v>
       </c>
       <c r="H62" t="n">
-        <v>7515.339844</v>
+        <v>7533.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>25873.179688</v>
+        <v>26095.494141</v>
       </c>
       <c r="J62" t="n">
-        <v>52498.640625</v>
+        <v>52471</v>
       </c>
       <c r="K62" t="n">
-        <v>4035.899902</v>
+        <v>4041.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>79.81999999999999</v>
+        <v>79.040001</v>
       </c>
       <c r="M62" t="n">
-        <v>85.260002</v>
+        <v>84.449997</v>
       </c>
       <c r="N62" t="n">
-        <v>1195.5</v>
+        <v>1195</v>
       </c>
       <c r="O62" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P62" t="n">
-        <v>2.159582</v>
+        <v>2.131116</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.691513</v>
+        <v>2.129542</v>
       </c>
       <c r="R62" t="n">
-        <v>2.241154</v>
+        <v>1.537318</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.837827</v>
+        <v>-0.805688</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.070462</v>
+        <v>-1.956603</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.111823</v>
+        <v>-1.805937</v>
       </c>
       <c r="V62" t="n">
-        <v>0.213085</v>
+        <v>0.458841</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.299095</v>
+        <v>-0.45101</v>
       </c>
       <c r="X62" t="n">
-        <v>0.342974</v>
+        <v>0.290144</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.32315</v>
+        <v>0.469814</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.84892</v>
+        <v>13.72662</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.922661</v>
+        <v>15.811847</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.051713</v>
+        <v>7.00694</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.658995</v>
+        <v>13.385827</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12502,10 +12138,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.0742</v>
+        <v>5.0727</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0736</v>
+        <v>5.0721</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12516,33 +12152,31 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
+      <c r="AW62" t="n">
+        <v>-2.007109</v>
+      </c>
       <c r="AX62" t="n">
-        <v>-1.978132</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>-1.978362</v>
-      </c>
+        <v>-2.007342</v>
+      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
+      <c r="BF62" t="n">
+        <v>0</v>
+      </c>
       <c r="BG62" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,95 +643,105 @@
       </c>
       <c r="AS1" t="inlineStr">
         <is>
+          <t>bcb_sgs_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pf</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -843,12 +853,14 @@
         <v>1.58</v>
       </c>
       <c r="AS2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AT2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>355671</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -865,6 +877,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -1000,54 +1014,60 @@
         <v>1.56</v>
       </c>
       <c r="AS3" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AT3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.631159</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.641498</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="n">
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>1</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
       <c r="BI3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BK3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BL3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1185,54 +1205,60 @@
         <v>1.43</v>
       </c>
       <c r="AS4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AT4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>368886</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>-0.055529</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-2.109407</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>1</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
       <c r="BI4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BK4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BL4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1370,54 +1396,60 @@
         <v>1.43</v>
       </c>
       <c r="AS5" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AT5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>367927</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.53429</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.58875</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
       <c r="BI5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BK5" t="n">
         <v>0</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BL5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1555,54 +1587,60 @@
         <v>1.46</v>
       </c>
       <c r="AS6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AT6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>367772</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>1.599501</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>1.372425</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="n">
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
         <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0.005012</v>
       </c>
       <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03</v>
+        <v>0.005012</v>
       </c>
       <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
       <c r="BK6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1740,54 +1778,60 @@
         <v>1.4</v>
       </c>
       <c r="AS7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>362204</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>0.250195</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>1.49538</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="n">
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
       <c r="BI7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BK7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BL7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1925,54 +1969,60 @@
         <v>1.46</v>
       </c>
       <c r="AS8" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AT8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>358398</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-1.889415</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>-7.693212</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="n">
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
         <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
       <c r="BI8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BK8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BL8" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2110,54 +2160,60 @@
         <v>1.44</v>
       </c>
       <c r="AS9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AT9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>357740</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>0.982105</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>4.32272</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="n">
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
         <v>1.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
       <c r="BI9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BK9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BL9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2295,54 +2351,60 @@
         <v>1.55</v>
       </c>
       <c r="AS10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>353169</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>1.194746</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>9.292268999999999</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="n">
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
       <c r="BI10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BK10" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BL10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2480,54 +2542,60 @@
         <v>1.57</v>
       </c>
       <c r="AS11" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AT11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>345097</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>0.004178</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>-4.113018</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="n">
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
         <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
       <c r="BI11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BK11" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BL11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2665,54 +2733,60 @@
         <v>1.57</v>
       </c>
       <c r="AS12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>346415</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>0.112442</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>-0.479114</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="n">
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
         <v>1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
       <c r="BI12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BL12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2850,60 +2924,66 @@
         <v>1.52</v>
       </c>
       <c r="AS13" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="AT13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>341958</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.156589</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.436337</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BG13" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
       <c r="BI13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BK13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BL13" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3041,60 +3121,66 @@
         <v>1.6</v>
       </c>
       <c r="AS14" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AT14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>346403</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>1.9075</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>4.677002</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BA14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BB14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BC14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BF14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BG14" t="n">
         <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
       <c r="BI14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BK14" t="n">
         <v>0.08</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BL14" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3232,60 +3318,66 @@
         <v>1.62</v>
       </c>
       <c r="AS15" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AT15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>339664</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>-0.307887</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.536686</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AZ15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BA15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BD15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BF15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BG15" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
       <c r="BI15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BK15" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BL15" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3423,60 +3515,66 @@
         <v>1.65</v>
       </c>
       <c r="AS16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>327580</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>0.051214</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>-3.18585</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BA16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BC16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BE16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BF16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BG16" t="n">
         <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
       <c r="BI16" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BK16" t="n">
         <v>0.03</v>
       </c>
-      <c r="BK16" t="n">
+      <c r="BL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3614,46 +3712,46 @@
         <v>1.77</v>
       </c>
       <c r="AS17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AT17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>325546</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>0.283274</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>-1.093446</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AZ17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BA17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BC17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
         <v>6.460076</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3662,12 +3760,18 @@
         <v>0</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
       <c r="BK17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3805,46 +3909,46 @@
         <v>1.81</v>
       </c>
       <c r="AS18" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AT18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>331505</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>-0.725155</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>-0.925949</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BA18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BB18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BD18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BF18" t="n">
         <v>5.974439</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3853,12 +3957,18 @@
         <v>0</v>
       </c>
       <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BK18" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BL18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3996,60 +4106,66 @@
         <v>1.8</v>
       </c>
       <c r="AS19" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AT19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>324703</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>-0.249038</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>0.821323</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BA19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BC19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BD19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BE19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BF19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BG19" t="n">
         <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>-0</v>
       </c>
       <c r="BH19" t="n">
         <v>-0</v>
       </c>
       <c r="BI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>0</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BK19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BL19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4187,46 +4303,46 @@
         <v>1.94</v>
       </c>
       <c r="AS20" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AT20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>331122</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>-0.342048</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>-4.871671</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AZ20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BA20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BB20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BD20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BF20" t="n">
         <v>5.711379</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4235,12 +4351,18 @@
         <v>0</v>
       </c>
       <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BK20" t="n">
         <v>0.14</v>
       </c>
-      <c r="BK20" t="n">
+      <c r="BL20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4378,46 +4500,46 @@
         <v>2.17</v>
       </c>
       <c r="AS21" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AT21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>328098</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>2.881581</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>3.737316</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BA21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BD21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BF21" t="n">
         <v>5.47065</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4426,12 +4548,18 @@
         <v>0</v>
       </c>
       <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BK21" t="n">
         <v>0.23</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BL21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4569,46 +4697,46 @@
         <v>2.2</v>
       </c>
       <c r="AS22" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AT22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>341158</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>0.100866</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>12.127661</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BA22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BC22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BD22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BE22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BF22" t="n">
         <v>4.361088</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4617,12 +4745,18 @@
         <v>0</v>
       </c>
       <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BK22" t="n">
         <v>0.03</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BL22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4760,46 +4894,46 @@
         <v>2.45</v>
       </c>
       <c r="AS23" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="AT23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>345725</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>1.051427</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>-5.945456</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BA23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BC23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BD23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BE23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BF23" t="n">
         <v>3.834324</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -4808,12 +4942,18 @@
         <v>0</v>
       </c>
       <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BK23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BL23" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4951,60 +5091,66 @@
         <v>2.58</v>
       </c>
       <c r="AS24" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AT24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>343489</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>-1.655253</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>-1.271212</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AY24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BA24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BB24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BD24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BF24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BG24" t="n">
         <v>0</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>-0</v>
       </c>
       <c r="BH24" t="n">
         <v>-0</v>
       </c>
       <c r="BI24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BK24" t="n">
         <v>0.13</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BL24" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5142,46 +5288,46 @@
         <v>2.63</v>
       </c>
       <c r="AS25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AT25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>343620</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>-0.06297</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>-0.424293</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AZ25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BA25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BC25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BD25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BE25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BF25" t="n">
         <v>2.998957</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5190,12 +5336,18 @@
         <v>0</v>
       </c>
       <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BK25" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BL25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5333,46 +5485,46 @@
         <v>2.73</v>
       </c>
       <c r="AS26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AT26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>345476</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>0.458481</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>2.993707</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="AZ26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BA26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BB26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BC26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BD26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BE26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BF26" t="n">
         <v>3.527423</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5381,12 +5533,18 @@
         <v>0</v>
       </c>
       <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BK26" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BL26" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5524,60 +5682,66 @@
         <v>2.82</v>
       </c>
       <c r="AS27" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AT27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>344177</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>-0.374379</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>0.680131</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AX27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AY27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AZ27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BA27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BB27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BC27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BD27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BE27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BF27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BG27" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
       <c r="BI27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BK27" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BL27" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5715,60 +5879,66 @@
         <v>2.82</v>
       </c>
       <c r="AS28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>340324</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>0.012734</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>-4.055314</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="AZ28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BA28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BB28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BC28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BD28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BE28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BF28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BG28" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
       <c r="BI28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="BJ28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BK28" t="n">
         <v>0</v>
       </c>
-      <c r="BK28" t="n">
+      <c r="BL28" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5906,60 +6076,66 @@
         <v>2.92</v>
       </c>
       <c r="AS29" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AT29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>340247</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>0.313403</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>0.169608</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AY29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AZ29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BA29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BB29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BC29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BD29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BE29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BF29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BG29" t="n">
         <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
       <c r="BI29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BK29" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK29" t="n">
+      <c r="BL29" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6097,60 +6273,66 @@
         <v>2.99</v>
       </c>
       <c r="AS30" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AT30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>348406</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>0.739043</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>-0.243155</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AY30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AZ30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BA30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BB30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BC30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BD30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BE30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BF30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BG30" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
       <c r="BI30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="BJ30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BK30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK30" t="n">
+      <c r="BL30" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6288,60 +6470,66 @@
         <v>2.59</v>
       </c>
       <c r="AS31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>355034</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>1.06955</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>-0.000138</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AZ31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BA31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BB31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BC31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BD31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BE31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BF31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BG31" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
       <c r="BI31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="BJ31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BK31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BK31" t="n">
+      <c r="BL31" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6479,60 +6667,66 @@
         <v>2.77</v>
       </c>
       <c r="AS32" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AT32" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>355066</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>-0.194024</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>-2.349549</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AZ32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BA32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BB32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BC32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BD32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BE32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BF32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BG32" t="n">
         <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
       <c r="BI32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="BJ32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BK32" t="n">
         <v>0.18</v>
       </c>
-      <c r="BK32" t="n">
+      <c r="BL32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6670,60 +6864,66 @@
         <v>2.76</v>
       </c>
       <c r="AS33" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AT33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>352705</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>0.14777</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>2.878185</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AX33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AZ33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BA33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BB33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BC33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BD33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BE33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BF33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BG33" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
       <c r="BI33" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="BJ33" t="n">
         <v>0</v>
       </c>
-      <c r="BJ33" t="n">
+      <c r="BK33" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BK33" t="n">
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6861,60 +7061,66 @@
         <v>2.71</v>
       </c>
       <c r="AS34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AT34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>355008</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>0.081216</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>7.260937</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AZ34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BA34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BB34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BC34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BF34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BG34" t="n">
         <v>-0.5</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.05</v>
+        <v>-0.000537</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7052,60 +7258,66 @@
         <v>2.76</v>
       </c>
       <c r="AS35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>351599</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>0.236126</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>-0.285629</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AX35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AY35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AZ35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BA35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BB35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BC35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BD35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BE35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BF35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BG35" t="n">
         <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
       <c r="BI35" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ35" t="n">
+      <c r="BK35" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK35" t="n">
+      <c r="BL35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7243,60 +7455,66 @@
         <v>2.8</v>
       </c>
       <c r="AS36" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>355560</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>0.664278</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>-4.15681</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AX36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AY36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AZ36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BA36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BB36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BC36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BD36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BE36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BF36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BG36" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
       <c r="BI36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="BJ36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BK36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK36" t="n">
+      <c r="BL36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7434,60 +7652,66 @@
         <v>2.64</v>
       </c>
       <c r="AS37" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AT37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>357827</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>0.864098</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>1.103268</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AX37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AY37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AZ37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BA37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BB37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BC37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BD37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BE37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BF37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BG37" t="n">
         <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
       <c r="BI37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="BJ37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BK37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BL37" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7625,46 +7849,46 @@
         <v>2.52</v>
       </c>
       <c r="AS38" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AT38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>363282</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>0.35244</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>5.331331</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AY38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="AZ38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BA38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BB38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BC38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BD38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BE38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="BE38" t="n">
+      <c r="BF38" t="n">
         <v>4.060953</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -7673,12 +7897,18 @@
         <v>0</v>
       </c>
       <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BK38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK38" t="n">
+      <c r="BL38" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7816,46 +8046,46 @@
         <v>2.55</v>
       </c>
       <c r="AS39" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AT39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>369214</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>0.171599</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>-1.299435</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="AZ39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BA39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BB39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BC39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BD39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BE39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="BE39" t="n">
+      <c r="BF39" t="n">
         <v>3.707852</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -7864,12 +8094,18 @@
         <v>0</v>
       </c>
       <c r="BI39" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
       <c r="BK39" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8007,60 +8243,66 @@
         <v>2.56</v>
       </c>
       <c r="AS40" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AT40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>372016</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>0.80633</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>-2.710366</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AY40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="AZ40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BA40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BB40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BC40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BD40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BE40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BF40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BG40" t="n">
         <v>0.25</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.01</v>
+        <v>0.000342</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8198,60 +8440,66 @@
         <v>2.52</v>
       </c>
       <c r="AS41" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="AT41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AU41" t="n">
         <v>366096</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
         <v>0.192241</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AW41" t="n">
         <v>1.966032</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AX41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AY41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="AZ41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BA41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BB41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BC41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BD41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BE41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BF41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BG41" t="n">
         <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
       <c r="BI41" t="n">
-        <v>-0.04</v>
+        <v>0.000556</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8389,60 +8637,66 @@
         <v>2.5</v>
       </c>
       <c r="AS42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AU42" t="n">
         <v>363003</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
         <v>-0.221546</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AW42" t="n">
         <v>-3.385643</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AX42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AY42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="AZ42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BA42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BB42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BC42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BD42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BE42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BF42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BG42" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
       <c r="BI42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="BJ42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BK42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK42" t="n">
+      <c r="BL42" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8580,60 +8834,66 @@
         <v>2.21</v>
       </c>
       <c r="AS43" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AT43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>329730</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
         <v>-0.76507</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>-1.261045</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AY43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="AZ43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BA43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BB43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BC43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BD43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BF43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BG43" t="n">
         <v>1</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
       <c r="BI43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="BJ43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BK43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BL43" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8771,60 +9031,66 @@
         <v>2.43</v>
       </c>
       <c r="AS44" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AT44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>328303</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
         <v>1.000655</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>-1.374453</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AY44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="AZ44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BA44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BB44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BC44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BD44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BE44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BF44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BG44" t="n">
         <v>1</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
       <c r="BI44" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
-      <c r="BJ44" t="n">
+      <c r="BK44" t="n">
         <v>0.22</v>
       </c>
-      <c r="BK44" t="n">
+      <c r="BL44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8962,60 +9228,66 @@
         <v>2.52</v>
       </c>
       <c r="AS45" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AT45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AU45" t="n">
         <v>332508</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
         <v>0.491628</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AW45" t="n">
         <v>4.086263</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AX45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AY45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="AZ45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BA45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BB45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BC45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BD45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BE45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BF45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BG45" t="n">
         <v>0</v>
-      </c>
-      <c r="BG45" t="n">
-        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
       <c r="BI45" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ45" t="n">
+      <c r="BK45" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK45" t="n">
+      <c r="BL45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9153,60 +9425,66 @@
         <v>2.49</v>
       </c>
       <c r="AS46" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AT46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AU46" t="n">
         <v>336157</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
         <v>1.341273</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AW46" t="n">
         <v>6.727909</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AY46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="AZ46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BA46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BB46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BC46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BD46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BE46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BF46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BG46" t="n">
         <v>1</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
       <c r="BI46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="BJ46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BK46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK46" t="n">
+      <c r="BL46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9344,60 +9622,66 @@
         <v>2.72</v>
       </c>
       <c r="AS47" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AT47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AU47" t="n">
         <v>340789</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
         <v>-0.131764</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AW47" t="n">
         <v>-1.249299</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AY47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="AZ47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BA47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BB47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BC47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BD47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BE47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BF47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BG47" t="n">
         <v>0</v>
-      </c>
-      <c r="BG47" t="n">
-        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.23</v>
+        <v>0.002023</v>
       </c>
       <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
       <c r="BK47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9535,60 +9819,66 @@
         <v>2.67</v>
       </c>
       <c r="AS48" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="AT48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AU48" t="n">
         <v>341459</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
         <v>-0.883188</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AW48" t="n">
         <v>-3.583696</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AX48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="AZ48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BA48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BB48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BC48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BD48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BE48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BF48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BG48" t="n">
         <v>0.5</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
       <c r="BI48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="BJ48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BK48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BL48" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9726,60 +10016,66 @@
         <v>2.67</v>
       </c>
       <c r="AS49" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="AT49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>344440</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
         <v>-0.208448</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AW49" t="n">
         <v>-1.100964</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="AZ49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BA49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BB49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BC49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BD49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BE49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BF49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BG49" t="n">
         <v>0.25</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
       <c r="BI49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="BJ49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BK49" t="n">
         <v>0</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BL49" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9917,60 +10213,66 @@
         <v>2.79</v>
       </c>
       <c r="AS50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AT50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>345111</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
         <v>-0.410362</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
         <v>5.358126</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AX50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AY50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="AZ50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BA50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BB50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BC50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BD50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BE50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BF50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BG50" t="n">
         <v>0</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>0.000562</v>
       </c>
       <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
       <c r="BI50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BJ50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BK50" t="n">
         <v>0.12</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BL50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10108,46 +10410,46 @@
         <v>2.85</v>
       </c>
       <c r="AS51" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AT51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AU51" t="n">
         <v>350767</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
         <v>0.393384</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>-2.419208</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AY51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="AZ51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BA51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BB51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BC51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BD51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BE51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BF51" t="n">
         <v>5.054283</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10156,12 +10458,18 @@
         <v>0</v>
       </c>
       <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BK51" t="n">
         <v>0.06</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BL51" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10299,46 +10607,46 @@
         <v>2.77</v>
       </c>
       <c r="AS52" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AT52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AU52" t="n">
         <v>356582</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
         <v>-0.070866</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AW52" t="n">
         <v>-0.816658</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AY52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="AZ52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BA52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BB52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BC52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BD52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BE52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="BE52" t="n">
+      <c r="BF52" t="n">
         <v>5.096104</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
@@ -10347,12 +10655,18 @@
         <v>0</v>
       </c>
       <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ52" t="n">
+      <c r="BK52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK52" t="n">
+      <c r="BL52" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10490,46 +10804,46 @@
         <v>2.82</v>
       </c>
       <c r="AS53" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AT53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AU53" t="n">
         <v>357103</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
         <v>0.02339</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AW53" t="n">
         <v>0.539717</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AX53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AY53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="AZ53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BA53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BB53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BC53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BD53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BE53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="BE53" t="n">
+      <c r="BF53" t="n">
         <v>4.490243</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -10538,12 +10852,18 @@
         <v>0</v>
       </c>
       <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BK53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK53" t="n">
+      <c r="BL53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10681,60 +11001,66 @@
         <v>2.74</v>
       </c>
       <c r="AS54" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AT54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AU54" t="n">
         <v>360578</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
         <v>0.470751</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AW54" t="n">
         <v>-3.155924</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AX54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AY54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AZ54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BA54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BB54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BC54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BD54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BE54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BF54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BG54" t="n">
         <v>0</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>-0</v>
       </c>
       <c r="BH54" t="n">
         <v>-0</v>
       </c>
       <c r="BI54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BK54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK54" t="n">
+      <c r="BL54" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10872,46 +11198,46 @@
         <v>2.68</v>
       </c>
       <c r="AS55" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="AT55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AU55" t="n">
         <v>358234</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
         <v>-0.026441</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AW55" t="n">
         <v>0.550798</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AY55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="AZ55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BA55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BB55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BC55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BD55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="BD55" t="n">
+      <c r="BE55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="BE55" t="n">
+      <c r="BF55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -10920,12 +11246,18 @@
         <v>0</v>
       </c>
       <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BK55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BK55" t="n">
+      <c r="BL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11063,46 +11395,46 @@
         <v>2.87</v>
       </c>
       <c r="AS56" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="AT56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AU56" t="n">
         <v>364367</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
         <v>0.755789</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AW56" t="n">
         <v>-3.241421</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AX56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AY56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="AZ56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BA56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BB56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BC56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BD56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BE56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="BE56" t="n">
+      <c r="BF56" t="n">
         <v>4.303068</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11111,12 +11443,18 @@
         <v>0</v>
       </c>
       <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BK56" t="n">
         <v>0.19</v>
       </c>
-      <c r="BK56" t="n">
+      <c r="BL56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11254,46 +11592,46 @@
         <v>3.07</v>
       </c>
       <c r="AS57" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AT57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AU57" t="n">
         <v>371074</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
         <v>0.625412</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AW57" t="n">
         <v>2.812663</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AX57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AY57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="AZ57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BA57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BB57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BC57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BD57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BE57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="BE57" t="n">
+      <c r="BF57" t="n">
         <v>3.357475</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11302,12 +11640,18 @@
         <v>0</v>
       </c>
       <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BK57" t="n">
         <v>0.2</v>
       </c>
-      <c r="BK57" t="n">
+      <c r="BL57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11445,60 +11789,66 @@
         <v>3.04</v>
       </c>
       <c r="AS58" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AU58" t="n">
         <v>362002</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
         <v>-0.180258</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AW58" t="n">
         <v>10.500625</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AX58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AY58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="AZ58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BA58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BB58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BC58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BD58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BE58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BF58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BG58" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="BG58" t="n">
-        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
       <c r="BI58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="BJ58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ58" t="n">
+      <c r="BK58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK58" t="n">
+      <c r="BL58" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11636,60 +11986,66 @@
         <v>3.15</v>
       </c>
       <c r="AS59" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AT59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AU59" t="n">
         <v>366913</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
         <v>0.511964</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AW59" t="n">
         <v>-3.561276</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AX59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AY59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="AZ59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BA59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BB59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BC59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BD59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BE59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BF59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BG59" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
       <c r="BI59" t="n">
-        <v>0.11</v>
+        <v>-0.000554</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11823,56 +12179,62 @@
         <v>3.24</v>
       </c>
       <c r="AS60" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AT60" t="n">
         <v>33.42</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="n">
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AY60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="AZ60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BA60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BB60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BC60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BD60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BE60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BF60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BG60" t="n">
         <v>0</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
       <c r="BI60" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ60" t="n">
+      <c r="BK60" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK60" t="n">
+      <c r="BL60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -11996,132 +12358,134 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="n">
         <v>367558</v>
       </c>
-      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="n">
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AX61" t="n">
+      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="n">
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BD61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="BD61" t="n">
+      <c r="BE61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="BE61" t="n">
+      <c r="BF61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BG61" t="n">
         <v>-0.25</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-0.000372</v>
       </c>
       <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="inlineStr"/>
+      <c r="BI61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175690.03125</v>
+        <v>176011</v>
       </c>
       <c r="C62" t="n">
-        <v>172.649994</v>
+        <v>172.759995</v>
       </c>
       <c r="D62" t="n">
-        <v>109.639999</v>
+        <v>109.690002</v>
       </c>
       <c r="E62" t="n">
-        <v>432.140015</v>
+        <v>433.399994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0804</v>
+        <v>5.0761</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8103</v>
+        <v>5.8178</v>
       </c>
       <c r="H62" t="n">
-        <v>7533.77002</v>
+        <v>7572.399902</v>
       </c>
       <c r="I62" t="n">
-        <v>26095.494141</v>
+        <v>26269.230469</v>
       </c>
       <c r="J62" t="n">
-        <v>52471</v>
+        <v>52658.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4041.800049</v>
+        <v>4029.300049</v>
       </c>
       <c r="L62" t="n">
-        <v>79.040001</v>
+        <v>79.489998</v>
       </c>
       <c r="M62" t="n">
-        <v>84.449997</v>
+        <v>84.660004</v>
       </c>
       <c r="N62" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="O62" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="P62" t="n">
-        <v>2.131116</v>
+        <v>2.3177</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.129542</v>
+        <v>2.194612</v>
       </c>
       <c r="R62" t="n">
-        <v>1.537318</v>
+        <v>1.583626</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.805688</v>
+        <v>-0.51647</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.956603</v>
+        <v>-2.039589</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.805937</v>
+        <v>-1.679184</v>
       </c>
       <c r="V62" t="n">
-        <v>0.458841</v>
+        <v>0.97395</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.45101</v>
+        <v>0.211758</v>
       </c>
       <c r="X62" t="n">
-        <v>0.290144</v>
+        <v>0.6487889999999999</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.469814</v>
+        <v>0.159093</v>
       </c>
       <c r="Z62" t="n">
-        <v>13.72662</v>
+        <v>14.374098</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.811847</v>
+        <v>16.099843</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.385827</v>
+        <v>14.112659</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12152,31 +12516,33 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="n">
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="n">
         <v>-2.007109</v>
       </c>
-      <c r="AX62" t="n">
+      <c r="AY62" t="n">
         <v>-2.007342</v>
       </c>
-      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="n">
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
         <v>0</v>
-      </c>
-      <c r="BG62" t="n">
-        <v>-0.000497</v>
       </c>
       <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="inlineStr"/>
+      <c r="BI62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12404,88 +12404,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176011</v>
+        <v>173825</v>
       </c>
       <c r="C62" t="n">
-        <v>172.759995</v>
+        <v>170.770004</v>
       </c>
       <c r="D62" t="n">
-        <v>109.690002</v>
+        <v>108.419998</v>
       </c>
       <c r="E62" t="n">
-        <v>433.399994</v>
+        <v>433.040009</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0761</v>
+        <v>5.1028</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8178</v>
+        <v>5.8311</v>
       </c>
       <c r="H62" t="n">
-        <v>7572.399902</v>
+        <v>7533.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26269.230469</v>
+        <v>25881.949219</v>
       </c>
       <c r="J62" t="n">
-        <v>52658.640625</v>
+        <v>52552.96875</v>
       </c>
       <c r="K62" t="n">
-        <v>4029.300049</v>
+        <v>3995.699951</v>
       </c>
       <c r="L62" t="n">
-        <v>79.489998</v>
+        <v>80.139999</v>
       </c>
       <c r="M62" t="n">
-        <v>84.660004</v>
+        <v>85.949997</v>
       </c>
       <c r="N62" t="n">
-        <v>1204.5</v>
+        <v>1195</v>
       </c>
       <c r="O62" t="n">
-        <v>471</v>
+        <v>463.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.3177</v>
+        <v>1.046947</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.194612</v>
+        <v>1.017451</v>
       </c>
       <c r="R62" t="n">
-        <v>1.583626</v>
+        <v>0.407478</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.51647</v>
+        <v>-0.599101</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.039589</v>
+        <v>-1.524322</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.679184</v>
+        <v>-1.454415</v>
       </c>
       <c r="V62" t="n">
-        <v>0.97395</v>
+        <v>0.458841</v>
       </c>
       <c r="W62" t="n">
-        <v>0.211758</v>
+        <v>-1.265641</v>
       </c>
       <c r="X62" t="n">
-        <v>0.6487889999999999</v>
+        <v>0.446814</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.159093</v>
+        <v>-0.676128</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.374098</v>
+        <v>15.309352</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.099843</v>
+        <v>17.868896</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.857623</v>
+        <v>7.00694</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.112659</v>
+        <v>12.295578</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12502,10 +12502,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.0727</v>
+        <v>5.0975</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0721</v>
+        <v>5.0969</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12518,10 +12518,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-2.007109</v>
+        <v>-1.52803</v>
       </c>
       <c r="AY62" t="n">
-        <v>-2.007342</v>
+        <v>-1.528207</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -826,10 +826,10 @@
         <v>1.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96.42256999999999</v>
+        <v>96.31464</v>
       </c>
       <c r="AK2" t="n">
-        <v>99.83515</v>
+        <v>99.83978</v>
       </c>
       <c r="AL2" t="n">
         <v>5.1216</v>
@@ -987,10 +987,10 @@
         <v>0.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.03115</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.19471</v>
+        <v>99.32829</v>
       </c>
       <c r="AL3" t="n">
         <v>5.1433</v>
@@ -1023,10 +1023,10 @@
         <v>370395</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.631159</v>
+        <v>0.79016</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.641498</v>
+        <v>-0.512311</v>
       </c>
       <c r="AX3" t="n">
         <v>0.423696</v>
@@ -1178,10 +1178,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.97727</v>
+        <v>96.95968999999999</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.10229</v>
+        <v>97.24746</v>
       </c>
       <c r="AL4" t="n">
         <v>5.4394</v>
@@ -1214,10 +1214,10 @@
         <v>368886</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.055529</v>
+        <v>-0.119484</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.109407</v>
+        <v>-2.094902</v>
       </c>
       <c r="AX4" t="n">
         <v>5.757004</v>
@@ -1369,10 +1369,10 @@
         <v>1.16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.49541000000001</v>
+        <v>97.48142</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.53060000000001</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="AL5" t="n">
         <v>5.643</v>
@@ -1405,10 +1405,10 @@
         <v>367927</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53429</v>
+        <v>0.53809</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.58875</v>
+        <v>-0.644377</v>
       </c>
       <c r="AX5" t="n">
         <v>3.74306</v>
@@ -1560,10 +1560,10 @@
         <v>0.84</v>
       </c>
       <c r="AJ6" t="n">
-        <v>99.05485</v>
+        <v>98.97262000000001</v>
       </c>
       <c r="AK6" t="n">
-        <v>97.85541000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="AL6" t="n">
         <v>5.6199</v>
@@ -1596,10 +1596,10 @@
         <v>367772</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.599501</v>
+        <v>1.529727</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.372425</v>
+        <v>1.487112</v>
       </c>
       <c r="AX6" t="n">
         <v>-0.409357</v>
@@ -1751,10 +1751,10 @@
         <v>0.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.30268</v>
+        <v>99.35339</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.31872</v>
+        <v>99.33126</v>
       </c>
       <c r="AL7" t="n">
         <v>5.5805</v>
@@ -1787,10 +1787,10 @@
         <v>362204</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.250195</v>
+        <v>0.384723</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.49538</v>
+        <v>1.298807</v>
       </c>
       <c r="AX7" t="n">
         <v>-0.70108</v>
@@ -1942,10 +1942,10 @@
         <v>0.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.42644</v>
+        <v>97.34401</v>
       </c>
       <c r="AK8" t="n">
-        <v>91.67792</v>
+        <v>90.45032</v>
       </c>
       <c r="AL8" t="n">
         <v>5.3574</v>
@@ -1978,10 +1978,10 @@
         <v>358398</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.889415</v>
+        <v>-2.022457</v>
       </c>
       <c r="AW8" t="n">
-        <v>-7.693212</v>
+        <v>-8.94073</v>
       </c>
       <c r="AX8" t="n">
         <v>-3.99785</v>
@@ -2133,10 +2133,10 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.38327</v>
+        <v>98.43725000000001</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.6409</v>
+        <v>95.72214</v>
       </c>
       <c r="AL9" t="n">
         <v>5.1394</v>
@@ -2169,10 +2169,10 @@
         <v>357740</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.982105</v>
+        <v>1.123069</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.32272</v>
+        <v>5.828415</v>
       </c>
       <c r="AX9" t="n">
         <v>-4.069138</v>
@@ -2324,10 +2324,10 @@
         <v>1.71</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.5587</v>
+        <v>99.55981</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.52811</v>
+        <v>104.61484</v>
       </c>
       <c r="AL10" t="n">
         <v>4.7378</v>
@@ -2360,10 +2360,10 @@
         <v>353169</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.194746</v>
+        <v>1.140381</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.292268999999999</v>
+        <v>9.290118</v>
       </c>
       <c r="AX10" t="n">
         <v>-7.814142</v>
@@ -2515,10 +2515,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.56286</v>
+        <v>99.51646</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.22885</v>
+        <v>100.42352</v>
       </c>
       <c r="AL11" t="n">
         <v>4.9191</v>
@@ -2551,10 +2551,10 @@
         <v>345097</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.004178</v>
+        <v>-0.043542</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.113018</v>
+        <v>-4.00643</v>
       </c>
       <c r="AX11" t="n">
         <v>3.826671</v>
@@ -2706,10 +2706,10 @@
         <v>0.45</v>
       </c>
       <c r="AJ12" t="n">
-        <v>99.67480999999999</v>
+        <v>99.67415</v>
       </c>
       <c r="AK12" t="n">
-        <v>99.74863999999999</v>
+        <v>99.79777</v>
       </c>
       <c r="AL12" t="n">
         <v>4.7289</v>
@@ -2742,10 +2742,10 @@
         <v>346415</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.112442</v>
+        <v>0.158456</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.479114</v>
+        <v>-0.623111</v>
       </c>
       <c r="AX12" t="n">
         <v>-3.866561</v>
@@ -2897,10 +2897,10 @@
         <v>0.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99.51873000000001</v>
+        <v>99.6343</v>
       </c>
       <c r="AK13" t="n">
-        <v>99.3134</v>
+        <v>99.53784</v>
       </c>
       <c r="AL13" t="n">
         <v>5.238</v>
@@ -2933,10 +2933,10 @@
         <v>341958</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.156589</v>
+        <v>-0.03998</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.436337</v>
+        <v>-0.260457</v>
       </c>
       <c r="AX13" t="n">
         <v>10.765717</v>
@@ -3094,10 +3094,10 @@
         <v>-0.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>101.41705</v>
+        <v>101.27684</v>
       </c>
       <c r="AK14" t="n">
-        <v>103.95829</v>
+        <v>103.95861</v>
       </c>
       <c r="AL14" t="n">
         <v>5.1884</v>
@@ -3130,10 +3130,10 @@
         <v>346403</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.9075</v>
+        <v>1.648569</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.677002</v>
+        <v>4.441296</v>
       </c>
       <c r="AX14" t="n">
         <v>-0.946926</v>
@@ -3291,10 +3291,10 @@
         <v>-0.31</v>
       </c>
       <c r="AJ15" t="n">
-        <v>101.1048</v>
+        <v>101.07328</v>
       </c>
       <c r="AK15" t="n">
-        <v>104.51622</v>
+        <v>104.56278</v>
       </c>
       <c r="AL15" t="n">
         <v>5.179</v>
@@ -3327,10 +3327,10 @@
         <v>339664</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.307887</v>
+        <v>-0.200994</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.536686</v>
+        <v>0.581164</v>
       </c>
       <c r="AX15" t="n">
         <v>-0.181173</v>
@@ -3488,10 +3488,10 @@
         <v>-0.32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>101.15658</v>
+        <v>101.17973</v>
       </c>
       <c r="AK16" t="n">
-        <v>101.18649</v>
+        <v>101.38087</v>
       </c>
       <c r="AL16" t="n">
         <v>5.4066</v>
@@ -3524,10 +3524,10 @@
         <v>327580</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.051214</v>
+        <v>0.10532</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.18585</v>
+        <v>-3.043062</v>
       </c>
       <c r="AX16" t="n">
         <v>4.394671</v>
@@ -3685,10 +3685,10 @@
         <v>0.47</v>
       </c>
       <c r="AJ17" t="n">
-        <v>101.44313</v>
+        <v>101.46342</v>
       </c>
       <c r="AK17" t="n">
-        <v>100.08007</v>
+        <v>100.20398</v>
       </c>
       <c r="AL17" t="n">
         <v>5.257</v>
@@ -3721,10 +3721,10 @@
         <v>325546</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.283274</v>
+        <v>0.280382</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.093446</v>
+        <v>-1.16086</v>
       </c>
       <c r="AX17" t="n">
         <v>-2.766988</v>
@@ -3882,10 +3882,10 @@
         <v>0.38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.70751</v>
+        <v>100.66227</v>
       </c>
       <c r="AK18" t="n">
-        <v>99.15338</v>
+        <v>99.36927</v>
       </c>
       <c r="AL18" t="n">
         <v>5.2941</v>
@@ -3918,10 +3918,10 @@
         <v>331505</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.725155</v>
+        <v>-0.789595</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.925949</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="AX18" t="n">
         <v>0.705726</v>
@@ -4079,10 +4079,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100.45671</v>
+        <v>100.58196</v>
       </c>
       <c r="AK19" t="n">
-        <v>99.96775</v>
+        <v>99.97806</v>
       </c>
       <c r="AL19" t="n">
         <v>5.2177</v>
@@ -4115,10 +4115,10 @@
         <v>324703</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.249038</v>
+        <v>-0.07978200000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.821323</v>
+        <v>0.612654</v>
       </c>
       <c r="AX19" t="n">
         <v>-1.443116</v>
@@ -4276,10 +4276,10 @@
         <v>0.46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100.1131</v>
+        <v>100.05178</v>
       </c>
       <c r="AK20" t="n">
-        <v>95.09765</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="AL20" t="n">
         <v>5.0993</v>
@@ -4312,10 +4312,10 @@
         <v>331122</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.342048</v>
+        <v>-0.527112</v>
       </c>
       <c r="AW20" t="n">
-        <v>-4.871671</v>
+        <v>-6.187047</v>
       </c>
       <c r="AX20" t="n">
         <v>-2.269199</v>
@@ -4473,10 +4473,10 @@
         <v>0.77</v>
       </c>
       <c r="AJ21" t="n">
-        <v>102.99794</v>
+        <v>103.00964</v>
       </c>
       <c r="AK21" t="n">
-        <v>98.65175000000001</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="AL21" t="n">
         <v>5.2078</v>
@@ -4509,10 +4509,10 @@
         <v>328098</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.881581</v>
+        <v>2.956329</v>
       </c>
       <c r="AW21" t="n">
-        <v>3.737316</v>
+        <v>5.286443</v>
       </c>
       <c r="AX21" t="n">
         <v>2.127743</v>
@@ -4670,10 +4670,10 @@
         <v>0.64</v>
       </c>
       <c r="AJ22" t="n">
-        <v>103.10183</v>
+        <v>103.09341</v>
       </c>
       <c r="AK22" t="n">
-        <v>110.6159</v>
+        <v>110.62354</v>
       </c>
       <c r="AL22" t="n">
         <v>5.0804</v>
@@ -4706,10 +4706,10 @@
         <v>341158</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.100866</v>
+        <v>0.08132200000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.127661</v>
+        <v>12.023101</v>
       </c>
       <c r="AX22" t="n">
         <v>-2.446331</v>
@@ -4867,10 +4867,10 @@
         <v>0.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>104.18587</v>
+        <v>104.1626</v>
       </c>
       <c r="AK23" t="n">
-        <v>104.03928</v>
+        <v>104.34152</v>
       </c>
       <c r="AL23" t="n">
         <v>5.0007</v>
@@ -4903,10 +4903,10 @@
         <v>345725</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.051427</v>
+        <v>1.037108</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.945456</v>
+        <v>-5.678737</v>
       </c>
       <c r="AX23" t="n">
         <v>-1.568774</v>
@@ -5064,10 +5064,10 @@
         <v>0.36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>102.46133</v>
+        <v>102.3642</v>
       </c>
       <c r="AK24" t="n">
-        <v>102.71672</v>
+        <v>102.66392</v>
       </c>
       <c r="AL24" t="n">
         <v>5.0959</v>
@@ -5100,10 +5100,10 @@
         <v>343489</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.655253</v>
+        <v>-1.726531</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.271212</v>
+        <v>-1.607797</v>
       </c>
       <c r="AX24" t="n">
         <v>1.903733</v>
@@ -5261,10 +5261,10 @@
         <v>-0.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>102.39681</v>
+        <v>102.50431</v>
       </c>
       <c r="AK25" t="n">
-        <v>102.2809</v>
+        <v>102.53174</v>
       </c>
       <c r="AL25" t="n">
         <v>4.8192</v>
@@ -5297,10 +5297,10 @@
         <v>343620</v>
       </c>
       <c r="AV25" t="n">
-        <v>-0.06297</v>
+        <v>0.136874</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.424293</v>
+        <v>-0.12875</v>
       </c>
       <c r="AX25" t="n">
         <v>-5.429855</v>
@@ -5458,10 +5458,10 @@
         <v>-0.09</v>
       </c>
       <c r="AJ26" t="n">
-        <v>102.86628</v>
+        <v>102.83357</v>
       </c>
       <c r="AK26" t="n">
-        <v>105.34289</v>
+        <v>105.47522</v>
       </c>
       <c r="AL26" t="n">
         <v>4.7415</v>
@@ -5494,10 +5494,10 @@
         <v>345476</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.458481</v>
+        <v>0.321216</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.993707</v>
+        <v>2.870799</v>
       </c>
       <c r="AX26" t="n">
         <v>-1.612301</v>
@@ -5655,10 +5655,10 @@
         <v>0.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>102.48117</v>
+        <v>102.45222</v>
       </c>
       <c r="AK27" t="n">
-        <v>106.05936</v>
+        <v>106.13139</v>
       </c>
       <c r="AL27" t="n">
         <v>4.9219</v>
@@ -5691,10 +5691,10 @@
         <v>344177</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.374379</v>
+        <v>-0.370842</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.680131</v>
+        <v>0.622108</v>
       </c>
       <c r="AX27" t="n">
         <v>3.804703</v>
@@ -5852,10 +5852,10 @@
         <v>0.11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>102.49422</v>
+        <v>102.57885</v>
       </c>
       <c r="AK28" t="n">
-        <v>101.75832</v>
+        <v>102.00419</v>
       </c>
       <c r="AL28" t="n">
         <v>5.0076</v>
@@ -5888,10 +5888,10 @@
         <v>340324</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.012734</v>
+        <v>0.123599</v>
       </c>
       <c r="AW28" t="n">
-        <v>-4.055314</v>
+        <v>-3.888765</v>
       </c>
       <c r="AX28" t="n">
         <v>1.741198</v>
@@ -6049,10 +6049,10 @@
         <v>0.12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>102.81544</v>
+        <v>102.87707</v>
       </c>
       <c r="AK29" t="n">
-        <v>101.93091</v>
+        <v>102.0744</v>
       </c>
       <c r="AL29" t="n">
         <v>5.0575</v>
@@ -6085,10 +6085,10 @@
         <v>340247</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.313403</v>
+        <v>0.290723</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.169608</v>
+        <v>0.068831</v>
       </c>
       <c r="AX29" t="n">
         <v>0.996485</v>
@@ -6246,10 +6246,10 @@
         <v>0.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>103.57529</v>
+        <v>103.528</v>
       </c>
       <c r="AK30" t="n">
-        <v>101.68306</v>
+        <v>101.86494</v>
       </c>
       <c r="AL30" t="n">
         <v>4.9355</v>
@@ -6282,10 +6282,10 @@
         <v>348406</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.739043</v>
+        <v>0.632726</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.243155</v>
+        <v>-0.205203</v>
       </c>
       <c r="AX30" t="n">
         <v>-2.412259</v>
@@ -6443,10 +6443,10 @@
         <v>0.55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>104.68308</v>
+        <v>104.8991</v>
       </c>
       <c r="AK31" t="n">
-        <v>101.68292</v>
+        <v>101.74606</v>
       </c>
       <c r="AL31" t="n">
         <v>4.8413</v>
@@ -6479,10 +6479,10 @@
         <v>355034</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.06955</v>
+        <v>1.324376</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.000138</v>
+        <v>-0.116704</v>
       </c>
       <c r="AX31" t="n">
         <v>-1.908621</v>
@@ -6640,10 +6640,10 @@
         <v>0.57</v>
       </c>
       <c r="AJ32" t="n">
-        <v>104.47997</v>
+        <v>104.53245</v>
       </c>
       <c r="AK32" t="n">
-        <v>99.29383</v>
+        <v>98.01879</v>
       </c>
       <c r="AL32" t="n">
         <v>4.9535</v>
@@ -6676,10 +6676,10 @@
         <v>355066</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.194024</v>
+        <v>-0.349526</v>
       </c>
       <c r="AW32" t="n">
-        <v>-2.349549</v>
+        <v>-3.663306</v>
       </c>
       <c r="AX32" t="n">
         <v>2.317559</v>
@@ -6837,10 +6837,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>104.63436</v>
+        <v>104.75961</v>
       </c>
       <c r="AK33" t="n">
-        <v>102.15169</v>
+        <v>102.37988</v>
       </c>
       <c r="AL33" t="n">
         <v>4.9833</v>
@@ -6873,10 +6873,10 @@
         <v>352705</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.14777</v>
+        <v>0.217311</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.878185</v>
+        <v>4.449239</v>
       </c>
       <c r="AX33" t="n">
         <v>0.601595</v>
@@ -7034,10 +7034,10 @@
         <v>0.19</v>
       </c>
       <c r="AJ34" t="n">
-        <v>104.71934</v>
+        <v>104.7097</v>
       </c>
       <c r="AK34" t="n">
-        <v>109.56886</v>
+        <v>109.58504</v>
       </c>
       <c r="AL34" t="n">
         <v>4.9962</v>
@@ -7070,10 +7070,10 @@
         <v>355008</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.081216</v>
+        <v>-0.047642</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.260937</v>
+        <v>7.037672</v>
       </c>
       <c r="AX34" t="n">
         <v>0.258865</v>
@@ -7231,10 +7231,10 @@
         <v>0.37</v>
       </c>
       <c r="AJ35" t="n">
-        <v>104.96661</v>
+        <v>104.75682</v>
       </c>
       <c r="AK35" t="n">
-        <v>109.2559</v>
+        <v>109.36335</v>
       </c>
       <c r="AL35" t="n">
         <v>5.1718</v>
@@ -7267,10 +7267,10 @@
         <v>351599</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.236126</v>
+        <v>0.045001</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.285629</v>
+        <v>-0.2023</v>
       </c>
       <c r="AX35" t="n">
         <v>3.514671</v>
@@ -7428,10 +7428,10 @@
         <v>0.46</v>
       </c>
       <c r="AJ36" t="n">
-        <v>105.66388</v>
+        <v>105.70704</v>
       </c>
       <c r="AK36" t="n">
-        <v>104.71434</v>
+        <v>104.84682</v>
       </c>
       <c r="AL36" t="n">
         <v>5.2416</v>
@@ -7464,10 +7464,10 @@
         <v>355560</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.664278</v>
+        <v>0.907072</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.15681</v>
+        <v>-4.129839</v>
       </c>
       <c r="AX36" t="n">
         <v>1.349627</v>
@@ -7625,10 +7625,10 @@
         <v>0.25</v>
       </c>
       <c r="AJ37" t="n">
-        <v>106.57692</v>
+        <v>106.57623</v>
       </c>
       <c r="AK37" t="n">
-        <v>105.86962</v>
+        <v>106.03093</v>
       </c>
       <c r="AL37" t="n">
         <v>5.5589</v>
@@ -7661,10 +7661,10 @@
         <v>357827</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.864098</v>
+        <v>0.822263</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.103268</v>
+        <v>1.129371</v>
       </c>
       <c r="AX37" t="n">
         <v>6.053495</v>
@@ -7822,10 +7822,10 @@
         <v>0.26</v>
       </c>
       <c r="AJ38" t="n">
-        <v>106.95254</v>
+        <v>106.88756</v>
       </c>
       <c r="AK38" t="n">
-        <v>111.51388</v>
+        <v>111.55002</v>
       </c>
       <c r="AL38" t="n">
         <v>5.6621</v>
@@ -7858,10 +7858,10 @@
         <v>363282</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.35244</v>
+        <v>0.29212</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.331331</v>
+        <v>5.20517</v>
       </c>
       <c r="AX38" t="n">
         <v>1.856482</v>
@@ -8019,10 +8019,10 @@
         <v>-0.14</v>
       </c>
       <c r="AJ39" t="n">
-        <v>107.13607</v>
+        <v>107.14396</v>
       </c>
       <c r="AK39" t="n">
-        <v>110.06483</v>
+        <v>110.19363</v>
       </c>
       <c r="AL39" t="n">
         <v>5.6562</v>
@@ -8055,10 +8055,10 @@
         <v>369214</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.171599</v>
+        <v>0.239878</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.299435</v>
+        <v>-1.215948</v>
       </c>
       <c r="AX39" t="n">
         <v>-0.104202</v>
@@ -8216,10 +8216,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ40" t="n">
-        <v>107.99994</v>
+        <v>107.99916</v>
       </c>
       <c r="AK40" t="n">
-        <v>107.08167</v>
+        <v>107.28836</v>
       </c>
       <c r="AL40" t="n">
         <v>5.4481</v>
@@ -8252,10 +8252,10 @@
         <v>372016</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.80633</v>
+        <v>0.7981780000000001</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.710366</v>
+        <v>-2.636514</v>
       </c>
       <c r="AX40" t="n">
         <v>-3.679149</v>
@@ -8413,10 +8413,10 @@
         <v>0.61</v>
       </c>
       <c r="AJ41" t="n">
-        <v>108.20756</v>
+        <v>108.15356</v>
       </c>
       <c r="AK41" t="n">
-        <v>109.18693</v>
+        <v>109.21678</v>
       </c>
       <c r="AL41" t="n">
         <v>5.7779</v>
@@ -8449,10 +8449,10 @@
         <v>366096</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.192241</v>
+        <v>0.142964</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.966032</v>
+        <v>1.797418</v>
       </c>
       <c r="AX41" t="n">
         <v>6.053487</v>
@@ -8610,10 +8610,10 @@
         <v>0.33</v>
       </c>
       <c r="AJ42" t="n">
-        <v>107.96783</v>
+        <v>107.98489</v>
       </c>
       <c r="AK42" t="n">
-        <v>105.49025</v>
+        <v>105.74688</v>
       </c>
       <c r="AL42" t="n">
         <v>6.0535</v>
@@ -8646,10 +8646,10 @@
         <v>363003</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.221546</v>
+        <v>-0.155954</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.385643</v>
+        <v>-3.177076</v>
       </c>
       <c r="AX42" t="n">
         <v>4.769899</v>
@@ -8807,10 +8807,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ43" t="n">
-        <v>107.1418</v>
+        <v>107.44467</v>
       </c>
       <c r="AK43" t="n">
-        <v>104.15997</v>
+        <v>104.2734</v>
       </c>
       <c r="AL43" t="n">
         <v>6.1923</v>
@@ -8843,10 +8843,10 @@
         <v>329730</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.76507</v>
+        <v>-0.500274</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.261045</v>
+        <v>-1.393403</v>
       </c>
       <c r="AX43" t="n">
         <v>2.292888</v>
@@ -9004,10 +9004,10 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>108.21392</v>
+        <v>108.06979</v>
       </c>
       <c r="AK44" t="n">
-        <v>102.72834</v>
+        <v>101.23438</v>
       </c>
       <c r="AL44" t="n">
         <v>5.8301</v>
@@ -9040,10 +9040,10 @@
         <v>328303</v>
       </c>
       <c r="AV44" t="n">
-        <v>1.000655</v>
+        <v>0.581806</v>
       </c>
       <c r="AW44" t="n">
-        <v>-1.374453</v>
+        <v>-2.914473</v>
       </c>
       <c r="AX44" t="n">
         <v>-5.8492</v>
@@ -9201,10 +9201,10 @@
         <v>1.48</v>
       </c>
       <c r="AJ45" t="n">
-        <v>108.74593</v>
+        <v>108.77346</v>
       </c>
       <c r="AK45" t="n">
-        <v>106.92609</v>
+        <v>107.07838</v>
       </c>
       <c r="AL45" t="n">
         <v>5.8488</v>
@@ -9237,10 +9237,10 @@
         <v>332508</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.491628</v>
+        <v>0.651126</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.086263</v>
+        <v>5.772742</v>
       </c>
       <c r="AX45" t="n">
         <v>0.320749</v>
@@ -9398,10 +9398,10 @@
         <v>0.51</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110.20451</v>
+        <v>110.09056</v>
       </c>
       <c r="AK46" t="n">
-        <v>114.11998</v>
+        <v>114.05013</v>
       </c>
       <c r="AL46" t="n">
         <v>5.7422</v>
@@ -9434,10 +9434,10 @@
         <v>336157</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.341273</v>
+        <v>1.210865</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.727909</v>
+        <v>6.510885</v>
       </c>
       <c r="AX46" t="n">
         <v>-1.822596</v>
@@ -9595,10 +9595,10 @@
         <v>0.48</v>
       </c>
       <c r="AJ47" t="n">
-        <v>110.0593</v>
+        <v>109.72323</v>
       </c>
       <c r="AK47" t="n">
-        <v>112.69428</v>
+        <v>112.73813</v>
       </c>
       <c r="AL47" t="n">
         <v>5.6608</v>
@@ -9631,10 +9631,10 @@
         <v>340789</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.131764</v>
+        <v>-0.333662</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.249299</v>
+        <v>-1.150371</v>
       </c>
       <c r="AX47" t="n">
         <v>-1.417575</v>
@@ -9792,10 +9792,10 @@
         <v>0.35</v>
       </c>
       <c r="AJ48" t="n">
-        <v>109.08727</v>
+        <v>109.00057</v>
       </c>
       <c r="AK48" t="n">
-        <v>108.65566</v>
+        <v>108.66481</v>
       </c>
       <c r="AL48" t="n">
         <v>5.7087</v>
@@ -9828,10 +9828,10 @@
         <v>341459</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.883188</v>
+        <v>-0.658621</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.583696</v>
+        <v>-3.613081</v>
       </c>
       <c r="AX48" t="n">
         <v>0.84617</v>
@@ -9989,10 +9989,10 @@
         <v>0.23</v>
       </c>
       <c r="AJ49" t="n">
-        <v>108.85988</v>
+        <v>108.76683</v>
       </c>
       <c r="AK49" t="n">
-        <v>107.4594</v>
+        <v>107.55639</v>
       </c>
       <c r="AL49" t="n">
         <v>5.4571</v>
@@ -10025,10 +10025,10 @@
         <v>344440</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.208448</v>
+        <v>-0.214439</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.100964</v>
+        <v>-1.020036</v>
       </c>
       <c r="AX49" t="n">
         <v>-4.407308</v>
@@ -10186,10 +10186,10 @@
         <v>0.21</v>
       </c>
       <c r="AJ50" t="n">
-        <v>108.41316</v>
+        <v>108.27053</v>
       </c>
       <c r="AK50" t="n">
-        <v>113.21721</v>
+        <v>113.14433</v>
       </c>
       <c r="AL50" t="n">
         <v>5.6021</v>
@@ -10222,10 +10222,10 @@
         <v>345111</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.410362</v>
+        <v>-0.456297</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.358126</v>
+        <v>5.195358</v>
       </c>
       <c r="AX50" t="n">
         <v>2.657089</v>
@@ -10383,10 +10383,10 @@
         <v>-0.21</v>
       </c>
       <c r="AJ51" t="n">
-        <v>108.83964</v>
+        <v>108.80021</v>
       </c>
       <c r="AK51" t="n">
-        <v>110.47825</v>
+        <v>110.57963</v>
       </c>
       <c r="AL51" t="n">
         <v>5.4264</v>
@@ -10419,10 +10419,10 @@
         <v>350767</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.393384</v>
+        <v>0.489219</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.419208</v>
+        <v>-2.266751</v>
       </c>
       <c r="AX51" t="n">
         <v>-3.136324</v>
@@ -10580,10 +10580,10 @@
         <v>0.52</v>
       </c>
       <c r="AJ52" t="n">
-        <v>108.76251</v>
+        <v>108.63642</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.57602</v>
+        <v>109.59513</v>
       </c>
       <c r="AL52" t="n">
         <v>5.3186</v>
@@ -10616,10 +10616,10 @@
         <v>356582</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.070866</v>
+        <v>-0.150542</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.816658</v>
+        <v>-0.890309</v>
       </c>
       <c r="AX52" t="n">
         <v>-1.986584</v>
@@ -10777,10 +10777,10 @@
         <v>0.03</v>
       </c>
       <c r="AJ53" t="n">
-        <v>108.78795</v>
+        <v>108.7159</v>
       </c>
       <c r="AK53" t="n">
-        <v>110.16742</v>
+        <v>110.16346</v>
       </c>
       <c r="AL53" t="n">
         <v>5.3843</v>
@@ -10813,10 +10813,10 @@
         <v>357103</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.02339</v>
+        <v>0.073161</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.539717</v>
+        <v>0.518572</v>
       </c>
       <c r="AX53" t="n">
         <v>1.235287</v>
@@ -10974,10 +10974,10 @@
         <v>0.03</v>
       </c>
       <c r="AJ54" t="n">
-        <v>109.30007</v>
+        <v>109.27405</v>
       </c>
       <c r="AK54" t="n">
-        <v>106.69062</v>
+        <v>106.90236</v>
       </c>
       <c r="AL54" t="n">
         <v>5.3338</v>
@@ -11010,10 +11010,10 @@
         <v>360578</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.470751</v>
+        <v>0.513402</v>
       </c>
       <c r="AW54" t="n">
-        <v>-3.155924</v>
+        <v>-2.960237</v>
       </c>
       <c r="AX54" t="n">
         <v>-0.937912</v>
@@ -11171,10 +11171,10 @@
         <v>0.21</v>
       </c>
       <c r="AJ55" t="n">
-        <v>109.27117</v>
+        <v>109.41762</v>
       </c>
       <c r="AK55" t="n">
-        <v>107.27827</v>
+        <v>107.17649</v>
       </c>
       <c r="AL55" t="n">
         <v>5.5024</v>
@@ -11207,10 +11207,10 @@
         <v>358234</v>
       </c>
       <c r="AV55" t="n">
-        <v>-0.026441</v>
+        <v>0.131385</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.550798</v>
+        <v>0.25643</v>
       </c>
       <c r="AX55" t="n">
         <v>3.160973</v>
@@ -11368,10 +11368,10 @@
         <v>0.39</v>
       </c>
       <c r="AJ56" t="n">
-        <v>110.09703</v>
+        <v>110.05486</v>
       </c>
       <c r="AK56" t="n">
-        <v>103.80093</v>
+        <v>102.36456</v>
       </c>
       <c r="AL56" t="n">
         <v>5.2301</v>
@@ -11404,10 +11404,10 @@
         <v>364367</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.755789</v>
+        <v>0.582392</v>
       </c>
       <c r="AW56" t="n">
-        <v>-3.241421</v>
+        <v>-4.489725</v>
       </c>
       <c r="AX56" t="n">
         <v>-4.94875</v>
@@ -11565,10 +11565,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110.78559</v>
+        <v>110.65892</v>
       </c>
       <c r="AK57" t="n">
-        <v>106.7205</v>
+        <v>106.82125</v>
       </c>
       <c r="AL57" t="n">
         <v>5.1495</v>
@@ -11601,10 +11601,10 @@
         <v>371074</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.625412</v>
+        <v>0.548872</v>
       </c>
       <c r="AW57" t="n">
-        <v>2.812663</v>
+        <v>4.353743</v>
       </c>
       <c r="AX57" t="n">
         <v>-1.54108</v>
@@ -11762,10 +11762,10 @@
         <v>0.91</v>
       </c>
       <c r="AJ58" t="n">
-        <v>110.58589</v>
+        <v>110.51078</v>
       </c>
       <c r="AK58" t="n">
-        <v>117.92682</v>
+        <v>117.8089</v>
       </c>
       <c r="AL58" t="n">
         <v>5.2194</v>
@@ -11798,10 +11798,10 @@
         <v>362002</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.180258</v>
+        <v>-0.133871</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.500625</v>
+        <v>10.286015</v>
       </c>
       <c r="AX58" t="n">
         <v>1.357413</v>
@@ -11959,10 +11959,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ59" t="n">
-        <v>111.15205</v>
+        <v>110.95732</v>
       </c>
       <c r="AK59" t="n">
-        <v>113.72712</v>
+        <v>113.99365</v>
       </c>
       <c r="AL59" t="n">
         <v>4.9886</v>
@@ -11995,10 +11995,10 @@
         <v>366913</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.511964</v>
+        <v>0.404069</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.561276</v>
+        <v>-3.238507</v>
       </c>
       <c r="AX59" t="n">
         <v>-4.421964</v>
@@ -12155,8 +12155,12 @@
       <c r="AI60" t="n">
         <v>0.65</v>
       </c>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
+      <c r="AJ60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>109.52993</v>
+      </c>
       <c r="AL60" t="n">
         <v>5.0569</v>
       </c>
@@ -12187,8 +12191,12 @@
       <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AV60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr"/>
+      <c r="AV60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>-3.915762</v>
+      </c>
       <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
@@ -12404,88 +12412,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173825</v>
+        <v>173714</v>
       </c>
       <c r="C62" t="n">
-        <v>170.770004</v>
+        <v>170.630005</v>
       </c>
       <c r="D62" t="n">
-        <v>108.419998</v>
+        <v>107.43</v>
       </c>
       <c r="E62" t="n">
-        <v>433.040009</v>
+        <v>429.119995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1028</v>
+        <v>5.1108</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8311</v>
+        <v>5.8439</v>
       </c>
       <c r="H62" t="n">
-        <v>7533.77002</v>
+        <v>7457.689941</v>
       </c>
       <c r="I62" t="n">
-        <v>25881.949219</v>
+        <v>25520.240234</v>
       </c>
       <c r="J62" t="n">
-        <v>52552.96875</v>
+        <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>3995.699951</v>
+        <v>4012.699951</v>
       </c>
       <c r="L62" t="n">
-        <v>80.139999</v>
+        <v>82.489998</v>
       </c>
       <c r="M62" t="n">
-        <v>85.949997</v>
+        <v>88.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1195</v>
+        <v>1204.5</v>
       </c>
       <c r="O62" t="n">
-        <v>463.5</v>
+        <v>444.75</v>
       </c>
       <c r="P62" t="n">
-        <v>1.046947</v>
+        <v>0.982421</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.017451</v>
+        <v>0.934636</v>
       </c>
       <c r="R62" t="n">
-        <v>0.407478</v>
+        <v>-0.509356</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.599101</v>
+        <v>-1.498909</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.524322</v>
+        <v>-1.369937</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.454415</v>
+        <v>-1.238091</v>
       </c>
       <c r="V62" t="n">
-        <v>0.458841</v>
+        <v>-0.555646</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.265641</v>
+        <v>-2.645487</v>
       </c>
       <c r="X62" t="n">
-        <v>0.446814</v>
+        <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.676128</v>
+        <v>-0.253547</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.309352</v>
+        <v>18.690644</v>
       </c>
       <c r="AA62" t="n">
-        <v>17.868896</v>
+        <v>20.817335</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.00694</v>
+        <v>7.857623</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.295578</v>
+        <v>7.752877</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12502,10 +12510,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.0975</v>
+        <v>5.1176</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0969</v>
+        <v>5.117</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12518,10 +12526,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.52803</v>
+        <v>-1.139744</v>
       </c>
       <c r="AY62" t="n">
-        <v>-1.528207</v>
+        <v>-1.139876</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12439,19 +12439,19 @@
         <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>4012.699951</v>
+        <v>4018.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>82.489998</v>
+        <v>81.779999</v>
       </c>
       <c r="M62" t="n">
         <v>88.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1204.5</v>
+        <v>1203</v>
       </c>
       <c r="O62" t="n">
-        <v>444.75</v>
+        <v>467.5</v>
       </c>
       <c r="P62" t="n">
         <v>0.982421</v>
@@ -12481,19 +12481,19 @@
         <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.253547</v>
+        <v>-0.101913</v>
       </c>
       <c r="Z62" t="n">
-        <v>18.690644</v>
+        <v>17.669063</v>
       </c>
       <c r="AA62" t="n">
         <v>20.817335</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.857623</v>
+        <v>7.723304</v>
       </c>
       <c r="AC62" t="n">
-        <v>7.752877</v>
+        <v>13.264688</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12424,10 +12424,10 @@
         <v>429.119995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1108</v>
+        <v>5.1072</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8439</v>
+        <v>5.8329</v>
       </c>
       <c r="H62" t="n">
         <v>7457.689941</v>
@@ -12439,19 +12439,19 @@
         <v>52146.421875</v>
       </c>
       <c r="K62" t="n">
-        <v>4018.800049</v>
+        <v>4020</v>
       </c>
       <c r="L62" t="n">
-        <v>81.779999</v>
+        <v>81.400002</v>
       </c>
       <c r="M62" t="n">
-        <v>88.099998</v>
+        <v>88.220001</v>
       </c>
       <c r="N62" t="n">
-        <v>1203</v>
+        <v>1220</v>
       </c>
       <c r="O62" t="n">
-        <v>467.5</v>
+        <v>475.25</v>
       </c>
       <c r="P62" t="n">
         <v>0.982421</v>
@@ -12466,10 +12466,10 @@
         <v>-1.498909</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.369937</v>
+        <v>-1.439404</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.238091</v>
+        <v>-1.423994</v>
       </c>
       <c r="V62" t="n">
         <v>-0.555646</v>
@@ -12481,19 +12481,19 @@
         <v>-0.330237</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.101913</v>
+        <v>-0.072085</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.669063</v>
+        <v>17.122304</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.817335</v>
+        <v>20.981903</v>
       </c>
       <c r="AB62" t="n">
-        <v>7.723304</v>
+        <v>9.245578999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>13.264688</v>
+        <v>15.142338</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12412,88 +12412,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173714</v>
+        <v>173371</v>
       </c>
       <c r="C62" t="n">
-        <v>170.630005</v>
+        <v>170.300003</v>
       </c>
       <c r="D62" t="n">
-        <v>107.43</v>
+        <v>106.230003</v>
       </c>
       <c r="E62" t="n">
-        <v>429.119995</v>
+        <v>426.970001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1072</v>
+        <v>5.0921</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8329</v>
+        <v>5.8157</v>
       </c>
       <c r="H62" t="n">
-        <v>7457.689941</v>
+        <v>7443.279785</v>
       </c>
       <c r="I62" t="n">
-        <v>25520.240234</v>
+        <v>25508.070312</v>
       </c>
       <c r="J62" t="n">
-        <v>52146.421875</v>
+        <v>51839.261719</v>
       </c>
       <c r="K62" t="n">
-        <v>4020</v>
+        <v>4064.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>81.400002</v>
+        <v>83.620003</v>
       </c>
       <c r="M62" t="n">
-        <v>88.220001</v>
+        <v>90.400002</v>
       </c>
       <c r="N62" t="n">
-        <v>1220</v>
+        <v>1226.5</v>
       </c>
       <c r="O62" t="n">
-        <v>475.25</v>
+        <v>471.5</v>
       </c>
       <c r="P62" t="n">
-        <v>0.982421</v>
+        <v>0.78303</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.934636</v>
+        <v>0.739426</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.509356</v>
+        <v>-1.62067</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.498909</v>
+        <v>-1.992423</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.439404</v>
+        <v>-1.73081</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.423994</v>
+        <v>-1.714674</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.555646</v>
+        <v>-0.747798</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.645487</v>
+        <v>-2.691912</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.330237</v>
+        <v>-0.917326</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.072085</v>
+        <v>1.041541</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.122304</v>
+        <v>20.316551</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.981903</v>
+        <v>23.971481</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.245578999999999</v>
+        <v>9.827624999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.142338</v>
+        <v>14.233798</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12510,10 +12510,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.1176</v>
+        <v>5.0894</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.117</v>
+        <v>5.0888</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12526,10 +12526,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.139744</v>
+        <v>-1.684503</v>
       </c>
       <c r="AY62" t="n">
-        <v>-1.139876</v>
+        <v>-1.684699</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12412,88 +12412,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173371</v>
+        <v>173326</v>
       </c>
       <c r="C62" t="n">
-        <v>170.300003</v>
+        <v>170.339996</v>
       </c>
       <c r="D62" t="n">
-        <v>106.230003</v>
+        <v>105.949997</v>
       </c>
       <c r="E62" t="n">
-        <v>426.970001</v>
+        <v>430.109985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0921</v>
+        <v>5.072</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8157</v>
+        <v>5.7838</v>
       </c>
       <c r="H62" t="n">
-        <v>7443.279785</v>
+        <v>7509.200195</v>
       </c>
       <c r="I62" t="n">
-        <v>25508.070312</v>
+        <v>25837.210938</v>
       </c>
       <c r="J62" t="n">
-        <v>51839.261719</v>
+        <v>52224.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4064.800049</v>
+        <v>4122.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>83.620003</v>
+        <v>87.129997</v>
       </c>
       <c r="M62" t="n">
-        <v>90.400002</v>
+        <v>84.800003</v>
       </c>
       <c r="N62" t="n">
-        <v>1226.5</v>
+        <v>1227</v>
       </c>
       <c r="O62" t="n">
-        <v>471.5</v>
+        <v>481</v>
       </c>
       <c r="P62" t="n">
-        <v>0.78303</v>
+        <v>0.756871</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.739426</v>
+        <v>0.763084</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.62067</v>
+        <v>-1.879984</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.992423</v>
+        <v>-1.271665</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.73081</v>
+        <v>-2.118709</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.714674</v>
+        <v>-2.253782</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.747798</v>
+        <v>0.131216</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.691912</v>
+        <v>-1.436308</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.917326</v>
+        <v>-0.180734</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.041541</v>
+        <v>2.483281</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.316551</v>
+        <v>25.366903</v>
       </c>
       <c r="AA62" t="n">
-        <v>23.971481</v>
+        <v>16.291834</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.827624999999999</v>
+        <v>9.872398</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.233798</v>
+        <v>16.535433</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12510,10 +12510,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.0894</v>
+        <v>5.078</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0888</v>
+        <v>5.0774</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12526,10 +12526,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.684503</v>
+        <v>-1.904725</v>
       </c>
       <c r="AY62" t="n">
-        <v>-1.684699</v>
+        <v>-1.904946</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12412,88 +12412,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>173326</v>
+        <v>177548</v>
       </c>
       <c r="C62" t="n">
-        <v>170.339996</v>
+        <v>174.699997</v>
       </c>
       <c r="D62" t="n">
-        <v>105.949997</v>
+        <v>107.5</v>
       </c>
       <c r="E62" t="n">
-        <v>430.109985</v>
+        <v>428.859985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.072</v>
+        <v>5.0572</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7838</v>
+        <v>5.7601</v>
       </c>
       <c r="H62" t="n">
-        <v>7509.200195</v>
+        <v>7498.959961</v>
       </c>
       <c r="I62" t="n">
-        <v>25837.210938</v>
+        <v>25690.900391</v>
       </c>
       <c r="J62" t="n">
-        <v>52224.640625</v>
+        <v>52218.578125</v>
       </c>
       <c r="K62" t="n">
-        <v>4122.799805</v>
+        <v>4077.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>87.129997</v>
+        <v>91.06999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>84.800003</v>
+        <v>93.30999799999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1227</v>
+        <v>1244</v>
       </c>
       <c r="O62" t="n">
-        <v>481</v>
+        <v>488.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0.756871</v>
+        <v>3.21118</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.763084</v>
+        <v>3.342203</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.879984</v>
+        <v>-0.44453</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.271665</v>
+        <v>-1.558593</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.118709</v>
+        <v>-2.404326</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.253782</v>
+        <v>-2.654316</v>
       </c>
       <c r="V62" t="n">
-        <v>0.131216</v>
+        <v>-0.005332</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.436308</v>
+        <v>-1.994453</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.180734</v>
+        <v>-0.192322</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.483281</v>
+        <v>1.367173</v>
       </c>
       <c r="Z62" t="n">
-        <v>25.366903</v>
+        <v>31.035971</v>
       </c>
       <c r="AA62" t="n">
-        <v>16.291834</v>
+        <v>27.96215</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.872398</v>
+        <v>11.394672</v>
       </c>
       <c r="AC62" t="n">
-        <v>16.535433</v>
+        <v>18.413083</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12510,10 +12510,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.078</v>
+        <v>5.0638</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0774</v>
+        <v>5.0632</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12526,10 +12526,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-1.904725</v>
+        <v>-2.179036</v>
       </c>
       <c r="AY62" t="n">
-        <v>-1.904946</v>
+        <v>-2.179289</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -12412,88 +12412,88 @@
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>177548</v>
+        <v>176724</v>
       </c>
       <c r="C62" t="n">
-        <v>174.699997</v>
+        <v>173.449997</v>
       </c>
       <c r="D62" t="n">
-        <v>107.5</v>
+        <v>106.18</v>
       </c>
       <c r="E62" t="n">
-        <v>428.859985</v>
+        <v>425.519989</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0572</v>
+        <v>5.0821</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7601</v>
+        <v>5.7826</v>
       </c>
       <c r="H62" t="n">
-        <v>7498.959961</v>
+        <v>7408.299805</v>
       </c>
       <c r="I62" t="n">
-        <v>25690.900391</v>
+        <v>25137.689453</v>
       </c>
       <c r="J62" t="n">
-        <v>52218.578125</v>
+        <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4077.899902</v>
+        <v>4062.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>91.06999999999999</v>
+        <v>89.879997</v>
       </c>
       <c r="M62" t="n">
-        <v>93.30999799999999</v>
+        <v>92</v>
       </c>
       <c r="N62" t="n">
-        <v>1244</v>
+        <v>1247.5</v>
       </c>
       <c r="O62" t="n">
-        <v>488.75</v>
+        <v>487</v>
       </c>
       <c r="P62" t="n">
-        <v>3.21118</v>
+        <v>2.732177</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.342203</v>
+        <v>2.602777</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.44453</v>
+        <v>-1.666978</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.558593</v>
+        <v>-2.325262</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.404326</v>
+        <v>-1.923798</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.654316</v>
+        <v>-2.274066</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.005332</v>
+        <v>-1.214238</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.994453</v>
+        <v>-4.10484</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.192322</v>
+        <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.367173</v>
+        <v>0.974426</v>
       </c>
       <c r="Z62" t="n">
-        <v>31.035971</v>
+        <v>29.323737</v>
       </c>
       <c r="AA62" t="n">
-        <v>27.96215</v>
+        <v>26.165664</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.394672</v>
+        <v>11.708081</v>
       </c>
       <c r="AC62" t="n">
-        <v>18.413083</v>
+        <v>17.989098</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12510,10 +12510,10 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.0638</v>
+        <v>5.0807</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.0632</v>
+        <v>5.0801</v>
       </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
@@ -12526,10 +12526,10 @@
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
-        <v>-2.179036</v>
+        <v>-1.852567</v>
       </c>
       <c r="AY62" t="n">
-        <v>-2.179289</v>
+        <v>-1.852782</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,170 +578,160 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_cdi</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -814,53 +804,51 @@
         <v>0.016137</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.02</v>
+        <v>96.31464</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="AK2" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -877,8 +865,6 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -975,99 +961,93 @@
         <v>0.019413</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.019413</v>
+        <v>0.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.88</v>
+        <v>97.07568000000001</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>0.79016</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.79016</v>
+        <v>-0.512311</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.512311</v>
+        <v>0.423696</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
+        <v>0.423745</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.423745</v>
+        <v>1.736829</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.736829</v>
+        <v>0.972464</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.972464</v>
+        <v>2.311409</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1166,99 +1146,93 @@
         <v>0.021003</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.021003</v>
+        <v>1.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>96.95968999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.95968999999999</v>
+        <v>97.24746</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.24746</v>
+        <v>5.4394</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>-0.119484</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.119484</v>
+        <v>-2.094902</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.094902</v>
+        <v>5.757004</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
+        <v>5.757676</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.757676</v>
+        <v>2.185796</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.185796</v>
+        <v>2.329166</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.329166</v>
+        <v>2.079394</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BF4" t="n">
+        <v>1</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1357,99 +1331,93 @@
         <v>0.024244</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.024244</v>
+        <v>1.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.16</v>
+        <v>97.48142</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.48142</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.643</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>0.53809</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53809</v>
+        <v>-0.644377</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.644377</v>
+        <v>3.74306</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
+        <v>3.743473</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.743473</v>
+        <v>1.596467</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.596467</v>
+        <v>0.888065</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.888065</v>
+        <v>2.123375</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1548,99 +1516,93 @@
         <v>0.029256</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.84</v>
+        <v>98.97262000000001</v>
       </c>
       <c r="AJ6" t="n">
-        <v>98.97262000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="AK6" t="n">
-        <v>98.05768</v>
+        <v>5.6199</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="AN6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="AO6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="AP6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="AU6" t="n">
-        <v>367772</v>
+        <v>1.529727</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.529727</v>
+        <v>1.487112</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.487112</v>
+        <v>-0.409357</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.409357</v>
+        <v>-0.4094</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.4094</v>
+        <v>1.896096</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.896096</v>
+        <v>1.160214</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.160214</v>
+        <v>2.436662</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1739,99 +1701,93 @@
         <v>0.033316</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="AG7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0.87</v>
-      </c>
       <c r="AI7" t="n">
-        <v>0.73</v>
+        <v>99.35339</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.35339</v>
+        <v>99.33126</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.33126</v>
+        <v>5.5805</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>0.384723</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.384723</v>
+        <v>1.298807</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.298807</v>
+        <v>-0.70108</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
+        <v>-0.701155</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.701155</v>
+        <v>1.856332</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.856332</v>
+        <v>2.135418</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.135418</v>
+        <v>1.653884</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BF7" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1930,99 +1886,93 @@
         <v>0.034749</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.67</v>
+        <v>97.34401</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.34401</v>
+        <v>90.45032</v>
       </c>
       <c r="AK8" t="n">
-        <v>90.45032</v>
+        <v>5.3574</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-2.022457</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.022457</v>
+        <v>-8.94073</v>
       </c>
       <c r="AW8" t="n">
-        <v>-8.94073</v>
+        <v>-3.99785</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
+        <v>-3.99828</v>
       </c>
       <c r="AY8" t="n">
-        <v>-3.99828</v>
+        <v>-0.015397</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.015397</v>
+        <v>-1.385541</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.385541</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2121,99 +2071,93 @@
         <v>0.039598</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>98.43725000000001</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.43725000000001</v>
+        <v>95.72214</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.72214</v>
+        <v>5.1394</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>1.123069</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.123069</v>
+        <v>5.828415</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.828415</v>
+        <v>-4.069138</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
+        <v>-4.069594</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.069594</v>
+        <v>0.975774</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.975774</v>
+        <v>1.257759</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.257759</v>
+        <v>0.775073</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BF9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2312,99 +2256,93 @@
         <v>0.041954</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.71</v>
+        <v>99.55981</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.55981</v>
+        <v>104.61484</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.61484</v>
+        <v>4.7378</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>1.140381</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.140381</v>
+        <v>9.290118</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.290118</v>
+        <v>-7.814142</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
+        <v>-7.815054</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.815054</v>
+        <v>1.412174</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.412174</v>
+        <v>1.146068</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.146068</v>
+        <v>1.602477</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BF10" t="n">
+        <v>1</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2503,99 +2441,93 @@
         <v>0.043739</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>99.51646</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.51646</v>
+        <v>100.42352</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.42352</v>
+        <v>4.9191</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>-0.043542</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.043542</v>
+        <v>-4.00643</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.00643</v>
+        <v>3.826671</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
+        <v>3.827155</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.827155</v>
+        <v>0.816526</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.816526</v>
+        <v>0.461006</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.461006</v>
+        <v>1.06968</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2694,99 +2626,93 @@
         <v>0.046796</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.45</v>
+        <v>99.67415</v>
       </c>
       <c r="AJ12" t="n">
-        <v>99.67415</v>
+        <v>99.79777</v>
       </c>
       <c r="AK12" t="n">
-        <v>99.79777</v>
+        <v>4.7289</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="AN12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="AO12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="AP12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>0.158456</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.158456</v>
+        <v>-0.623111</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.623111</v>
+        <v>-3.866561</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
+        <v>-3.867033</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.867033</v>
+        <v>1.151595</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.151595</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
+        <v>1.598738</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BF12" t="n">
+        <v>1</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2885,105 +2811,99 @@
         <v>0.048116</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.62</v>
+        <v>99.6343</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99.6343</v>
+        <v>99.53784</v>
       </c>
       <c r="AK13" t="n">
-        <v>99.53784</v>
+        <v>5.238</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="AN13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="AO13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="AP13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>-0.03998</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.03998</v>
+        <v>-0.260457</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.260457</v>
+        <v>10.765717</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>10.767083</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>1.558597</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>1.928912</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>1.299314</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>-1.286607</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>11.88673</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>10.700862</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>11.919595</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>0.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3082,105 +3002,99 @@
         <v>0.049037</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.6</v>
+        <v>101.27684</v>
       </c>
       <c r="AJ14" t="n">
-        <v>101.27684</v>
+        <v>103.95861</v>
       </c>
       <c r="AK14" t="n">
-        <v>103.95861</v>
+        <v>5.1884</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="AN14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="AO14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="AP14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>1.648569</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.648569</v>
+        <v>4.441296</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.441296</v>
+        <v>-0.946926</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>-0.947035</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>0.677481</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>-0.269467</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>1.344714</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>1.299867</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>10.069235</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>10.074751</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>10.124804</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3279,105 +3193,99 @@
         <v>0.05056</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.31</v>
+        <v>101.07328</v>
       </c>
       <c r="AJ15" t="n">
-        <v>101.07328</v>
+        <v>104.56278</v>
       </c>
       <c r="AK15" t="n">
-        <v>104.56278</v>
+        <v>5.179</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="AN15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="AO15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="AP15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>-0.200994</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.200994</v>
+        <v>0.581164</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.581164</v>
+        <v>-0.181173</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>-0.181194</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>1.469562</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>0.837552</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>1.907759</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>-1.945422</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.58755</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>8.825751</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3476,105 +3384,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.32</v>
+        <v>101.17973</v>
       </c>
       <c r="AJ16" t="n">
-        <v>101.17973</v>
+        <v>101.38087</v>
       </c>
       <c r="AK16" t="n">
-        <v>101.38087</v>
+        <v>5.4066</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="AN16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="AO16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="AP16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>0.10532</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.10532</v>
+        <v>-3.043062</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.043062</v>
+        <v>4.394671</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>4.39518</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>1.814888</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>2.210221</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>1.543645</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>-3.557633</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>7.168596</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>7.191214</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3673,105 +3575,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.47</v>
+        <v>101.46342</v>
       </c>
       <c r="AJ17" t="n">
-        <v>101.46342</v>
+        <v>100.20398</v>
       </c>
       <c r="AK17" t="n">
-        <v>100.20398</v>
+        <v>5.257</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="AN17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="AO17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="AP17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>0.280382</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.280382</v>
+        <v>-1.16086</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.16086</v>
+        <v>-2.766988</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>-2.767296</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>0.991621</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>-0.187221</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>1.805747</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.470016</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>6.517038</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>6.460076</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3870,105 +3766,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.38</v>
+        <v>100.66227</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.66227</v>
+        <v>99.36927</v>
       </c>
       <c r="AK18" t="n">
-        <v>99.36927</v>
+        <v>5.2941</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="AN18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="AO18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="AP18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>-0.789595</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.789595</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>0.705726</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>0.705806</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>1.335643</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>1.161333</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>1.453667</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>1.830463</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>5.900488</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>5.899363</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>5.974439</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4067,105 +3957,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.6899999999999999</v>
+        <v>100.58196</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100.58196</v>
+        <v>99.97806</v>
       </c>
       <c r="AK19" t="n">
-        <v>99.97806</v>
+        <v>5.2177</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="AN19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="AO19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="AP19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>-0.07978200000000001</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>0.612654</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.612654</v>
+        <v>-1.443116</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>-1.443279</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>1.521325</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>2.249624</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>1.029618</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>-2.051854</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>5.784842</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>5.458422</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>5.932356</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH19" t="n">
         <v>0</v>
       </c>
-      <c r="BH19" t="n">
-        <v>-0</v>
-      </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4264,105 +4148,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.46</v>
+        <v>100.05178</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100.05178</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="AK20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0993</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="AN20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="AO20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="AP20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-0.527112</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.527112</v>
+        <v>-6.187047</v>
       </c>
       <c r="AW20" t="n">
-        <v>-6.187047</v>
+        <v>-2.269199</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>-2.26946</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>0.133468</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>-1.232052</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>1.066493</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>1.976883</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>5.77432</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>3.79089</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>5.711379</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4461,105 +4339,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.77</v>
+        <v>103.00964</v>
       </c>
       <c r="AJ21" t="n">
-        <v>103.00964</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="AK21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2078</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="AN21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="AO21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="AP21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>2.956329</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.956329</v>
+        <v>5.286443</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.286443</v>
+        <v>2.127743</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>2.127993</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>-0.042451</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>-0.710886</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>0.403932</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>-0.913259</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>5.596302</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>1.864495</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>5.47065</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4658,105 +4530,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.64</v>
+        <v>103.09341</v>
       </c>
       <c r="AJ22" t="n">
-        <v>103.09341</v>
+        <v>110.62354</v>
       </c>
       <c r="AK22" t="n">
-        <v>110.62354</v>
+        <v>5.0804</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="AM22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="AN22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="AO22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="AP22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>0.08132200000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.08132200000000001</v>
+        <v>12.023101</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.023101</v>
+        <v>-2.446331</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>-2.446612</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>1.002821</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>0.879872</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>1.083978</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>3.980518</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>4.650694</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>0.172427</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>4.361088</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4855,105 +4721,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.53</v>
+        <v>104.1626</v>
       </c>
       <c r="AJ23" t="n">
-        <v>104.1626</v>
+        <v>104.34152</v>
       </c>
       <c r="AK23" t="n">
-        <v>104.34152</v>
+        <v>5.0007</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="AN23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="AO23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="AP23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>1.037108</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.037108</v>
+        <v>-5.678737</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.678737</v>
+        <v>-1.568774</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>-1.568959</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>0.027577</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>-0.459418</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>0.348572</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>1.338676</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>4.184706</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>-2.158772</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>3.834324</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5052,105 +4912,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.36</v>
+        <v>102.3642</v>
       </c>
       <c r="AJ24" t="n">
-        <v>102.3642</v>
+        <v>102.66392</v>
       </c>
       <c r="AK24" t="n">
-        <v>102.66392</v>
+        <v>5.0959</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="AN24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="AO24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="AP24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>-1.726531</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.726531</v>
+        <v>-1.607797</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.607797</v>
+        <v>1.903733</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>1.903962</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>0.504966</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>0.024709</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>0.818881</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>-0.646757</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>3.935832</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>-4.45588</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>3.741292</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5249,105 +5103,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
-        <v>-0.1</v>
+        <v>102.50431</v>
       </c>
       <c r="AJ25" t="n">
-        <v>102.50431</v>
+        <v>102.53174</v>
       </c>
       <c r="AK25" t="n">
-        <v>102.53174</v>
+        <v>4.8192</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="AM25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="AN25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="AO25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="AP25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="AU25" t="n">
-        <v>343620</v>
+        <v>0.136874</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.136874</v>
+        <v>-0.12875</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.12875</v>
+        <v>-5.429855</v>
       </c>
       <c r="AX25" t="n">
-        <v>-5.429855</v>
+        <v>-5.430495</v>
       </c>
       <c r="AY25" t="n">
-        <v>-5.430495</v>
+        <v>0.472174</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.472174</v>
+        <v>1.122473</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.122473</v>
+        <v>0.050421</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.050421</v>
+        <v>0.038138</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.038138</v>
+        <v>3.161501</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.161501</v>
+        <v>-6.84947</v>
       </c>
       <c r="BE25" t="n">
-        <v>-6.84947</v>
+        <v>2.998957</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5446,105 +5294,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.09</v>
+        <v>102.83357</v>
       </c>
       <c r="AJ26" t="n">
-        <v>102.83357</v>
+        <v>105.47522</v>
       </c>
       <c r="AK26" t="n">
-        <v>105.47522</v>
+        <v>4.7415</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="AN26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="AO26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="AP26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>0.321216</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.321216</v>
+        <v>2.870799</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.870799</v>
+        <v>-1.612301</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>-1.612502</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>0.098769</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>-0.740777</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>-7.713954</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>3.527423</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5643,105 +5485,99 @@
         <v>0.049189</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.2</v>
+        <v>102.45222</v>
       </c>
       <c r="AJ27" t="n">
-        <v>102.45222</v>
+        <v>106.13139</v>
       </c>
       <c r="AK27" t="n">
-        <v>106.13139</v>
+        <v>4.9219</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="AN27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="AO27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="AP27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>-0.370842</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.370842</v>
+        <v>0.622108</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.622108</v>
+        <v>3.804703</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>3.805185</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>1.352666</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>0.887701</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>1.653244</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>-0.376003</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>4.608216</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>-7.193509</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>4.057054</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BI27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5840,105 +5676,99 @@
         <v>0.048422</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.11</v>
+        <v>102.57885</v>
       </c>
       <c r="AJ28" t="n">
-        <v>102.57885</v>
+        <v>102.00419</v>
       </c>
       <c r="AK28" t="n">
-        <v>102.00419</v>
+        <v>5.0076</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="AN28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="AO28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="AP28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>0.123599</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.123599</v>
+        <v>-3.888765</v>
       </c>
       <c r="AW28" t="n">
-        <v>-3.888765</v>
+        <v>1.741198</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>1.74141</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>1.203116</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>1.956912</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>0.719465</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>-1.119482</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>5.185235</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>-5.956714</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>4.505936</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6037,105 +5867,99 @@
         <v>0.047279</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.12</v>
+        <v>102.87707</v>
       </c>
       <c r="AJ29" t="n">
-        <v>102.87707</v>
+        <v>102.0744</v>
       </c>
       <c r="AK29" t="n">
-        <v>102.0744</v>
+        <v>5.0575</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="AN29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="AO29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.290723</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.290723</v>
+        <v>0.068831</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.068831</v>
+        <v>0.996485</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>0.996605</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>0.495259</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>-0.467999</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>1.120891</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>-0.022625</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>4.819246</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>-4.560737</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>4.141877</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BI29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6234,105 +6058,99 @@
         <v>0.045601</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1</v>
+        <v>103.528</v>
       </c>
       <c r="AJ30" t="n">
-        <v>103.528</v>
+        <v>101.86494</v>
       </c>
       <c r="AK30" t="n">
-        <v>101.86494</v>
+        <v>4.9355</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="AN30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="AO30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="AP30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>0.632726</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.632726</v>
+        <v>-0.205203</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.205203</v>
+        <v>-2.412259</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>-2.412545</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>1.013388</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>0.723782</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>1.198521</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>2.397964</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>4.683537</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>-3.457004</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>3.851383</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BI30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6431,105 +6249,99 @@
         <v>0.044537</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.55</v>
+        <v>104.8991</v>
       </c>
       <c r="AJ31" t="n">
-        <v>104.8991</v>
+        <v>101.74606</v>
       </c>
       <c r="AK31" t="n">
-        <v>101.74606</v>
+        <v>4.8413</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="AN31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="AO31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="AP31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>1.324376</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.324376</v>
+        <v>-0.116704</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.116704</v>
+        <v>-1.908621</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>-1.908853</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>1.646862</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>2.824206</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>0.897764</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>1.902378</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>4.621114</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>-3.178284</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>3.706988</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6628,105 +6440,99 @@
         <v>0.043739</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.57</v>
+        <v>104.53245</v>
       </c>
       <c r="AJ32" t="n">
-        <v>104.53245</v>
+        <v>98.01879</v>
       </c>
       <c r="AK32" t="n">
-        <v>98.01879</v>
+        <v>4.9535</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="AN32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="AO32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="AP32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>-0.349526</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.349526</v>
+        <v>-3.663306</v>
       </c>
       <c r="AW32" t="n">
-        <v>-3.663306</v>
+        <v>2.317559</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>2.317847</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>-0.180012</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>-2.151229</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>1.098143</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>0.009013</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>4.506637</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>-3.31355</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>3.820543</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6825,105 +6631,99 @@
         <v>0.041957</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.8100000000000001</v>
+        <v>104.75961</v>
       </c>
       <c r="AJ33" t="n">
-        <v>104.75961</v>
+        <v>102.37988</v>
       </c>
       <c r="AK33" t="n">
-        <v>102.37988</v>
+        <v>4.9833</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="AN33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="AO33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="AP33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>0.217311</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.217311</v>
+        <v>4.449239</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.449239</v>
+        <v>0.601595</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>0.601668</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>0.366662</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>0.04207</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>0.570366</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>-0.664947</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>4.496274</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>-3.758575</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>3.861754</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>-0.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BI33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7022,105 +6822,99 @@
         <v>0.04142</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.19</v>
+        <v>104.7097</v>
       </c>
       <c r="AJ34" t="n">
-        <v>104.7097</v>
+        <v>109.58504</v>
       </c>
       <c r="AK34" t="n">
-        <v>109.58504</v>
+        <v>4.9962</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="AM34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="AN34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="AO34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="AP34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>-0.047642</v>
       </c>
       <c r="AV34" t="n">
-        <v>-0.047642</v>
+        <v>7.037672</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.037672</v>
+        <v>0.258865</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>0.258896</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>1.440658</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>2.257995</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>0.930417</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>0.652954</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>3.925596</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>-4.25878</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>3.397348</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7219,105 +7013,99 @@
         <v>0.040168</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.37</v>
+        <v>104.75682</v>
       </c>
       <c r="AJ35" t="n">
-        <v>104.75682</v>
+        <v>109.36335</v>
       </c>
       <c r="AK35" t="n">
-        <v>109.36335</v>
+        <v>5.1718</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="AN35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="AO35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="AP35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>0.045001</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.045001</v>
+        <v>-0.2023</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.2023</v>
+        <v>3.514671</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>3.515093</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>0.267741</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>0.904602</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>-0.96026</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>3.688016</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>-3.040871</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>3.232784</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7416,105 +7204,99 @@
         <v>0.039484</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="AG36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AH36" t="n">
-        <v>0.89</v>
-      </c>
       <c r="AI36" t="n">
-        <v>0.46</v>
+        <v>105.70704</v>
       </c>
       <c r="AJ36" t="n">
-        <v>105.70704</v>
+        <v>104.84682</v>
       </c>
       <c r="AK36" t="n">
-        <v>104.84682</v>
+        <v>5.2416</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="AN36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="AO36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="AP36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>0.907072</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.907072</v>
+        <v>-4.129839</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.129839</v>
+        <v>1.349627</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>1.349783</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>0.64951</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>0.415624</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>0.795057</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>1.126567</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>3.925952</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>-0.344269</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>3.335647</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>-0.25</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BI36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7613,105 +7395,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.25</v>
+        <v>106.57623</v>
       </c>
       <c r="AJ37" t="n">
-        <v>106.57623</v>
+        <v>106.03093</v>
       </c>
       <c r="AK37" t="n">
-        <v>106.03093</v>
+        <v>5.5589</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="AN37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="AO37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="AP37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>0.822263</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.822263</v>
+        <v>1.129371</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.129371</v>
+        <v>6.053495</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>6.054188</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>1.476967</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>2.569845</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>0.799559</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>0.637586</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>4.227578</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>2.440035</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>3.697684</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7810,105 +7586,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.26</v>
+        <v>106.88756</v>
       </c>
       <c r="AJ38" t="n">
-        <v>106.88756</v>
+        <v>111.55002</v>
       </c>
       <c r="AK38" t="n">
-        <v>111.55002</v>
+        <v>5.6621</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="AN38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="AO38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="AP38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>0.29212</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.29212</v>
+        <v>5.20517</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.20517</v>
+        <v>1.856482</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>1.856683</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>0.451961</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>-0.577528</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>1.101283</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>1.52448</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>4.498245</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>3.812368</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>4.060953</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8007,105 +7777,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.14</v>
+        <v>107.14396</v>
       </c>
       <c r="AJ39" t="n">
-        <v>107.14396</v>
+        <v>110.19363</v>
       </c>
       <c r="AK39" t="n">
-        <v>110.19363</v>
+        <v>5.6562</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="AN39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="AO39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="AP39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>0.239878</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.239878</v>
+        <v>-1.215948</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.215948</v>
+        <v>-0.104202</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>-0.104213</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>1.088989</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>0.905369</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>1.202826</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>1.632891</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>4.237599</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>4.259387</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>3.707852</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8204,105 +7968,99 @@
         <v>0.039612</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.48</v>
+        <v>107.99916</v>
       </c>
       <c r="AJ40" t="n">
-        <v>107.99916</v>
+        <v>107.28836</v>
       </c>
       <c r="AK40" t="n">
-        <v>107.28836</v>
+        <v>5.4481</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="AN40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="AO40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="AP40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>0.7981780000000001</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.7981780000000001</v>
+        <v>-2.636514</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.636514</v>
+        <v>-3.679149</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>-3.679539</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>1.323978</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>1.72458</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>1.076262</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.42474</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>4.519075</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>4.091149</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.25</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8401,105 +8159,99 @@
         <v>0.040168</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.61</v>
+        <v>108.15356</v>
       </c>
       <c r="AJ41" t="n">
-        <v>108.15356</v>
+        <v>109.21678</v>
       </c>
       <c r="AK41" t="n">
-        <v>109.21678</v>
+        <v>5.7779</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="AN41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="AO41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="AP41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>0.142964</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.142964</v>
+        <v>1.797418</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.797418</v>
+        <v>6.053487</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>6.054153</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>0.532743</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>1.197484</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>-1.591329</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>4.758099</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>5.579866</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>4.600584</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8598,105 +8350,99 @@
         <v>0.04158</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.33</v>
+        <v>107.98489</v>
       </c>
       <c r="AJ42" t="n">
-        <v>107.98489</v>
+        <v>105.74688</v>
       </c>
       <c r="AK42" t="n">
-        <v>105.74688</v>
+        <v>6.0535</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="AM42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="AN42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="AO42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="AP42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>-0.155954</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.155954</v>
+        <v>-3.177076</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.177076</v>
+        <v>4.769899</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>4.770394</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>1.443368</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>1.605359</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>1.343208</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>4.873011</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>6.325086</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>4.840925</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>0.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8795,105 +8541,99 @@
         <v>0.044158</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.48</v>
+        <v>107.44467</v>
       </c>
       <c r="AJ43" t="n">
-        <v>107.44467</v>
+        <v>104.2734</v>
       </c>
       <c r="AK43" t="n">
-        <v>104.2734</v>
+        <v>6.1923</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="AN43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="AO43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="AP43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>-0.500274</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.500274</v>
+        <v>-1.393403</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.393403</v>
+        <v>2.292888</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>2.293116</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>1.55383</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>2.592546</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>0.909924</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>4.831296</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>6.536174</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>4.767938</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>1</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8992,105 +8732,99 @@
         <v>0.045833</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>108.06979</v>
       </c>
       <c r="AJ44" t="n">
-        <v>108.06979</v>
+        <v>101.23438</v>
       </c>
       <c r="AK44" t="n">
-        <v>101.23438</v>
+        <v>5.8301</v>
       </c>
       <c r="AL44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="AN44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="AO44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="AP44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>0.581806</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.581806</v>
+        <v>-2.914473</v>
       </c>
       <c r="AW44" t="n">
-        <v>-2.914473</v>
+        <v>-5.8492</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>-5.849767</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>0.006404</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>-1.889422</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>1.201233</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>-0.432778</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>4.559874</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>6.749097</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>4.174145</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>1</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9189,105 +8923,99 @@
         <v>0.049037</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.48</v>
+        <v>108.77346</v>
       </c>
       <c r="AJ45" t="n">
-        <v>108.77346</v>
+        <v>107.07838</v>
       </c>
       <c r="AK45" t="n">
-        <v>107.07838</v>
+        <v>5.8488</v>
       </c>
       <c r="AL45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="AN45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="AO45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="AP45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>0.651126</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.651126</v>
+        <v>5.772742</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.772742</v>
+        <v>0.320749</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>0.320782</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>1.027506</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>0.529123</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>1.280829</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>5.05763</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>8.444549</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>4.866504</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9386,105 +9114,99 @@
         <v>0.050508</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="AH46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.51</v>
+        <v>110.09056</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110.09056</v>
+        <v>114.05013</v>
       </c>
       <c r="AK46" t="n">
-        <v>114.05013</v>
+        <v>5.7422</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="AN46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="AO46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="AP46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>1.210865</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.210865</v>
+        <v>6.510885</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.510885</v>
+        <v>-1.822596</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>-1.822783</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>0.99855</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>0.852229</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>1.088394</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>1.097417</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>5.47719</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>8.586193</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>5.201441</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>1</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9583,105 +9305,99 @@
         <v>0.052531</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.48</v>
+        <v>109.72323</v>
       </c>
       <c r="AJ47" t="n">
-        <v>109.72323</v>
+        <v>112.73813</v>
       </c>
       <c r="AK47" t="n">
-        <v>112.73813</v>
+        <v>5.6608</v>
       </c>
       <c r="AL47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="AN47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="AO47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="AP47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-0.333662</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.333662</v>
+        <v>-1.150371</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.150371</v>
+        <v>-1.417575</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>-1.417723</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>0.722029</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>0.566954</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>1.377928</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>5.529729</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>8.510418</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>5.316736</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9780,105 +9496,99 @@
         <v>0.053936</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="AH48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.35</v>
+        <v>109.00057</v>
       </c>
       <c r="AJ48" t="n">
-        <v>109.00057</v>
+        <v>108.66481</v>
       </c>
       <c r="AK48" t="n">
-        <v>108.66481</v>
+        <v>5.7087</v>
       </c>
       <c r="AL48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="AN48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="AO48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="AP48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>-0.658621</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.658621</v>
+        <v>-3.613081</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.613081</v>
+        <v>0.84617</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.84626</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>0.639181</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>0.807268</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.196603</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>5.319636</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>7.026183</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>5.201418</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.5</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9977,105 +9687,99 @@
         <v>0.054569</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="AH49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.23</v>
+        <v>108.76683</v>
       </c>
       <c r="AJ49" t="n">
-        <v>108.76683</v>
+        <v>107.55639</v>
       </c>
       <c r="AK49" t="n">
-        <v>107.55639</v>
+        <v>5.4571</v>
       </c>
       <c r="AL49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="AN49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="AO49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="AP49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-0.214439</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.214439</v>
+        <v>-1.020036</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.020036</v>
+        <v>-4.407308</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>-4.407771</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.591659</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>0.541686</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>0.873018</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>5.351165</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>4.393261</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>5.18043</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.25</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10174,105 +9878,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="AI50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>113.14433</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>5.195358</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BH50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AJ50" t="n">
-        <v>108.27053</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>113.14433</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>-0.456297</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>5.195358</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>5.225222</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>2.961368</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>5.127976</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>0.000562</v>
-      </c>
       <c r="BI50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10371,105 +10069,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.21</v>
+        <v>108.80021</v>
       </c>
       <c r="AJ51" t="n">
-        <v>108.80021</v>
+        <v>110.57963</v>
       </c>
       <c r="AK51" t="n">
-        <v>110.57963</v>
+        <v>5.4264</v>
       </c>
       <c r="AL51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="AM51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="AN51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="AO51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="AP51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>0.489219</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.489219</v>
+        <v>-2.266751</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.266751</v>
+        <v>-3.136324</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>-3.13666</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>0.612293</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>0.073298</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>1.638893</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>5.130501</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>3.033233</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>5.054283</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10568,105 +10260,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.52</v>
+        <v>108.63642</v>
       </c>
       <c r="AJ52" t="n">
-        <v>108.63642</v>
+        <v>109.59513</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.59513</v>
+        <v>5.3186</v>
       </c>
       <c r="AL52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="AN52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="AO52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="AP52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-0.150542</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.150542</v>
+        <v>-0.890309</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.890309</v>
+        <v>-1.986584</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>-1.986804</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>1.155358</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>1.710427</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>0.821088</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>1.657796</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>5.172369</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>2.828436</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>5.096104</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10765,105 +10451,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.09</v>
+        <v>-0.36</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.03</v>
+        <v>108.7159</v>
       </c>
       <c r="AJ53" t="n">
-        <v>108.7159</v>
+        <v>110.16346</v>
       </c>
       <c r="AK53" t="n">
-        <v>110.16346</v>
+        <v>5.3843</v>
       </c>
       <c r="AL53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="AN53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="AO53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="AP53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="AU53" t="n">
-        <v>357103</v>
+        <v>0.073161</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.073161</v>
+        <v>0.518572</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.518572</v>
+        <v>1.235287</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.235287</v>
+        <v>1.235427</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.235427</v>
+        <v>1.038729</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.038729</v>
+        <v>0.301682</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.301682</v>
+        <v>1.486504</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.486504</v>
+        <v>0.146109</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.146109</v>
+        <v>4.680811</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.680811</v>
+        <v>0.924206</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>4.490243</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10962,105 +10642,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03</v>
+        <v>109.27405</v>
       </c>
       <c r="AJ54" t="n">
-        <v>109.27405</v>
+        <v>106.90236</v>
       </c>
       <c r="AK54" t="n">
-        <v>106.90236</v>
+        <v>5.3338</v>
       </c>
       <c r="AL54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="AN54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="AO54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="AP54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>0.513402</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.513402</v>
+        <v>-2.960237</v>
       </c>
       <c r="AW54" t="n">
-        <v>-2.960237</v>
+        <v>-0.937912</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>-0.938017</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>1.146567</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>0.715383</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>1.405488</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>0.973109</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>4.461836</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>-0.101973</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>4.177803</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>0</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="BI54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11159,105 +10833,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.21</v>
+        <v>109.41762</v>
       </c>
       <c r="AJ55" t="n">
-        <v>109.41762</v>
+        <v>107.17649</v>
       </c>
       <c r="AK55" t="n">
-        <v>107.17649</v>
+        <v>5.5024</v>
       </c>
       <c r="AL55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="AN55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="AO55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="AP55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>0.131385</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.131385</v>
+        <v>0.25643</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.25643</v>
+        <v>3.160973</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>3.161329</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>1.90144</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>3.24641</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>1.099346</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>-0.650067</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>4.264385</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>-1.042167</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>3.897866</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>0</v>
       </c>
-      <c r="BI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11356,105 +11024,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.39</v>
+        <v>110.05486</v>
       </c>
       <c r="AJ56" t="n">
-        <v>110.05486</v>
+        <v>102.36456</v>
       </c>
       <c r="AK56" t="n">
-        <v>102.36456</v>
+        <v>5.2301</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="AN56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="AO56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="AP56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>0.582392</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.582392</v>
+        <v>-4.489725</v>
       </c>
       <c r="AW56" t="n">
-        <v>-4.489725</v>
+        <v>-4.94875</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>-4.949289</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>-0.083179</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>-1.743482</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>0.927966</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>1.712009</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>4.441351</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>-0.903999</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>4.303068</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11553,105 +11215,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.5600000000000001</v>
+        <v>110.65892</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110.65892</v>
+        <v>106.82125</v>
       </c>
       <c r="AK57" t="n">
-        <v>106.82125</v>
+        <v>5.1495</v>
       </c>
       <c r="AL57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="AN57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="AO57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="AP57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>0.548872</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.548872</v>
+        <v>4.353743</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.353743</v>
+        <v>-1.54108</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>-1.541256</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>0.371461</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>0.070797</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>0.549722</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>1.840727</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>3.812497</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>-2.659212</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>3.357475</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11750,105 +11406,99 @@
         <v>0.054777</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.91</v>
+        <v>110.51078</v>
       </c>
       <c r="AJ58" t="n">
-        <v>110.51078</v>
+        <v>117.8089</v>
       </c>
       <c r="AK58" t="n">
-        <v>117.8089</v>
+        <v>5.2194</v>
       </c>
       <c r="AL58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="AN58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="AO58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="AP58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="AQ58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>-0.133871</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.133871</v>
+        <v>10.286015</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.286015</v>
+        <v>1.357413</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>1.357572</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>1.12824</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>1.133877</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>1.124914</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>-2.444795</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>4.142847</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>-1.819225</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>3.768807</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.25</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BI58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11947,105 +11597,99 @@
         <v>0.054223</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.8100000000000001</v>
+        <v>110.95732</v>
       </c>
       <c r="AJ59" t="n">
-        <v>110.95732</v>
+        <v>113.99365</v>
       </c>
       <c r="AK59" t="n">
-        <v>113.99365</v>
+        <v>4.9886</v>
       </c>
       <c r="AL59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="AN59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="AO59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="AP59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>0.404069</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.404069</v>
+        <v>-3.238507</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.238507</v>
+        <v>-4.421964</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>-4.422473</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>0.288267</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>-0.052977</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>0.489642</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>1.356622</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>4.39172</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>0.619623</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>4.109608</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>-0.25</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BI59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12144,105 +11788,99 @@
         <v>0.0534</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.65</v>
+        <v>111.03587</v>
       </c>
       <c r="AJ60" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="AK60" t="n">
-        <v>109.52993</v>
+        <v>5.0569</v>
       </c>
       <c r="AL60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="AN60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="AO60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="AP60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="AQ60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
+        <v>371137</v>
       </c>
       <c r="AU60" t="n">
-        <v>371137</v>
+        <v>0.07079299999999999</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.07079299999999999</v>
+        <v>-3.915762</v>
       </c>
       <c r="AW60" t="n">
-        <v>-3.915762</v>
+        <v>1.369122</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>1.369286</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>0.565068</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>0.742264</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>0.461065</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>1.151227</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>4.724907</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>1.964454</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>4.420848</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12341,159 +11979,153 @@
         <v>0.053028</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
+      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AK61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="AL61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
+      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="n">
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
+      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
+      <c r="AW61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="AX61" t="n">
-        <v>2.367063</v>
-      </c>
-      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="inlineStr"/>
+      <c r="BB61" t="n">
+        <v>-0.964334</v>
+      </c>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
+        <v>4.641328</v>
       </c>
       <c r="BD61" t="n">
-        <v>4.641328</v>
+        <v>3.177699</v>
       </c>
       <c r="BE61" t="n">
-        <v>3.177699</v>
+        <v>4.327084</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.327084</v>
+        <v>-0.25</v>
       </c>
       <c r="BG61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176724</v>
+        <v>174042</v>
       </c>
       <c r="C62" t="n">
-        <v>173.449997</v>
+        <v>170.949997</v>
       </c>
       <c r="D62" t="n">
-        <v>106.18</v>
+        <v>105.050003</v>
       </c>
       <c r="E62" t="n">
-        <v>425.519989</v>
+        <v>425.049988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0821</v>
+        <v>5.0751</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7826</v>
+        <v>5.7816</v>
       </c>
       <c r="H62" t="n">
-        <v>7408.299805</v>
+        <v>7411.97998</v>
       </c>
       <c r="I62" t="n">
-        <v>25137.689453</v>
+        <v>24975.820312</v>
       </c>
       <c r="J62" t="n">
-        <v>51711.648438</v>
+        <v>51947.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4062.100098</v>
+        <v>4067.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>89.879997</v>
+        <v>89.30999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>92</v>
+        <v>96.779999</v>
       </c>
       <c r="N62" t="n">
-        <v>1247.5</v>
+        <v>1248</v>
       </c>
       <c r="O62" t="n">
-        <v>487</v>
+        <v>464.25</v>
       </c>
       <c r="P62" t="n">
-        <v>2.732177</v>
+        <v>1.173092</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.602777</v>
+        <v>1.123924</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.666978</v>
+        <v>-2.713466</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.325262</v>
+        <v>-2.433147</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.923798</v>
+        <v>-2.058886</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.274066</v>
+        <v>-2.290964</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.214238</v>
+        <v>-1.165165</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.10484</v>
+        <v>-4.722338</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.161239</v>
+        <v>-0.710923</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.974426</v>
+        <v>1.111144</v>
       </c>
       <c r="Z62" t="n">
-        <v>29.323737</v>
+        <v>28.503594</v>
       </c>
       <c r="AA62" t="n">
-        <v>26.165664</v>
+        <v>32.720792</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.708081</v>
+        <v>11.752854</v>
       </c>
       <c r="AC62" t="n">
-        <v>17.989098</v>
+        <v>12.477286</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12501,20 +12133,18 @@
       <c r="AE62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="AF62" t="n">
-        <v>0.052531</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AK62" t="n">
+        <v>5.0666</v>
+      </c>
       <c r="AL62" t="n">
-        <v>5.0807</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>5.0801</v>
-      </c>
+        <v>5.066</v>
+      </c>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12524,33 +12154,29 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
+      <c r="AW62" t="n">
+        <v>-2.124947</v>
+      </c>
       <c r="AX62" t="n">
-        <v>-1.852567</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>-1.852782</v>
-      </c>
+        <v>-2.125193</v>
+      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
+      <c r="BF62" t="n">
+        <v>0</v>
+      </c>
       <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,160 +578,170 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br_sa</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -804,51 +814,53 @@
         <v>0.016137</v>
       </c>
       <c r="AF2" t="n">
+        <v>0.016137</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.96</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.78</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>1.02</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>96.31464</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>5.121</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>4271865</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>1833179</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>2438686</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>2.94</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>355671</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -865,6 +877,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -961,93 +975,99 @@
         <v>0.019413</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.019413</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.87</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>0.66</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>0.88</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>97.07568000000001</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>4346060</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>1851006</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>2495054</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
         <v>0.79016</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AW3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AX3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AY3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="AZ3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BA3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="n">
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>1</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BI3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BK3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BL3" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1146,93 +1166,99 @@
         <v>0.021003</v>
       </c>
       <c r="AF4" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.16</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>96.95968999999999</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>4441056</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>1894119</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>2546936</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>2.34</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>368886</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
         <v>-0.119484</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AW4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AX4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AY4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="AZ4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BA4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="n">
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>1</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BI4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BK4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BL4" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1331,93 +1357,99 @@
         <v>0.024244</v>
       </c>
       <c r="AF5" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>0.64</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>97.48142</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>5.643</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>2.99</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>367927</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
         <v>0.53809</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AW5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AX5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AY5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AZ5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BA5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="n">
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BI5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BK5" t="n">
         <v>0</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1516,93 +1548,99 @@
         <v>0.029256</v>
       </c>
       <c r="AF6" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.95</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>0.84</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
         <v>98.97262000000001</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AK6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>367772</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
         <v>1.529727</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AW6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AX6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AY6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="AZ6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BA6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BB6" t="n">
+      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="n">
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BI6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BK6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1701,93 +1739,99 @@
         <v>0.033316</v>
       </c>
       <c r="AF7" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="AG7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>0.87</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
         <v>99.35339</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>3.05</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>362204</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
         <v>0.384723</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AW7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AX7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="AZ7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="n">
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BI7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BK7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BL7" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1886,93 +1930,99 @@
         <v>0.034749</v>
       </c>
       <c r="AF8" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.54</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>1.82</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
         <v>97.34401</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AK8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>3.26</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>358398</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
         <v>-2.022457</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AW8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AY8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BA8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
       <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="n">
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
         <v>0</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BI8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BK8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>0.21</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2071,93 +2121,99 @@
         <v>0.039598</v>
       </c>
       <c r="AF9" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
         <v>98.43725000000001</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AK9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>3.38</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>357740</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
         <v>1.123069</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AW9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AY9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BA9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="n">
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BI9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BK9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
         <v>0.12</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2256,93 +2312,99 @@
         <v>0.041954</v>
       </c>
       <c r="AF10" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>1.74</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>99.55981</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AK10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>353169</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
         <v>1.140381</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AW10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AX10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AY10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BA10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="n">
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>1</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BI10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BK10" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2441,93 +2503,99 @@
         <v>0.043739</v>
       </c>
       <c r="AF11" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1.41</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
         <v>99.51646</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AK11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>3.54</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>345097</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
         <v>-0.043542</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AW11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AX11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AY11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="AZ11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BA11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="n">
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BI11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="BJ11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BK11" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2626,93 +2694,99 @@
         <v>0.046796</v>
       </c>
       <c r="AF12" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="AG12" t="n">
         <v>0.47</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>0.45</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
         <v>99.67415</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AK12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>346415</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
         <v>0.158456</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AW12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AX12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AY12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="AZ12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BA12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
       <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="n">
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
         <v>1</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BI12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="BJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2811,99 +2885,105 @@
         <v>0.048116</v>
       </c>
       <c r="AF13" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>0.62</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
         <v>99.6343</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AK13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>5.238</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>3.57</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>341958</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
         <v>-0.03998</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AW13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AX13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AY13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="AZ13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BA13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BC13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BD13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BG13" t="n">
         <v>0.5</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BI13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3002,99 +3082,105 @@
         <v>0.049037</v>
       </c>
       <c r="AF14" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG14" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
         <v>101.27684</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AL14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AN14" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>346403</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
         <v>1.648569</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AW14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AX14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AY14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BA14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BB14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BC14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BD14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BE14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BF14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BI14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BK14" t="n">
         <v>0.08</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>0.14</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3193,99 +3279,105 @@
         <v>0.05056</v>
       </c>
       <c r="AF15" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="AG15" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
         <v>101.07328</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AK15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AL15" t="n">
         <v>5.179</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AM15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>339664</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
         <v>-0.200994</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AY15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="AZ15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BA15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BC15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BD15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BF15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BG15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BI15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="BJ15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BK15" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3384,99 +3476,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF16" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG16" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
         <v>101.17973</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AK16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AL16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
         <v>5.406</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AN16" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AO16" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>327580</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
         <v>0.10532</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AW16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AX16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AY16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="AZ16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BA16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BC16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BD16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BE16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BF16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BG16" t="n">
         <v>0</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="BH16" t="n">
-        <v>0.02</v>
-      </c>
       <c r="BI16" t="n">
-        <v>0.03</v>
+        <v>0.000228</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3575,99 +3673,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF17" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG17" t="n">
         <v>0.59</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
         <v>-0.97</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>0.47</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
         <v>101.46342</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AK17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AL17" t="n">
         <v>5.257</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AM17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AN17" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>325546</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
         <v>0.280382</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AW17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AY17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="AZ17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BA17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BC17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BD17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BE17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
         <v>6.460076</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BK17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BL17" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3766,99 +3870,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF18" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG18" t="n">
         <v>0.41</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>0.38</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
         <v>100.66227</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AK18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AL18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AN18" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AS18" t="n">
         <v>3.92</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>331505</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
         <v>-0.789595</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AW18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AY18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="AZ18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BA18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BB18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BC18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BD18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BF18" t="n">
         <v>5.974439</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3957,99 +4067,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF19" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG19" t="n">
         <v>0.62</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AI19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
         <v>100.58196</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AK19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AM19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AN19" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>3.94</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>324703</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
         <v>-0.07978200000000001</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AW19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AY19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BA19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BC19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BD19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BE19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BF19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BG19" t="n">
         <v>0</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BH19" t="n">
         <v>-0</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BI19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ19" t="n">
         <v>0</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BK19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4148,99 +4264,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF20" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG20" t="n">
         <v>0.53</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
         <v>100.05178</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AK20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AL20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AN20" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>331122</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
         <v>-0.527112</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AW20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AY20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="AZ20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BA20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BB20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BC20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BD20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BF20" t="n">
         <v>5.711379</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4339,99 +4461,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF21" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG21" t="n">
         <v>0.84</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>0.77</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
         <v>103.00964</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AK21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AL21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AM21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AN21" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AS21" t="n">
         <v>4.16</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>328098</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
         <v>2.956329</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AW21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AX21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AY21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BA21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BC21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BD21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BF21" t="n">
         <v>5.47065</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BK21" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4530,99 +4658,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF22" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG22" t="n">
         <v>0.71</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>0.64</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
         <v>103.09341</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AK22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AL22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>341158</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
         <v>0.08132200000000001</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AW22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AY22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="AZ22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BA22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BC22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BD22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BE22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BF22" t="n">
         <v>4.361088</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BK22" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4721,99 +4855,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF23" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG23" t="n">
         <v>0.61</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>0.53</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
         <v>104.1626</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AK23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>4.26</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>345725</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
         <v>1.037108</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AW23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AY23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BA23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BC23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BD23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BE23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BF23" t="n">
         <v>3.834324</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BK23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>0.15</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4912,99 +5052,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF24" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>0.36</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
         <v>102.3642</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AK24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>4.35</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>343489</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
         <v>-1.726531</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AW24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AX24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AY24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="AZ24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BA24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BB24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BC24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BD24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BF24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BG24" t="n">
         <v>0</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BH24" t="n">
         <v>-0</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BI24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BK24" t="n">
         <v>0.13</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5103,99 +5249,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF25" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG25" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>-1.93</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
         <v>102.50431</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AK25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>343620</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
         <v>0.136874</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AW25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AX25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AY25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="AZ25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BA25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BC25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BD25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BE25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BF25" t="n">
         <v>2.998957</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BK25" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5294,99 +5446,105 @@
         <v>0.050788</v>
       </c>
       <c r="AF26" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AH26" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
         <v>102.83357</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AK26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>4.22</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>345476</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
         <v>0.321216</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AW26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AY26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="AZ26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BA26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BB26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BC26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BD26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BE26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BF26" t="n">
         <v>3.527423</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BK26" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5485,99 +5643,105 @@
         <v>0.049189</v>
       </c>
       <c r="AF27" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
         <v>102.45222</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AK27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>4.12</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>344177</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
         <v>-0.370842</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AW27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AX27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AY27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AZ27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BA27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BB27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BC27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BD27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BE27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BF27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BG27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BI27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BK27" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5676,99 +5840,105 @@
         <v>0.048422</v>
       </c>
       <c r="AF28" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
         <v>102.57885</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AK28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>5.007</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>4</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>340324</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
         <v>0.123599</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AW28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AX28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="AZ28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BA28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BB28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BC28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BD28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BE28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BF28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BG28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BH28" t="n">
+      <c r="BI28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="BJ28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BK28" t="n">
         <v>0</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BL28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK28" t="n">
+      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5867,99 +6037,105 @@
         <v>0.047279</v>
       </c>
       <c r="AF29" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
         <v>102.87707</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AK29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.97</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>340247</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
         <v>0.290723</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AW29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AX29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AY29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AZ29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BA29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BB29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BC29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BD29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BE29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BF29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BG29" t="n">
         <v>0</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BH29" t="n">
+      <c r="BI29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BK29" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BL29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK29" t="n">
+      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6058,99 +6234,105 @@
         <v>0.045601</v>
       </c>
       <c r="AF30" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.28</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
         <v>103.528</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AK30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.88</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>348406</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
         <v>0.632726</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AW30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AY30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AZ30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BA30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BB30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BC30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BD30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BE30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BF30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BG30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BH30" t="n">
+      <c r="BI30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="BJ30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BK30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BL30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BK30" t="n">
+      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6249,99 +6431,105 @@
         <v>0.044537</v>
       </c>
       <c r="AF31" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>0.74</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
         <v>104.8991</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AK31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>355034</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
         <v>1.324376</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AW31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AZ31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BA31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BB31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BC31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BD31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BE31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BF31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BG31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BI31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="BJ31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BK31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BL31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BK31" t="n">
+      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6440,99 +6628,105 @@
         <v>0.043739</v>
       </c>
       <c r="AF32" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.42</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>0.57</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
         <v>104.53245</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AK32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>355066</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
         <v>-0.349526</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AW32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AX32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AY32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AZ32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BA32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BB32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BC32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BD32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BE32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BF32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BG32" t="n">
         <v>0</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BH32" t="n">
+      <c r="BI32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="BJ32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BK32" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BL32" t="n">
         <v>0.01</v>
       </c>
-      <c r="BK32" t="n">
+      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6631,99 +6825,105 @@
         <v>0.041957</v>
       </c>
       <c r="AF33" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.83</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
         <v>104.75961</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AK33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>352705</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
         <v>0.217311</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AW33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AX33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AY33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AZ33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BA33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BB33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BC33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BD33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BE33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BF33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BG33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
       <c r="BI33" t="n">
-        <v>-0.01</v>
+        <v>-0.001782</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6822,99 +7022,105 @@
         <v>0.04142</v>
       </c>
       <c r="AF34" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AH34" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
         <v>104.7097</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AK34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>355008</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
         <v>-0.047642</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AW34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AX34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AZ34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BA34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BB34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BC34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BD34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BE34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BF34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BG34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="BH34" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="BI34" t="n">
-        <v>-0.05</v>
+        <v>-0.000537</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7013,99 +7219,105 @@
         <v>0.040168</v>
       </c>
       <c r="AF35" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>0.31</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>0.37</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
         <v>104.75682</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AK35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>351599</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
         <v>0.045001</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AW35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AX35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AY35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AZ35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BA35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BB35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BC35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BD35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BE35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BF35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BG35" t="n">
         <v>0</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="BH35" t="n">
-        <v>0.04</v>
-      </c>
       <c r="BI35" t="n">
-        <v>0.05</v>
+        <v>-0.001252</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7204,99 +7416,105 @@
         <v>0.039484</v>
       </c>
       <c r="AF36" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AH36" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AI36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
         <v>105.70704</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AK36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AL36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>5.241</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AN36" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>355560</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
         <v>0.907072</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AW36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AX36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AY36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AZ36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BA36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BB36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BC36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BD36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BE36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BF36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BG36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BH36" t="n">
+      <c r="BI36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="BJ36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI36" t="n">
+      <c r="BK36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BL36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK36" t="n">
+      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7395,99 +7613,105 @@
         <v>0.03927</v>
       </c>
       <c r="AF37" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AI37" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
         <v>106.57623</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AK37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AL37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AM37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AN37" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>357827</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
         <v>0.822263</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AW37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AX37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AY37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AZ37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BA37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BB37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BC37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BD37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BE37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BF37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BG37" t="n">
         <v>0</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BH37" t="n">
+      <c r="BI37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="BJ37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BI37" t="n">
+      <c r="BK37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BL37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7586,99 +7810,105 @@
         <v>0.03927</v>
       </c>
       <c r="AF38" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AH38" t="n">
         <v>0.61</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
         <v>106.88756</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AK38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AL38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AN38" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>363282</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
         <v>0.29212</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AW38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AX38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AY38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="AZ38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BA38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BB38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BC38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BD38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BE38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="BE38" t="n">
+      <c r="BF38" t="n">
         <v>4.060953</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI38" t="n">
+      <c r="BK38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BL38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK38" t="n">
+      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7777,99 +8007,105 @@
         <v>0.03927</v>
       </c>
       <c r="AF39" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG39" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AH39" t="n">
         <v>0.29</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AI39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AJ39" t="n">
         <v>107.14396</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AK39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AM39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>369214</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
         <v>0.239878</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AW39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AY39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="AZ39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BA39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BB39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BC39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BD39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BE39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="BE39" t="n">
+      <c r="BF39" t="n">
         <v>3.707852</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI39" t="n">
+      <c r="BK39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ39" t="n">
+      <c r="BL39" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK39" t="n">
+      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7968,99 +8204,105 @@
         <v>0.039612</v>
       </c>
       <c r="AF40" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>0.62</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AJ40" t="n">
         <v>107.99916</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AK40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AL40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>3.83</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>372016</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
         <v>0.7981780000000001</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AW40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AY40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="AZ40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BA40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BB40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BC40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BD40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BE40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BF40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BG40" t="n">
         <v>0.25</v>
       </c>
-      <c r="BG40" t="n">
+      <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="BH40" t="n">
-        <v>0.01</v>
-      </c>
       <c r="BI40" t="n">
-        <v>0.01</v>
+        <v>0.000342</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8159,99 +8401,105 @@
         <v>0.040168</v>
       </c>
       <c r="AF41" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>1.52</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
         <v>108.15356</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AK41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AL41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AM41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AN41" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>3.79</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AT41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AU41" t="n">
         <v>366096</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
         <v>0.142964</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AW41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AX41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AY41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="AZ41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BA41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BB41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BC41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BD41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BE41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BF41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BG41" t="n">
         <v>0</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="BH41" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="BI41" t="n">
-        <v>-0.04</v>
+        <v>0.000556</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8350,99 +8598,105 @@
         <v>0.04158</v>
       </c>
       <c r="AF42" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AH42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AI42" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
         <v>107.98489</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AK42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AL42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AT42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AU42" t="n">
         <v>363003</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
         <v>-0.155954</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AW42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AX42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AY42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="AZ42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BA42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BB42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BC42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BD42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BE42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BF42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BG42" t="n">
         <v>0.5</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BH42" t="n">
+      <c r="BI42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="BJ42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI42" t="n">
+      <c r="BK42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BL42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BK42" t="n">
+      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8541,99 +8795,105 @@
         <v>0.044158</v>
       </c>
       <c r="AF43" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="AG43" t="n">
         <v>0.52</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AH43" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AI43" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
         <v>107.44467</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AK43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AL43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AM43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>3.63</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>329730</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
         <v>-0.500274</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AW43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AX43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AY43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="AZ43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BA43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BB43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BC43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BD43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BF43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BG43" t="n">
         <v>1</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BH43" t="n">
+      <c r="BI43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="BJ43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BK43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BL43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8732,99 +8992,105 @@
         <v>0.045833</v>
       </c>
       <c r="AF44" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
         <v>108.06979</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AK44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AL44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AM44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>328303</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
         <v>0.581806</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AW44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AX44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AY44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="AZ44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BA44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BB44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BC44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BD44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BE44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BF44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BG44" t="n">
         <v>1</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="BH44" t="n">
-        <v>0.26</v>
-      </c>
       <c r="BI44" t="n">
-        <v>0.22</v>
+        <v>0.001675</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8923,99 +9189,105 @@
         <v>0.049037</v>
       </c>
       <c r="AF45" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.31</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AH45" t="n">
         <v>1.06</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AI45" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
         <v>108.77346</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AK45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AL45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AN45" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>3.96</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AT45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AU45" t="n">
         <v>332508</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
         <v>0.651126</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AW45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AX45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AY45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="AZ45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BA45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BB45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BC45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BD45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BE45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BF45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BG45" t="n">
         <v>0</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="BH45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="BI45" t="n">
-        <v>0.09</v>
+        <v>0.003204</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9114,99 +9386,105 @@
         <v>0.050508</v>
       </c>
       <c r="AF46" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AH46" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AI46" t="n">
         <v>0.51</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
         <v>110.09056</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AK46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AL46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AM46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4.03</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AU46" t="n">
         <v>336157</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
         <v>1.210865</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AW46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AY46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="AZ46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BA46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BB46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BC46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BD46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BE46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BF46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BG46" t="n">
         <v>1</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BH46" t="n">
+      <c r="BI46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="BJ46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI46" t="n">
+      <c r="BK46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BL46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK46" t="n">
+      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9305,99 +9583,105 @@
         <v>0.052531</v>
       </c>
       <c r="AF47" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.43</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>0.24</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AJ47" t="n">
         <v>109.72323</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AK47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AL47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AM47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AN47" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AT47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AU47" t="n">
         <v>340789</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
         <v>-0.333662</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AW47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AY47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="AZ47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BA47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BB47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BC47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BD47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BE47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BF47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BG47" t="n">
         <v>0</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BH47" t="n">
+      <c r="BI47" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BK47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BL47" t="n">
         <v>0.22</v>
       </c>
-      <c r="BK47" t="n">
+      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9496,99 +9780,105 @@
         <v>0.053936</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AH48" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
         <v>0.35</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
         <v>109.00057</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AK48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AL48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AM48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>4.36</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AT48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AU48" t="n">
         <v>341459</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
         <v>-0.658621</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AW48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AX48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AY48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="AZ48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BA48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BB48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BC48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BD48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BE48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BF48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BG48" t="n">
         <v>0.5</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BH48" t="n">
+      <c r="BI48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="BJ48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BK48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BL48" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9687,99 +9977,105 @@
         <v>0.054569</v>
       </c>
       <c r="AF49" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AH49" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AJ49" t="n">
         <v>108.76683</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AK49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AM49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>4.41</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>344440</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
         <v>-0.214439</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AW49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AY49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="AZ49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BA49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BB49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BC49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BD49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BE49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BF49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BG49" t="n">
         <v>0.25</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BH49" t="n">
+      <c r="BI49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="BJ49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BK49" t="n">
         <v>0</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BL49" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9878,99 +10174,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF50" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG50" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AH50" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AI50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
         <v>108.27053</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AK50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>4.66</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>345111</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
         <v>-0.456297</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AW50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AX50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AY50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="AZ50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BA50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BB50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BC50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BD50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BE50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BF50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BG50" t="n">
         <v>0</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BH50" t="n">
+      <c r="BI50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BJ50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BK50" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BL50" t="n">
         <v>0.25</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10069,99 +10371,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF51" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG51" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AH51" t="n">
         <v>0.36</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AI51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
         <v>108.80021</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AK51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AM51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>4.92</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AT51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AU51" t="n">
         <v>350767</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
         <v>0.489219</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AW51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AX51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AY51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="AZ51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BA51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BB51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BC51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BD51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BE51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="BE51" t="n">
+      <c r="BF51" t="n">
         <v>5.054283</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BK51" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BL51" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10260,99 +10568,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF52" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG52" t="n">
         <v>0.48</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AH52" t="n">
         <v>0.42</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AI52" t="n">
         <v>0.52</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
         <v>108.63642</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AK52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AL52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AM52" t="n">
         <v>5.318</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AN52" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>4.89</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AT52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AU52" t="n">
         <v>356582</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
         <v>-0.150542</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AW52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AY52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="AZ52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BA52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BB52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BC52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BD52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BE52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="BE52" t="n">
+      <c r="BF52" t="n">
         <v>5.096104</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BI52" t="n">
+      <c r="BK52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ52" t="n">
+      <c r="BL52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK52" t="n">
+      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10451,99 +10765,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF53" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AI53" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
         <v>108.7159</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AK53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AL53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AM53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AN53" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>4.99</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AT53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AU53" t="n">
         <v>357103</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
         <v>0.073161</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AW53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AX53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AY53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="AZ53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BA53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BB53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BC53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BD53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BE53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="BE53" t="n">
+      <c r="BF53" t="n">
         <v>4.490243</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI53" t="n">
+      <c r="BK53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BL53" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK53" t="n">
+      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10642,99 +10962,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF54" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AH54" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
         <v>109.27405</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AK54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AL54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AM54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AN54" t="n">
         <v>7003273</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2616213</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>4387061</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>4.23</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.74</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AT54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AU54" t="n">
         <v>360578</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
         <v>0.513402</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AW54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AX54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AY54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AZ54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BA54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BB54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BC54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BD54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BE54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BF54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BG54" t="n">
         <v>0</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BH54" t="n">
         <v>-0</v>
       </c>
-      <c r="BH54" t="n">
+      <c r="BI54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI54" t="n">
+      <c r="BK54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BL54" t="n">
         <v>0.13</v>
       </c>
-      <c r="BK54" t="n">
+      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10833,99 +11159,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF55" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG55" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AH55" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
         <v>109.41762</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AK55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AM55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AN55" t="n">
         <v>7136436</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2701146</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>4435290</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.68</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AT55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AU55" t="n">
         <v>358234</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
         <v>0.131385</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AW55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AX55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AY55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="AZ55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BA55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BB55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BC55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BD55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="BD55" t="n">
+      <c r="BE55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="BE55" t="n">
+      <c r="BF55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI55" t="n">
+      <c r="BK55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BL55" t="n">
         <v>0</v>
       </c>
-      <c r="BK55" t="n">
+      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11024,99 +11356,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF56" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AH56" t="n">
         <v>0.41</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AI56" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
         <v>110.05486</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AK56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AM56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AN56" t="n">
         <v>7130500</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2654052</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>4476448</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>4.45</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>5.38</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AT56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AU56" t="n">
         <v>364367</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
         <v>0.582392</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AW56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AX56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AY56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="AZ56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BA56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BB56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BC56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BD56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BE56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="BE56" t="n">
+      <c r="BF56" t="n">
         <v>4.303068</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BI56" t="n">
+      <c r="BK56" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BL56" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK56" t="n">
+      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11215,99 +11553,105 @@
         <v>0.055131</v>
       </c>
       <c r="AF57" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG57" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AH57" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
         <v>110.65892</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AK57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AL57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AM57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AN57" t="n">
         <v>7156987</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2655931</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>4501056</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>5.56</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AT57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AU57" t="n">
         <v>371074</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
         <v>0.548872</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AW57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AX57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AY57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="AZ57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BA57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BB57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BC57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BD57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BE57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="BE57" t="n">
+      <c r="BF57" t="n">
         <v>3.357475</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI57" t="n">
+      <c r="BK57" t="n">
         <v>0.2</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BL57" t="n">
         <v>0.18</v>
       </c>
-      <c r="BK57" t="n">
+      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11406,99 +11750,105 @@
         <v>0.054777</v>
       </c>
       <c r="AF58" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.88</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>0.91</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
         <v>110.51078</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AK58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AL58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AM58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AN58" t="n">
         <v>7237735</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2686046</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>4551689</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>3.04</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AT58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AU58" t="n">
         <v>362002</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
         <v>-0.133871</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AW58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AX58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AY58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="AZ58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BA58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BB58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BC58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BD58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BE58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BF58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BG58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BH58" t="n">
+      <c r="BI58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="BJ58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BI58" t="n">
+      <c r="BK58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ58" t="n">
+      <c r="BL58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BK58" t="n">
+      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11597,99 +11947,105 @@
         <v>0.054223</v>
       </c>
       <c r="AF59" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>2.73</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AJ59" t="n">
         <v>110.95732</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AK59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AL59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AM59" t="n">
         <v>4.988</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AN59" t="n">
         <v>7258599</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2684623</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>4573976</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>4.63</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AT59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AU59" t="n">
         <v>366913</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
         <v>0.404069</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AW59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AX59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AY59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="AZ59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BA59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BB59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BC59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BD59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BE59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BF59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BG59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="BH59" t="n">
-        <v>0.11</v>
-      </c>
       <c r="BI59" t="n">
-        <v>0.11</v>
+        <v>-0.000554</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11788,99 +12144,105 @@
         <v>0.0534</v>
       </c>
       <c r="AF60" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AG60" t="n">
         <v>0.58</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AH60" t="n">
         <v>0.84</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>0.65</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AJ60" t="n">
         <v>111.03587</v>
       </c>
-      <c r="AJ60" t="n">
+      <c r="AK60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="AK60" t="n">
+      <c r="AL60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AM60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AN60" t="n">
         <v>7299615</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2704550</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>4595065</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>4.74</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>3.24</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>5.62</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AT60" t="n">
         <v>33.42</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AU60" t="n">
+      <c r="AV60" t="n">
         <v>0.07079299999999999</v>
       </c>
-      <c r="AV60" t="n">
+      <c r="AW60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="AW60" t="n">
+      <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AY60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="AZ60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BA60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BB60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BC60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BD60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BE60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BF60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BG60" t="n">
         <v>0</v>
       </c>
-      <c r="BG60" t="n">
+      <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="BH60" t="n">
-        <v>0.11</v>
-      </c>
       <c r="BI60" t="n">
-        <v>0.09</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -11979,72 +12341,78 @@
         <v>0.053028</v>
       </c>
       <c r="AF61" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="AG61" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AH61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH61" t="n">
+      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="n">
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
-      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="n">
         <v>367558</v>
       </c>
-      <c r="AU61" t="inlineStr"/>
       <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="n">
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AX61" t="n">
+      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="n">
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BD61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="BD61" t="n">
+      <c r="BE61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="BE61" t="n">
+      <c r="BF61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BG61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BH61" t="inlineStr"/>
-      <c r="BI61" t="inlineStr"/>
+      <c r="BI61" t="n">
+        <v>-0.000372</v>
+      </c>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>174042</v>
+        <v>176724</v>
       </c>
       <c r="C62" t="n">
         <v>170.949997</v>
@@ -12062,16 +12430,16 @@
         <v>5.7816</v>
       </c>
       <c r="H62" t="n">
-        <v>7411.97998</v>
+        <v>7408.299805</v>
       </c>
       <c r="I62" t="n">
-        <v>24975.820312</v>
+        <v>25137.689453</v>
       </c>
       <c r="J62" t="n">
-        <v>51947.25</v>
+        <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4067.600098</v>
+        <v>4070.800049</v>
       </c>
       <c r="L62" t="n">
         <v>89.30999799999999</v>
@@ -12080,13 +12448,13 @@
         <v>96.779999</v>
       </c>
       <c r="N62" t="n">
-        <v>1248</v>
+        <v>1253.5</v>
       </c>
       <c r="O62" t="n">
-        <v>464.25</v>
+        <v>487.25</v>
       </c>
       <c r="P62" t="n">
-        <v>1.173092</v>
+        <v>2.732177</v>
       </c>
       <c r="Q62" t="n">
         <v>1.123924</v>
@@ -12104,16 +12472,16 @@
         <v>-2.290964</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.165165</v>
+        <v>-1.214238</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.722338</v>
+        <v>-4.10484</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.710923</v>
+        <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.111144</v>
+        <v>1.190687</v>
       </c>
       <c r="Z62" t="n">
         <v>28.503594</v>
@@ -12122,10 +12490,10 @@
         <v>32.720792</v>
       </c>
       <c r="AB62" t="n">
-        <v>11.752854</v>
+        <v>12.245355</v>
       </c>
       <c r="AC62" t="n">
-        <v>12.477286</v>
+        <v>18.049667</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12133,18 +12501,20 @@
       <c r="AE62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
+      <c r="AF62" t="n">
+        <v>0.052531</v>
+      </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="n">
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="n">
         <v>5.0666</v>
       </c>
-      <c r="AL62" t="n">
+      <c r="AM62" t="n">
         <v>5.066</v>
       </c>
-      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12154,29 +12524,33 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="n">
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="n">
         <v>-2.124947</v>
       </c>
-      <c r="AX62" t="n">
+      <c r="AY62" t="n">
         <v>-2.125193</v>
       </c>
-      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="n">
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
         <v>0</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BH62" t="inlineStr"/>
-      <c r="BI62" t="inlineStr"/>
+      <c r="BI62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,150 +598,140 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -826,41 +816,39 @@
         <v>1.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96.31464</v>
+        <v>99.83978</v>
       </c>
       <c r="AK2" t="n">
-        <v>99.83978</v>
+        <v>5.1216</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.1216</v>
+        <v>5.121</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>4271865</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>1833179</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>2438686</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>2.36</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>1.58</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
+        <v>2.94</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -877,8 +865,6 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -987,87 +973,81 @@
         <v>0.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.07568000000001</v>
+        <v>99.32829</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.32829</v>
+        <v>5.1433</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.1433</v>
+        <v>5.1427</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>4346060</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>1851006</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>2495054</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>2.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>1.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>2.96</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>370395</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>-0.512311</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.79016</v>
+        <v>0.423696</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.512311</v>
+        <v>0.423745</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
+        <v>1.736829</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.423745</v>
+        <v>0.972464</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.736829</v>
+        <v>2.311409</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.003276</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
+        <v>0.003276</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.003276</v>
+        <v>0.01</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1178,87 +1158,81 @@
         <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.95968999999999</v>
+        <v>97.24746</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.24746</v>
+        <v>5.4394</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4394</v>
+        <v>5.4388</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>4441056</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>1894119</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>2546936</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>2.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>1.43</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>3.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>-2.094902</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.119484</v>
+        <v>5.757004</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.094902</v>
+        <v>5.757676</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
+        <v>2.185796</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.757676</v>
+        <v>2.329166</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.185796</v>
+        <v>2.079394</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
+        <v>0.001591</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001591</v>
+        <v>-0.03</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1369,87 +1343,81 @@
         <v>1.16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.48142</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.643</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.643</v>
+        <v>5.6424</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>4511956</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>1910940</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>2601017</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>2.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.43</v>
+        <v>2.99</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>-0.644377</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53809</v>
+        <v>3.74306</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.644377</v>
+        <v>3.743473</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
+        <v>1.596467</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.743473</v>
+        <v>0.888065</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.596467</v>
+        <v>2.123375</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BE5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>0.00324</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00324</v>
+        <v>-0.01</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1560,87 +1528,81 @@
         <v>0.84</v>
       </c>
       <c r="AJ6" t="n">
-        <v>98.97262000000001</v>
+        <v>98.05768</v>
       </c>
       <c r="AK6" t="n">
-        <v>98.05768</v>
+        <v>5.6199</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.6199</v>
+        <v>5.6193</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.6193</v>
+        <v>4597507</v>
       </c>
       <c r="AN6" t="n">
-        <v>4597507</v>
+        <v>1933111</v>
       </c>
       <c r="AO6" t="n">
-        <v>1933111</v>
+        <v>2664395</v>
       </c>
       <c r="AP6" t="n">
-        <v>2664395</v>
+        <v>2.36</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.36</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.46</v>
+        <v>3.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AT6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="AU6" t="n">
-        <v>367772</v>
+        <v>1.487112</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.529727</v>
+        <v>-0.409357</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.487112</v>
+        <v>-0.4094</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.409357</v>
+        <v>1.896096</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.4094</v>
+        <v>1.160214</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.896096</v>
+        <v>2.436662</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>0.005012</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1751,87 +1713,81 @@
         <v>0.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.35339</v>
+        <v>99.33126</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.33126</v>
+        <v>5.5805</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.5805</v>
+        <v>5.5799</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>4682852</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>1974391</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>2708461</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>2.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>1.298807</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.384723</v>
+        <v>-0.70108</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.298807</v>
+        <v>-0.701155</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
+        <v>1.856332</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.701155</v>
+        <v>2.135418</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.856332</v>
+        <v>1.653884</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+      <c r="BE7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
+        <v>0.00406</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00406</v>
+        <v>-0.01</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1942,87 +1898,81 @@
         <v>0.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.34401</v>
+        <v>90.45032</v>
       </c>
       <c r="AK8" t="n">
-        <v>90.45032</v>
+        <v>5.3574</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.3574</v>
+        <v>5.3568</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>4682131</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>1947035</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>2735096</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>2.51</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>1.46</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.46</v>
+        <v>3.26</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-8.94073</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.022457</v>
+        <v>-3.99785</v>
       </c>
       <c r="AW8" t="n">
-        <v>-8.94073</v>
+        <v>-3.99828</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
+        <v>-0.015397</v>
       </c>
       <c r="AY8" t="n">
-        <v>-3.99828</v>
+        <v>-1.385541</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.015397</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>0.001433</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001433</v>
+        <v>0.16</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2133,87 +2083,81 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.43725000000001</v>
+        <v>95.72214</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.72214</v>
+        <v>5.1394</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.1394</v>
+        <v>5.1388</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>4727818</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>1971524</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>2756295</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>2.57</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.44</v>
+        <v>3.38</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>5.828415</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.123069</v>
+        <v>-4.069138</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.828415</v>
+        <v>-4.069594</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
+        <v>0.975774</v>
       </c>
       <c r="AY9" t="n">
-        <v>-4.069594</v>
+        <v>1.257759</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.975774</v>
+        <v>0.775073</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
+        <v>0.004849</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004849</v>
+        <v>0.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2324,87 +2268,81 @@
         <v>1.71</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.55981</v>
+        <v>104.61484</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.61484</v>
+        <v>4.7378</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.7378</v>
+        <v>4.7372</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>4794583</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>1994119</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>2800464</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>2.66</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>9.290118</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.140381</v>
+        <v>-7.814142</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.290118</v>
+        <v>-7.815054</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
+        <v>1.412174</v>
       </c>
       <c r="AY10" t="n">
-        <v>-7.815054</v>
+        <v>1.146068</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.412174</v>
+        <v>1.602477</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+      <c r="BE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
+        <v>0.002356</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.002356</v>
+        <v>0.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2515,87 +2453,81 @@
         <v>1.04</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.51646</v>
+        <v>100.42352</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.42352</v>
+        <v>4.9191</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9191</v>
+        <v>4.9185</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>4833732</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2003312</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>2830420</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>2.72</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>3.54</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>-4.00643</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.043542</v>
+        <v>3.826671</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.00643</v>
+        <v>3.827155</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
+        <v>0.816526</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.827155</v>
+        <v>0.461006</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.816526</v>
+        <v>1.06968</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.001785</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>0.001785</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001785</v>
+        <v>0.06</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001785</v>
+        <v>0.02</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2706,87 +2638,81 @@
         <v>0.45</v>
       </c>
       <c r="AJ12" t="n">
-        <v>99.67415</v>
+        <v>99.79777</v>
       </c>
       <c r="AK12" t="n">
-        <v>99.79777</v>
+        <v>4.7289</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.7289</v>
+        <v>4.7283</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.7283</v>
+        <v>4889397</v>
       </c>
       <c r="AN12" t="n">
-        <v>4889397</v>
+        <v>2013726</v>
       </c>
       <c r="AO12" t="n">
-        <v>2013726</v>
+        <v>2875671</v>
       </c>
       <c r="AP12" t="n">
-        <v>2875671</v>
+        <v>2.79</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>27.42</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>346415</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>-0.623111</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.158456</v>
+        <v>-3.866561</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.623111</v>
+        <v>-3.867033</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
+        <v>1.151595</v>
       </c>
       <c r="AY12" t="n">
-        <v>-3.867033</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.151595</v>
+        <v>1.598738</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.598738</v>
-      </c>
-      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+      <c r="BE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.003057</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
+        <v>0.003057</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.003057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.003057</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2897,93 +2823,87 @@
         <v>0.62</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99.6343</v>
+        <v>99.53784</v>
       </c>
       <c r="AK13" t="n">
-        <v>99.53784</v>
+        <v>5.238</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.238</v>
+        <v>5.2374</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.2374</v>
+        <v>4965603</v>
       </c>
       <c r="AN13" t="n">
-        <v>4965603</v>
+        <v>2052569</v>
       </c>
       <c r="AO13" t="n">
-        <v>2052569</v>
+        <v>2913035</v>
       </c>
       <c r="AP13" t="n">
-        <v>2913035</v>
+        <v>2.73</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>3.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>27.88</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>341958</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>-0.260457</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.03998</v>
+        <v>10.765717</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.260457</v>
+        <v>10.767083</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>1.558597</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>1.928912</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>1.299314</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>-1.286607</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>11.88673</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>10.700862</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>11.919595</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>0.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>0.00132</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>0.00132</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.00132</v>
+        <v>-0.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.00132</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3094,93 +3014,87 @@
         <v>-0.6</v>
       </c>
       <c r="AJ14" t="n">
-        <v>101.27684</v>
+        <v>103.95861</v>
       </c>
       <c r="AK14" t="n">
-        <v>103.95861</v>
+        <v>5.1884</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.1884</v>
+        <v>5.1878</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.1878</v>
+        <v>4999244</v>
       </c>
       <c r="AN14" t="n">
-        <v>4999244</v>
+        <v>2047038</v>
       </c>
       <c r="AO14" t="n">
-        <v>2047038</v>
+        <v>2952207</v>
       </c>
       <c r="AP14" t="n">
-        <v>2952207</v>
+        <v>2.84</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>3.71</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>29.24</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>346403</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>4.441296</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.648569</v>
+        <v>-0.946926</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.441296</v>
+        <v>-0.947035</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>0.677481</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>-0.269467</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>1.344714</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>1.299867</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>10.069235</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>10.074751</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>10.124804</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3291,93 +3205,87 @@
         <v>-0.31</v>
       </c>
       <c r="AJ15" t="n">
-        <v>101.07328</v>
+        <v>104.56278</v>
       </c>
       <c r="AK15" t="n">
-        <v>104.56278</v>
+        <v>5.179</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.179</v>
+        <v>5.1784</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1784</v>
+        <v>5072711</v>
       </c>
       <c r="AN15" t="n">
-        <v>5072711</v>
+        <v>2064183</v>
       </c>
       <c r="AO15" t="n">
-        <v>2064183</v>
+        <v>3008528</v>
       </c>
       <c r="AP15" t="n">
-        <v>3008528</v>
+        <v>2.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>28.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>339664</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>0.581164</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.200994</v>
+        <v>-0.181173</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.581164</v>
+        <v>-0.181194</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>1.469562</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>0.837552</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>1.907759</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>-1.945422</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>8.58755</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>8.825751</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>0.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.001523</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
+        <v>0.001523</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001523</v>
+        <v>0.06</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001523</v>
+        <v>0.02</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3488,93 +3396,87 @@
         <v>-0.32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>101.17973</v>
+        <v>101.38087</v>
       </c>
       <c r="AK16" t="n">
-        <v>101.38087</v>
+        <v>5.4066</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.4066</v>
+        <v>5.406</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.406</v>
+        <v>5164775</v>
       </c>
       <c r="AN16" t="n">
-        <v>5164775</v>
+        <v>2109806</v>
       </c>
       <c r="AO16" t="n">
-        <v>2109806</v>
+        <v>3054969</v>
       </c>
       <c r="AP16" t="n">
-        <v>3054969</v>
+        <v>2.92</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.92</v>
+        <v>1.65</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>28.57</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>327580</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>-3.043062</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.10532</v>
+        <v>4.394671</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.043062</v>
+        <v>4.39518</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>1.814888</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>2.210221</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>1.543645</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>-3.557633</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>7.168596</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>7.191214</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0.000228</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>0.000228</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.000228</v>
+        <v>0.02</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.000228</v>
+        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3685,93 +3587,87 @@
         <v>0.47</v>
       </c>
       <c r="AJ17" t="n">
-        <v>101.46342</v>
+        <v>100.20398</v>
       </c>
       <c r="AK17" t="n">
-        <v>100.20398</v>
+        <v>5.257</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.257</v>
+        <v>5.2564</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.2564</v>
+        <v>5215990</v>
       </c>
       <c r="AN17" t="n">
-        <v>5215990</v>
+        <v>2105856</v>
       </c>
       <c r="AO17" t="n">
-        <v>2105856</v>
+        <v>3110134</v>
       </c>
       <c r="AP17" t="n">
-        <v>3110134</v>
+        <v>3.04</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.04</v>
+        <v>1.77</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>3.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>29.68</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>325546</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>-1.16086</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.280382</v>
+        <v>-2.766988</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.16086</v>
+        <v>-2.767296</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>0.991621</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>-0.187221</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>1.805747</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>6.470016</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>6.517038</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>6.460076</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3882,93 +3778,87 @@
         <v>0.38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.66227</v>
+        <v>99.36927</v>
       </c>
       <c r="AK18" t="n">
-        <v>99.36927</v>
+        <v>5.2941</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.2941</v>
+        <v>5.2935</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.2935</v>
+        <v>5285657</v>
       </c>
       <c r="AN18" t="n">
-        <v>5285657</v>
+        <v>2130312</v>
       </c>
       <c r="AO18" t="n">
-        <v>2130312</v>
+        <v>3155345</v>
       </c>
       <c r="AP18" t="n">
-        <v>3155345</v>
+        <v>3.07</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.07</v>
+        <v>1.81</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>3.92</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>30.52</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>331505</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.789595</v>
+        <v>0.705726</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>0.705806</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>1.335643</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>1.161333</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>1.453667</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>1.830463</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>5.900488</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>5.899363</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>5.974439</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4079,93 +3969,87 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100.58196</v>
+        <v>99.97806</v>
       </c>
       <c r="AK19" t="n">
-        <v>99.97806</v>
+        <v>5.2177</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.2177</v>
+        <v>5.2171</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.2171</v>
+        <v>5366069</v>
       </c>
       <c r="AN19" t="n">
-        <v>5366069</v>
+        <v>2178236</v>
       </c>
       <c r="AO19" t="n">
-        <v>2178236</v>
+        <v>3187833</v>
       </c>
       <c r="AP19" t="n">
-        <v>3187833</v>
+        <v>3.07</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.07</v>
+        <v>1.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>3.94</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>29.64</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>324703</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>0.612654</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>-1.443116</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.612654</v>
+        <v>-1.443279</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>1.521325</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>2.249624</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>1.029618</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>-2.051854</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>5.784842</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>5.458422</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>5.932356</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>-0</v>
       </c>
       <c r="BG19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH19" t="n">
         <v>0</v>
       </c>
-      <c r="BH19" t="n">
-        <v>-0</v>
-      </c>
       <c r="BI19" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4276,93 +4160,87 @@
         <v>0.46</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100.05178</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="AK20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0993</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.0993</v>
+        <v>5.0987</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.0987</v>
+        <v>5373231</v>
       </c>
       <c r="AN20" t="n">
-        <v>5373231</v>
+        <v>2151399</v>
       </c>
       <c r="AO20" t="n">
-        <v>2151399</v>
+        <v>3221831</v>
       </c>
       <c r="AP20" t="n">
-        <v>3221831</v>
+        <v>3.24</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.24</v>
+        <v>1.94</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.94</v>
+        <v>4.11</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>30.54</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>331122</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-6.187047</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.527112</v>
+        <v>-2.269199</v>
       </c>
       <c r="AW20" t="n">
-        <v>-6.187047</v>
+        <v>-2.26946</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>0.133468</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>-1.232052</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>1.066493</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>1.976883</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>5.77432</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>3.79089</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>5.711379</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4473,93 +4351,87 @@
         <v>0.77</v>
       </c>
       <c r="AJ21" t="n">
-        <v>103.00964</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="AK21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2078</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.2078</v>
+        <v>5.2072</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.2072</v>
+        <v>5370950</v>
       </c>
       <c r="AN21" t="n">
-        <v>5370950</v>
+        <v>2136105</v>
       </c>
       <c r="AO21" t="n">
-        <v>2136105</v>
+        <v>3234845</v>
       </c>
       <c r="AP21" t="n">
-        <v>3234845</v>
+        <v>3.36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.36</v>
+        <v>2.17</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>4.16</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>30.48</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>328098</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>5.286443</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.956329</v>
+        <v>2.127743</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.286443</v>
+        <v>2.127993</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>-0.042451</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>-0.710886</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>0.403932</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>-0.913259</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>5.596302</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>1.864495</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>5.47065</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BI21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="BJ21" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4670,93 +4542,87 @@
         <v>0.64</v>
       </c>
       <c r="AJ22" t="n">
-        <v>103.09341</v>
+        <v>110.62354</v>
       </c>
       <c r="AK22" t="n">
-        <v>110.62354</v>
+        <v>5.0804</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.0804</v>
+        <v>5.0798</v>
       </c>
       <c r="AM22" t="n">
-        <v>5.0798</v>
+        <v>5424811</v>
       </c>
       <c r="AN22" t="n">
-        <v>5424811</v>
+        <v>2154900</v>
       </c>
       <c r="AO22" t="n">
-        <v>2154900</v>
+        <v>3269910</v>
       </c>
       <c r="AP22" t="n">
-        <v>3269910</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>4.11</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>30.99</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>341158</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>12.023101</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.08132200000000001</v>
+        <v>-2.446331</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.023101</v>
+        <v>-2.446612</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>1.002821</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>0.879872</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>1.083978</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>3.980518</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>4.650694</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>0.172427</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>4.361088</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="BI22" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ22" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4867,93 +4733,87 @@
         <v>0.53</v>
       </c>
       <c r="AJ23" t="n">
-        <v>104.1626</v>
+        <v>104.34152</v>
       </c>
       <c r="AK23" t="n">
-        <v>104.34152</v>
+        <v>5.0007</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.0007</v>
+        <v>5.0001</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.0001</v>
+        <v>5426307</v>
       </c>
       <c r="AN23" t="n">
-        <v>5426307</v>
+        <v>2145000</v>
       </c>
       <c r="AO23" t="n">
-        <v>2145000</v>
+        <v>3281308</v>
       </c>
       <c r="AP23" t="n">
-        <v>3281308</v>
+        <v>3.54</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.54</v>
+        <v>2.45</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>31.62</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>345725</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>-5.678737</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.037108</v>
+        <v>-1.568774</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.678737</v>
+        <v>-1.568959</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>0.027577</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>-0.459418</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>0.348572</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>1.338676</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>4.184706</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>-2.158772</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>3.834324</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI23" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BJ23" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5064,93 +4924,87 @@
         <v>0.36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>102.3642</v>
+        <v>102.66392</v>
       </c>
       <c r="AK24" t="n">
-        <v>102.66392</v>
+        <v>5.0959</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.0959</v>
+        <v>5.0953</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.0953</v>
+        <v>5453708</v>
       </c>
       <c r="AN24" t="n">
-        <v>5453708</v>
+        <v>2145530</v>
       </c>
       <c r="AO24" t="n">
-        <v>2145530</v>
+        <v>3308178</v>
       </c>
       <c r="AP24" t="n">
-        <v>3308178</v>
+        <v>3.65</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.58</v>
+        <v>4.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>31.63</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>343489</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>-1.607797</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.726531</v>
+        <v>1.903733</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.607797</v>
+        <v>1.903962</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>0.504966</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>0.024709</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>0.818881</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>-0.646757</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>3.935832</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>-4.45588</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>3.741292</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>-0</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH24" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="BI24" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="BJ24" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5261,93 +5115,87 @@
         <v>-0.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>102.50431</v>
+        <v>102.53174</v>
       </c>
       <c r="AK25" t="n">
-        <v>102.53174</v>
+        <v>4.8192</v>
       </c>
       <c r="AL25" t="n">
-        <v>4.8192</v>
+        <v>4.8186</v>
       </c>
       <c r="AM25" t="n">
-        <v>4.8186</v>
+        <v>5479459</v>
       </c>
       <c r="AN25" t="n">
-        <v>5479459</v>
+        <v>2169613</v>
       </c>
       <c r="AO25" t="n">
-        <v>2169613</v>
+        <v>3309846</v>
       </c>
       <c r="AP25" t="n">
-        <v>3309846</v>
+        <v>3.61</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.61</v>
+        <v>2.63</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.63</v>
+        <v>4.25</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.25</v>
+        <v>30.85</v>
       </c>
       <c r="AT25" t="n">
-        <v>30.85</v>
+        <v>343620</v>
       </c>
       <c r="AU25" t="n">
-        <v>343620</v>
+        <v>-0.12875</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.136874</v>
+        <v>-5.429855</v>
       </c>
       <c r="AW25" t="n">
-        <v>-0.12875</v>
+        <v>-5.430495</v>
       </c>
       <c r="AX25" t="n">
-        <v>-5.429855</v>
+        <v>0.472174</v>
       </c>
       <c r="AY25" t="n">
-        <v>-5.430495</v>
+        <v>1.122473</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.472174</v>
+        <v>0.050421</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.122473</v>
+        <v>0.038138</v>
       </c>
       <c r="BB25" t="n">
-        <v>0.050421</v>
+        <v>3.161501</v>
       </c>
       <c r="BC25" t="n">
-        <v>0.038138</v>
+        <v>-6.84947</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.161501</v>
+        <v>2.998957</v>
       </c>
       <c r="BE25" t="n">
-        <v>-6.84947</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.998957</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="BI25" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ25" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5458,93 +5306,87 @@
         <v>-0.09</v>
       </c>
       <c r="AJ26" t="n">
-        <v>102.83357</v>
+        <v>105.47522</v>
       </c>
       <c r="AK26" t="n">
-        <v>105.47522</v>
+        <v>4.7415</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.7415</v>
+        <v>4.7409</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.7409</v>
+        <v>5484871</v>
       </c>
       <c r="AN26" t="n">
-        <v>5484871</v>
+        <v>2153541</v>
       </c>
       <c r="AO26" t="n">
-        <v>2153541</v>
+        <v>3331330</v>
       </c>
       <c r="AP26" t="n">
-        <v>3331330</v>
+        <v>3.63</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.73</v>
+        <v>4.22</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>30.43</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>345476</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>2.870799</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.321216</v>
+        <v>-1.612301</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.870799</v>
+        <v>-1.612502</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>0.098769</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>-0.740777</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>0.6490939999999999</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>3.992444</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>-7.713954</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>3.527423</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BI26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5655,93 +5497,87 @@
         <v>0.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>102.45222</v>
+        <v>106.13139</v>
       </c>
       <c r="AK27" t="n">
-        <v>106.13139</v>
+        <v>4.9219</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.9219</v>
+        <v>4.9213</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.9213</v>
+        <v>5559063</v>
       </c>
       <c r="AN27" t="n">
-        <v>5559063</v>
+        <v>2172658</v>
       </c>
       <c r="AO27" t="n">
-        <v>2172658</v>
+        <v>3386405</v>
       </c>
       <c r="AP27" t="n">
-        <v>3386405</v>
+        <v>3.61</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.61</v>
+        <v>2.82</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.82</v>
+        <v>4.12</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>29.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>344177</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>0.622108</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.370842</v>
+        <v>3.804703</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.622108</v>
+        <v>3.805185</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>1.352666</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>0.887701</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>1.653244</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>-0.376003</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>4.608216</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>-7.193509</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>4.057054</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>-0.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.001599</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
+        <v>-0.001599</v>
       </c>
       <c r="BH27" t="n">
-        <v>-0.001599</v>
+        <v>-0.02</v>
       </c>
       <c r="BI27" t="n">
-        <v>-0.001599</v>
+        <v>0.09</v>
       </c>
       <c r="BJ27" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5852,93 +5688,87 @@
         <v>0.11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>102.57885</v>
+        <v>102.00419</v>
       </c>
       <c r="AK28" t="n">
-        <v>102.00419</v>
+        <v>5.0076</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.0076</v>
+        <v>5.007</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.007</v>
+        <v>5625945</v>
       </c>
       <c r="AN28" t="n">
-        <v>5625945</v>
+        <v>2215175</v>
       </c>
       <c r="AO28" t="n">
-        <v>2215175</v>
+        <v>3410769</v>
       </c>
       <c r="AP28" t="n">
-        <v>3410769</v>
+        <v>3.54</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.54</v>
+        <v>2.82</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>29.66</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>340324</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>-3.888765</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.123599</v>
+        <v>1.741198</v>
       </c>
       <c r="AW28" t="n">
-        <v>-3.888765</v>
+        <v>1.74141</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>1.203116</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>1.956912</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>0.719465</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>-1.119482</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>5.185235</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>-5.956714</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>4.505936</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>-0.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.000768</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
+        <v>-0.000768</v>
       </c>
       <c r="BH28" t="n">
-        <v>-0.000768</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BI28" t="n">
-        <v>-0.000768</v>
+        <v>0</v>
       </c>
       <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6049,93 +5879,87 @@
         <v>0.12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>102.87707</v>
+        <v>102.0744</v>
       </c>
       <c r="AK29" t="n">
-        <v>102.0744</v>
+        <v>5.0575</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.0575</v>
+        <v>5.0569</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.0569</v>
+        <v>5653808</v>
       </c>
       <c r="AN29" t="n">
-        <v>5653808</v>
+        <v>2204808</v>
       </c>
       <c r="AO29" t="n">
-        <v>2204808</v>
+        <v>3449000</v>
       </c>
       <c r="AP29" t="n">
-        <v>3449000</v>
+        <v>3.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.56</v>
+        <v>2.92</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.92</v>
+        <v>3.97</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>29.24</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>340247</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.068831</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.290723</v>
+        <v>0.996485</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.068831</v>
+        <v>0.996605</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>0.495259</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>-0.467999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>1.120891</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>-0.022625</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>4.819246</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>-4.560737</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>4.141877</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>-0.001143</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>-0.001143</v>
       </c>
       <c r="BH29" t="n">
-        <v>-0.001143</v>
+        <v>0.02</v>
       </c>
       <c r="BI29" t="n">
-        <v>-0.001143</v>
+        <v>0.1</v>
       </c>
       <c r="BJ29" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6246,93 +6070,87 @@
         <v>0.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>103.528</v>
+        <v>101.86494</v>
       </c>
       <c r="AK30" t="n">
-        <v>101.86494</v>
+        <v>4.9355</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.9355</v>
+        <v>4.9349</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.9349</v>
+        <v>5711103</v>
       </c>
       <c r="AN30" t="n">
-        <v>5711103</v>
+        <v>2220766</v>
       </c>
       <c r="AO30" t="n">
-        <v>2220766</v>
+        <v>3490337</v>
       </c>
       <c r="AP30" t="n">
-        <v>3490337</v>
+        <v>3.53</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.53</v>
+        <v>2.99</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>29.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>348406</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>-0.205203</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.632726</v>
+        <v>-2.412259</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.205203</v>
+        <v>-2.412545</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>1.013388</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>0.723782</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>1.198521</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>2.397964</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>4.683537</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>-3.457004</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>3.851383</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>-0.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.001678</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
+        <v>-0.001678</v>
       </c>
       <c r="BH30" t="n">
-        <v>-0.001678</v>
+        <v>-0.03</v>
       </c>
       <c r="BI30" t="n">
-        <v>-0.001678</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BJ30" t="n">
-        <v>-0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6443,93 +6261,87 @@
         <v>0.55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>104.8991</v>
+        <v>101.74606</v>
       </c>
       <c r="AK31" t="n">
-        <v>101.74606</v>
+        <v>4.8413</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.8413</v>
+        <v>4.8407</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.8407</v>
+        <v>5805157</v>
       </c>
       <c r="AN31" t="n">
-        <v>5805157</v>
+        <v>2283485</v>
       </c>
       <c r="AO31" t="n">
-        <v>2283485</v>
+        <v>3521672</v>
       </c>
       <c r="AP31" t="n">
-        <v>3521672</v>
+        <v>3.29</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.29</v>
+        <v>2.59</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>28.14</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>355034</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>-0.116704</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.324376</v>
+        <v>-1.908621</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.116704</v>
+        <v>-1.908853</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>1.646862</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>2.824206</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>0.897764</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>1.902378</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>4.621114</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>-3.178284</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>3.706988</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>-0.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.001064</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
+        <v>-0.001064</v>
       </c>
       <c r="BH31" t="n">
-        <v>-0.001064</v>
+        <v>-0.24</v>
       </c>
       <c r="BI31" t="n">
-        <v>-0.001064</v>
+        <v>-0.4</v>
       </c>
       <c r="BJ31" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6640,93 +6452,87 @@
         <v>0.57</v>
       </c>
       <c r="AJ32" t="n">
-        <v>104.53245</v>
+        <v>98.01879</v>
       </c>
       <c r="AK32" t="n">
-        <v>98.01879</v>
+        <v>4.9535</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.9535</v>
+        <v>4.9529</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.9529</v>
+        <v>5794707</v>
       </c>
       <c r="AN32" t="n">
-        <v>5794707</v>
+        <v>2234362</v>
       </c>
       <c r="AO32" t="n">
-        <v>2234362</v>
+        <v>3560345</v>
       </c>
       <c r="AP32" t="n">
-        <v>3560345</v>
+        <v>3.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.38</v>
+        <v>2.77</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.77</v>
+        <v>3.76</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>28</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>355066</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>-3.663306</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.349526</v>
+        <v>2.317559</v>
       </c>
       <c r="AW32" t="n">
-        <v>-3.663306</v>
+        <v>2.317847</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>-0.180012</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>-2.151229</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>1.098143</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>0.009013</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>4.506637</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>-3.31355</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>3.820543</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>-0.000798</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>-0.000798</v>
       </c>
       <c r="BH32" t="n">
-        <v>-0.000798</v>
+        <v>0.09</v>
       </c>
       <c r="BI32" t="n">
-        <v>-0.000798</v>
+        <v>0.18</v>
       </c>
       <c r="BJ32" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6837,93 +6643,87 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ33" t="n">
-        <v>104.75961</v>
+        <v>102.37988</v>
       </c>
       <c r="AK33" t="n">
-        <v>102.37988</v>
+        <v>4.9833</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.9833</v>
+        <v>4.9827</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.9827</v>
+        <v>5815954</v>
       </c>
       <c r="AN33" t="n">
-        <v>5815954</v>
+        <v>2235302</v>
       </c>
       <c r="AO33" t="n">
-        <v>2235302</v>
+        <v>3580652</v>
       </c>
       <c r="AP33" t="n">
-        <v>3580652</v>
+        <v>3.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.76</v>
+        <v>3.76</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>27.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>352705</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>4.449239</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.217311</v>
+        <v>0.601595</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.449239</v>
+        <v>0.601668</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>0.366662</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>0.04207</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>0.570366</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>-0.664947</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>4.496274</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>-3.758575</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>3.861754</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>-0.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>-0.001782</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
+        <v>-0.001782</v>
       </c>
       <c r="BH33" t="n">
-        <v>-0.001782</v>
+        <v>0</v>
       </c>
       <c r="BI33" t="n">
-        <v>-0.001782</v>
+        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7034,93 +6834,87 @@
         <v>0.19</v>
       </c>
       <c r="AJ34" t="n">
-        <v>104.7097</v>
+        <v>109.58504</v>
       </c>
       <c r="AK34" t="n">
-        <v>109.58504</v>
+        <v>4.9962</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.9962</v>
+        <v>4.9956</v>
       </c>
       <c r="AM34" t="n">
-        <v>4.9956</v>
+        <v>5899742</v>
       </c>
       <c r="AN34" t="n">
-        <v>5899742</v>
+        <v>2285775</v>
       </c>
       <c r="AO34" t="n">
-        <v>2285775</v>
+        <v>3613967</v>
       </c>
       <c r="AP34" t="n">
-        <v>3613967</v>
+        <v>3.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.71</v>
+        <v>3.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>28.14</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>355008</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>7.037672</v>
       </c>
       <c r="AV34" t="n">
-        <v>-0.047642</v>
+        <v>0.258865</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.037672</v>
+        <v>0.258896</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>1.440658</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>2.257995</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>0.930417</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>0.652954</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>3.925596</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>-4.25878</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>3.397348</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>-0.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.000537</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
+        <v>-0.000537</v>
       </c>
       <c r="BH34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BI34" t="n">
-        <v>-0.000537</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7231,93 +7025,87 @@
         <v>0.37</v>
       </c>
       <c r="AJ35" t="n">
-        <v>104.75682</v>
+        <v>109.36335</v>
       </c>
       <c r="AK35" t="n">
-        <v>109.36335</v>
+        <v>5.1718</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.1718</v>
+        <v>5.1712</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.1712</v>
+        <v>5915538</v>
       </c>
       <c r="AN35" t="n">
-        <v>5915538</v>
+        <v>2268879</v>
       </c>
       <c r="AO35" t="n">
-        <v>2268879</v>
+        <v>3646659</v>
       </c>
       <c r="AP35" t="n">
-        <v>3646659</v>
+        <v>3.37</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.37</v>
+        <v>2.76</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>27.86</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>351599</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>-0.2023</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.045001</v>
+        <v>3.514671</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.2023</v>
+        <v>3.515093</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>0.267741</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>0.904602</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>-0.96026</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>3.688016</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>-3.040871</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>3.232784</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>-0.001252</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>-0.001252</v>
       </c>
       <c r="BH35" t="n">
-        <v>-0.001252</v>
+        <v>0.04</v>
       </c>
       <c r="BI35" t="n">
-        <v>-0.001252</v>
+        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7428,93 +7216,87 @@
         <v>0.46</v>
       </c>
       <c r="AJ36" t="n">
-        <v>105.70704</v>
+        <v>104.84682</v>
       </c>
       <c r="AK36" t="n">
-        <v>104.84682</v>
+        <v>5.2416</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.2416</v>
+        <v>5.241</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.241</v>
+        <v>5953960</v>
       </c>
       <c r="AN36" t="n">
-        <v>5953960</v>
+        <v>2278309</v>
       </c>
       <c r="AO36" t="n">
-        <v>2278309</v>
+        <v>3675652</v>
       </c>
       <c r="AP36" t="n">
-        <v>3675652</v>
+        <v>3.43</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.43</v>
+        <v>2.8</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>27.75</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>355560</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>-4.129839</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.907072</v>
+        <v>1.349627</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.129839</v>
+        <v>1.349783</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>0.64951</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>0.415624</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>0.795057</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>1.126567</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>3.925952</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>-0.344269</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>3.335647</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>-0.25</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>-0.000684</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
+        <v>-0.000684</v>
       </c>
       <c r="BH36" t="n">
-        <v>-0.000684</v>
+        <v>0.06</v>
       </c>
       <c r="BI36" t="n">
-        <v>-0.000684</v>
+        <v>0.04</v>
       </c>
       <c r="BJ36" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7625,93 +7407,87 @@
         <v>0.25</v>
       </c>
       <c r="AJ37" t="n">
-        <v>106.57623</v>
+        <v>106.03093</v>
       </c>
       <c r="AK37" t="n">
-        <v>106.03093</v>
+        <v>5.5589</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.5589</v>
+        <v>5.5583</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.5583</v>
+        <v>6041898</v>
       </c>
       <c r="AN37" t="n">
-        <v>6041898</v>
+        <v>2336858</v>
       </c>
       <c r="AO37" t="n">
-        <v>2336858</v>
+        <v>3705041</v>
       </c>
       <c r="AP37" t="n">
-        <v>3705041</v>
+        <v>3.29</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.29</v>
+        <v>2.64</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.64</v>
+        <v>3.71</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>27.81</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>357827</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>1.129371</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.822263</v>
+        <v>6.053495</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.129371</v>
+        <v>6.054188</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>1.476967</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>2.569845</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>0.799559</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>0.637586</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>4.227578</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>2.440035</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>3.697684</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>-0.000214</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>-0.000214</v>
       </c>
       <c r="BH37" t="n">
-        <v>-0.000214</v>
+        <v>-0.14</v>
       </c>
       <c r="BI37" t="n">
-        <v>-0.000214</v>
+        <v>-0.16</v>
       </c>
       <c r="BJ37" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7822,93 +7598,87 @@
         <v>0.26</v>
       </c>
       <c r="AJ38" t="n">
-        <v>106.88756</v>
+        <v>111.55002</v>
       </c>
       <c r="AK38" t="n">
-        <v>111.55002</v>
+        <v>5.6621</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.6621</v>
+        <v>5.6615</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.6615</v>
+        <v>6069205</v>
       </c>
       <c r="AN38" t="n">
-        <v>6069205</v>
+        <v>2323362</v>
       </c>
       <c r="AO38" t="n">
-        <v>2323362</v>
+        <v>3745844</v>
       </c>
       <c r="AP38" t="n">
-        <v>3745844</v>
+        <v>3.3</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.52</v>
+        <v>3.78</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>27.74</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>363282</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>5.20517</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.29212</v>
+        <v>1.856482</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.20517</v>
+        <v>1.856683</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>0.451961</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>-0.577528</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>1.101283</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>1.52448</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>4.498245</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>3.812368</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>4.060953</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BI38" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="BJ38" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8019,93 +7789,87 @@
         <v>-0.14</v>
       </c>
       <c r="AJ39" t="n">
-        <v>107.14396</v>
+        <v>110.19363</v>
       </c>
       <c r="AK39" t="n">
-        <v>110.19363</v>
+        <v>5.6562</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.6562</v>
+        <v>5.6556</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.6556</v>
+        <v>6135298</v>
       </c>
       <c r="AN39" t="n">
-        <v>6135298</v>
+        <v>2344397</v>
       </c>
       <c r="AO39" t="n">
-        <v>2344397</v>
+        <v>3790900</v>
       </c>
       <c r="AP39" t="n">
-        <v>3790900</v>
+        <v>3.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.33</v>
+        <v>2.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>27.59</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>369214</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>-1.215948</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.239878</v>
+        <v>-0.104202</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.215948</v>
+        <v>-0.104213</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>1.088989</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>0.905369</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>1.202826</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>1.632891</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>4.237599</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>4.259387</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>3.707852</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BI39" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BJ39" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8216,93 +7980,87 @@
         <v>0.48</v>
       </c>
       <c r="AJ40" t="n">
-        <v>107.99916</v>
+        <v>107.28836</v>
       </c>
       <c r="AK40" t="n">
-        <v>107.28836</v>
+        <v>5.4481</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.4481</v>
+        <v>5.4475</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.4475</v>
+        <v>6216528</v>
       </c>
       <c r="AN40" t="n">
-        <v>6216528</v>
+        <v>2384828</v>
       </c>
       <c r="AO40" t="n">
-        <v>2384828</v>
+        <v>3831700</v>
       </c>
       <c r="AP40" t="n">
-        <v>3831700</v>
+        <v>3.34</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.34</v>
+        <v>2.56</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.56</v>
+        <v>3.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>27.49</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>372016</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>-2.636514</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.7981780000000001</v>
+        <v>-3.679149</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.636514</v>
+        <v>-3.679539</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>1.323978</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>1.72458</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>1.076262</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>4.42474</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>4.519075</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>4.091149</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>0.25</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.000342</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
+        <v>0.000342</v>
       </c>
       <c r="BH40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BI40" t="n">
-        <v>0.000342</v>
+        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8413,93 +8171,87 @@
         <v>0.61</v>
       </c>
       <c r="AJ41" t="n">
-        <v>108.15356</v>
+        <v>109.21678</v>
       </c>
       <c r="AK41" t="n">
-        <v>109.21678</v>
+        <v>5.7779</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.7779</v>
+        <v>5.7773</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.7773</v>
+        <v>6275117</v>
       </c>
       <c r="AN41" t="n">
-        <v>6275117</v>
+        <v>2397533</v>
       </c>
       <c r="AO41" t="n">
-        <v>2397533</v>
+        <v>3877584</v>
       </c>
       <c r="AP41" t="n">
-        <v>3877584</v>
+        <v>3.3</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.52</v>
+        <v>3.79</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>27.94</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>366096</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>1.797418</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.142964</v>
+        <v>6.053487</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.797418</v>
+        <v>6.054153</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>0.532743</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>1.197484</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>-1.591329</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>4.758099</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>5.579866</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>4.600584</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>0.000556</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
+        <v>0.000556</v>
       </c>
       <c r="BH41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BI41" t="n">
-        <v>0.000556</v>
+        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8610,93 +8362,87 @@
         <v>0.33</v>
       </c>
       <c r="AJ42" t="n">
-        <v>107.98489</v>
+        <v>105.74688</v>
       </c>
       <c r="AK42" t="n">
-        <v>105.74688</v>
+        <v>6.0535</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.0535</v>
+        <v>6.0529</v>
       </c>
       <c r="AM42" t="n">
-        <v>6.0529</v>
+        <v>6365690</v>
       </c>
       <c r="AN42" t="n">
-        <v>6365690</v>
+        <v>2436022</v>
       </c>
       <c r="AO42" t="n">
-        <v>2436022</v>
+        <v>3929668</v>
       </c>
       <c r="AP42" t="n">
-        <v>3929668</v>
+        <v>3.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>28.45</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>363003</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>-3.177076</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.155954</v>
+        <v>4.769899</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.177076</v>
+        <v>4.770394</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>1.443368</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>1.605359</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>1.343208</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>4.873011</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>6.325086</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>4.840925</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>0.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>0.001412</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
+        <v>0.001412</v>
       </c>
       <c r="BH42" t="n">
-        <v>0.001412</v>
+        <v>-0.03</v>
       </c>
       <c r="BI42" t="n">
-        <v>0.001412</v>
+        <v>-0.02</v>
       </c>
       <c r="BJ42" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8807,93 +8553,87 @@
         <v>0.48</v>
       </c>
       <c r="AJ43" t="n">
-        <v>107.44467</v>
+        <v>104.2734</v>
       </c>
       <c r="AK43" t="n">
-        <v>104.2734</v>
+        <v>6.1923</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.1923</v>
+        <v>6.1917</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.1917</v>
+        <v>6464602</v>
       </c>
       <c r="AN43" t="n">
-        <v>6464602</v>
+        <v>2499177</v>
       </c>
       <c r="AO43" t="n">
-        <v>2499177</v>
+        <v>3965425</v>
       </c>
       <c r="AP43" t="n">
-        <v>3965425</v>
+        <v>3.08</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.21</v>
+        <v>3.63</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>28.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>329730</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>-1.393403</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.500274</v>
+        <v>2.292888</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.393403</v>
+        <v>2.293116</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>1.55383</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>2.592546</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>0.909924</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>4.831296</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>6.536174</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>4.767938</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>1</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>0.002578</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
+        <v>0.002578</v>
       </c>
       <c r="BH43" t="n">
-        <v>0.002578</v>
+        <v>-0.19</v>
       </c>
       <c r="BI43" t="n">
-        <v>0.002578</v>
+        <v>-0.29</v>
       </c>
       <c r="BJ43" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -9004,93 +8744,87 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>108.06979</v>
+        <v>101.23438</v>
       </c>
       <c r="AK44" t="n">
-        <v>101.23438</v>
+        <v>5.8301</v>
       </c>
       <c r="AL44" t="n">
-        <v>5.8301</v>
+        <v>5.8295</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.8295</v>
+        <v>6465016</v>
       </c>
       <c r="AN44" t="n">
-        <v>6465016</v>
+        <v>2451957</v>
       </c>
       <c r="AO44" t="n">
-        <v>2451957</v>
+        <v>4013059</v>
       </c>
       <c r="AP44" t="n">
-        <v>4013059</v>
+        <v>3.34</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.34</v>
+        <v>2.43</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>29.88</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>328303</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>-2.914473</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.581806</v>
+        <v>-5.8492</v>
       </c>
       <c r="AW44" t="n">
-        <v>-2.914473</v>
+        <v>-5.849767</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>0.006404</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>-1.889422</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>1.201233</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>-0.432778</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>4.559874</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>6.749097</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>4.174145</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>1</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>0.001675</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
+        <v>0.001675</v>
       </c>
       <c r="BH44" t="n">
-        <v>0.001675</v>
+        <v>0.26</v>
       </c>
       <c r="BI44" t="n">
-        <v>0.001675</v>
+        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9201,93 +8935,87 @@
         <v>1.48</v>
       </c>
       <c r="AJ45" t="n">
-        <v>108.77346</v>
+        <v>107.07838</v>
       </c>
       <c r="AK45" t="n">
-        <v>107.07838</v>
+        <v>5.8488</v>
       </c>
       <c r="AL45" t="n">
-        <v>5.8488</v>
+        <v>5.8482</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.8482</v>
+        <v>6511444</v>
       </c>
       <c r="AN45" t="n">
-        <v>6511444</v>
+        <v>2477151</v>
       </c>
       <c r="AO45" t="n">
-        <v>2477151</v>
+        <v>4034293</v>
       </c>
       <c r="AP45" t="n">
-        <v>4034293</v>
+        <v>3.41</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.41</v>
+        <v>2.52</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.52</v>
+        <v>3.96</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>30.53</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>332508</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>5.772742</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.651126</v>
+        <v>0.320749</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.772742</v>
+        <v>0.320782</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>1.027506</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>0.529123</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>1.280829</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>5.05763</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>8.444549</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>4.866504</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0.003204</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
+        <v>0.003204</v>
       </c>
       <c r="BH45" t="n">
-        <v>0.003204</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI45" t="n">
-        <v>0.003204</v>
+        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9398,93 +9126,87 @@
         <v>0.51</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110.09056</v>
+        <v>114.05013</v>
       </c>
       <c r="AK46" t="n">
-        <v>114.05013</v>
+        <v>5.7422</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.7422</v>
+        <v>5.7416</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.7416</v>
+        <v>6576464</v>
       </c>
       <c r="AN46" t="n">
-        <v>6576464</v>
+        <v>2498262</v>
       </c>
       <c r="AO46" t="n">
-        <v>2498262</v>
+        <v>4078202</v>
       </c>
       <c r="AP46" t="n">
-        <v>4078202</v>
+        <v>3.44</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.44</v>
+        <v>2.49</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.49</v>
+        <v>4.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>31.34</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>336157</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>6.510885</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.210865</v>
+        <v>-1.822596</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.510885</v>
+        <v>-1.822783</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>0.99855</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>0.852229</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>1.088394</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>1.097417</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>5.47719</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>8.586193</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>5.201441</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>1</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>0.001471</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
+        <v>0.001471</v>
       </c>
       <c r="BH46" t="n">
-        <v>0.001471</v>
+        <v>0.03</v>
       </c>
       <c r="BI46" t="n">
-        <v>0.001471</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ46" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9595,93 +9317,87 @@
         <v>0.48</v>
       </c>
       <c r="AJ47" t="n">
-        <v>109.72323</v>
+        <v>112.73813</v>
       </c>
       <c r="AK47" t="n">
-        <v>112.73813</v>
+        <v>5.6608</v>
       </c>
       <c r="AL47" t="n">
-        <v>5.6608</v>
+        <v>5.6602</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.6602</v>
+        <v>6623948</v>
       </c>
       <c r="AN47" t="n">
-        <v>6623948</v>
+        <v>2512426</v>
       </c>
       <c r="AO47" t="n">
-        <v>2512426</v>
+        <v>4111522</v>
       </c>
       <c r="AP47" t="n">
-        <v>4111522</v>
+        <v>3.67</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.67</v>
+        <v>2.72</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.72</v>
+        <v>4.25</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>31.63</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>340789</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-1.150371</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.333662</v>
+        <v>-1.417575</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.150371</v>
+        <v>-1.417723</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>0.722029</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>0.566954</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>0.8170269999999999</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>1.377928</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>5.529729</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>8.510418</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>5.316736</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0.002023</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="BH47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BI47" t="n">
-        <v>0.002023</v>
+        <v>0.23</v>
       </c>
       <c r="BJ47" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9792,93 +9508,87 @@
         <v>0.35</v>
       </c>
       <c r="AJ48" t="n">
-        <v>109.00057</v>
+        <v>108.66481</v>
       </c>
       <c r="AK48" t="n">
-        <v>108.66481</v>
+        <v>5.7087</v>
       </c>
       <c r="AL48" t="n">
-        <v>5.7087</v>
+        <v>5.7081</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.7081</v>
+        <v>6666287</v>
       </c>
       <c r="AN48" t="n">
-        <v>6666287</v>
+        <v>2532708</v>
       </c>
       <c r="AO48" t="n">
-        <v>2532708</v>
+        <v>4133579</v>
       </c>
       <c r="AP48" t="n">
-        <v>4133579</v>
+        <v>3.72</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.72</v>
+        <v>2.67</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.67</v>
+        <v>4.36</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>31.7</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>341459</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>-3.613081</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.658621</v>
+        <v>0.84617</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.613081</v>
+        <v>0.84626</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.639181</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>0.807268</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>0.5364679999999999</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>0.196603</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>5.319636</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>7.026183</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>5.201418</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>0.5</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.001405</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
+        <v>0.001405</v>
       </c>
       <c r="BH48" t="n">
-        <v>0.001405</v>
+        <v>0.05</v>
       </c>
       <c r="BI48" t="n">
-        <v>0.001405</v>
+        <v>-0.05</v>
       </c>
       <c r="BJ48" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9989,93 +9699,87 @@
         <v>0.23</v>
       </c>
       <c r="AJ49" t="n">
-        <v>108.76683</v>
+        <v>107.55639</v>
       </c>
       <c r="AK49" t="n">
-        <v>107.55639</v>
+        <v>5.4571</v>
       </c>
       <c r="AL49" t="n">
-        <v>5.4571</v>
+        <v>5.4565</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.4565</v>
+        <v>6703663</v>
       </c>
       <c r="AN49" t="n">
-        <v>6703663</v>
+        <v>2547693</v>
       </c>
       <c r="AO49" t="n">
-        <v>2547693</v>
+        <v>4155970</v>
       </c>
       <c r="AP49" t="n">
-        <v>4155970</v>
+        <v>3.75</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.75</v>
+        <v>2.67</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.67</v>
+        <v>4.41</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>31.85</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>344440</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-1.020036</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.214439</v>
+        <v>-4.407308</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.020036</v>
+        <v>-4.407771</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>0.591659</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>0.541686</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>0.873018</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>5.351165</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>4.393261</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>5.18043</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>0.25</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.000633</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
+        <v>0.000633</v>
       </c>
       <c r="BH49" t="n">
-        <v>0.000633</v>
+        <v>0.03</v>
       </c>
       <c r="BI49" t="n">
-        <v>0.000633</v>
+        <v>0</v>
       </c>
       <c r="BJ49" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10186,93 +9890,87 @@
         <v>0.21</v>
       </c>
       <c r="AJ50" t="n">
-        <v>108.27053</v>
+        <v>113.14433</v>
       </c>
       <c r="AK50" t="n">
-        <v>113.14433</v>
+        <v>5.6021</v>
       </c>
       <c r="AL50" t="n">
-        <v>5.6021</v>
+        <v>5.6015</v>
       </c>
       <c r="AM50" t="n">
-        <v>5.6015</v>
+        <v>6733209</v>
       </c>
       <c r="AN50" t="n">
-        <v>6733209</v>
+        <v>2544400</v>
       </c>
       <c r="AO50" t="n">
-        <v>2544400</v>
+        <v>4188808</v>
       </c>
       <c r="AP50" t="n">
-        <v>4188808</v>
+        <v>3.96</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.96</v>
+        <v>2.79</v>
       </c>
       <c r="AR50" t="n">
-        <v>2.79</v>
+        <v>4.66</v>
       </c>
       <c r="AS50" t="n">
-        <v>4.66</v>
+        <v>31.75</v>
       </c>
       <c r="AT50" t="n">
-        <v>31.75</v>
+        <v>345111</v>
       </c>
       <c r="AU50" t="n">
-        <v>345111</v>
+        <v>5.195358</v>
       </c>
       <c r="AV50" t="n">
-        <v>-0.456297</v>
+        <v>2.657089</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.195358</v>
+        <v>2.657381</v>
       </c>
       <c r="AX50" t="n">
-        <v>2.657089</v>
+        <v>0.440744</v>
       </c>
       <c r="AY50" t="n">
-        <v>2.657381</v>
+        <v>-0.129254</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.440744</v>
+        <v>0.79014</v>
       </c>
       <c r="BA50" t="n">
-        <v>-0.129254</v>
+        <v>0.194809</v>
       </c>
       <c r="BB50" t="n">
-        <v>0.79014</v>
+        <v>5.225222</v>
       </c>
       <c r="BC50" t="n">
-        <v>0.194809</v>
+        <v>2.961368</v>
       </c>
       <c r="BD50" t="n">
-        <v>5.225222</v>
+        <v>5.127976</v>
       </c>
       <c r="BE50" t="n">
-        <v>2.961368</v>
+        <v>0</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.127976</v>
+        <v>0.000562</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
+        <v>0.000562</v>
       </c>
       <c r="BH50" t="n">
-        <v>0.000562</v>
+        <v>0.21</v>
       </c>
       <c r="BI50" t="n">
-        <v>0.000562</v>
+        <v>0.12</v>
       </c>
       <c r="BJ50" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10383,93 +10081,87 @@
         <v>-0.21</v>
       </c>
       <c r="AJ51" t="n">
-        <v>108.80021</v>
+        <v>110.57963</v>
       </c>
       <c r="AK51" t="n">
-        <v>110.57963</v>
+        <v>5.4264</v>
       </c>
       <c r="AL51" t="n">
-        <v>5.4264</v>
+        <v>5.4258</v>
       </c>
       <c r="AM51" t="n">
-        <v>5.4258</v>
+        <v>6774436</v>
       </c>
       <c r="AN51" t="n">
-        <v>6774436</v>
+        <v>2546265</v>
       </c>
       <c r="AO51" t="n">
-        <v>2546265</v>
+        <v>4228171</v>
       </c>
       <c r="AP51" t="n">
-        <v>4228171</v>
+        <v>4.14</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.14</v>
+        <v>2.85</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.85</v>
+        <v>4.92</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>31.87</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>350767</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>-2.266751</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.489219</v>
+        <v>-3.136324</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.266751</v>
+        <v>-3.13666</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>0.612293</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>0.073298</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>0.9397180000000001</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>1.638893</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>5.130501</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>3.033233</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>5.054283</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>0</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="BI51" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="BJ51" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10580,93 +10272,87 @@
         <v>0.52</v>
       </c>
       <c r="AJ52" t="n">
-        <v>108.63642</v>
+        <v>109.59513</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.59513</v>
+        <v>5.3186</v>
       </c>
       <c r="AL52" t="n">
-        <v>5.3186</v>
+        <v>5.318</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.318</v>
+        <v>6852705</v>
       </c>
       <c r="AN52" t="n">
-        <v>6852705</v>
+        <v>2589817</v>
       </c>
       <c r="AO52" t="n">
-        <v>2589817</v>
+        <v>4262888</v>
       </c>
       <c r="AP52" t="n">
-        <v>4262888</v>
+        <v>4.09</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.09</v>
+        <v>2.77</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.77</v>
+        <v>4.89</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>31.47</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>356582</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-0.890309</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.150542</v>
+        <v>-1.986584</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.890309</v>
+        <v>-1.986804</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>1.155358</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>1.710427</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>0.821088</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>1.657796</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>5.172369</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>2.828436</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>5.096104</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>0</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="BI52" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ52" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10777,93 +10463,87 @@
         <v>0.03</v>
       </c>
       <c r="AJ53" t="n">
-        <v>108.7159</v>
+        <v>110.16346</v>
       </c>
       <c r="AK53" t="n">
-        <v>110.16346</v>
+        <v>5.3843</v>
       </c>
       <c r="AL53" t="n">
-        <v>5.3843</v>
+        <v>5.3837</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.3837</v>
+        <v>6923886</v>
       </c>
       <c r="AN53" t="n">
-        <v>6923886</v>
+        <v>2597630</v>
       </c>
       <c r="AO53" t="n">
-        <v>2597630</v>
+        <v>4326256</v>
       </c>
       <c r="AP53" t="n">
-        <v>4326256</v>
+        <v>4.18</v>
       </c>
       <c r="AQ53" t="n">
-        <v>4.18</v>
+        <v>2.82</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.82</v>
+        <v>4.99</v>
       </c>
       <c r="AS53" t="n">
-        <v>4.99</v>
+        <v>32.04</v>
       </c>
       <c r="AT53" t="n">
-        <v>32.04</v>
+        <v>357103</v>
       </c>
       <c r="AU53" t="n">
-        <v>357103</v>
+        <v>0.518572</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.073161</v>
+        <v>1.235287</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.518572</v>
+        <v>1.235427</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.235287</v>
+        <v>1.038729</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.235427</v>
+        <v>0.301682</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.038729</v>
+        <v>1.486504</v>
       </c>
       <c r="BA53" t="n">
-        <v>0.301682</v>
+        <v>0.146109</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.486504</v>
+        <v>4.680811</v>
       </c>
       <c r="BC53" t="n">
-        <v>0.146109</v>
+        <v>0.924206</v>
       </c>
       <c r="BD53" t="n">
-        <v>4.680811</v>
+        <v>4.490243</v>
       </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>0</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BI53" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="BJ53" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10974,93 +10654,87 @@
         <v>0.03</v>
       </c>
       <c r="AJ54" t="n">
-        <v>109.27405</v>
+        <v>106.90236</v>
       </c>
       <c r="AK54" t="n">
-        <v>106.90236</v>
+        <v>5.3338</v>
       </c>
       <c r="AL54" t="n">
-        <v>5.3338</v>
+        <v>5.3332</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.3332</v>
+        <v>7003273</v>
       </c>
       <c r="AN54" t="n">
-        <v>7003273</v>
+        <v>2616213</v>
       </c>
       <c r="AO54" t="n">
-        <v>2616213</v>
+        <v>4387061</v>
       </c>
       <c r="AP54" t="n">
-        <v>4387061</v>
+        <v>4.23</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.23</v>
+        <v>2.74</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.74</v>
+        <v>5.12</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>32.32</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>360578</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>-2.960237</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.513402</v>
+        <v>-0.937912</v>
       </c>
       <c r="AW54" t="n">
-        <v>-2.960237</v>
+        <v>-0.938017</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>1.146567</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>0.715383</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>1.405488</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>0.973109</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>4.461836</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>-0.101973</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>4.177803</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>0</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>-0</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BH54" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="BI54" t="n">
-        <v>-0</v>
+        <v>-0.08</v>
       </c>
       <c r="BJ54" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11171,93 +10845,87 @@
         <v>0.21</v>
       </c>
       <c r="AJ55" t="n">
-        <v>109.41762</v>
+        <v>107.17649</v>
       </c>
       <c r="AK55" t="n">
-        <v>107.17649</v>
+        <v>5.5024</v>
       </c>
       <c r="AL55" t="n">
-        <v>5.5024</v>
+        <v>5.5018</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5018</v>
+        <v>7136436</v>
       </c>
       <c r="AN55" t="n">
-        <v>7136436</v>
+        <v>2701146</v>
       </c>
       <c r="AO55" t="n">
-        <v>2701146</v>
+        <v>4435290</v>
       </c>
       <c r="AP55" t="n">
-        <v>4435290</v>
+        <v>4.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.68</v>
+        <v>5.12</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>31.99</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>358234</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>0.25643</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.131385</v>
+        <v>3.160973</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.25643</v>
+        <v>3.161329</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>1.90144</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>3.24641</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>1.099346</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>-0.650067</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>4.264385</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>-1.042167</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>3.897866</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>0</v>
       </c>
-      <c r="BI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11368,93 +11036,87 @@
         <v>0.39</v>
       </c>
       <c r="AJ56" t="n">
-        <v>110.05486</v>
+        <v>102.36456</v>
       </c>
       <c r="AK56" t="n">
-        <v>102.36456</v>
+        <v>5.2301</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.2301</v>
+        <v>5.2295</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.2295</v>
+        <v>7130500</v>
       </c>
       <c r="AN56" t="n">
-        <v>7130500</v>
+        <v>2654052</v>
       </c>
       <c r="AO56" t="n">
-        <v>2654052</v>
+        <v>4476448</v>
       </c>
       <c r="AP56" t="n">
-        <v>4476448</v>
+        <v>4.45</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4.45</v>
+        <v>2.87</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.87</v>
+        <v>5.38</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>32.6</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>364367</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>-4.489725</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.582392</v>
+        <v>-4.94875</v>
       </c>
       <c r="AW56" t="n">
-        <v>-4.489725</v>
+        <v>-4.949289</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>-0.083179</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>-1.743482</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>0.927966</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>1.712009</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>4.441351</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>-0.903999</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>4.303068</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11565,93 +11227,87 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110.65892</v>
+        <v>106.82125</v>
       </c>
       <c r="AK57" t="n">
-        <v>106.82125</v>
+        <v>5.1495</v>
       </c>
       <c r="AL57" t="n">
-        <v>5.1495</v>
+        <v>5.1489</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.1489</v>
+        <v>7156987</v>
       </c>
       <c r="AN57" t="n">
-        <v>7156987</v>
+        <v>2655931</v>
       </c>
       <c r="AO57" t="n">
-        <v>2655931</v>
+        <v>4501056</v>
       </c>
       <c r="AP57" t="n">
-        <v>4501056</v>
+        <v>4.64</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4.64</v>
+        <v>3.07</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.07</v>
+        <v>5.56</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>32.78</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>371074</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>4.353743</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.548872</v>
+        <v>-1.54108</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.353743</v>
+        <v>-1.541256</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>0.371461</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>0.070797</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>0.549722</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>1.840727</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>3.812497</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>-2.659212</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>3.357475</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11762,93 +11418,87 @@
         <v>0.91</v>
       </c>
       <c r="AJ58" t="n">
-        <v>110.51078</v>
+        <v>117.8089</v>
       </c>
       <c r="AK58" t="n">
-        <v>117.8089</v>
+        <v>5.2194</v>
       </c>
       <c r="AL58" t="n">
-        <v>5.2194</v>
+        <v>5.2188</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.2188</v>
+        <v>7237735</v>
       </c>
       <c r="AN58" t="n">
-        <v>7237735</v>
+        <v>2686046</v>
       </c>
       <c r="AO58" t="n">
-        <v>2686046</v>
+        <v>4551689</v>
       </c>
       <c r="AP58" t="n">
-        <v>4551689</v>
+        <v>4.52</v>
       </c>
       <c r="AQ58" t="n">
-        <v>4.52</v>
+        <v>3.04</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.04</v>
+        <v>5.4</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>32.99</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>362002</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>10.286015</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.133871</v>
+        <v>1.357413</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.286015</v>
+        <v>1.357572</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>1.12824</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>1.133877</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>1.124914</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>-2.444795</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>4.142847</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>-1.819225</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>3.768807</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>-0.25</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.000354</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
+        <v>-0.000354</v>
       </c>
       <c r="BH58" t="n">
-        <v>-0.000354</v>
+        <v>-0.12</v>
       </c>
       <c r="BI58" t="n">
-        <v>-0.000354</v>
+        <v>-0.03</v>
       </c>
       <c r="BJ58" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11959,93 +11609,87 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ59" t="n">
-        <v>110.95732</v>
+        <v>113.99365</v>
       </c>
       <c r="AK59" t="n">
-        <v>113.99365</v>
+        <v>4.9886</v>
       </c>
       <c r="AL59" t="n">
-        <v>4.9886</v>
+        <v>4.988</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.988</v>
+        <v>7258599</v>
       </c>
       <c r="AN59" t="n">
-        <v>7258599</v>
+        <v>2684623</v>
       </c>
       <c r="AO59" t="n">
-        <v>2684623</v>
+        <v>4573976</v>
       </c>
       <c r="AP59" t="n">
-        <v>4573976</v>
+        <v>4.63</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.63</v>
+        <v>3.15</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.15</v>
+        <v>5.51</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>33.51</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>366913</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>-3.238507</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.404069</v>
+        <v>-4.421964</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.238507</v>
+        <v>-4.422473</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>0.288267</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>-0.052977</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>0.489642</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>1.356622</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>4.39172</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>0.619623</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>4.109608</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>-0.25</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>-0.000554</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
+        <v>-0.000554</v>
       </c>
       <c r="BH59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BI59" t="n">
-        <v>-0.000554</v>
+        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12156,93 +11800,87 @@
         <v>0.65</v>
       </c>
       <c r="AJ60" t="n">
-        <v>111.03587</v>
+        <v>109.52993</v>
       </c>
       <c r="AK60" t="n">
-        <v>109.52993</v>
+        <v>5.0569</v>
       </c>
       <c r="AL60" t="n">
-        <v>5.0569</v>
+        <v>5.0563</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.0563</v>
+        <v>7299615</v>
       </c>
       <c r="AN60" t="n">
-        <v>7299615</v>
+        <v>2704550</v>
       </c>
       <c r="AO60" t="n">
-        <v>2704550</v>
+        <v>4595065</v>
       </c>
       <c r="AP60" t="n">
-        <v>4595065</v>
+        <v>4.74</v>
       </c>
       <c r="AQ60" t="n">
-        <v>4.74</v>
+        <v>3.24</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.24</v>
+        <v>5.62</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>33.42</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
+        <v>371137</v>
       </c>
       <c r="AU60" t="n">
-        <v>371137</v>
+        <v>-3.915762</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.07079299999999999</v>
+        <v>1.369122</v>
       </c>
       <c r="AW60" t="n">
-        <v>-3.915762</v>
+        <v>1.369286</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>0.565068</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>0.742264</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>0.461065</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>1.151227</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>4.724907</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>1.964454</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>4.420848</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BH60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12353,59 +11991,57 @@
         <v>0.14</v>
       </c>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
+      <c r="AK61" t="n">
+        <v>5.1766</v>
+      </c>
       <c r="AL61" t="n">
-        <v>5.1766</v>
-      </c>
-      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
+      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AU61" t="n">
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
-      <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="n">
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AY61" t="n">
+      <c r="AW61" t="n">
         <v>2.367344</v>
       </c>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="inlineStr"/>
+      <c r="BA61" t="n">
+        <v>-0.964334</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>4.641328</v>
+      </c>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
+        <v>3.177699</v>
       </c>
       <c r="BD61" t="n">
-        <v>4.641328</v>
+        <v>4.327084</v>
       </c>
       <c r="BE61" t="n">
-        <v>3.177699</v>
+        <v>-0.25</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.327084</v>
+        <v>-0.000372</v>
       </c>
       <c r="BG61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -12424,10 +12060,10 @@
         <v>425.049988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0751</v>
+        <v>5.0846</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7816</v>
+        <v>5.7877</v>
       </c>
       <c r="H62" t="n">
         <v>7408.299805</v>
@@ -12439,19 +12075,19 @@
         <v>51711.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4070.800049</v>
+        <v>4089.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>89.30999799999999</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>96.779999</v>
+        <v>90.550003</v>
       </c>
       <c r="N62" t="n">
-        <v>1253.5</v>
+        <v>1220.25</v>
       </c>
       <c r="O62" t="n">
-        <v>487.25</v>
+        <v>473.75</v>
       </c>
       <c r="P62" t="n">
         <v>2.732177</v>
@@ -12466,10 +12102,10 @@
         <v>-2.433147</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.058886</v>
+        <v>-1.875551</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.290964</v>
+        <v>-2.187871</v>
       </c>
       <c r="V62" t="n">
         <v>-1.214238</v>
@@ -12481,19 +12117,19 @@
         <v>-1.161239</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.190687</v>
+        <v>1.665465</v>
       </c>
       <c r="Z62" t="n">
-        <v>28.503594</v>
+        <v>20.76259</v>
       </c>
       <c r="AA62" t="n">
-        <v>32.720792</v>
+        <v>24.177188</v>
       </c>
       <c r="AB62" t="n">
-        <v>12.245355</v>
+        <v>9.267965</v>
       </c>
       <c r="AC62" t="n">
-        <v>18.049667</v>
+        <v>14.778922</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12508,13 +12144,13 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
+      <c r="AK62" t="n">
+        <v>5.0666</v>
+      </c>
       <c r="AL62" t="n">
-        <v>5.0666</v>
-      </c>
-      <c r="AM62" t="n">
         <v>5.066</v>
       </c>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12523,34 +12159,32 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
-      <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="n">
+      <c r="AV62" t="n">
         <v>-2.124947</v>
       </c>
-      <c r="AY62" t="n">
+      <c r="AW62" t="n">
         <v>-2.125193</v>
       </c>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
+      <c r="BE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BM62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,140 +598,150 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
+          <t>bcb_sgs_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -816,39 +826,41 @@
         <v>1.02</v>
       </c>
       <c r="AJ2" t="n">
+        <v>96.31464</v>
+      </c>
+      <c r="AK2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AM2" t="n">
         <v>5.121</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AN2" t="n">
         <v>4271865</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AO2" t="n">
         <v>1833179</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AP2" t="n">
         <v>2438686</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AQ2" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>2.94</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AT2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
         <v>355671</v>
       </c>
-      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -865,6 +877,8 @@
       <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="inlineStr"/>
       <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -973,81 +987,87 @@
         <v>0.88</v>
       </c>
       <c r="AJ3" t="n">
+        <v>97.07568000000001</v>
+      </c>
+      <c r="AK3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AM3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AN3" t="n">
         <v>4346060</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AO3" t="n">
         <v>1851006</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AP3" t="n">
         <v>2495054</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AQ3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AR3" t="n">
         <v>1.56</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AS3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AT3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="AW3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AX3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AY3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AZ3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BA3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BB3" t="n">
         <v>2.311409</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BC3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="n">
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="n">
         <v>1</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BH3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BI3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BJ3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BK3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BL3" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1158,81 +1178,87 @@
         <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
+        <v>96.95968999999999</v>
+      </c>
+      <c r="AK4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AM4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AN4" t="n">
         <v>4441056</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AO4" t="n">
         <v>1894119</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AP4" t="n">
         <v>2546936</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AQ4" t="n">
         <v>2.34</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AR4" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AS4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AT4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
         <v>368886</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
+        <v>-0.119484</v>
+      </c>
+      <c r="AW4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AX4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AY4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AZ4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BA4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BB4" t="n">
         <v>2.079394</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BC4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="n">
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="n">
         <v>1</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BH4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BI4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BJ4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BK4" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BL4" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1343,81 +1369,87 @@
         <v>1.16</v>
       </c>
       <c r="AJ5" t="n">
+        <v>97.48142</v>
+      </c>
+      <c r="AK5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>5.643</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AM5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AN5" t="n">
         <v>4511956</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AO5" t="n">
         <v>1910940</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AP5" t="n">
         <v>2601017</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AQ5" t="n">
         <v>2.33</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
         <v>1.43</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AS5" t="n">
         <v>2.99</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AT5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
         <v>367927</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>0.53809</v>
+      </c>
+      <c r="AW5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AY5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BB5" t="n">
         <v>2.123375</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BC5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="n">
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BH5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BI5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BJ5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BK5" t="n">
         <v>0</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BL5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1528,81 +1560,87 @@
         <v>0.84</v>
       </c>
       <c r="AJ6" t="n">
+        <v>98.97262000000001</v>
+      </c>
+      <c r="AK6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AM6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AN6" t="n">
         <v>4597507</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AO6" t="n">
         <v>1933111</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AP6" t="n">
         <v>2664395</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AQ6" t="n">
         <v>2.36</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AR6" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
         <v>3.01</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AT6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
         <v>367772</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
+        <v>1.529727</v>
+      </c>
+      <c r="AW6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AX6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AZ6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BA6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BB6" t="n">
         <v>2.436662</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BC6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="n">
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
         <v>0</v>
       </c>
-      <c r="BF6" t="n">
+      <c r="BH6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BI6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BH6" t="n">
+      <c r="BJ6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI6" t="n">
+      <c r="BK6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ6" t="n">
+      <c r="BL6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK6" t="n">
+      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1713,81 +1751,87 @@
         <v>0.73</v>
       </c>
       <c r="AJ7" t="n">
+        <v>99.35339</v>
+      </c>
+      <c r="AK7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AL7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AM7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AN7" t="n">
         <v>4682852</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AO7" t="n">
         <v>1974391</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AP7" t="n">
         <v>2708461</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AQ7" t="n">
         <v>2.35</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AR7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AS7" t="n">
         <v>3.05</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
         <v>362204</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
+        <v>0.384723</v>
+      </c>
+      <c r="AW7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AX7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AY7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AZ7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BA7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BB7" t="n">
         <v>1.653884</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BC7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="n">
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BH7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BI7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BJ7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BK7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BL7" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK7" t="n">
+      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1898,81 +1942,87 @@
         <v>0.67</v>
       </c>
       <c r="AJ8" t="n">
+        <v>97.34401</v>
+      </c>
+      <c r="AK8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AL8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AM8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AN8" t="n">
         <v>4682131</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AO8" t="n">
         <v>1947035</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AP8" t="n">
         <v>2735096</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AQ8" t="n">
         <v>2.51</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AR8" t="n">
         <v>1.46</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AS8" t="n">
         <v>3.26</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AT8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
         <v>358398</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
+        <v>-2.022457</v>
+      </c>
+      <c r="AW8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AY8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BA8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BB8" t="n">
         <v>0.9834000000000001</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BC8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="n">
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="n">
         <v>0</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BH8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BI8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BJ8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BK8" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BL8" t="n">
         <v>0.21</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2083,81 +2133,87 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
+        <v>98.43725000000001</v>
+      </c>
+      <c r="AK9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AL9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AM9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AN9" t="n">
         <v>4727818</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AO9" t="n">
         <v>1971524</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AP9" t="n">
         <v>2756295</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AQ9" t="n">
         <v>2.57</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AR9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AS9" t="n">
         <v>3.38</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AU9" t="n">
         <v>357740</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
+        <v>1.123069</v>
+      </c>
+      <c r="AW9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AY9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AZ9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BA9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BB9" t="n">
         <v>0.775073</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BC9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="n">
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
         <v>1.5</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BH9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BI9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BJ9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BK9" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BL9" t="n">
         <v>0.12</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2268,81 +2324,87 @@
         <v>1.71</v>
       </c>
       <c r="AJ10" t="n">
+        <v>99.55981</v>
+      </c>
+      <c r="AK10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AL10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AM10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AN10" t="n">
         <v>4794583</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AO10" t="n">
         <v>1994119</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AP10" t="n">
         <v>2800464</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AQ10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AR10" t="n">
         <v>1.55</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AS10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AT10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AU10" t="n">
         <v>353169</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
+        <v>1.140381</v>
+      </c>
+      <c r="AW10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AY10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AZ10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BB10" t="n">
         <v>1.602477</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BC10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="n">
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
         <v>1</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BH10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BI10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BJ10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BK10" t="n">
         <v>0.11</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BL10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2453,81 +2515,87 @@
         <v>1.04</v>
       </c>
       <c r="AJ11" t="n">
+        <v>99.51646</v>
+      </c>
+      <c r="AK11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AL11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AM11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AN11" t="n">
         <v>4833732</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AO11" t="n">
         <v>2003312</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AP11" t="n">
         <v>2830420</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AQ11" t="n">
         <v>2.72</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AR11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
         <v>3.54</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AT11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AU11" t="n">
         <v>345097</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
+        <v>-0.043542</v>
+      </c>
+      <c r="AW11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AY11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AZ11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BA11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BB11" t="n">
         <v>1.06968</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="n">
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
         <v>0</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BH11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BI11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BJ11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BK11" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BL11" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2638,81 +2706,87 @@
         <v>0.45</v>
       </c>
       <c r="AJ12" t="n">
+        <v>99.67415</v>
+      </c>
+      <c r="AK12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AL12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AM12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AN12" t="n">
         <v>4889397</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AO12" t="n">
         <v>2013726</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AP12" t="n">
         <v>2875671</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AQ12" t="n">
         <v>2.79</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AR12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AS12" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AT12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AU12" t="n">
         <v>346415</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
+        <v>0.158456</v>
+      </c>
+      <c r="AW12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AX12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AY12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AZ12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BA12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BB12" t="n">
         <v>1.598738</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BC12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="n">
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
         <v>1</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BH12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BI12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BJ12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BK12" t="n">
         <v>0</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BL12" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2823,87 +2897,93 @@
         <v>0.62</v>
       </c>
       <c r="AJ13" t="n">
+        <v>99.6343</v>
+      </c>
+      <c r="AK13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>5.238</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AM13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AN13" t="n">
         <v>4965603</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AO13" t="n">
         <v>2052569</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AP13" t="n">
         <v>2913035</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AR13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AS13" t="n">
         <v>3.57</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AT13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AU13" t="n">
         <v>341958</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
+        <v>-0.03998</v>
+      </c>
+      <c r="AW13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AX13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AZ13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BA13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BB13" t="n">
         <v>1.299314</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BD13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BE13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BF13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BG13" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BH13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BI13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BJ13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BK13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BL13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3014,87 +3094,93 @@
         <v>-0.6</v>
       </c>
       <c r="AJ14" t="n">
+        <v>101.27684</v>
+      </c>
+      <c r="AK14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AL14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AM14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AN14" t="n">
         <v>4999244</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AO14" t="n">
         <v>2047038</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AP14" t="n">
         <v>2952207</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AQ14" t="n">
         <v>2.84</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AS14" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AT14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AU14" t="n">
         <v>346403</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
+        <v>1.648569</v>
+      </c>
+      <c r="AW14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AX14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AY14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AZ14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BA14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BB14" t="n">
         <v>1.344714</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BD14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BE14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BF14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BG14" t="n">
         <v>0</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BH14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BI14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BJ14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BK14" t="n">
         <v>0.08</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BL14" t="n">
         <v>0.14</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3205,87 +3291,93 @@
         <v>-0.31</v>
       </c>
       <c r="AJ15" t="n">
+        <v>101.07328</v>
+      </c>
+      <c r="AK15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AL15" t="n">
         <v>5.179</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AM15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AN15" t="n">
         <v>5072711</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
         <v>2064183</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AP15" t="n">
         <v>3008528</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AQ15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AR15" t="n">
         <v>1.62</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AS15" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AT15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AU15" t="n">
         <v>339664</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AV15" t="n">
+        <v>-0.200994</v>
+      </c>
+      <c r="AW15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AY15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="AZ15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BA15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BB15" t="n">
         <v>1.907759</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BC15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BD15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BE15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BF15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BG15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BH15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BI15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BJ15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BK15" t="n">
         <v>0.02</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BL15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3396,87 +3488,93 @@
         <v>-0.32</v>
       </c>
       <c r="AJ16" t="n">
+        <v>101.17973</v>
+      </c>
+      <c r="AK16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AL16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AM16" t="n">
         <v>5.406</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AN16" t="n">
         <v>5164775</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AO16" t="n">
         <v>2109806</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AP16" t="n">
         <v>3054969</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
         <v>2.92</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AR16" t="n">
         <v>1.65</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AS16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AT16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AU16" t="n">
         <v>327580</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AV16" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="AW16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AX16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AY16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="AZ16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BA16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BB16" t="n">
         <v>1.543645</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BC16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BD16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BE16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BF16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BG16" t="n">
         <v>0</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BH16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BI16" t="n">
         <v>0.000228</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0.03</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
       <c r="BK16" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3587,87 +3685,93 @@
         <v>0.47</v>
       </c>
       <c r="AJ17" t="n">
+        <v>101.46342</v>
+      </c>
+      <c r="AK17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AL17" t="n">
         <v>5.257</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AM17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AN17" t="n">
         <v>5215990</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AO17" t="n">
         <v>2105856</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AP17" t="n">
         <v>3110134</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
         <v>3.04</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AR17" t="n">
         <v>1.77</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AS17" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AT17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AU17" t="n">
         <v>325546</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
+        <v>0.280382</v>
+      </c>
+      <c r="AW17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AX17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AY17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BA17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BB17" t="n">
         <v>1.805747</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BC17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BD17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BE17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BF17" t="n">
         <v>6.460076</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
       <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BK17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BL17" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3778,87 +3882,93 @@
         <v>0.38</v>
       </c>
       <c r="AJ18" t="n">
+        <v>100.66227</v>
+      </c>
+      <c r="AK18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AL18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AN18" t="n">
         <v>5285657</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AO18" t="n">
         <v>2130312</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AP18" t="n">
         <v>3155345</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AQ18" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AR18" t="n">
         <v>1.81</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AS18" t="n">
         <v>3.92</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AT18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AU18" t="n">
         <v>331505</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
+        <v>-0.789595</v>
+      </c>
+      <c r="AW18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AY18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AZ18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BA18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BB18" t="n">
         <v>1.453667</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BC18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BD18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BE18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BF18" t="n">
         <v>5.974439</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
       <c r="BK18" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3969,87 +4079,93 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AJ19" t="n">
+        <v>100.58196</v>
+      </c>
+      <c r="AK19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AL19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AM19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AN19" t="n">
         <v>5366069</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AO19" t="n">
         <v>2178236</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
         <v>3187833</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
         <v>3.07</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AS19" t="n">
         <v>3.94</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AT19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AU19" t="n">
         <v>324703</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
+        <v>-0.07978200000000001</v>
+      </c>
+      <c r="AW19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AY19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AZ19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BA19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BB19" t="n">
         <v>1.029618</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BC19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BD19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BE19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BF19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BG19" t="n">
         <v>0</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BH19" t="n">
         <v>-0</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BI19" t="n">
         <v>-0</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BJ19" t="n">
         <v>0</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BK19" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BL19" t="n">
         <v>0.02</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4160,87 +4276,93 @@
         <v>0.46</v>
       </c>
       <c r="AJ20" t="n">
+        <v>100.05178</v>
+      </c>
+      <c r="AK20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AL20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AM20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AN20" t="n">
         <v>5373231</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AO20" t="n">
         <v>2151399</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AP20" t="n">
         <v>3221831</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AQ20" t="n">
         <v>3.24</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AR20" t="n">
         <v>1.94</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AS20" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AT20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AU20" t="n">
         <v>331122</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AV20" t="n">
+        <v>-0.527112</v>
+      </c>
+      <c r="AW20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AX20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AY20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="AZ20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BA20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BB20" t="n">
         <v>1.066493</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BC20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BD20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BE20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BF20" t="n">
         <v>5.711379</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
       </c>
       <c r="BH20" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="BI20" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
       <c r="BK20" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4351,87 +4473,93 @@
         <v>0.77</v>
       </c>
       <c r="AJ21" t="n">
+        <v>103.00964</v>
+      </c>
+      <c r="AK21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AL21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AM21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AN21" t="n">
         <v>5370950</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AO21" t="n">
         <v>2136105</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>3234845</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
         <v>3.36</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AR21" t="n">
         <v>2.17</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AS21" t="n">
         <v>4.16</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AT21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AU21" t="n">
         <v>328098</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
+        <v>2.956329</v>
+      </c>
+      <c r="AW21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AX21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AY21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AZ21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BA21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BB21" t="n">
         <v>0.403932</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BC21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BD21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BE21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BF21" t="n">
         <v>5.47065</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
       </c>
       <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BK21" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BL21" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4542,87 +4670,93 @@
         <v>0.64</v>
       </c>
       <c r="AJ22" t="n">
+        <v>103.09341</v>
+      </c>
+      <c r="AK22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AL22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AM22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AN22" t="n">
         <v>5424811</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AO22" t="n">
         <v>2154900</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AP22" t="n">
         <v>3269910</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AQ22" t="n">
         <v>3.35</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AR22" t="n">
         <v>2.2</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
         <v>4.11</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AU22" t="n">
         <v>341158</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
+        <v>0.08132200000000001</v>
+      </c>
+      <c r="AW22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AY22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BA22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BB22" t="n">
         <v>1.083978</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BC22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BD22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BE22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BF22" t="n">
         <v>4.361088</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
       </c>
       <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BK22" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BL22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4733,87 +4867,93 @@
         <v>0.53</v>
       </c>
       <c r="AJ23" t="n">
+        <v>104.1626</v>
+      </c>
+      <c r="AK23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AL23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AM23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AN23" t="n">
         <v>5426307</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AO23" t="n">
         <v>2145000</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AP23" t="n">
         <v>3281308</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AQ23" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR23" t="n">
         <v>2.45</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AS23" t="n">
         <v>4.26</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AU23" t="n">
         <v>345725</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
+        <v>1.037108</v>
+      </c>
+      <c r="AW23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AY23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AZ23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BB23" t="n">
         <v>0.348572</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BC23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BD23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BE23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BF23" t="n">
         <v>3.834324</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
       </c>
       <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BK23" t="n">
         <v>0.25</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BL23" t="n">
         <v>0.15</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4924,87 +5064,93 @@
         <v>0.36</v>
       </c>
       <c r="AJ24" t="n">
+        <v>102.3642</v>
+      </c>
+      <c r="AK24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AL24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AM24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AN24" t="n">
         <v>5453708</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AO24" t="n">
         <v>2145530</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AP24" t="n">
         <v>3308178</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AQ24" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AR24" t="n">
         <v>2.58</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AS24" t="n">
         <v>4.35</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AT24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AU24" t="n">
         <v>343489</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
+        <v>-1.726531</v>
+      </c>
+      <c r="AW24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AX24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AY24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AZ24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BB24" t="n">
         <v>0.818881</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BC24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BD24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BE24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BF24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BG24" t="n">
         <v>0</v>
       </c>
-      <c r="BF24" t="n">
+      <c r="BH24" t="n">
         <v>-0</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BI24" t="n">
         <v>-0</v>
       </c>
-      <c r="BH24" t="n">
+      <c r="BJ24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BI24" t="n">
+      <c r="BK24" t="n">
         <v>0.13</v>
       </c>
-      <c r="BJ24" t="n">
+      <c r="BL24" t="n">
         <v>0.09</v>
       </c>
-      <c r="BK24" t="n">
+      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5115,87 +5261,93 @@
         <v>-0.1</v>
       </c>
       <c r="AJ25" t="n">
+        <v>102.50431</v>
+      </c>
+      <c r="AK25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AL25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AM25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AN25" t="n">
         <v>5479459</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AO25" t="n">
         <v>2169613</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AP25" t="n">
         <v>3309846</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AQ25" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AR25" t="n">
         <v>2.63</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AS25" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AT25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AU25" t="n">
         <v>343620</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AV25" t="n">
+        <v>0.136874</v>
+      </c>
+      <c r="AW25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AX25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AY25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="AZ25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="BA25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BB25" t="n">
         <v>0.050421</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BC25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BD25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BE25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BF25" t="n">
         <v>2.998957</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
       </c>
       <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BI25" t="n">
+      <c r="BK25" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ25" t="n">
+      <c r="BL25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK25" t="n">
+      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5306,87 +5458,93 @@
         <v>-0.09</v>
       </c>
       <c r="AJ26" t="n">
+        <v>102.83357</v>
+      </c>
+      <c r="AK26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AL26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AM26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AN26" t="n">
         <v>5484871</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AO26" t="n">
         <v>2153541</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AP26" t="n">
         <v>3331330</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AQ26" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AR26" t="n">
         <v>2.73</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AS26" t="n">
         <v>4.22</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AT26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
         <v>345476</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
+        <v>0.321216</v>
+      </c>
+      <c r="AW26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AY26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BA26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BB26" t="n">
         <v>0.6490939999999999</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BC26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BD26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BE26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BF26" t="n">
         <v>3.527423</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
       </c>
       <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI26" t="n">
+      <c r="BK26" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ26" t="n">
+      <c r="BL26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK26" t="n">
+      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5497,87 +5655,93 @@
         <v>0.2</v>
       </c>
       <c r="AJ27" t="n">
+        <v>102.45222</v>
+      </c>
+      <c r="AK27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AL27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AM27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AN27" t="n">
         <v>5559063</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AO27" t="n">
         <v>2172658</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AP27" t="n">
         <v>3386405</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AQ27" t="n">
         <v>3.61</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AR27" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AS27" t="n">
         <v>4.12</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AT27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
         <v>344177</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AV27" t="n">
+        <v>-0.370842</v>
+      </c>
+      <c r="AW27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AX27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AY27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AZ27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="BA27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BB27" t="n">
         <v>1.653244</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BC27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BD27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BE27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BF27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BG27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BH27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BI27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BH27" t="n">
+      <c r="BJ27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BI27" t="n">
+      <c r="BK27" t="n">
         <v>0.09</v>
       </c>
-      <c r="BJ27" t="n">
+      <c r="BL27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BK27" t="n">
+      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5688,87 +5852,93 @@
         <v>0.11</v>
       </c>
       <c r="AJ28" t="n">
+        <v>102.57885</v>
+      </c>
+      <c r="AK28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AL28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AM28" t="n">
         <v>5.007</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AN28" t="n">
         <v>5625945</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AO28" t="n">
         <v>2215175</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AP28" t="n">
         <v>3410769</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AQ28" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AR28" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AS28" t="n">
         <v>4</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AT28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AU28" t="n">
         <v>340324</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
+        <v>0.123599</v>
+      </c>
+      <c r="AW28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AX28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AY28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AZ28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BB28" t="n">
         <v>0.719465</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BC28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BD28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BE28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BF28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BG28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF28" t="n">
+      <c r="BH28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BI28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BH28" t="n">
+      <c r="BJ28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BI28" t="n">
+      <c r="BK28" t="n">
         <v>0</v>
       </c>
-      <c r="BJ28" t="n">
+      <c r="BL28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK28" t="n">
+      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5879,87 +6049,93 @@
         <v>0.12</v>
       </c>
       <c r="AJ29" t="n">
+        <v>102.87707</v>
+      </c>
+      <c r="AK29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AL29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AM29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AN29" t="n">
         <v>5653808</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AO29" t="n">
         <v>2204808</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AP29" t="n">
         <v>3449000</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AQ29" t="n">
         <v>3.56</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AR29" t="n">
         <v>2.92</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AS29" t="n">
         <v>3.97</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AT29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AU29" t="n">
         <v>340247</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
+        <v>0.290723</v>
+      </c>
+      <c r="AW29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AX29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AY29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AZ29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BA29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BB29" t="n">
         <v>1.120891</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BC29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BD29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BE29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BF29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BG29" t="n">
         <v>0</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BH29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BI29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BH29" t="n">
+      <c r="BJ29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BI29" t="n">
+      <c r="BK29" t="n">
         <v>0.1</v>
       </c>
-      <c r="BJ29" t="n">
+      <c r="BL29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK29" t="n">
+      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6070,87 +6246,93 @@
         <v>0.1</v>
       </c>
       <c r="AJ30" t="n">
+        <v>103.528</v>
+      </c>
+      <c r="AK30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AL30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AM30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AN30" t="n">
         <v>5711103</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AO30" t="n">
         <v>2220766</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AP30" t="n">
         <v>3490337</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AQ30" t="n">
         <v>3.53</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AR30" t="n">
         <v>2.99</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AS30" t="n">
         <v>3.88</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AT30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AU30" t="n">
         <v>348406</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
+        <v>0.632726</v>
+      </c>
+      <c r="AW30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AY30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AZ30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BA30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BB30" t="n">
         <v>1.198521</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BC30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BD30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BE30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BF30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BG30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF30" t="n">
+      <c r="BH30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BI30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BH30" t="n">
+      <c r="BJ30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI30" t="n">
+      <c r="BK30" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BJ30" t="n">
+      <c r="BL30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BK30" t="n">
+      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6261,87 +6443,93 @@
         <v>0.55</v>
       </c>
       <c r="AJ31" t="n">
+        <v>104.8991</v>
+      </c>
+      <c r="AK31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AL31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AM31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AN31" t="n">
         <v>5805157</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AO31" t="n">
         <v>2283485</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AP31" t="n">
         <v>3521672</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AQ31" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AR31" t="n">
         <v>2.59</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AS31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AT31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AU31" t="n">
         <v>355034</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
+        <v>1.324376</v>
+      </c>
+      <c r="AW31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AY31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AZ31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BA31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BB31" t="n">
         <v>0.897764</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BC31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BD31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BE31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BF31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BE31" t="n">
+      <c r="BG31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF31" t="n">
+      <c r="BH31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BI31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BH31" t="n">
+      <c r="BJ31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BI31" t="n">
+      <c r="BK31" t="n">
         <v>-0.4</v>
       </c>
-      <c r="BJ31" t="n">
+      <c r="BL31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BK31" t="n">
+      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6452,87 +6640,93 @@
         <v>0.57</v>
       </c>
       <c r="AJ32" t="n">
+        <v>104.53245</v>
+      </c>
+      <c r="AK32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AL32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AM32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AN32" t="n">
         <v>5794707</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AO32" t="n">
         <v>2234362</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
         <v>3560345</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AQ32" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AR32" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AS32" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AT32" t="n">
         <v>28</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AU32" t="n">
         <v>355066</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
+        <v>-0.349526</v>
+      </c>
+      <c r="AW32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AX32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AY32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AZ32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BA32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BB32" t="n">
         <v>1.098143</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BC32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BD32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BE32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BF32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BE32" t="n">
+      <c r="BG32" t="n">
         <v>0</v>
       </c>
-      <c r="BF32" t="n">
+      <c r="BH32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BI32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BH32" t="n">
+      <c r="BJ32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI32" t="n">
+      <c r="BK32" t="n">
         <v>0.18</v>
       </c>
-      <c r="BJ32" t="n">
+      <c r="BL32" t="n">
         <v>0.01</v>
       </c>
-      <c r="BK32" t="n">
+      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6643,87 +6837,93 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ33" t="n">
+        <v>104.75961</v>
+      </c>
+      <c r="AK33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AL33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AM33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AN33" t="n">
         <v>5815954</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AO33" t="n">
         <v>2235302</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AP33" t="n">
         <v>3580652</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AQ33" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AR33" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AS33" t="n">
         <v>3.76</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AT33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
         <v>352705</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
+        <v>0.217311</v>
+      </c>
+      <c r="AW33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AX33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AY33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AZ33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BA33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BB33" t="n">
         <v>0.570366</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BC33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BD33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BE33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BF33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BG33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BH33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BI33" t="n">
         <v>-0.001782</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>-0.01</v>
       </c>
       <c r="BJ33" t="n">
         <v>0</v>
       </c>
       <c r="BK33" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6834,87 +7034,93 @@
         <v>0.19</v>
       </c>
       <c r="AJ34" t="n">
+        <v>104.7097</v>
+      </c>
+      <c r="AK34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AL34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AM34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AN34" t="n">
         <v>5899742</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AO34" t="n">
         <v>2285775</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AP34" t="n">
         <v>3613967</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AQ34" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AR34" t="n">
         <v>2.71</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AS34" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AT34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AU34" t="n">
         <v>355008</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
+        <v>-0.047642</v>
+      </c>
+      <c r="AW34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AX34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AY34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AZ34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="BA34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BB34" t="n">
         <v>0.930417</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BC34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BD34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BE34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BF34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BG34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BF34" t="n">
+      <c r="BH34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="BG34" t="n">
+      <c r="BI34" t="n">
         <v>-0.000537</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>-0.05</v>
       </c>
       <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
       <c r="BK34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7025,87 +7231,93 @@
         <v>0.37</v>
       </c>
       <c r="AJ35" t="n">
+        <v>104.75682</v>
+      </c>
+      <c r="AK35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AL35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AM35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AN35" t="n">
         <v>5915538</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AO35" t="n">
         <v>2268879</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AP35" t="n">
         <v>3646659</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AQ35" t="n">
         <v>3.37</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AR35" t="n">
         <v>2.76</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AS35" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AT35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
         <v>351599</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
+        <v>0.045001</v>
+      </c>
+      <c r="AW35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AX35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AY35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AZ35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="BA35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BB35" t="n">
         <v>0.904602</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BC35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BD35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BE35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BF35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BE35" t="n">
+      <c r="BG35" t="n">
         <v>0</v>
       </c>
-      <c r="BF35" t="n">
+      <c r="BH35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BI35" t="n">
         <v>-0.001252</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>0.05</v>
       </c>
       <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
       <c r="BK35" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7216,87 +7428,93 @@
         <v>0.46</v>
       </c>
       <c r="AJ36" t="n">
+        <v>105.70704</v>
+      </c>
+      <c r="AK36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AL36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AM36" t="n">
         <v>5.241</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AN36" t="n">
         <v>5953960</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AO36" t="n">
         <v>2278309</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AP36" t="n">
         <v>3675652</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AQ36" t="n">
         <v>3.43</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AR36" t="n">
         <v>2.8</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AS36" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AT36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
         <v>355560</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
+        <v>0.907072</v>
+      </c>
+      <c r="AW36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AX36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AY36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AZ36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BA36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BB36" t="n">
         <v>0.795057</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BC36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BD36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BE36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BF36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BE36" t="n">
+      <c r="BG36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF36" t="n">
+      <c r="BH36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BI36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BH36" t="n">
+      <c r="BJ36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BI36" t="n">
+      <c r="BK36" t="n">
         <v>0.04</v>
       </c>
-      <c r="BJ36" t="n">
+      <c r="BL36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK36" t="n">
+      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7407,87 +7625,93 @@
         <v>0.25</v>
       </c>
       <c r="AJ37" t="n">
+        <v>106.57623</v>
+      </c>
+      <c r="AK37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AL37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AM37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AN37" t="n">
         <v>6041898</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AO37" t="n">
         <v>2336858</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AP37" t="n">
         <v>3705041</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AQ37" t="n">
         <v>3.29</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AR37" t="n">
         <v>2.64</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AS37" t="n">
         <v>3.71</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AT37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
         <v>357827</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
+        <v>0.822263</v>
+      </c>
+      <c r="AW37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AX37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AY37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AZ37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="BA37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BB37" t="n">
         <v>0.799559</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BC37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BD37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BE37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BF37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BG37" t="n">
         <v>0</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BH37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BI37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BH37" t="n">
+      <c r="BJ37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BI37" t="n">
+      <c r="BK37" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BJ37" t="n">
+      <c r="BL37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BK37" t="n">
+      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7598,87 +7822,93 @@
         <v>0.26</v>
       </c>
       <c r="AJ38" t="n">
+        <v>106.88756</v>
+      </c>
+      <c r="AK38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AL38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AM38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AN38" t="n">
         <v>6069205</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AO38" t="n">
         <v>2323362</v>
       </c>
-      <c r="AO38" t="n">
+      <c r="AP38" t="n">
         <v>3745844</v>
       </c>
-      <c r="AP38" t="n">
+      <c r="AQ38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AR38" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AS38" t="n">
         <v>3.78</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AT38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
         <v>363282</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AW38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AX38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AY38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AZ38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="BA38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BB38" t="n">
         <v>1.101283</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BC38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BD38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BE38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BF38" t="n">
         <v>4.060953</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
       </c>
       <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BI38" t="n">
+      <c r="BK38" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BJ38" t="n">
+      <c r="BL38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK38" t="n">
+      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7789,87 +8019,93 @@
         <v>-0.14</v>
       </c>
       <c r="AJ39" t="n">
+        <v>107.14396</v>
+      </c>
+      <c r="AK39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AL39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AM39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AN39" t="n">
         <v>6135298</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AO39" t="n">
         <v>2344397</v>
       </c>
-      <c r="AO39" t="n">
+      <c r="AP39" t="n">
         <v>3790900</v>
       </c>
-      <c r="AP39" t="n">
+      <c r="AQ39" t="n">
         <v>3.33</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AR39" t="n">
         <v>2.55</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AS39" t="n">
         <v>3.82</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AT39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
         <v>369214</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
+        <v>0.239878</v>
+      </c>
+      <c r="AW39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AY39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AZ39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="BA39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BB39" t="n">
         <v>1.202826</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BC39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BD39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BE39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BF39" t="n">
         <v>3.707852</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
       </c>
       <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI39" t="n">
+      <c r="BK39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BJ39" t="n">
+      <c r="BL39" t="n">
         <v>0.04</v>
       </c>
-      <c r="BK39" t="n">
+      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7980,87 +8216,93 @@
         <v>0.48</v>
       </c>
       <c r="AJ40" t="n">
+        <v>107.99916</v>
+      </c>
+      <c r="AK40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AL40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AM40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AN40" t="n">
         <v>6216528</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AO40" t="n">
         <v>2384828</v>
       </c>
-      <c r="AO40" t="n">
+      <c r="AP40" t="n">
         <v>3831700</v>
       </c>
-      <c r="AP40" t="n">
+      <c r="AQ40" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AR40" t="n">
         <v>2.56</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AS40" t="n">
         <v>3.83</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AT40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
         <v>372016</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
+        <v>0.7981780000000001</v>
+      </c>
+      <c r="AW40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AY40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AZ40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BA40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BB40" t="n">
         <v>1.076262</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BC40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BD40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BE40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BF40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BG40" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF40" t="n">
+      <c r="BH40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="BG40" t="n">
+      <c r="BI40" t="n">
         <v>0.000342</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>0.01</v>
       </c>
       <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
       <c r="BK40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8171,87 +8413,93 @@
         <v>0.61</v>
       </c>
       <c r="AJ41" t="n">
+        <v>108.15356</v>
+      </c>
+      <c r="AK41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AL41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AM41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AN41" t="n">
         <v>6275117</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AO41" t="n">
         <v>2397533</v>
       </c>
-      <c r="AO41" t="n">
+      <c r="AP41" t="n">
         <v>3877584</v>
       </c>
-      <c r="AP41" t="n">
+      <c r="AQ41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AR41" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AS41" t="n">
         <v>3.79</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AT41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AU41" t="n">
         <v>366096</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
+        <v>0.142964</v>
+      </c>
+      <c r="AW41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AX41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AY41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AZ41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="BA41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BB41" t="n">
         <v>1.197484</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BC41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BD41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BE41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BF41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BG41" t="n">
         <v>0</v>
       </c>
-      <c r="BF41" t="n">
+      <c r="BH41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="BG41" t="n">
+      <c r="BI41" t="n">
         <v>0.000556</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
       <c r="BK41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8362,87 +8610,93 @@
         <v>0.33</v>
       </c>
       <c r="AJ42" t="n">
+        <v>107.98489</v>
+      </c>
+      <c r="AK42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AL42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AM42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AN42" t="n">
         <v>6365690</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AO42" t="n">
         <v>2436022</v>
       </c>
-      <c r="AO42" t="n">
+      <c r="AP42" t="n">
         <v>3929668</v>
       </c>
-      <c r="AP42" t="n">
+      <c r="AQ42" t="n">
         <v>3.27</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AR42" t="n">
         <v>2.5</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AS42" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AT42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AU42" t="n">
         <v>363003</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
+        <v>-0.155954</v>
+      </c>
+      <c r="AW42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AX42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AY42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AZ42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="BA42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BB42" t="n">
         <v>1.343208</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BC42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BD42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BE42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BF42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BE42" t="n">
+      <c r="BG42" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF42" t="n">
+      <c r="BH42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BI42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BH42" t="n">
+      <c r="BJ42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI42" t="n">
+      <c r="BK42" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BJ42" t="n">
+      <c r="BL42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BK42" t="n">
+      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8553,87 +8807,93 @@
         <v>0.48</v>
       </c>
       <c r="AJ43" t="n">
+        <v>107.44467</v>
+      </c>
+      <c r="AK43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AL43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AM43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AN43" t="n">
         <v>6464602</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AO43" t="n">
         <v>2499177</v>
       </c>
-      <c r="AO43" t="n">
+      <c r="AP43" t="n">
         <v>3965425</v>
       </c>
-      <c r="AP43" t="n">
+      <c r="AQ43" t="n">
         <v>3.08</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AR43" t="n">
         <v>2.21</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AS43" t="n">
         <v>3.63</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AT43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AU43" t="n">
         <v>329730</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
+        <v>-0.500274</v>
+      </c>
+      <c r="AW43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AX43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AY43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AZ43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="BA43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BB43" t="n">
         <v>0.909924</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BC43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BD43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BE43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BF43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BE43" t="n">
+      <c r="BG43" t="n">
         <v>1</v>
       </c>
-      <c r="BF43" t="n">
+      <c r="BH43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BI43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BH43" t="n">
+      <c r="BJ43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BI43" t="n">
+      <c r="BK43" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BJ43" t="n">
+      <c r="BL43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BK43" t="n">
+      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8744,87 +9004,93 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
+        <v>108.06979</v>
+      </c>
+      <c r="AK44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AL44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AM44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AN44" t="n">
         <v>6465016</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AO44" t="n">
         <v>2451957</v>
       </c>
-      <c r="AO44" t="n">
+      <c r="AP44" t="n">
         <v>4013059</v>
       </c>
-      <c r="AP44" t="n">
+      <c r="AQ44" t="n">
         <v>3.34</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AR44" t="n">
         <v>2.43</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AS44" t="n">
         <v>3.89</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AT44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AU44" t="n">
         <v>328303</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
+        <v>0.581806</v>
+      </c>
+      <c r="AW44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AX44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AY44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AZ44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="BA44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BB44" t="n">
         <v>1.201233</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BC44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BD44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BE44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BF44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BE44" t="n">
+      <c r="BG44" t="n">
         <v>1</v>
       </c>
-      <c r="BF44" t="n">
+      <c r="BH44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BI44" t="n">
         <v>0.001675</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>0.22</v>
       </c>
       <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
       <c r="BK44" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8935,87 +9201,93 @@
         <v>1.48</v>
       </c>
       <c r="AJ45" t="n">
+        <v>108.77346</v>
+      </c>
+      <c r="AK45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AL45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AM45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AN45" t="n">
         <v>6511444</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AO45" t="n">
         <v>2477151</v>
       </c>
-      <c r="AO45" t="n">
+      <c r="AP45" t="n">
         <v>4034293</v>
       </c>
-      <c r="AP45" t="n">
+      <c r="AQ45" t="n">
         <v>3.41</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AR45" t="n">
         <v>2.52</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AS45" t="n">
         <v>3.96</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AT45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AU45" t="n">
         <v>332508</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
+        <v>0.651126</v>
+      </c>
+      <c r="AW45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AX45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AY45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AZ45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="BA45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BB45" t="n">
         <v>0.529123</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BC45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BD45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BE45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BF45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BE45" t="n">
+      <c r="BG45" t="n">
         <v>0</v>
       </c>
-      <c r="BF45" t="n">
+      <c r="BH45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BI45" t="n">
         <v>0.003204</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="BK45" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9126,87 +9398,93 @@
         <v>0.51</v>
       </c>
       <c r="AJ46" t="n">
+        <v>110.09056</v>
+      </c>
+      <c r="AK46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AL46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AM46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AN46" t="n">
         <v>6576464</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AO46" t="n">
         <v>2498262</v>
       </c>
-      <c r="AO46" t="n">
+      <c r="AP46" t="n">
         <v>4078202</v>
       </c>
-      <c r="AP46" t="n">
+      <c r="AQ46" t="n">
         <v>3.44</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AR46" t="n">
         <v>2.49</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AS46" t="n">
         <v>4.03</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AT46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AU46" t="n">
         <v>336157</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
+        <v>1.210865</v>
+      </c>
+      <c r="AW46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AY46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AZ46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BA46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BB46" t="n">
         <v>1.088394</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BC46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BD46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BE46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BF46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BE46" t="n">
+      <c r="BG46" t="n">
         <v>1</v>
       </c>
-      <c r="BF46" t="n">
+      <c r="BH46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BI46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BH46" t="n">
+      <c r="BJ46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI46" t="n">
+      <c r="BK46" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ46" t="n">
+      <c r="BL46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BK46" t="n">
+      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9317,87 +9595,93 @@
         <v>0.48</v>
       </c>
       <c r="AJ47" t="n">
+        <v>109.72323</v>
+      </c>
+      <c r="AK47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AL47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AM47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AN47" t="n">
         <v>6623948</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AO47" t="n">
         <v>2512426</v>
       </c>
-      <c r="AO47" t="n">
+      <c r="AP47" t="n">
         <v>4111522</v>
       </c>
-      <c r="AP47" t="n">
+      <c r="AQ47" t="n">
         <v>3.67</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AR47" t="n">
         <v>2.72</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AS47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AT47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AU47" t="n">
         <v>340789</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
+        <v>-0.333662</v>
+      </c>
+      <c r="AW47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AY47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AZ47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="BA47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BB47" t="n">
         <v>0.8170269999999999</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BC47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BD47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BE47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BF47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BE47" t="n">
+      <c r="BG47" t="n">
         <v>0</v>
       </c>
-      <c r="BF47" t="n">
+      <c r="BH47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BI47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BH47" t="n">
+      <c r="BJ47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BI47" t="n">
+      <c r="BK47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BJ47" t="n">
+      <c r="BL47" t="n">
         <v>0.22</v>
       </c>
-      <c r="BK47" t="n">
+      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9508,87 +9792,93 @@
         <v>0.35</v>
       </c>
       <c r="AJ48" t="n">
+        <v>109.00057</v>
+      </c>
+      <c r="AK48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AL48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AM48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AN48" t="n">
         <v>6666287</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AO48" t="n">
         <v>2532708</v>
       </c>
-      <c r="AO48" t="n">
+      <c r="AP48" t="n">
         <v>4133579</v>
       </c>
-      <c r="AP48" t="n">
+      <c r="AQ48" t="n">
         <v>3.72</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AR48" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AS48" t="n">
         <v>4.36</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AT48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AU48" t="n">
         <v>341459</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
+        <v>-0.658621</v>
+      </c>
+      <c r="AW48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AX48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AY48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AZ48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BA48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BB48" t="n">
         <v>0.5364679999999999</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BC48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BD48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BE48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BF48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BE48" t="n">
+      <c r="BG48" t="n">
         <v>0.5</v>
       </c>
-      <c r="BF48" t="n">
+      <c r="BH48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BI48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BH48" t="n">
+      <c r="BJ48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI48" t="n">
+      <c r="BK48" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BJ48" t="n">
+      <c r="BL48" t="n">
         <v>0.11</v>
       </c>
-      <c r="BK48" t="n">
+      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9699,87 +9989,93 @@
         <v>0.23</v>
       </c>
       <c r="AJ49" t="n">
+        <v>108.76683</v>
+      </c>
+      <c r="AK49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AL49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AM49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AN49" t="n">
         <v>6703663</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AO49" t="n">
         <v>2547693</v>
       </c>
-      <c r="AO49" t="n">
+      <c r="AP49" t="n">
         <v>4155970</v>
       </c>
-      <c r="AP49" t="n">
+      <c r="AQ49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AR49" t="n">
         <v>2.67</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AS49" t="n">
         <v>4.41</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AT49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AU49" t="n">
         <v>344440</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
+        <v>-0.214439</v>
+      </c>
+      <c r="AW49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AY49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AZ49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="BA49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BB49" t="n">
         <v>0.541686</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BC49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BD49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BE49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BF49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BE49" t="n">
+      <c r="BG49" t="n">
         <v>0.25</v>
       </c>
-      <c r="BF49" t="n">
+      <c r="BH49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BI49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BH49" t="n">
+      <c r="BJ49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BI49" t="n">
+      <c r="BK49" t="n">
         <v>0</v>
       </c>
-      <c r="BJ49" t="n">
+      <c r="BL49" t="n">
         <v>0.05</v>
       </c>
-      <c r="BK49" t="n">
+      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9890,87 +10186,93 @@
         <v>0.21</v>
       </c>
       <c r="AJ50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="AK50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AL50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AM50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AN50" t="n">
         <v>6733209</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AO50" t="n">
         <v>2544400</v>
       </c>
-      <c r="AO50" t="n">
+      <c r="AP50" t="n">
         <v>4188808</v>
       </c>
-      <c r="AP50" t="n">
+      <c r="AQ50" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AR50" t="n">
         <v>2.79</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AS50" t="n">
         <v>4.66</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AT50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AU50" t="n">
         <v>345111</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="AW50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AX50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AY50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AZ50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="BA50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BB50" t="n">
         <v>0.79014</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BC50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BD50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BE50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BF50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BE50" t="n">
+      <c r="BG50" t="n">
         <v>0</v>
       </c>
-      <c r="BF50" t="n">
+      <c r="BH50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BI50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BH50" t="n">
+      <c r="BJ50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BI50" t="n">
+      <c r="BK50" t="n">
         <v>0.12</v>
       </c>
-      <c r="BJ50" t="n">
+      <c r="BL50" t="n">
         <v>0.25</v>
       </c>
-      <c r="BK50" t="n">
+      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10081,87 +10383,93 @@
         <v>-0.21</v>
       </c>
       <c r="AJ51" t="n">
+        <v>108.80021</v>
+      </c>
+      <c r="AK51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AL51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AM51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AN51" t="n">
         <v>6774436</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AO51" t="n">
         <v>2546265</v>
       </c>
-      <c r="AO51" t="n">
+      <c r="AP51" t="n">
         <v>4228171</v>
       </c>
-      <c r="AP51" t="n">
+      <c r="AQ51" t="n">
         <v>4.14</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AR51" t="n">
         <v>2.85</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AS51" t="n">
         <v>4.92</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AT51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AU51" t="n">
         <v>350767</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
+        <v>0.489219</v>
+      </c>
+      <c r="AW51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AX51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AY51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AZ51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="BA51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BB51" t="n">
         <v>0.9397180000000001</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BC51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BD51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BE51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BF51" t="n">
         <v>5.054283</v>
-      </c>
-      <c r="BE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF51" t="n">
-        <v>0</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
       </c>
       <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BI51" t="n">
+      <c r="BK51" t="n">
         <v>0.06</v>
       </c>
-      <c r="BJ51" t="n">
+      <c r="BL51" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK51" t="n">
+      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10272,87 +10580,93 @@
         <v>0.52</v>
       </c>
       <c r="AJ52" t="n">
+        <v>108.63642</v>
+      </c>
+      <c r="AK52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AL52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AM52" t="n">
         <v>5.318</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AN52" t="n">
         <v>6852705</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AO52" t="n">
         <v>2589817</v>
       </c>
-      <c r="AO52" t="n">
+      <c r="AP52" t="n">
         <v>4262888</v>
       </c>
-      <c r="AP52" t="n">
+      <c r="AQ52" t="n">
         <v>4.09</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AR52" t="n">
         <v>2.77</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AS52" t="n">
         <v>4.89</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AT52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AU52" t="n">
         <v>356582</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
+        <v>-0.150542</v>
+      </c>
+      <c r="AW52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AY52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AZ52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="BA52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BB52" t="n">
         <v>0.821088</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BC52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BD52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BE52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BF52" t="n">
         <v>5.096104</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
       </c>
       <c r="BG52" t="n">
         <v>0</v>
       </c>
       <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BI52" t="n">
+      <c r="BK52" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ52" t="n">
+      <c r="BL52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BK52" t="n">
+      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10463,87 +10777,93 @@
         <v>0.03</v>
       </c>
       <c r="AJ53" t="n">
+        <v>108.7159</v>
+      </c>
+      <c r="AK53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AL53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AM53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AN53" t="n">
         <v>6923886</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AO53" t="n">
         <v>2597630</v>
       </c>
-      <c r="AO53" t="n">
+      <c r="AP53" t="n">
         <v>4326256</v>
       </c>
-      <c r="AP53" t="n">
+      <c r="AQ53" t="n">
         <v>4.18</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AR53" t="n">
         <v>2.82</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AS53" t="n">
         <v>4.99</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AT53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AU53" t="n">
         <v>357103</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
+        <v>0.073161</v>
+      </c>
+      <c r="AW53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AX53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AY53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AZ53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="BA53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BB53" t="n">
         <v>1.486504</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BC53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BD53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BE53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BF53" t="n">
         <v>4.490243</v>
-      </c>
-      <c r="BE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF53" t="n">
-        <v>0</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
       </c>
       <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BI53" t="n">
+      <c r="BK53" t="n">
         <v>0.05</v>
       </c>
-      <c r="BJ53" t="n">
+      <c r="BL53" t="n">
         <v>0.1</v>
       </c>
-      <c r="BK53" t="n">
+      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10654,87 +10974,93 @@
         <v>0.03</v>
       </c>
       <c r="AJ54" t="n">
+        <v>109.27405</v>
+      </c>
+      <c r="AK54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AL54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AM54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AN54" t="n">
         <v>7003273</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AO54" t="n">
         <v>2616213</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AP54" t="n">
         <v>4387061</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AQ54" t="n">
         <v>4.23</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AR54" t="n">
         <v>2.74</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AS54" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AT54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AU54" t="n">
         <v>360578</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
+        <v>0.513402</v>
+      </c>
+      <c r="AW54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AX54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AY54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AZ54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="BA54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BB54" t="n">
         <v>1.405488</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BC54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BD54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BE54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BF54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BG54" t="n">
         <v>0</v>
       </c>
-      <c r="BF54" t="n">
+      <c r="BH54" t="n">
         <v>-0</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BI54" t="n">
         <v>-0</v>
       </c>
-      <c r="BH54" t="n">
+      <c r="BJ54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BI54" t="n">
+      <c r="BK54" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BJ54" t="n">
+      <c r="BL54" t="n">
         <v>0.13</v>
       </c>
-      <c r="BK54" t="n">
+      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10845,87 +11171,93 @@
         <v>0.21</v>
       </c>
       <c r="AJ55" t="n">
+        <v>109.41762</v>
+      </c>
+      <c r="AK55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AL55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AM55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AN55" t="n">
         <v>7136436</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AO55" t="n">
         <v>2701146</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AP55" t="n">
         <v>4435290</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AQ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AR55" t="n">
         <v>2.68</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AS55" t="n">
         <v>5.12</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AT55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AU55" t="n">
         <v>358234</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
+        <v>0.131385</v>
+      </c>
+      <c r="AW55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AX55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AY55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AZ55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="BA55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BB55" t="n">
         <v>1.099346</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BC55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BD55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BE55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="BD55" t="n">
+      <c r="BF55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
       </c>
       <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ55" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BI55" t="n">
+      <c r="BK55" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BJ55" t="n">
+      <c r="BL55" t="n">
         <v>0</v>
       </c>
-      <c r="BK55" t="n">
+      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11036,87 +11368,93 @@
         <v>0.39</v>
       </c>
       <c r="AJ56" t="n">
+        <v>110.05486</v>
+      </c>
+      <c r="AK56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AL56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AM56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AN56" t="n">
         <v>7130500</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AO56" t="n">
         <v>2654052</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AP56" t="n">
         <v>4476448</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AQ56" t="n">
         <v>4.45</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AR56" t="n">
         <v>2.87</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AS56" t="n">
         <v>5.38</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AT56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AU56" t="n">
         <v>364367</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
+        <v>0.582392</v>
+      </c>
+      <c r="AW56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AX56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AY56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AZ56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="BA56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BB56" t="n">
         <v>0.927966</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BC56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BD56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BE56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BF56" t="n">
         <v>4.303068</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
       </c>
       <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BI56" t="n">
+      <c r="BK56" t="n">
         <v>0.19</v>
       </c>
-      <c r="BJ56" t="n">
+      <c r="BL56" t="n">
         <v>0.26</v>
       </c>
-      <c r="BK56" t="n">
+      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11227,87 +11565,93 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AJ57" t="n">
+        <v>110.65892</v>
+      </c>
+      <c r="AK57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AL57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AM57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AN57" t="n">
         <v>7156987</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AO57" t="n">
         <v>2655931</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AP57" t="n">
         <v>4501056</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AQ57" t="n">
         <v>4.64</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AR57" t="n">
         <v>3.07</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AS57" t="n">
         <v>5.56</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AT57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AU57" t="n">
         <v>371074</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
+        <v>0.548872</v>
+      </c>
+      <c r="AW57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AX57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AY57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AZ57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="BA57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BB57" t="n">
         <v>0.549722</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BC57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BD57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BE57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BF57" t="n">
         <v>3.357475</v>
-      </c>
-      <c r="BE57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF57" t="n">
-        <v>0</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
       </c>
       <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BI57" t="n">
+      <c r="BK57" t="n">
         <v>0.2</v>
       </c>
-      <c r="BJ57" t="n">
+      <c r="BL57" t="n">
         <v>0.18</v>
       </c>
-      <c r="BK57" t="n">
+      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11418,87 +11762,93 @@
         <v>0.91</v>
       </c>
       <c r="AJ58" t="n">
+        <v>110.51078</v>
+      </c>
+      <c r="AK58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AL58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AL58" t="n">
+      <c r="AM58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AM58" t="n">
+      <c r="AN58" t="n">
         <v>7237735</v>
       </c>
-      <c r="AN58" t="n">
+      <c r="AO58" t="n">
         <v>2686046</v>
       </c>
-      <c r="AO58" t="n">
+      <c r="AP58" t="n">
         <v>4551689</v>
       </c>
-      <c r="AP58" t="n">
+      <c r="AQ58" t="n">
         <v>4.52</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AR58" t="n">
         <v>3.04</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AS58" t="n">
         <v>5.4</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AT58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AU58" t="n">
         <v>362002</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
+        <v>-0.133871</v>
+      </c>
+      <c r="AW58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AX58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AY58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AZ58" t="n">
         <v>1.12824</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="BA58" t="n">
         <v>1.133877</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BB58" t="n">
         <v>1.124914</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BC58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BD58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BE58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="BD58" t="n">
+      <c r="BF58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BE58" t="n">
+      <c r="BG58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF58" t="n">
+      <c r="BH58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BI58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BH58" t="n">
+      <c r="BJ58" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BI58" t="n">
+      <c r="BK58" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BJ58" t="n">
+      <c r="BL58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BK58" t="n">
+      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11609,87 +11959,93 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AJ59" t="n">
+        <v>110.95732</v>
+      </c>
+      <c r="AK59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AL59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AL59" t="n">
+      <c r="AM59" t="n">
         <v>4.988</v>
       </c>
-      <c r="AM59" t="n">
+      <c r="AN59" t="n">
         <v>7258599</v>
       </c>
-      <c r="AN59" t="n">
+      <c r="AO59" t="n">
         <v>2684623</v>
       </c>
-      <c r="AO59" t="n">
+      <c r="AP59" t="n">
         <v>4573976</v>
       </c>
-      <c r="AP59" t="n">
+      <c r="AQ59" t="n">
         <v>4.63</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AR59" t="n">
         <v>3.15</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AS59" t="n">
         <v>5.51</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AT59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AU59" t="n">
         <v>366913</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
+        <v>0.404069</v>
+      </c>
+      <c r="AW59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AX59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AY59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AZ59" t="n">
         <v>0.288267</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="BA59" t="n">
         <v>-0.052977</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BB59" t="n">
         <v>0.489642</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BC59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BD59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BE59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BF59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BG59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF59" t="n">
+      <c r="BH59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="BG59" t="n">
+      <c r="BI59" t="n">
         <v>-0.000554</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI59" t="n">
-        <v>0.11</v>
       </c>
       <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
       <c r="BK59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BL59" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11800,87 +12156,93 @@
         <v>0.65</v>
       </c>
       <c r="AJ60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="AK60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="AK60" t="n">
+      <c r="AL60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL60" t="n">
+      <c r="AM60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AM60" t="n">
+      <c r="AN60" t="n">
         <v>7299615</v>
       </c>
-      <c r="AN60" t="n">
+      <c r="AO60" t="n">
         <v>2704550</v>
       </c>
-      <c r="AO60" t="n">
+      <c r="AP60" t="n">
         <v>4595065</v>
       </c>
-      <c r="AP60" t="n">
+      <c r="AQ60" t="n">
         <v>4.74</v>
       </c>
-      <c r="AQ60" t="n">
+      <c r="AR60" t="n">
         <v>3.24</v>
       </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
         <v>5.62</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AT60" t="n">
         <v>33.42</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AU60" t="n">
         <v>371137</v>
       </c>
-      <c r="AU60" t="n">
+      <c r="AV60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="AW60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="AV60" t="n">
+      <c r="AX60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AW60" t="n">
+      <c r="AY60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AZ60" t="n">
         <v>0.565068</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="BA60" t="n">
         <v>0.742264</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BB60" t="n">
         <v>0.461065</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BC60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BD60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BE60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BF60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BE60" t="n">
+      <c r="BG60" t="n">
         <v>0</v>
       </c>
-      <c r="BF60" t="n">
+      <c r="BH60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="BG60" t="n">
+      <c r="BI60" t="n">
         <v>-0.0008229999999999999</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>0.09</v>
       </c>
       <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
       <c r="BK60" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BL60" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -11991,145 +12353,147 @@
         <v>0.14</v>
       </c>
       <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="n">
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AL61" t="n">
+      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
-      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AT61" t="inlineStr"/>
+      <c r="AU61" t="n">
         <v>367558</v>
       </c>
-      <c r="AU61" t="inlineStr"/>
-      <c r="AV61" t="n">
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AW61" t="n">
+      <c r="AY61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="AX61" t="inlineStr"/>
-      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="n">
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="BB61" t="n">
+      <c r="BD61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BE61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="BD61" t="n">
+      <c r="BF61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="BE61" t="n">
+      <c r="BG61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BF61" t="n">
+      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BG61" t="n">
+      <c r="BI61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BH61" t="inlineStr"/>
-      <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
       <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>176724</v>
+        <v>175335</v>
       </c>
       <c r="C62" t="n">
-        <v>170.949997</v>
+        <v>172.75</v>
       </c>
       <c r="D62" t="n">
-        <v>105.050003</v>
+        <v>106.699997</v>
       </c>
       <c r="E62" t="n">
-        <v>425.049988</v>
+        <v>426.859985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0846</v>
+        <v>5.1097</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7877</v>
+        <v>5.8091</v>
       </c>
       <c r="H62" t="n">
-        <v>7408.299805</v>
+        <v>7413.180176</v>
       </c>
       <c r="I62" t="n">
-        <v>25137.689453</v>
+        <v>24932.080078</v>
       </c>
       <c r="J62" t="n">
-        <v>51711.648438</v>
+        <v>52210.078125</v>
       </c>
       <c r="K62" t="n">
-        <v>4089.899902</v>
+        <v>4026.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>83.93000000000001</v>
+        <v>81.860001</v>
       </c>
       <c r="M62" t="n">
-        <v>90.550003</v>
+        <v>87.160004</v>
       </c>
       <c r="N62" t="n">
-        <v>1220.25</v>
+        <v>1208.5</v>
       </c>
       <c r="O62" t="n">
-        <v>473.75</v>
+        <v>475.75</v>
       </c>
       <c r="P62" t="n">
-        <v>2.732177</v>
+        <v>1.924731</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.123924</v>
+        <v>2.1887</v>
       </c>
       <c r="R62" t="n">
-        <v>-2.713466</v>
+        <v>-1.185411</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.433147</v>
+        <v>-2.017677</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.875551</v>
+        <v>-1.391157</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.187871</v>
+        <v>-1.826212</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.214238</v>
+        <v>-1.149161</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.10484</v>
+        <v>-4.889198</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.161239</v>
+        <v>-0.208568</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.665465</v>
+        <v>0.091978</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.76259</v>
+        <v>17.784174</v>
       </c>
       <c r="AA62" t="n">
-        <v>24.177188</v>
+        <v>19.528258</v>
       </c>
       <c r="AB62" t="n">
-        <v>9.267965</v>
+        <v>8.215805</v>
       </c>
       <c r="AC62" t="n">
-        <v>14.778922</v>
+        <v>15.263477</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12144,13 +12508,13 @@
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="n">
-        <v>5.0666</v>
-      </c>
+      <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="n">
-        <v>5.066</v>
-      </c>
-      <c r="AM62" t="inlineStr"/>
+        <v>5.1005</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>5.0998</v>
+      </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
@@ -12159,32 +12523,34 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
       <c r="AU62" t="inlineStr"/>
-      <c r="AV62" t="n">
-        <v>-2.124947</v>
-      </c>
-      <c r="AW62" t="n">
-        <v>-2.125193</v>
-      </c>
-      <c r="AX62" t="inlineStr"/>
-      <c r="AY62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="n">
+        <v>-1.470077</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>-1.472179</v>
+      </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
-      <c r="BE62" t="n">
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="n">
         <v>0</v>
       </c>
-      <c r="BF62" t="n">
+      <c r="BH62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BG62" t="n">
+      <c r="BI62" t="n">
         <v>-0.000497</v>
       </c>
-      <c r="BH62" t="inlineStr"/>
-      <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
       <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM62"/>
+  <dimension ref="A1:BG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,170 +578,140 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>bcb_sgs_cdi</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_saldo_credito_pf</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
-        </is>
-      </c>
-      <c r="BC1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_cdi</t>
-        </is>
-      </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pj</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -814,53 +784,47 @@
         <v>0.016137</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.016137</v>
+        <v>0.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.96</v>
+        <v>0.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.02</v>
+        <v>99.83978</v>
       </c>
       <c r="AJ2" t="n">
-        <v>96.31464</v>
+        <v>5.1216</v>
       </c>
       <c r="AK2" t="n">
-        <v>99.83978</v>
+        <v>5.121</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>2.36</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>1.58</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>2.94</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>20.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AU2" t="n">
         <v>355671</v>
       </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
@@ -873,12 +837,6 @@
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -975,99 +933,81 @@
         <v>0.019413</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.019413</v>
+        <v>0.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.87</v>
+        <v>0.66</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.66</v>
+        <v>0.88</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.88</v>
+        <v>99.32829</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>1851006</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>2.37</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>1.56</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>2.96</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>20.92</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.56</v>
+        <v>370395</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.96</v>
+        <v>-0.512311</v>
       </c>
       <c r="AT3" t="n">
-        <v>20.92</v>
+        <v>0.423696</v>
       </c>
       <c r="AU3" t="n">
-        <v>370395</v>
+        <v>0.423745</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.79016</v>
+        <v>1.736829</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.512311</v>
+        <v>0.972464</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423696</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0.423745</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.736829</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0.972464</v>
-      </c>
+        <v>4.139781</v>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>2.311409</v>
+        <v>1</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.139781</v>
-      </c>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+        <v>0.003276</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="BG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0.003276</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1166,99 +1106,81 @@
         <v>0.021003</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.021003</v>
+        <v>1.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.16</v>
+        <v>-0.64</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.64</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.2</v>
+        <v>97.24746</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.95968999999999</v>
+        <v>5.4394</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.24746</v>
+        <v>5.4388</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4394</v>
+        <v>4441056</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>1894119</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>2.34</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>1.43</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>3.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>21.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.43</v>
+        <v>368886</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.01</v>
+        <v>-2.094902</v>
       </c>
       <c r="AT4" t="n">
-        <v>21.42</v>
+        <v>5.757004</v>
       </c>
       <c r="AU4" t="n">
-        <v>368886</v>
+        <v>5.757676</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.119484</v>
+        <v>2.185796</v>
       </c>
       <c r="AW4" t="n">
-        <v>-2.094902</v>
+        <v>2.329166</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757004</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>5.757676</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.185796</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.329166</v>
-      </c>
+        <v>-0.407403</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>2.079394</v>
+        <v>1</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.407403</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+        <v>0.001591</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.05</v>
+      </c>
       <c r="BG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0.001591</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.001591</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1357,99 +1279,81 @@
         <v>0.024244</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.024244</v>
+        <v>1.25</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.16</v>
+        <v>96.62081999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.48142</v>
+        <v>5.643</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.6424</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.643</v>
+        <v>4511956</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>1910940</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>2.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>1.43</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>2.99</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>22.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.43</v>
+        <v>367927</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.99</v>
+        <v>-0.644377</v>
       </c>
       <c r="AT5" t="n">
-        <v>22.89</v>
+        <v>3.74306</v>
       </c>
       <c r="AU5" t="n">
-        <v>367927</v>
+        <v>3.743473</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.53809</v>
+        <v>1.596467</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.644377</v>
+        <v>0.888065</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.74306</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.743473</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.596467</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.888065</v>
-      </c>
+        <v>-0.259972</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>2.123375</v>
+        <v>1.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.259972</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+        <v>0.00324</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>-0.02</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0.00324</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0.00324</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BM5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1548,99 +1452,81 @@
         <v>0.029256</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.029256</v>
+        <v>0.95</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.95</v>
+        <v>0.02</v>
       </c>
       <c r="AH6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>98.05768</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5.6199</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>5.6193</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4597507</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1933111</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>367772</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.487112</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0.409357</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0.4094</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.896096</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.160214</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.042128</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AI6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>98.97262000000001</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>98.05768</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>5.6199</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>5.6193</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>4597507</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1933111</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2664395</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>23.91</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>367772</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.529727</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.487112</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>-0.409357</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>-0.4094</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>-0.042128</v>
-      </c>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>0.005012</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1739,99 +1625,81 @@
         <v>0.033316</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.033316</v>
+        <v>0.73</v>
       </c>
       <c r="AG7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AH7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0.87</v>
-      </c>
       <c r="AI7" t="n">
-        <v>0.73</v>
+        <v>99.33126</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.35339</v>
+        <v>5.5805</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.33126</v>
+        <v>5.5799</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.5805</v>
+        <v>4682852</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>1974391</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>2.35</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>1.4</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>3.05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>24.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.4</v>
+        <v>362204</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>1.298807</v>
       </c>
       <c r="AT7" t="n">
-        <v>24.21</v>
+        <v>-0.70108</v>
       </c>
       <c r="AU7" t="n">
-        <v>362204</v>
+        <v>-0.701155</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.384723</v>
+        <v>1.856332</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.298807</v>
+        <v>2.135418</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.70108</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>-0.701155</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>1.856332</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>2.135418</v>
-      </c>
+        <v>-1.513981</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="n">
-        <v>1.653884</v>
+        <v>1.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>-1.513981</v>
-      </c>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+        <v>0.00406</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.04</v>
+      </c>
       <c r="BG7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0.00406</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1930,99 +1798,81 @@
         <v>0.034749</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.034749</v>
+        <v>0.54</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.54</v>
+        <v>1.82</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>0.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.67</v>
+        <v>90.45032</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.34401</v>
+        <v>5.3574</v>
       </c>
       <c r="AK8" t="n">
-        <v>90.45032</v>
+        <v>5.3568</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.3574</v>
+        <v>4682131</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>1947035</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>2.51</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>1.46</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>3.26</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>25.23</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.46</v>
+        <v>358398</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.26</v>
+        <v>-8.94073</v>
       </c>
       <c r="AT8" t="n">
-        <v>25.23</v>
+        <v>-3.99785</v>
       </c>
       <c r="AU8" t="n">
-        <v>358398</v>
+        <v>-3.99828</v>
       </c>
       <c r="AV8" t="n">
-        <v>-2.022457</v>
+        <v>-0.015397</v>
       </c>
       <c r="AW8" t="n">
-        <v>-8.94073</v>
+        <v>-1.385541</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99785</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>-3.99828</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-0.015397</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>-1.385541</v>
-      </c>
+        <v>-1.050789</v>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="n">
-        <v>0.9834000000000001</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-1.050789</v>
-      </c>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+        <v>0.001433</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0.21</v>
+      </c>
       <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>0.001433</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BM8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2121,99 +1971,81 @@
         <v>0.039598</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.039598</v>
+        <v>1.01</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.83</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>95.72214</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.43725000000001</v>
+        <v>5.1394</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.72214</v>
+        <v>5.1388</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.1394</v>
+        <v>4727818</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>1971524</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>2.57</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>1.44</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>3.38</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>25.63</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.44</v>
+        <v>357740</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.38</v>
+        <v>5.828415</v>
       </c>
       <c r="AT9" t="n">
-        <v>25.63</v>
+        <v>-4.069138</v>
       </c>
       <c r="AU9" t="n">
-        <v>357740</v>
+        <v>-4.069594</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.123069</v>
+        <v>0.975774</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.828415</v>
+        <v>1.257759</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069138</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>-4.069594</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.975774</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.257759</v>
-      </c>
+        <v>-0.183595</v>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="n">
-        <v>0.775073</v>
+        <v>1.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0.183595</v>
-      </c>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+        <v>0.004849</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.12</v>
+      </c>
       <c r="BG9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>0.004849</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BM9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2312,99 +2144,81 @@
         <v>0.041954</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.041954</v>
+        <v>1.62</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.71</v>
+        <v>104.61484</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.55981</v>
+        <v>4.7378</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.61484</v>
+        <v>4.7372</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.7378</v>
+        <v>4794583</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>1994119</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>2.66</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>1.55</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>3.45</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>26.54</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>353169</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.45</v>
+        <v>9.290118</v>
       </c>
       <c r="AT10" t="n">
-        <v>26.54</v>
+        <v>-7.814142</v>
       </c>
       <c r="AU10" t="n">
-        <v>353169</v>
+        <v>-7.815054</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.140381</v>
+        <v>1.412174</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.290118</v>
+        <v>1.146068</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.814142</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>-7.815054</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.412174</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.146068</v>
-      </c>
+        <v>-1.277744</v>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="n">
-        <v>1.602477</v>
+        <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>-1.277744</v>
-      </c>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+        <v>0.002356</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
       <c r="BG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>0.002356</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2503,99 +2317,81 @@
         <v>0.043739</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.043739</v>
+        <v>1.06</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.04</v>
+        <v>100.42352</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.51646</v>
+        <v>4.9191</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.42352</v>
+        <v>4.9185</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9191</v>
+        <v>4833732</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>2003312</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2.72</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>1.57</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>3.54</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>27.46</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.57</v>
+        <v>345097</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.54</v>
+        <v>-4.00643</v>
       </c>
       <c r="AT11" t="n">
-        <v>27.46</v>
+        <v>3.826671</v>
       </c>
       <c r="AU11" t="n">
-        <v>345097</v>
+        <v>3.827155</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.043542</v>
+        <v>0.816526</v>
       </c>
       <c r="AW11" t="n">
-        <v>-4.00643</v>
+        <v>0.461006</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.826671</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.827155</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.816526</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0.461006</v>
-      </c>
+        <v>-2.285591</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="n">
-        <v>1.06968</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-2.285591</v>
-      </c>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+        <v>0.001785</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.09</v>
+      </c>
       <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>0.001785</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2694,99 +2490,81 @@
         <v>0.046796</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.046796</v>
+        <v>0.47</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.47</v>
+        <v>0.52</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.45</v>
+        <v>99.79777</v>
       </c>
       <c r="AJ12" t="n">
-        <v>99.67415</v>
+        <v>4.7289</v>
       </c>
       <c r="AK12" t="n">
-        <v>99.79777</v>
+        <v>4.7283</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.7289</v>
+        <v>4889397</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.7283</v>
+        <v>2013726</v>
       </c>
       <c r="AN12" t="n">
-        <v>4889397</v>
+        <v>2.79</v>
       </c>
       <c r="AO12" t="n">
-        <v>2013726</v>
+        <v>1.57</v>
       </c>
       <c r="AP12" t="n">
-        <v>2875671</v>
+        <v>3.65</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.79</v>
+        <v>27.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.57</v>
+        <v>346415</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.65</v>
+        <v>-0.623111</v>
       </c>
       <c r="AT12" t="n">
-        <v>27.42</v>
+        <v>-3.866561</v>
       </c>
       <c r="AU12" t="n">
-        <v>346415</v>
+        <v>-3.867033</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.158456</v>
+        <v>1.151595</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.623111</v>
+        <v>0.5198390000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>-3.866561</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>-3.867033</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.151595</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0.5198390000000001</v>
-      </c>
+        <v>0.381922</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="n">
-        <v>1.598738</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.381922</v>
-      </c>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+        <v>0.003057</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0.11</v>
+      </c>
       <c r="BG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0.003057</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2885,105 +2663,87 @@
         <v>0.048116</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.048116</v>
+        <v>0.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.67</v>
+        <v>0.59</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.62</v>
+        <v>99.53784</v>
       </c>
       <c r="AJ13" t="n">
-        <v>99.6343</v>
+        <v>5.238</v>
       </c>
       <c r="AK13" t="n">
-        <v>99.53784</v>
+        <v>5.2374</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.238</v>
+        <v>4965603</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.2374</v>
+        <v>2052569</v>
       </c>
       <c r="AN13" t="n">
-        <v>4965603</v>
+        <v>2.73</v>
       </c>
       <c r="AO13" t="n">
-        <v>2052569</v>
+        <v>1.52</v>
       </c>
       <c r="AP13" t="n">
-        <v>2913035</v>
+        <v>3.57</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.73</v>
+        <v>27.88</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>341958</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.57</v>
+        <v>-0.260457</v>
       </c>
       <c r="AT13" t="n">
-        <v>27.88</v>
+        <v>10.765717</v>
       </c>
       <c r="AU13" t="n">
-        <v>341958</v>
+        <v>10.767083</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.03998</v>
+        <v>1.558597</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.260457</v>
+        <v>1.928912</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.765717</v>
+        <v>-1.286607</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.767083</v>
+        <v>11.88673</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.558597</v>
+        <v>10.700862</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.928912</v>
+        <v>11.919595</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.299314</v>
+        <v>0.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>-1.286607</v>
+        <v>0.00132</v>
       </c>
       <c r="BD13" t="n">
-        <v>11.88673</v>
+        <v>-0.06</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.700862</v>
+        <v>-0.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>11.919595</v>
+        <v>-0.08</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0.00132</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BM13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -3082,105 +2842,87 @@
         <v>0.049037</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.049037</v>
+        <v>-0.68</v>
       </c>
       <c r="AG14" t="n">
-        <v>-0.68</v>
+        <v>0.21</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.21</v>
+        <v>-0.6</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.6</v>
+        <v>103.95861</v>
       </c>
       <c r="AJ14" t="n">
-        <v>101.27684</v>
+        <v>5.1884</v>
       </c>
       <c r="AK14" t="n">
-        <v>103.95861</v>
+        <v>5.1878</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.1884</v>
+        <v>4999244</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.1878</v>
+        <v>2047038</v>
       </c>
       <c r="AN14" t="n">
-        <v>4999244</v>
+        <v>2.84</v>
       </c>
       <c r="AO14" t="n">
-        <v>2047038</v>
+        <v>1.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>2952207</v>
+        <v>3.71</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.84</v>
+        <v>29.24</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.6</v>
+        <v>346403</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.71</v>
+        <v>4.441296</v>
       </c>
       <c r="AT14" t="n">
-        <v>29.24</v>
+        <v>-0.946926</v>
       </c>
       <c r="AU14" t="n">
-        <v>346403</v>
+        <v>-0.947035</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.648569</v>
+        <v>0.677481</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.441296</v>
+        <v>-0.269467</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.946926</v>
+        <v>1.299867</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.947035</v>
+        <v>10.069235</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.677481</v>
+        <v>10.074751</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0.269467</v>
+        <v>10.124804</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.344714</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.299867</v>
+        <v>0.0009210000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.069235</v>
+        <v>0.11</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.074751</v>
+        <v>0.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>10.124804</v>
+        <v>0.14</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>0.0009210000000000001</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BM14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3279,105 +3021,87 @@
         <v>0.05056</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05056</v>
+        <v>-0.36</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0.36</v>
+        <v>-0.7</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0.7</v>
+        <v>-0.31</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.31</v>
+        <v>104.56278</v>
       </c>
       <c r="AJ15" t="n">
-        <v>101.07328</v>
+        <v>5.179</v>
       </c>
       <c r="AK15" t="n">
-        <v>104.56278</v>
+        <v>5.1784</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.179</v>
+        <v>5072711</v>
       </c>
       <c r="AM15" t="n">
-        <v>5.1784</v>
+        <v>2064183</v>
       </c>
       <c r="AN15" t="n">
-        <v>5072711</v>
+        <v>2.9</v>
       </c>
       <c r="AO15" t="n">
-        <v>2064183</v>
+        <v>1.62</v>
       </c>
       <c r="AP15" t="n">
-        <v>3008528</v>
+        <v>3.78</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.9</v>
+        <v>28.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.62</v>
+        <v>339664</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.78</v>
+        <v>0.581164</v>
       </c>
       <c r="AT15" t="n">
-        <v>28.6</v>
+        <v>-0.181173</v>
       </c>
       <c r="AU15" t="n">
-        <v>339664</v>
+        <v>-0.181194</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.200994</v>
+        <v>1.469562</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.581164</v>
+        <v>0.837552</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.181173</v>
+        <v>-1.945422</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.181194</v>
+        <v>8.727061000000001</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.469562</v>
+        <v>8.58755</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.837552</v>
+        <v>8.825751</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.907759</v>
+        <v>0.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>-1.945422</v>
+        <v>0.001523</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.727061000000001</v>
+        <v>0.06</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.58755</v>
+        <v>0.02</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.825751</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>0.001523</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3476,105 +3200,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.050788</v>
+        <v>-0.29</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.29</v>
+        <v>-0.95</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0.95</v>
+        <v>-0.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.32</v>
+        <v>101.38087</v>
       </c>
       <c r="AJ16" t="n">
-        <v>101.17973</v>
+        <v>5.4066</v>
       </c>
       <c r="AK16" t="n">
-        <v>101.38087</v>
+        <v>5.406</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.4066</v>
+        <v>5164775</v>
       </c>
       <c r="AM16" t="n">
-        <v>5.406</v>
+        <v>2109806</v>
       </c>
       <c r="AN16" t="n">
-        <v>5164775</v>
+        <v>2.92</v>
       </c>
       <c r="AO16" t="n">
-        <v>2109806</v>
+        <v>1.65</v>
       </c>
       <c r="AP16" t="n">
-        <v>3054969</v>
+        <v>3.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.92</v>
+        <v>28.57</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.65</v>
+        <v>327580</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.8</v>
+        <v>-3.043062</v>
       </c>
       <c r="AT16" t="n">
-        <v>28.57</v>
+        <v>4.394671</v>
       </c>
       <c r="AU16" t="n">
-        <v>327580</v>
+        <v>4.39518</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.10532</v>
+        <v>1.814888</v>
       </c>
       <c r="AW16" t="n">
-        <v>-3.043062</v>
+        <v>2.210221</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.394671</v>
+        <v>-3.557633</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.39518</v>
+        <v>7.168596</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.814888</v>
+        <v>8.248760000000001</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.210221</v>
+        <v>7.191214</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.543645</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-3.557633</v>
+        <v>0.000228</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.168596</v>
+        <v>0.02</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.248760000000001</v>
+        <v>0.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.191214</v>
+        <v>0.02</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>0.000228</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3673,105 +3379,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.050788</v>
+        <v>0.59</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.59</v>
+        <v>-0.97</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0.97</v>
+        <v>0.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.47</v>
+        <v>100.20398</v>
       </c>
       <c r="AJ17" t="n">
-        <v>101.46342</v>
+        <v>5.257</v>
       </c>
       <c r="AK17" t="n">
-        <v>100.20398</v>
+        <v>5.2564</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.257</v>
+        <v>5215990</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.2564</v>
+        <v>2105856</v>
       </c>
       <c r="AN17" t="n">
-        <v>5215990</v>
+        <v>3.04</v>
       </c>
       <c r="AO17" t="n">
-        <v>2105856</v>
+        <v>1.77</v>
       </c>
       <c r="AP17" t="n">
-        <v>3110134</v>
+        <v>3.89</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.04</v>
+        <v>29.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.77</v>
+        <v>325546</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.89</v>
+        <v>-1.16086</v>
       </c>
       <c r="AT17" t="n">
-        <v>29.68</v>
+        <v>-2.766988</v>
       </c>
       <c r="AU17" t="n">
-        <v>325546</v>
+        <v>-2.767296</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.280382</v>
+        <v>0.991621</v>
       </c>
       <c r="AW17" t="n">
-        <v>-1.16086</v>
+        <v>-0.187221</v>
       </c>
       <c r="AX17" t="n">
-        <v>-2.766988</v>
+        <v>-0.6209170000000001</v>
       </c>
       <c r="AY17" t="n">
-        <v>-2.767296</v>
+        <v>6.470016</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.991621</v>
+        <v>6.517038</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0.187221</v>
+        <v>6.460076</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.805747</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.6209170000000001</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.470016</v>
+        <v>0.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.517038</v>
+        <v>0.12</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.460076</v>
+        <v>0.09</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3870,105 +3558,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.050788</v>
+        <v>0.41</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AH18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.38</v>
+        <v>99.36927</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100.66227</v>
+        <v>5.2941</v>
       </c>
       <c r="AK18" t="n">
-        <v>99.36927</v>
+        <v>5.2935</v>
       </c>
       <c r="AL18" t="n">
-        <v>5.2941</v>
+        <v>5285657</v>
       </c>
       <c r="AM18" t="n">
-        <v>5.2935</v>
+        <v>2130312</v>
       </c>
       <c r="AN18" t="n">
-        <v>5285657</v>
+        <v>3.07</v>
       </c>
       <c r="AO18" t="n">
-        <v>2130312</v>
+        <v>1.81</v>
       </c>
       <c r="AP18" t="n">
-        <v>3155345</v>
+        <v>3.92</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.07</v>
+        <v>30.52</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>331505</v>
       </c>
       <c r="AS18" t="n">
-        <v>3.92</v>
+        <v>-0.8330109999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>30.52</v>
+        <v>0.705726</v>
       </c>
       <c r="AU18" t="n">
-        <v>331505</v>
+        <v>0.705806</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.789595</v>
+        <v>1.335643</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0.8330109999999999</v>
+        <v>1.161333</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.705726</v>
+        <v>1.830463</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.705806</v>
+        <v>5.900488</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.335643</v>
+        <v>5.899363</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.161333</v>
+        <v>5.974439</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.453667</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.830463</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.900488</v>
+        <v>0.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.899363</v>
+        <v>0.04</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.974439</v>
+        <v>0.03</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BM18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -4067,105 +3737,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.050788</v>
+        <v>0.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.6899999999999999</v>
+        <v>99.97806</v>
       </c>
       <c r="AJ19" t="n">
-        <v>100.58196</v>
+        <v>5.2177</v>
       </c>
       <c r="AK19" t="n">
-        <v>99.97806</v>
+        <v>5.2171</v>
       </c>
       <c r="AL19" t="n">
-        <v>5.2177</v>
+        <v>5366069</v>
       </c>
       <c r="AM19" t="n">
-        <v>5.2171</v>
+        <v>2178236</v>
       </c>
       <c r="AN19" t="n">
-        <v>5366069</v>
+        <v>3.07</v>
       </c>
       <c r="AO19" t="n">
-        <v>2178236</v>
+        <v>1.8</v>
       </c>
       <c r="AP19" t="n">
-        <v>3187833</v>
+        <v>3.94</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.07</v>
+        <v>29.64</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>324703</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.94</v>
+        <v>0.612654</v>
       </c>
       <c r="AT19" t="n">
-        <v>29.64</v>
+        <v>-1.443116</v>
       </c>
       <c r="AU19" t="n">
-        <v>324703</v>
+        <v>-1.443279</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.07978200000000001</v>
+        <v>1.521325</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.612654</v>
+        <v>2.249624</v>
       </c>
       <c r="AX19" t="n">
-        <v>-1.443116</v>
+        <v>-2.051854</v>
       </c>
       <c r="AY19" t="n">
-        <v>-1.443279</v>
+        <v>5.784842</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.521325</v>
+        <v>5.458422</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.249624</v>
+        <v>5.932356</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.029618</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>-2.051854</v>
+        <v>-0</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.784842</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.458422</v>
+        <v>-0.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.932356</v>
+        <v>0.02</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BM19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -4264,105 +3916,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.050788</v>
+        <v>0.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.46</v>
+        <v>93.79237000000001</v>
       </c>
       <c r="AJ20" t="n">
-        <v>100.05178</v>
+        <v>5.0993</v>
       </c>
       <c r="AK20" t="n">
-        <v>93.79237000000001</v>
+        <v>5.0987</v>
       </c>
       <c r="AL20" t="n">
-        <v>5.0993</v>
+        <v>5373231</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.0987</v>
+        <v>2151399</v>
       </c>
       <c r="AN20" t="n">
-        <v>5373231</v>
+        <v>3.24</v>
       </c>
       <c r="AO20" t="n">
-        <v>2151399</v>
+        <v>1.94</v>
       </c>
       <c r="AP20" t="n">
-        <v>3221831</v>
+        <v>4.11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.24</v>
+        <v>30.54</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.94</v>
+        <v>331122</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.11</v>
+        <v>-6.187047</v>
       </c>
       <c r="AT20" t="n">
-        <v>30.54</v>
+        <v>-2.269199</v>
       </c>
       <c r="AU20" t="n">
-        <v>331122</v>
+        <v>-2.26946</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.527112</v>
+        <v>0.133468</v>
       </c>
       <c r="AW20" t="n">
-        <v>-6.187047</v>
+        <v>-1.232052</v>
       </c>
       <c r="AX20" t="n">
-        <v>-2.269199</v>
+        <v>1.976883</v>
       </c>
       <c r="AY20" t="n">
-        <v>-2.26946</v>
+        <v>5.77432</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.133468</v>
+        <v>3.79089</v>
       </c>
       <c r="BA20" t="n">
-        <v>-1.232052</v>
+        <v>5.711379</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.066493</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.976883</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.77432</v>
+        <v>0.17</v>
       </c>
       <c r="BE20" t="n">
-        <v>3.79089</v>
+        <v>0.14</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.711379</v>
+        <v>0.17</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BM20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4461,105 +4095,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.050788</v>
+        <v>0.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.84</v>
+        <v>-0.06</v>
       </c>
       <c r="AH21" t="n">
-        <v>-0.06</v>
+        <v>0.77</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.77</v>
+        <v>98.75064999999999</v>
       </c>
       <c r="AJ21" t="n">
-        <v>103.00964</v>
+        <v>5.2078</v>
       </c>
       <c r="AK21" t="n">
-        <v>98.75064999999999</v>
+        <v>5.2072</v>
       </c>
       <c r="AL21" t="n">
-        <v>5.2078</v>
+        <v>5370950</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.2072</v>
+        <v>2136105</v>
       </c>
       <c r="AN21" t="n">
-        <v>5370950</v>
+        <v>3.36</v>
       </c>
       <c r="AO21" t="n">
-        <v>2136105</v>
+        <v>2.17</v>
       </c>
       <c r="AP21" t="n">
-        <v>3234845</v>
+        <v>4.16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.36</v>
+        <v>30.48</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.17</v>
+        <v>328098</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.16</v>
+        <v>5.286443</v>
       </c>
       <c r="AT21" t="n">
-        <v>30.48</v>
+        <v>2.127743</v>
       </c>
       <c r="AU21" t="n">
-        <v>328098</v>
+        <v>2.127993</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.956329</v>
+        <v>-0.042451</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.286443</v>
+        <v>-0.710886</v>
       </c>
       <c r="AX21" t="n">
-        <v>2.127743</v>
+        <v>-0.913259</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.127993</v>
+        <v>5.596302</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.042451</v>
+        <v>1.864495</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.710886</v>
+        <v>5.47065</v>
       </c>
       <c r="BB21" t="n">
-        <v>0.403932</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>-0.913259</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.596302</v>
+        <v>0.12</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.864495</v>
+        <v>0.23</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.47065</v>
+        <v>0.05</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4658,105 +4274,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.050788</v>
+        <v>0.71</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.71</v>
+        <v>0.05</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.64</v>
+        <v>110.62354</v>
       </c>
       <c r="AJ22" t="n">
-        <v>103.09341</v>
+        <v>5.0804</v>
       </c>
       <c r="AK22" t="n">
-        <v>110.62354</v>
+        <v>5.0798</v>
       </c>
       <c r="AL22" t="n">
-        <v>5.0804</v>
+        <v>5424811</v>
       </c>
       <c r="AM22" t="n">
-        <v>5.0798</v>
+        <v>2154900</v>
       </c>
       <c r="AN22" t="n">
-        <v>5424811</v>
+        <v>3.35</v>
       </c>
       <c r="AO22" t="n">
-        <v>2154900</v>
+        <v>2.2</v>
       </c>
       <c r="AP22" t="n">
-        <v>3269910</v>
+        <v>4.11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.35</v>
+        <v>30.99</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.2</v>
+        <v>341158</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.11</v>
+        <v>12.023101</v>
       </c>
       <c r="AT22" t="n">
-        <v>30.99</v>
+        <v>-2.446331</v>
       </c>
       <c r="AU22" t="n">
-        <v>341158</v>
+        <v>-2.446612</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.08132200000000001</v>
+        <v>1.002821</v>
       </c>
       <c r="AW22" t="n">
-        <v>12.023101</v>
+        <v>0.879872</v>
       </c>
       <c r="AX22" t="n">
-        <v>-2.446331</v>
+        <v>3.980518</v>
       </c>
       <c r="AY22" t="n">
-        <v>-2.446612</v>
+        <v>4.650694</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.002821</v>
+        <v>0.172427</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.879872</v>
+        <v>4.361088</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.083978</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.980518</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.650694</v>
+        <v>-0.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>0.172427</v>
+        <v>0.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.361088</v>
+        <v>-0.05</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4855,105 +4453,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.050788</v>
+        <v>0.61</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.61</v>
+        <v>-0.95</v>
       </c>
       <c r="AH23" t="n">
-        <v>-0.95</v>
+        <v>0.53</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.53</v>
+        <v>104.34152</v>
       </c>
       <c r="AJ23" t="n">
-        <v>104.1626</v>
+        <v>5.0007</v>
       </c>
       <c r="AK23" t="n">
-        <v>104.34152</v>
+        <v>5.0001</v>
       </c>
       <c r="AL23" t="n">
-        <v>5.0007</v>
+        <v>5426307</v>
       </c>
       <c r="AM23" t="n">
-        <v>5.0001</v>
+        <v>2145000</v>
       </c>
       <c r="AN23" t="n">
-        <v>5426307</v>
+        <v>3.54</v>
       </c>
       <c r="AO23" t="n">
-        <v>2145000</v>
+        <v>2.45</v>
       </c>
       <c r="AP23" t="n">
-        <v>3281308</v>
+        <v>4.26</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.54</v>
+        <v>31.62</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.45</v>
+        <v>345725</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.26</v>
+        <v>-5.678737</v>
       </c>
       <c r="AT23" t="n">
-        <v>31.62</v>
+        <v>-1.568774</v>
       </c>
       <c r="AU23" t="n">
-        <v>345725</v>
+        <v>-1.568959</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.037108</v>
+        <v>0.027577</v>
       </c>
       <c r="AW23" t="n">
-        <v>-5.678737</v>
+        <v>-0.459418</v>
       </c>
       <c r="AX23" t="n">
-        <v>-1.568774</v>
+        <v>1.338676</v>
       </c>
       <c r="AY23" t="n">
-        <v>-1.568959</v>
+        <v>4.184706</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027577</v>
+        <v>-2.158772</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.459418</v>
+        <v>3.834324</v>
       </c>
       <c r="BB23" t="n">
-        <v>0.348572</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.338676</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.184706</v>
+        <v>0.19</v>
       </c>
       <c r="BE23" t="n">
-        <v>-2.158772</v>
+        <v>0.25</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.834324</v>
+        <v>0.15</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ23" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BK23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="BM23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -5052,105 +4632,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.050788</v>
+        <v>0.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.23</v>
+        <v>-1.84</v>
       </c>
       <c r="AH24" t="n">
-        <v>-1.84</v>
+        <v>0.36</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.36</v>
+        <v>102.66392</v>
       </c>
       <c r="AJ24" t="n">
-        <v>102.3642</v>
+        <v>5.0959</v>
       </c>
       <c r="AK24" t="n">
-        <v>102.66392</v>
+        <v>5.0953</v>
       </c>
       <c r="AL24" t="n">
-        <v>5.0959</v>
+        <v>5453708</v>
       </c>
       <c r="AM24" t="n">
-        <v>5.0953</v>
+        <v>2145530</v>
       </c>
       <c r="AN24" t="n">
-        <v>5453708</v>
+        <v>3.65</v>
       </c>
       <c r="AO24" t="n">
-        <v>2145530</v>
+        <v>2.58</v>
       </c>
       <c r="AP24" t="n">
-        <v>3308178</v>
+        <v>4.35</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.65</v>
+        <v>31.63</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.58</v>
+        <v>343489</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.35</v>
+        <v>-1.607797</v>
       </c>
       <c r="AT24" t="n">
-        <v>31.63</v>
+        <v>1.903733</v>
       </c>
       <c r="AU24" t="n">
-        <v>343489</v>
+        <v>1.903962</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.726531</v>
+        <v>0.504966</v>
       </c>
       <c r="AW24" t="n">
-        <v>-1.607797</v>
+        <v>0.024709</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.903733</v>
+        <v>-0.646757</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.903962</v>
+        <v>3.935832</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.504966</v>
+        <v>-4.45588</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.024709</v>
+        <v>3.741292</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.818881</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>-0.646757</v>
+        <v>-0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.935832</v>
+        <v>0.11</v>
       </c>
       <c r="BE24" t="n">
-        <v>-4.45588</v>
+        <v>0.13</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.741292</v>
+        <v>0.09</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BI24" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BJ24" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BK24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BL24" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BM24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -5249,105 +4811,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.050788</v>
+        <v>-0.08</v>
       </c>
       <c r="AG25" t="n">
-        <v>-0.08</v>
+        <v>-1.93</v>
       </c>
       <c r="AH25" t="n">
-        <v>-1.93</v>
+        <v>-0.1</v>
       </c>
       <c r="AI25" t="n">
+        <v>102.53174</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>4.8192</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>4.8186</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>5479459</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2169613</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>343620</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>-0.12875</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>-5.429855</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>-5.430495</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.472174</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.122473</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.038138</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>3.161501</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>-6.84947</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.998957</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BF25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AJ25" t="n">
-        <v>102.50431</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>102.53174</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>4.8192</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>4.8186</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>5479459</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>2169613</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>3309846</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>30.85</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>343620</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0.136874</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>-0.12875</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>-5.429855</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>-5.430495</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.472174</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.122473</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0.050421</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0.038138</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.161501</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>-6.84947</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.998957</v>
-      </c>
       <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -5446,105 +4990,87 @@
         <v>0.050788</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.050788</v>
+        <v>0.12</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.12</v>
+        <v>-0.72</v>
       </c>
       <c r="AH26" t="n">
-        <v>-0.72</v>
+        <v>-0.09</v>
       </c>
       <c r="AI26" t="n">
-        <v>-0.09</v>
+        <v>105.47522</v>
       </c>
       <c r="AJ26" t="n">
-        <v>102.83357</v>
+        <v>4.7415</v>
       </c>
       <c r="AK26" t="n">
-        <v>105.47522</v>
+        <v>4.7409</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.7415</v>
+        <v>5484871</v>
       </c>
       <c r="AM26" t="n">
-        <v>4.7409</v>
+        <v>2153541</v>
       </c>
       <c r="AN26" t="n">
-        <v>5484871</v>
+        <v>3.63</v>
       </c>
       <c r="AO26" t="n">
-        <v>2153541</v>
+        <v>2.73</v>
       </c>
       <c r="AP26" t="n">
-        <v>3331330</v>
+        <v>4.22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.63</v>
+        <v>30.43</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.73</v>
+        <v>345476</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.22</v>
+        <v>2.870799</v>
       </c>
       <c r="AT26" t="n">
-        <v>30.43</v>
+        <v>-1.612301</v>
       </c>
       <c r="AU26" t="n">
-        <v>345476</v>
+        <v>-1.612502</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.321216</v>
+        <v>0.098769</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.870799</v>
+        <v>-0.740777</v>
       </c>
       <c r="AX26" t="n">
-        <v>-1.612301</v>
+        <v>0.5401319999999999</v>
       </c>
       <c r="AY26" t="n">
-        <v>-1.612502</v>
+        <v>3.992444</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.098769</v>
+        <v>-7.713954</v>
       </c>
       <c r="BA26" t="n">
-        <v>-0.740777</v>
+        <v>3.527423</v>
       </c>
       <c r="BB26" t="n">
-        <v>0.6490939999999999</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0.5401319999999999</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.992444</v>
+        <v>0.02</v>
       </c>
       <c r="BE26" t="n">
-        <v>-7.713954</v>
+        <v>0.1</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.527423</v>
+        <v>-0.03</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5643,105 +5169,87 @@
         <v>0.049189</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.049189</v>
+        <v>0.23</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AH27" t="n">
-        <v>-0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.2</v>
+        <v>106.13139</v>
       </c>
       <c r="AJ27" t="n">
-        <v>102.45222</v>
+        <v>4.9219</v>
       </c>
       <c r="AK27" t="n">
-        <v>106.13139</v>
+        <v>4.9213</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.9219</v>
+        <v>5559063</v>
       </c>
       <c r="AM27" t="n">
-        <v>4.9213</v>
+        <v>2172658</v>
       </c>
       <c r="AN27" t="n">
-        <v>5559063</v>
+        <v>3.61</v>
       </c>
       <c r="AO27" t="n">
-        <v>2172658</v>
+        <v>2.82</v>
       </c>
       <c r="AP27" t="n">
-        <v>3386405</v>
+        <v>4.12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.61</v>
+        <v>29.92</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.82</v>
+        <v>344177</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.12</v>
+        <v>0.622108</v>
       </c>
       <c r="AT27" t="n">
-        <v>29.92</v>
+        <v>3.804703</v>
       </c>
       <c r="AU27" t="n">
-        <v>344177</v>
+        <v>3.805185</v>
       </c>
       <c r="AV27" t="n">
-        <v>-0.370842</v>
+        <v>1.352666</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.622108</v>
+        <v>0.887701</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.804703</v>
+        <v>-0.376003</v>
       </c>
       <c r="AY27" t="n">
-        <v>3.805185</v>
+        <v>4.608216</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.352666</v>
+        <v>-7.193509</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.887701</v>
+        <v>4.057054</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.653244</v>
+        <v>-0.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>-0.376003</v>
+        <v>-0.001599</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.608216</v>
+        <v>-0.02</v>
       </c>
       <c r="BE27" t="n">
-        <v>-7.193509</v>
+        <v>0.09</v>
       </c>
       <c r="BF27" t="n">
-        <v>4.057054</v>
+        <v>-0.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH27" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="BI27" t="n">
-        <v>-0.001599</v>
-      </c>
-      <c r="BJ27" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BK27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL27" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BM27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5840,105 +5348,87 @@
         <v>0.048422</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.048422</v>
+        <v>0.26</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.11</v>
+        <v>102.00419</v>
       </c>
       <c r="AJ28" t="n">
-        <v>102.57885</v>
+        <v>5.0076</v>
       </c>
       <c r="AK28" t="n">
-        <v>102.00419</v>
+        <v>5.007</v>
       </c>
       <c r="AL28" t="n">
-        <v>5.0076</v>
+        <v>5625945</v>
       </c>
       <c r="AM28" t="n">
-        <v>5.007</v>
+        <v>2215175</v>
       </c>
       <c r="AN28" t="n">
-        <v>5625945</v>
+        <v>3.54</v>
       </c>
       <c r="AO28" t="n">
-        <v>2215175</v>
+        <v>2.82</v>
       </c>
       <c r="AP28" t="n">
-        <v>3410769</v>
+        <v>4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.54</v>
+        <v>29.66</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.82</v>
+        <v>340324</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>-3.888765</v>
       </c>
       <c r="AT28" t="n">
-        <v>29.66</v>
+        <v>1.741198</v>
       </c>
       <c r="AU28" t="n">
-        <v>340324</v>
+        <v>1.74141</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.123599</v>
+        <v>1.203116</v>
       </c>
       <c r="AW28" t="n">
-        <v>-3.888765</v>
+        <v>1.956912</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.741198</v>
+        <v>-1.119482</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.74141</v>
+        <v>5.185235</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.203116</v>
+        <v>-5.956714</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.956912</v>
+        <v>4.505936</v>
       </c>
       <c r="BB28" t="n">
-        <v>0.719465</v>
+        <v>-0.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>-1.119482</v>
+        <v>-0.000768</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.185235</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>-5.956714</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.505936</v>
+        <v>-0.12</v>
       </c>
       <c r="BG28" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>-0.000768</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -6037,105 +5527,87 @@
         <v>0.047279</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.047279</v>
+        <v>0.24</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.24</v>
+        <v>0.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.12</v>
+        <v>102.0744</v>
       </c>
       <c r="AJ29" t="n">
-        <v>102.87707</v>
+        <v>5.0575</v>
       </c>
       <c r="AK29" t="n">
-        <v>102.0744</v>
+        <v>5.0569</v>
       </c>
       <c r="AL29" t="n">
-        <v>5.0575</v>
+        <v>5653808</v>
       </c>
       <c r="AM29" t="n">
-        <v>5.0569</v>
+        <v>2204808</v>
       </c>
       <c r="AN29" t="n">
-        <v>5653808</v>
+        <v>3.56</v>
       </c>
       <c r="AO29" t="n">
-        <v>2204808</v>
+        <v>2.92</v>
       </c>
       <c r="AP29" t="n">
-        <v>3449000</v>
+        <v>3.97</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.56</v>
+        <v>29.24</v>
       </c>
       <c r="AR29" t="n">
-        <v>2.92</v>
+        <v>340247</v>
       </c>
       <c r="AS29" t="n">
-        <v>3.97</v>
+        <v>0.068831</v>
       </c>
       <c r="AT29" t="n">
-        <v>29.24</v>
+        <v>0.996485</v>
       </c>
       <c r="AU29" t="n">
-        <v>340247</v>
+        <v>0.996605</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.290723</v>
+        <v>0.495259</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.068831</v>
+        <v>-0.467999</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.996485</v>
+        <v>-0.022625</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.996605</v>
+        <v>4.819246</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.495259</v>
+        <v>-4.560737</v>
       </c>
       <c r="BA29" t="n">
-        <v>-0.467999</v>
+        <v>4.141877</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.120891</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>-0.022625</v>
+        <v>-0.001143</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.819246</v>
+        <v>0.02</v>
       </c>
       <c r="BE29" t="n">
-        <v>-4.560737</v>
+        <v>0.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.141877</v>
+        <v>-0.03</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="BI29" t="n">
-        <v>-0.001143</v>
-      </c>
-      <c r="BJ29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BK29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BL29" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -6234,105 +5706,87 @@
         <v>0.045601</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.045601</v>
+        <v>0.28</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.59</v>
+        <v>0.1</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1</v>
+        <v>101.86494</v>
       </c>
       <c r="AJ30" t="n">
-        <v>103.528</v>
+        <v>4.9355</v>
       </c>
       <c r="AK30" t="n">
-        <v>101.86494</v>
+        <v>4.9349</v>
       </c>
       <c r="AL30" t="n">
-        <v>4.9355</v>
+        <v>5711103</v>
       </c>
       <c r="AM30" t="n">
-        <v>4.9349</v>
+        <v>2220766</v>
       </c>
       <c r="AN30" t="n">
-        <v>5711103</v>
+        <v>3.53</v>
       </c>
       <c r="AO30" t="n">
-        <v>2220766</v>
+        <v>2.99</v>
       </c>
       <c r="AP30" t="n">
-        <v>3490337</v>
+        <v>3.88</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.53</v>
+        <v>29.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.99</v>
+        <v>348406</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.88</v>
+        <v>-0.205203</v>
       </c>
       <c r="AT30" t="n">
-        <v>29.01</v>
+        <v>-2.412259</v>
       </c>
       <c r="AU30" t="n">
-        <v>348406</v>
+        <v>-2.412545</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.632726</v>
+        <v>1.013388</v>
       </c>
       <c r="AW30" t="n">
-        <v>-0.205203</v>
+        <v>0.723782</v>
       </c>
       <c r="AX30" t="n">
-        <v>-2.412259</v>
+        <v>2.397964</v>
       </c>
       <c r="AY30" t="n">
-        <v>-2.412545</v>
+        <v>4.683537</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.013388</v>
+        <v>-3.457004</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.723782</v>
+        <v>3.851383</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.198521</v>
+        <v>-0.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.397964</v>
+        <v>-0.001678</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.683537</v>
+        <v>-0.03</v>
       </c>
       <c r="BE30" t="n">
-        <v>-3.457004</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.851383</v>
+        <v>-0.09</v>
       </c>
       <c r="BG30" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>-0.001678</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="BM30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -6431,105 +5885,87 @@
         <v>0.044537</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.044537</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.55</v>
+        <v>101.74606</v>
       </c>
       <c r="AJ31" t="n">
-        <v>104.8991</v>
+        <v>4.8413</v>
       </c>
       <c r="AK31" t="n">
-        <v>101.74606</v>
+        <v>4.8407</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.8413</v>
+        <v>5805157</v>
       </c>
       <c r="AM31" t="n">
-        <v>4.8407</v>
+        <v>2283485</v>
       </c>
       <c r="AN31" t="n">
-        <v>5805157</v>
+        <v>3.29</v>
       </c>
       <c r="AO31" t="n">
-        <v>2283485</v>
+        <v>2.59</v>
       </c>
       <c r="AP31" t="n">
-        <v>3521672</v>
+        <v>3.75</v>
       </c>
       <c r="AQ31" t="n">
-        <v>3.29</v>
+        <v>28.14</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.59</v>
+        <v>355034</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.75</v>
+        <v>-0.116704</v>
       </c>
       <c r="AT31" t="n">
-        <v>28.14</v>
+        <v>-1.908621</v>
       </c>
       <c r="AU31" t="n">
-        <v>355034</v>
+        <v>-1.908853</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.324376</v>
+        <v>1.646862</v>
       </c>
       <c r="AW31" t="n">
-        <v>-0.116704</v>
+        <v>2.824206</v>
       </c>
       <c r="AX31" t="n">
-        <v>-1.908621</v>
+        <v>1.902378</v>
       </c>
       <c r="AY31" t="n">
-        <v>-1.908853</v>
+        <v>4.621114</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.646862</v>
+        <v>-3.178284</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.824206</v>
+        <v>3.706988</v>
       </c>
       <c r="BB31" t="n">
-        <v>0.897764</v>
+        <v>-0.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.902378</v>
+        <v>-0.001064</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.621114</v>
+        <v>-0.24</v>
       </c>
       <c r="BE31" t="n">
-        <v>-3.178284</v>
+        <v>-0.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>3.706988</v>
+        <v>-0.13</v>
       </c>
       <c r="BG31" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="BI31" t="n">
-        <v>-0.001064</v>
-      </c>
-      <c r="BJ31" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="BK31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BL31" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BM31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6628,105 +6064,87 @@
         <v>0.043739</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.043739</v>
+        <v>0.42</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.57</v>
+        <v>98.01879</v>
       </c>
       <c r="AJ32" t="n">
-        <v>104.53245</v>
+        <v>4.9535</v>
       </c>
       <c r="AK32" t="n">
-        <v>98.01879</v>
+        <v>4.9529</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.9535</v>
+        <v>5794707</v>
       </c>
       <c r="AM32" t="n">
-        <v>4.9529</v>
+        <v>2234362</v>
       </c>
       <c r="AN32" t="n">
-        <v>5794707</v>
+        <v>3.38</v>
       </c>
       <c r="AO32" t="n">
-        <v>2234362</v>
+        <v>2.77</v>
       </c>
       <c r="AP32" t="n">
-        <v>3560345</v>
+        <v>3.76</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.38</v>
+        <v>28</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.77</v>
+        <v>355066</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.76</v>
+        <v>-3.663306</v>
       </c>
       <c r="AT32" t="n">
-        <v>28</v>
+        <v>2.317559</v>
       </c>
       <c r="AU32" t="n">
-        <v>355066</v>
+        <v>2.317847</v>
       </c>
       <c r="AV32" t="n">
-        <v>-0.349526</v>
+        <v>-0.180012</v>
       </c>
       <c r="AW32" t="n">
-        <v>-3.663306</v>
+        <v>-2.151229</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.317559</v>
+        <v>0.009013</v>
       </c>
       <c r="AY32" t="n">
-        <v>2.317847</v>
+        <v>4.506637</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.180012</v>
+        <v>-3.31355</v>
       </c>
       <c r="BA32" t="n">
-        <v>-2.151229</v>
+        <v>3.820543</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.098143</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0.009013</v>
+        <v>-0.000798</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.506637</v>
+        <v>0.09</v>
       </c>
       <c r="BE32" t="n">
-        <v>-3.31355</v>
+        <v>0.18</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.820543</v>
+        <v>0.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="BI32" t="n">
-        <v>-0.000798</v>
-      </c>
-      <c r="BJ32" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BK32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6825,105 +6243,87 @@
         <v>0.041957</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.041957</v>
+        <v>0.83</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.83</v>
+        <v>-0.52</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.8100000000000001</v>
+        <v>102.37988</v>
       </c>
       <c r="AJ33" t="n">
-        <v>104.75961</v>
+        <v>4.9833</v>
       </c>
       <c r="AK33" t="n">
-        <v>102.37988</v>
+        <v>4.9827</v>
       </c>
       <c r="AL33" t="n">
-        <v>4.9833</v>
+        <v>5815954</v>
       </c>
       <c r="AM33" t="n">
-        <v>4.9827</v>
+        <v>2235302</v>
       </c>
       <c r="AN33" t="n">
-        <v>5815954</v>
+        <v>3.38</v>
       </c>
       <c r="AO33" t="n">
-        <v>2235302</v>
+        <v>2.76</v>
       </c>
       <c r="AP33" t="n">
-        <v>3580652</v>
+        <v>3.76</v>
       </c>
       <c r="AQ33" t="n">
-        <v>3.38</v>
+        <v>27.85</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.76</v>
+        <v>352705</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.76</v>
+        <v>4.449239</v>
       </c>
       <c r="AT33" t="n">
-        <v>27.85</v>
+        <v>0.601595</v>
       </c>
       <c r="AU33" t="n">
-        <v>352705</v>
+        <v>0.601668</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.217311</v>
+        <v>0.366662</v>
       </c>
       <c r="AW33" t="n">
-        <v>4.449239</v>
+        <v>0.04207</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.601595</v>
+        <v>-0.664947</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.601668</v>
+        <v>4.496274</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.366662</v>
+        <v>-3.758575</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.04207</v>
+        <v>3.861754</v>
       </c>
       <c r="BB33" t="n">
-        <v>0.570366</v>
+        <v>-0.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>-0.664947</v>
+        <v>-0.001782</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.496274</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>-3.758575</v>
+        <v>-0.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.861754</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>-0.001782</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7022,105 +6422,87 @@
         <v>0.04142</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.04142</v>
+        <v>0.16</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.16</v>
+        <v>-0.47</v>
       </c>
       <c r="AH34" t="n">
-        <v>-0.47</v>
+        <v>0.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.19</v>
+        <v>109.58504</v>
       </c>
       <c r="AJ34" t="n">
-        <v>104.7097</v>
+        <v>4.9962</v>
       </c>
       <c r="AK34" t="n">
-        <v>109.58504</v>
+        <v>4.9956</v>
       </c>
       <c r="AL34" t="n">
-        <v>4.9962</v>
+        <v>5899742</v>
       </c>
       <c r="AM34" t="n">
-        <v>4.9956</v>
+        <v>2285775</v>
       </c>
       <c r="AN34" t="n">
-        <v>5899742</v>
+        <v>3.33</v>
       </c>
       <c r="AO34" t="n">
-        <v>2285775</v>
+        <v>2.71</v>
       </c>
       <c r="AP34" t="n">
-        <v>3613967</v>
+        <v>3.71</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.33</v>
+        <v>28.14</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.71</v>
+        <v>355008</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.71</v>
+        <v>7.037672</v>
       </c>
       <c r="AT34" t="n">
-        <v>28.14</v>
+        <v>0.258865</v>
       </c>
       <c r="AU34" t="n">
-        <v>355008</v>
+        <v>0.258896</v>
       </c>
       <c r="AV34" t="n">
-        <v>-0.047642</v>
+        <v>1.440658</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.037672</v>
+        <v>2.257995</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.258865</v>
+        <v>0.652954</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.258896</v>
+        <v>3.925596</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.440658</v>
+        <v>-4.25878</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.257995</v>
+        <v>3.397348</v>
       </c>
       <c r="BB34" t="n">
-        <v>0.930417</v>
+        <v>-0.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>0.652954</v>
+        <v>-0.000537</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.925596</v>
+        <v>-0.05</v>
       </c>
       <c r="BE34" t="n">
-        <v>-4.25878</v>
+        <v>-0.05</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.397348</v>
+        <v>-0.05</v>
       </c>
       <c r="BG34" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="BI34" t="n">
-        <v>-0.000537</v>
-      </c>
-      <c r="BJ34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BK34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BM34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -7219,105 +6601,87 @@
         <v>0.040168</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.040168</v>
+        <v>0.38</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.37</v>
+        <v>109.36335</v>
       </c>
       <c r="AJ35" t="n">
-        <v>104.75682</v>
+        <v>5.1718</v>
       </c>
       <c r="AK35" t="n">
-        <v>109.36335</v>
+        <v>5.1712</v>
       </c>
       <c r="AL35" t="n">
-        <v>5.1718</v>
+        <v>5915538</v>
       </c>
       <c r="AM35" t="n">
-        <v>5.1712</v>
+        <v>2268879</v>
       </c>
       <c r="AN35" t="n">
-        <v>5915538</v>
+        <v>3.37</v>
       </c>
       <c r="AO35" t="n">
-        <v>2268879</v>
+        <v>2.76</v>
       </c>
       <c r="AP35" t="n">
-        <v>3646659</v>
+        <v>3.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.37</v>
+        <v>27.86</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.76</v>
+        <v>351599</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.75</v>
+        <v>-0.2023</v>
       </c>
       <c r="AT35" t="n">
-        <v>27.86</v>
+        <v>3.514671</v>
       </c>
       <c r="AU35" t="n">
-        <v>351599</v>
+        <v>3.515093</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.045001</v>
+        <v>0.267741</v>
       </c>
       <c r="AW35" t="n">
-        <v>-0.2023</v>
+        <v>-0.7391799999999999</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.514671</v>
+        <v>-0.96026</v>
       </c>
       <c r="AY35" t="n">
-        <v>3.515093</v>
+        <v>3.688016</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.267741</v>
+        <v>-3.040871</v>
       </c>
       <c r="BA35" t="n">
-        <v>-0.7391799999999999</v>
+        <v>3.232784</v>
       </c>
       <c r="BB35" t="n">
-        <v>0.904602</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>-0.96026</v>
+        <v>-0.001252</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.688016</v>
+        <v>0.04</v>
       </c>
       <c r="BE35" t="n">
-        <v>-3.040871</v>
+        <v>0.05</v>
       </c>
       <c r="BF35" t="n">
-        <v>3.232784</v>
+        <v>0.04</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="BI35" t="n">
-        <v>-0.001252</v>
-      </c>
-      <c r="BJ35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BK35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL35" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -7416,105 +6780,87 @@
         <v>0.039484</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.039484</v>
+        <v>0.46</v>
       </c>
       <c r="AG36" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AH36" t="n">
-        <v>0.89</v>
-      </c>
       <c r="AI36" t="n">
-        <v>0.46</v>
+        <v>104.84682</v>
       </c>
       <c r="AJ36" t="n">
-        <v>105.70704</v>
+        <v>5.2416</v>
       </c>
       <c r="AK36" t="n">
-        <v>104.84682</v>
+        <v>5.241</v>
       </c>
       <c r="AL36" t="n">
-        <v>5.2416</v>
+        <v>5953960</v>
       </c>
       <c r="AM36" t="n">
-        <v>5.241</v>
+        <v>2278309</v>
       </c>
       <c r="AN36" t="n">
-        <v>5953960</v>
+        <v>3.43</v>
       </c>
       <c r="AO36" t="n">
-        <v>2278309</v>
+        <v>2.8</v>
       </c>
       <c r="AP36" t="n">
-        <v>3675652</v>
+        <v>3.82</v>
       </c>
       <c r="AQ36" t="n">
-        <v>3.43</v>
+        <v>27.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.8</v>
+        <v>355560</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.82</v>
+        <v>-4.129839</v>
       </c>
       <c r="AT36" t="n">
-        <v>27.75</v>
+        <v>1.349627</v>
       </c>
       <c r="AU36" t="n">
-        <v>355560</v>
+        <v>1.349783</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.907072</v>
+        <v>0.64951</v>
       </c>
       <c r="AW36" t="n">
-        <v>-4.129839</v>
+        <v>0.415624</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.349627</v>
+        <v>1.126567</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.349783</v>
+        <v>3.925952</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.64951</v>
+        <v>-0.344269</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.415624</v>
+        <v>3.335647</v>
       </c>
       <c r="BB36" t="n">
-        <v>0.795057</v>
+        <v>-0.25</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.126567</v>
+        <v>-0.000684</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.925952</v>
+        <v>0.06</v>
       </c>
       <c r="BE36" t="n">
-        <v>-0.344269</v>
+        <v>0.04</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.335647</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BG36" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="BI36" t="n">
-        <v>-0.000684</v>
-      </c>
-      <c r="BJ36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BK36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BL36" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -7613,105 +6959,87 @@
         <v>0.03927</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.03927</v>
+        <v>0.21</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.25</v>
+        <v>106.03093</v>
       </c>
       <c r="AJ37" t="n">
-        <v>106.57623</v>
+        <v>5.5589</v>
       </c>
       <c r="AK37" t="n">
-        <v>106.03093</v>
+        <v>5.5583</v>
       </c>
       <c r="AL37" t="n">
-        <v>5.5589</v>
+        <v>6041898</v>
       </c>
       <c r="AM37" t="n">
-        <v>5.5583</v>
+        <v>2336858</v>
       </c>
       <c r="AN37" t="n">
-        <v>6041898</v>
+        <v>3.29</v>
       </c>
       <c r="AO37" t="n">
-        <v>2336858</v>
+        <v>2.64</v>
       </c>
       <c r="AP37" t="n">
-        <v>3705041</v>
+        <v>3.71</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.29</v>
+        <v>27.81</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.64</v>
+        <v>357827</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.71</v>
+        <v>1.129371</v>
       </c>
       <c r="AT37" t="n">
-        <v>27.81</v>
+        <v>6.053495</v>
       </c>
       <c r="AU37" t="n">
-        <v>357827</v>
+        <v>6.054188</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.822263</v>
+        <v>1.476967</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.129371</v>
+        <v>2.569845</v>
       </c>
       <c r="AX37" t="n">
-        <v>6.053495</v>
+        <v>0.637586</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.054188</v>
+        <v>4.227578</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.476967</v>
+        <v>2.440035</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.569845</v>
+        <v>3.697684</v>
       </c>
       <c r="BB37" t="n">
-        <v>0.799559</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>0.637586</v>
+        <v>-0.000214</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.227578</v>
+        <v>-0.14</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.440035</v>
+        <v>-0.16</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.697684</v>
+        <v>-0.11</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="BI37" t="n">
-        <v>-0.000214</v>
-      </c>
-      <c r="BJ37" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BK37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BL37" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="BM37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7810,105 +7138,87 @@
         <v>0.03927</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.03927</v>
+        <v>0.38</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.61</v>
+        <v>0.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.26</v>
+        <v>111.55002</v>
       </c>
       <c r="AJ38" t="n">
-        <v>106.88756</v>
+        <v>5.6621</v>
       </c>
       <c r="AK38" t="n">
-        <v>111.55002</v>
+        <v>5.6615</v>
       </c>
       <c r="AL38" t="n">
-        <v>5.6621</v>
+        <v>6069205</v>
       </c>
       <c r="AM38" t="n">
-        <v>5.6615</v>
+        <v>2323362</v>
       </c>
       <c r="AN38" t="n">
-        <v>6069205</v>
+        <v>3.3</v>
       </c>
       <c r="AO38" t="n">
-        <v>2323362</v>
+        <v>2.52</v>
       </c>
       <c r="AP38" t="n">
-        <v>3745844</v>
+        <v>3.78</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.3</v>
+        <v>27.74</v>
       </c>
       <c r="AR38" t="n">
-        <v>2.52</v>
+        <v>363282</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.78</v>
+        <v>5.20517</v>
       </c>
       <c r="AT38" t="n">
-        <v>27.74</v>
+        <v>1.856482</v>
       </c>
       <c r="AU38" t="n">
-        <v>363282</v>
+        <v>1.856683</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.29212</v>
+        <v>0.451961</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.20517</v>
+        <v>-0.577528</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.856482</v>
+        <v>1.52448</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.856683</v>
+        <v>4.498245</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.451961</v>
+        <v>3.812368</v>
       </c>
       <c r="BA38" t="n">
-        <v>-0.577528</v>
+        <v>4.060953</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.101283</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52448</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.498245</v>
+        <v>0.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>3.812368</v>
+        <v>-0.12</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.060953</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ38" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BK38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BL38" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -8007,105 +7317,87 @@
         <v>0.03927</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.03927</v>
+        <v>-0.02</v>
       </c>
       <c r="AG39" t="n">
-        <v>-0.02</v>
+        <v>0.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.29</v>
+        <v>-0.14</v>
       </c>
       <c r="AI39" t="n">
-        <v>-0.14</v>
+        <v>110.19363</v>
       </c>
       <c r="AJ39" t="n">
-        <v>107.14396</v>
+        <v>5.6562</v>
       </c>
       <c r="AK39" t="n">
-        <v>110.19363</v>
+        <v>5.6556</v>
       </c>
       <c r="AL39" t="n">
-        <v>5.6562</v>
+        <v>6135298</v>
       </c>
       <c r="AM39" t="n">
-        <v>5.6556</v>
+        <v>2344397</v>
       </c>
       <c r="AN39" t="n">
-        <v>6135298</v>
+        <v>3.33</v>
       </c>
       <c r="AO39" t="n">
-        <v>2344397</v>
+        <v>2.55</v>
       </c>
       <c r="AP39" t="n">
-        <v>3790900</v>
+        <v>3.82</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.33</v>
+        <v>27.59</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.55</v>
+        <v>369214</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.82</v>
+        <v>-1.215948</v>
       </c>
       <c r="AT39" t="n">
-        <v>27.59</v>
+        <v>-0.104202</v>
       </c>
       <c r="AU39" t="n">
-        <v>369214</v>
+        <v>-0.104213</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.239878</v>
+        <v>1.088989</v>
       </c>
       <c r="AW39" t="n">
-        <v>-1.215948</v>
+        <v>0.905369</v>
       </c>
       <c r="AX39" t="n">
-        <v>-0.104202</v>
+        <v>1.632891</v>
       </c>
       <c r="AY39" t="n">
-        <v>-0.104213</v>
+        <v>4.237599</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.088989</v>
+        <v>4.259387</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.905369</v>
+        <v>3.707852</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.202826</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.632891</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.237599</v>
+        <v>0.03</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.259387</v>
+        <v>0.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>3.707852</v>
+        <v>0.04</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BM39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -8204,105 +7496,87 @@
         <v>0.039612</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.039612</v>
+        <v>0.44</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.44</v>
+        <v>0.62</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.62</v>
+        <v>0.48</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.48</v>
+        <v>107.28836</v>
       </c>
       <c r="AJ40" t="n">
-        <v>107.99916</v>
+        <v>5.4481</v>
       </c>
       <c r="AK40" t="n">
-        <v>107.28836</v>
+        <v>5.4475</v>
       </c>
       <c r="AL40" t="n">
-        <v>5.4481</v>
+        <v>6216528</v>
       </c>
       <c r="AM40" t="n">
-        <v>5.4475</v>
+        <v>2384828</v>
       </c>
       <c r="AN40" t="n">
-        <v>6216528</v>
+        <v>3.34</v>
       </c>
       <c r="AO40" t="n">
-        <v>2384828</v>
+        <v>2.56</v>
       </c>
       <c r="AP40" t="n">
-        <v>3831700</v>
+        <v>3.83</v>
       </c>
       <c r="AQ40" t="n">
-        <v>3.34</v>
+        <v>27.49</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.56</v>
+        <v>372016</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.83</v>
+        <v>-2.636514</v>
       </c>
       <c r="AT40" t="n">
-        <v>27.49</v>
+        <v>-3.679149</v>
       </c>
       <c r="AU40" t="n">
-        <v>372016</v>
+        <v>-3.679539</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.7981780000000001</v>
+        <v>1.323978</v>
       </c>
       <c r="AW40" t="n">
-        <v>-2.636514</v>
+        <v>1.72458</v>
       </c>
       <c r="AX40" t="n">
-        <v>-3.679149</v>
+        <v>0.7589089999999999</v>
       </c>
       <c r="AY40" t="n">
-        <v>-3.679539</v>
+        <v>4.42474</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.323978</v>
+        <v>4.519075</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.72458</v>
+        <v>4.091149</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.076262</v>
+        <v>0.25</v>
       </c>
       <c r="BC40" t="n">
-        <v>0.7589089999999999</v>
+        <v>0.000342</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.42474</v>
+        <v>0.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>4.519075</v>
+        <v>0.01</v>
       </c>
       <c r="BF40" t="n">
-        <v>4.091149</v>
+        <v>0.01</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="BI40" t="n">
-        <v>0.000342</v>
-      </c>
-      <c r="BJ40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BK40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BL40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BM40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -8401,105 +7675,87 @@
         <v>0.040168</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.040168</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.52</v>
+        <v>0.61</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.61</v>
+        <v>109.21678</v>
       </c>
       <c r="AJ41" t="n">
-        <v>108.15356</v>
+        <v>5.7779</v>
       </c>
       <c r="AK41" t="n">
-        <v>109.21678</v>
+        <v>5.7773</v>
       </c>
       <c r="AL41" t="n">
-        <v>5.7779</v>
+        <v>6275117</v>
       </c>
       <c r="AM41" t="n">
-        <v>5.7773</v>
+        <v>2397533</v>
       </c>
       <c r="AN41" t="n">
-        <v>6275117</v>
+        <v>3.3</v>
       </c>
       <c r="AO41" t="n">
-        <v>2397533</v>
+        <v>2.52</v>
       </c>
       <c r="AP41" t="n">
-        <v>3877584</v>
+        <v>3.79</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.3</v>
+        <v>27.94</v>
       </c>
       <c r="AR41" t="n">
-        <v>2.52</v>
+        <v>366096</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.79</v>
+        <v>1.797418</v>
       </c>
       <c r="AT41" t="n">
-        <v>27.94</v>
+        <v>6.053487</v>
       </c>
       <c r="AU41" t="n">
-        <v>366096</v>
+        <v>6.054153</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.142964</v>
+        <v>0.9424709999999999</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.797418</v>
+        <v>0.532743</v>
       </c>
       <c r="AX41" t="n">
-        <v>6.053487</v>
+        <v>-1.591329</v>
       </c>
       <c r="AY41" t="n">
-        <v>6.054153</v>
+        <v>4.758099</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.9424709999999999</v>
+        <v>5.579866</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.532743</v>
+        <v>4.600584</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.197484</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>-1.591329</v>
+        <v>0.000556</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.758099</v>
+        <v>-0.04</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.579866</v>
+        <v>-0.04</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.600584</v>
+        <v>-0.04</v>
       </c>
       <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="BI41" t="n">
-        <v>0.000556</v>
-      </c>
-      <c r="BJ41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BK41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BL41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -8598,105 +7854,87 @@
         <v>0.04158</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.04158</v>
+        <v>0.39</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.39</v>
+        <v>1.3</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.3</v>
+        <v>0.33</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.33</v>
+        <v>105.74688</v>
       </c>
       <c r="AJ42" t="n">
-        <v>107.98489</v>
+        <v>6.0535</v>
       </c>
       <c r="AK42" t="n">
-        <v>105.74688</v>
+        <v>6.0529</v>
       </c>
       <c r="AL42" t="n">
-        <v>6.0535</v>
+        <v>6365690</v>
       </c>
       <c r="AM42" t="n">
-        <v>6.0529</v>
+        <v>2436022</v>
       </c>
       <c r="AN42" t="n">
-        <v>6365690</v>
+        <v>3.27</v>
       </c>
       <c r="AO42" t="n">
-        <v>2436022</v>
+        <v>2.5</v>
       </c>
       <c r="AP42" t="n">
-        <v>3929668</v>
+        <v>3.75</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.27</v>
+        <v>28.45</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.5</v>
+        <v>363003</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.75</v>
+        <v>-3.177076</v>
       </c>
       <c r="AT42" t="n">
-        <v>28.45</v>
+        <v>4.769899</v>
       </c>
       <c r="AU42" t="n">
-        <v>363003</v>
+        <v>4.770394</v>
       </c>
       <c r="AV42" t="n">
-        <v>-0.155954</v>
+        <v>1.443368</v>
       </c>
       <c r="AW42" t="n">
-        <v>-3.177076</v>
+        <v>1.605359</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.769899</v>
+        <v>-0.8448600000000001</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.770394</v>
+        <v>4.873011</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.443368</v>
+        <v>6.325086</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.605359</v>
+        <v>4.840925</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.343208</v>
+        <v>0.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>-0.8448600000000001</v>
+        <v>0.001412</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.873011</v>
+        <v>-0.03</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.325086</v>
+        <v>-0.02</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.840925</v>
+        <v>-0.04</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>0.001412</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BM42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8795,105 +8033,87 @@
         <v>0.044158</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.044158</v>
+        <v>0.52</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.52</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.48</v>
+        <v>104.2734</v>
       </c>
       <c r="AJ43" t="n">
-        <v>107.44467</v>
+        <v>6.1923</v>
       </c>
       <c r="AK43" t="n">
-        <v>104.2734</v>
+        <v>6.1917</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.1923</v>
+        <v>6464602</v>
       </c>
       <c r="AM43" t="n">
-        <v>6.1917</v>
+        <v>2499177</v>
       </c>
       <c r="AN43" t="n">
-        <v>6464602</v>
+        <v>3.08</v>
       </c>
       <c r="AO43" t="n">
-        <v>2499177</v>
+        <v>2.21</v>
       </c>
       <c r="AP43" t="n">
-        <v>3965425</v>
+        <v>3.63</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.08</v>
+        <v>28.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.21</v>
+        <v>329730</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.63</v>
+        <v>-1.393403</v>
       </c>
       <c r="AT43" t="n">
-        <v>28.5</v>
+        <v>2.292888</v>
       </c>
       <c r="AU43" t="n">
-        <v>329730</v>
+        <v>2.293116</v>
       </c>
       <c r="AV43" t="n">
-        <v>-0.500274</v>
+        <v>1.55383</v>
       </c>
       <c r="AW43" t="n">
-        <v>-1.393403</v>
+        <v>2.592546</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.292888</v>
+        <v>-9.166040000000001</v>
       </c>
       <c r="AY43" t="n">
-        <v>2.293116</v>
+        <v>4.831296</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.55383</v>
+        <v>6.536174</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.592546</v>
+        <v>4.767938</v>
       </c>
       <c r="BB43" t="n">
-        <v>0.909924</v>
+        <v>1</v>
       </c>
       <c r="BC43" t="n">
-        <v>-9.166040000000001</v>
+        <v>0.002578</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.831296</v>
+        <v>-0.19</v>
       </c>
       <c r="BE43" t="n">
-        <v>6.536174</v>
+        <v>-0.29</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.767938</v>
+        <v>-0.12</v>
       </c>
       <c r="BG43" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH43" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="BI43" t="n">
-        <v>0.002578</v>
-      </c>
-      <c r="BJ43" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="BK43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BL43" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BM43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8992,105 +8212,87 @@
         <v>0.045833</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.045833</v>
+        <v>0.16</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>101.23438</v>
       </c>
       <c r="AJ44" t="n">
-        <v>108.06979</v>
+        <v>5.8301</v>
       </c>
       <c r="AK44" t="n">
-        <v>101.23438</v>
+        <v>5.8295</v>
       </c>
       <c r="AL44" t="n">
-        <v>5.8301</v>
+        <v>6465016</v>
       </c>
       <c r="AM44" t="n">
-        <v>5.8295</v>
+        <v>2451957</v>
       </c>
       <c r="AN44" t="n">
-        <v>6465016</v>
+        <v>3.34</v>
       </c>
       <c r="AO44" t="n">
-        <v>2451957</v>
+        <v>2.43</v>
       </c>
       <c r="AP44" t="n">
-        <v>4013059</v>
+        <v>3.89</v>
       </c>
       <c r="AQ44" t="n">
-        <v>3.34</v>
+        <v>29.88</v>
       </c>
       <c r="AR44" t="n">
-        <v>2.43</v>
+        <v>328303</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.89</v>
+        <v>-2.914473</v>
       </c>
       <c r="AT44" t="n">
-        <v>29.88</v>
+        <v>-5.8492</v>
       </c>
       <c r="AU44" t="n">
-        <v>328303</v>
+        <v>-5.849767</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.581806</v>
+        <v>0.006404</v>
       </c>
       <c r="AW44" t="n">
-        <v>-2.914473</v>
+        <v>-1.889422</v>
       </c>
       <c r="AX44" t="n">
-        <v>-5.8492</v>
+        <v>-0.432778</v>
       </c>
       <c r="AY44" t="n">
-        <v>-5.849767</v>
+        <v>4.559874</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.006404</v>
+        <v>6.749097</v>
       </c>
       <c r="BA44" t="n">
-        <v>-1.889422</v>
+        <v>4.174145</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.201233</v>
+        <v>1</v>
       </c>
       <c r="BC44" t="n">
-        <v>-0.432778</v>
+        <v>0.001675</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.559874</v>
+        <v>0.26</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.749097</v>
+        <v>0.22</v>
       </c>
       <c r="BF44" t="n">
-        <v>4.174145</v>
+        <v>0.26</v>
       </c>
       <c r="BG44" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH44" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="BI44" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="BJ44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BK44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BL44" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -9189,105 +8391,87 @@
         <v>0.049037</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.049037</v>
+        <v>1.31</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.31</v>
+        <v>1.06</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.48</v>
+        <v>107.07838</v>
       </c>
       <c r="AJ45" t="n">
-        <v>108.77346</v>
+        <v>5.8488</v>
       </c>
       <c r="AK45" t="n">
-        <v>107.07838</v>
+        <v>5.8482</v>
       </c>
       <c r="AL45" t="n">
-        <v>5.8488</v>
+        <v>6511444</v>
       </c>
       <c r="AM45" t="n">
-        <v>5.8482</v>
+        <v>2477151</v>
       </c>
       <c r="AN45" t="n">
-        <v>6511444</v>
+        <v>3.41</v>
       </c>
       <c r="AO45" t="n">
-        <v>2477151</v>
+        <v>2.52</v>
       </c>
       <c r="AP45" t="n">
-        <v>4034293</v>
+        <v>3.96</v>
       </c>
       <c r="AQ45" t="n">
-        <v>3.41</v>
+        <v>30.53</v>
       </c>
       <c r="AR45" t="n">
-        <v>2.52</v>
+        <v>332508</v>
       </c>
       <c r="AS45" t="n">
-        <v>3.96</v>
+        <v>5.772742</v>
       </c>
       <c r="AT45" t="n">
-        <v>30.53</v>
+        <v>0.320749</v>
       </c>
       <c r="AU45" t="n">
-        <v>332508</v>
+        <v>0.320782</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.651126</v>
+        <v>0.7181419999999999</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.772742</v>
+        <v>1.027506</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.320749</v>
+        <v>1.280829</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.320782</v>
+        <v>5.05763</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.7181419999999999</v>
+        <v>8.444549</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.027506</v>
+        <v>4.866504</v>
       </c>
       <c r="BB45" t="n">
-        <v>0.529123</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.280829</v>
+        <v>0.003204</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.05763</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE45" t="n">
-        <v>8.444549</v>
+        <v>0.09</v>
       </c>
       <c r="BF45" t="n">
-        <v>4.866504</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH45" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="BI45" t="n">
-        <v>0.003204</v>
-      </c>
-      <c r="BJ45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BK45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL45" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -9386,105 +8570,87 @@
         <v>0.050508</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.050508</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="AH46" t="n">
-        <v>-0.34</v>
+        <v>0.51</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.51</v>
+        <v>114.05013</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110.09056</v>
+        <v>5.7422</v>
       </c>
       <c r="AK46" t="n">
-        <v>114.05013</v>
+        <v>5.7416</v>
       </c>
       <c r="AL46" t="n">
-        <v>5.7422</v>
+        <v>6576464</v>
       </c>
       <c r="AM46" t="n">
-        <v>5.7416</v>
+        <v>2498262</v>
       </c>
       <c r="AN46" t="n">
-        <v>6576464</v>
+        <v>3.44</v>
       </c>
       <c r="AO46" t="n">
-        <v>2498262</v>
+        <v>2.49</v>
       </c>
       <c r="AP46" t="n">
-        <v>4078202</v>
+        <v>4.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>3.44</v>
+        <v>31.34</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.49</v>
+        <v>336157</v>
       </c>
       <c r="AS46" t="n">
-        <v>4.03</v>
+        <v>6.510885</v>
       </c>
       <c r="AT46" t="n">
-        <v>31.34</v>
+        <v>-1.822596</v>
       </c>
       <c r="AU46" t="n">
-        <v>336157</v>
+        <v>-1.822783</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.210865</v>
+        <v>0.99855</v>
       </c>
       <c r="AW46" t="n">
-        <v>6.510885</v>
+        <v>0.852229</v>
       </c>
       <c r="AX46" t="n">
-        <v>-1.822596</v>
+        <v>1.097417</v>
       </c>
       <c r="AY46" t="n">
-        <v>-1.822783</v>
+        <v>5.47719</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.99855</v>
+        <v>8.586193</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.852229</v>
+        <v>5.201441</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.088394</v>
+        <v>1</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.097417</v>
+        <v>0.001471</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.47719</v>
+        <v>0.03</v>
       </c>
       <c r="BE46" t="n">
-        <v>8.586193</v>
+        <v>-0.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.201441</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BG46" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="BI46" t="n">
-        <v>0.001471</v>
-      </c>
-      <c r="BJ46" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BK46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL46" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BM46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -9583,105 +8749,87 @@
         <v>0.052531</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.052531</v>
+        <v>0.43</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.48</v>
+        <v>112.73813</v>
       </c>
       <c r="AJ47" t="n">
-        <v>109.72323</v>
+        <v>5.6608</v>
       </c>
       <c r="AK47" t="n">
-        <v>112.73813</v>
+        <v>5.6602</v>
       </c>
       <c r="AL47" t="n">
-        <v>5.6608</v>
+        <v>6623948</v>
       </c>
       <c r="AM47" t="n">
-        <v>5.6602</v>
+        <v>2512426</v>
       </c>
       <c r="AN47" t="n">
-        <v>6623948</v>
+        <v>3.67</v>
       </c>
       <c r="AO47" t="n">
-        <v>2512426</v>
+        <v>2.72</v>
       </c>
       <c r="AP47" t="n">
-        <v>4111522</v>
+        <v>4.25</v>
       </c>
       <c r="AQ47" t="n">
-        <v>3.67</v>
+        <v>31.63</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.72</v>
+        <v>340789</v>
       </c>
       <c r="AS47" t="n">
-        <v>4.25</v>
+        <v>-1.150371</v>
       </c>
       <c r="AT47" t="n">
-        <v>31.63</v>
+        <v>-1.417575</v>
       </c>
       <c r="AU47" t="n">
-        <v>340789</v>
+        <v>-1.417723</v>
       </c>
       <c r="AV47" t="n">
-        <v>-0.333662</v>
+        <v>0.722029</v>
       </c>
       <c r="AW47" t="n">
-        <v>-1.150371</v>
+        <v>0.566954</v>
       </c>
       <c r="AX47" t="n">
-        <v>-1.417575</v>
+        <v>1.377928</v>
       </c>
       <c r="AY47" t="n">
-        <v>-1.417723</v>
+        <v>5.529729</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.722029</v>
+        <v>8.510418</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.566954</v>
+        <v>5.316736</v>
       </c>
       <c r="BB47" t="n">
-        <v>0.8170269999999999</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.377928</v>
+        <v>0.002023</v>
       </c>
       <c r="BD47" t="n">
-        <v>5.529729</v>
+        <v>0.23</v>
       </c>
       <c r="BE47" t="n">
-        <v>8.510418</v>
+        <v>0.23</v>
       </c>
       <c r="BF47" t="n">
-        <v>5.316736</v>
+        <v>0.22</v>
       </c>
       <c r="BG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH47" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="BI47" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="BJ47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BK47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BL47" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BM47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -9780,105 +8928,87 @@
         <v>0.053936</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.053936</v>
+        <v>0.26</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.26</v>
+        <v>-0.49</v>
       </c>
       <c r="AH48" t="n">
-        <v>-0.49</v>
+        <v>0.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.35</v>
+        <v>108.66481</v>
       </c>
       <c r="AJ48" t="n">
-        <v>109.00057</v>
+        <v>5.7087</v>
       </c>
       <c r="AK48" t="n">
-        <v>108.66481</v>
+        <v>5.7081</v>
       </c>
       <c r="AL48" t="n">
-        <v>5.7087</v>
+        <v>6666287</v>
       </c>
       <c r="AM48" t="n">
-        <v>5.7081</v>
+        <v>2532708</v>
       </c>
       <c r="AN48" t="n">
-        <v>6666287</v>
+        <v>3.72</v>
       </c>
       <c r="AO48" t="n">
-        <v>2532708</v>
+        <v>2.67</v>
       </c>
       <c r="AP48" t="n">
-        <v>4133579</v>
+        <v>4.36</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.72</v>
+        <v>31.7</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.67</v>
+        <v>341459</v>
       </c>
       <c r="AS48" t="n">
-        <v>4.36</v>
+        <v>-3.613081</v>
       </c>
       <c r="AT48" t="n">
-        <v>31.7</v>
+        <v>0.84617</v>
       </c>
       <c r="AU48" t="n">
-        <v>341459</v>
+        <v>0.84626</v>
       </c>
       <c r="AV48" t="n">
-        <v>-0.658621</v>
+        <v>0.639181</v>
       </c>
       <c r="AW48" t="n">
-        <v>-3.613081</v>
+        <v>0.807268</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.84617</v>
+        <v>0.196603</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.84626</v>
+        <v>5.319636</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.639181</v>
+        <v>7.026183</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.807268</v>
+        <v>5.201418</v>
       </c>
       <c r="BB48" t="n">
-        <v>0.5364679999999999</v>
+        <v>0.5</v>
       </c>
       <c r="BC48" t="n">
-        <v>0.196603</v>
+        <v>0.001405</v>
       </c>
       <c r="BD48" t="n">
-        <v>5.319636</v>
+        <v>0.05</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.026183</v>
+        <v>-0.05</v>
       </c>
       <c r="BF48" t="n">
-        <v>5.201418</v>
+        <v>0.11</v>
       </c>
       <c r="BG48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="BI48" t="n">
-        <v>0.001405</v>
-      </c>
-      <c r="BJ48" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BK48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BL48" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9977,105 +9107,87 @@
         <v>0.054569</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.054569</v>
+        <v>0.24</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.24</v>
+        <v>-1.67</v>
       </c>
       <c r="AH49" t="n">
-        <v>-1.67</v>
+        <v>0.23</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.23</v>
+        <v>107.55639</v>
       </c>
       <c r="AJ49" t="n">
-        <v>108.76683</v>
+        <v>5.4571</v>
       </c>
       <c r="AK49" t="n">
-        <v>107.55639</v>
+        <v>5.4565</v>
       </c>
       <c r="AL49" t="n">
-        <v>5.4571</v>
+        <v>6703663</v>
       </c>
       <c r="AM49" t="n">
-        <v>5.4565</v>
+        <v>2547693</v>
       </c>
       <c r="AN49" t="n">
-        <v>6703663</v>
+        <v>3.75</v>
       </c>
       <c r="AO49" t="n">
-        <v>2547693</v>
+        <v>2.67</v>
       </c>
       <c r="AP49" t="n">
-        <v>4155970</v>
+        <v>4.41</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.75</v>
+        <v>31.85</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.67</v>
+        <v>344440</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.41</v>
+        <v>-1.020036</v>
       </c>
       <c r="AT49" t="n">
-        <v>31.85</v>
+        <v>-4.407308</v>
       </c>
       <c r="AU49" t="n">
-        <v>344440</v>
+        <v>-4.407771</v>
       </c>
       <c r="AV49" t="n">
-        <v>-0.214439</v>
+        <v>0.5606719999999999</v>
       </c>
       <c r="AW49" t="n">
-        <v>-1.020036</v>
+        <v>0.591659</v>
       </c>
       <c r="AX49" t="n">
-        <v>-4.407308</v>
+        <v>0.873018</v>
       </c>
       <c r="AY49" t="n">
-        <v>-4.407771</v>
+        <v>5.351165</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.5606719999999999</v>
+        <v>4.393261</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.591659</v>
+        <v>5.18043</v>
       </c>
       <c r="BB49" t="n">
-        <v>0.541686</v>
+        <v>0.25</v>
       </c>
       <c r="BC49" t="n">
-        <v>0.873018</v>
+        <v>0.000633</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.351165</v>
+        <v>0.03</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.393261</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.18043</v>
+        <v>0.05</v>
       </c>
       <c r="BG49" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>0.000633</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BM49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -10174,105 +9286,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.055131</v>
+        <v>0.26</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.26</v>
+        <v>-0.77</v>
       </c>
       <c r="AH50" t="n">
-        <v>-0.77</v>
+        <v>0.21</v>
       </c>
       <c r="AI50" t="n">
+        <v>113.14433</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>5.6021</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>5.6015</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>6733209</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>2544400</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>345111</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>5.195358</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>2.657089</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>2.657381</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0.440744</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>-0.129254</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0.194809</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>5.225222</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>2.961368</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>5.127976</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BD50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AJ50" t="n">
-        <v>108.27053</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>113.14433</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>5.6021</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>5.6015</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>6733209</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>2544400</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>4188808</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>345111</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>-0.456297</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>5.195358</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>2.657089</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.657381</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0.440744</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>-0.129254</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>0.79014</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>0.194809</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>5.225222</v>
-      </c>
       <c r="BE50" t="n">
-        <v>2.961368</v>
+        <v>0.12</v>
       </c>
       <c r="BF50" t="n">
-        <v>5.127976</v>
+        <v>0.25</v>
       </c>
       <c r="BG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="BI50" t="n">
-        <v>0.000562</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BM50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -10371,105 +9465,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.055131</v>
+        <v>-0.11</v>
       </c>
       <c r="AG51" t="n">
-        <v>-0.11</v>
+        <v>0.36</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.36</v>
+        <v>-0.21</v>
       </c>
       <c r="AI51" t="n">
-        <v>-0.21</v>
+        <v>110.57963</v>
       </c>
       <c r="AJ51" t="n">
-        <v>108.80021</v>
+        <v>5.4264</v>
       </c>
       <c r="AK51" t="n">
-        <v>110.57963</v>
+        <v>5.4258</v>
       </c>
       <c r="AL51" t="n">
-        <v>5.4264</v>
+        <v>6774436</v>
       </c>
       <c r="AM51" t="n">
-        <v>5.4258</v>
+        <v>2546265</v>
       </c>
       <c r="AN51" t="n">
-        <v>6774436</v>
+        <v>4.14</v>
       </c>
       <c r="AO51" t="n">
-        <v>2546265</v>
+        <v>2.85</v>
       </c>
       <c r="AP51" t="n">
-        <v>4228171</v>
+        <v>4.92</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4.14</v>
+        <v>31.87</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.85</v>
+        <v>350767</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.92</v>
+        <v>-2.266751</v>
       </c>
       <c r="AT51" t="n">
-        <v>31.87</v>
+        <v>-3.136324</v>
       </c>
       <c r="AU51" t="n">
-        <v>350767</v>
+        <v>-3.13666</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.489219</v>
+        <v>0.612293</v>
       </c>
       <c r="AW51" t="n">
-        <v>-2.266751</v>
+        <v>0.073298</v>
       </c>
       <c r="AX51" t="n">
-        <v>-3.136324</v>
+        <v>1.638893</v>
       </c>
       <c r="AY51" t="n">
-        <v>-3.13666</v>
+        <v>5.130501</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.612293</v>
+        <v>3.033233</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.073298</v>
+        <v>5.054283</v>
       </c>
       <c r="BB51" t="n">
-        <v>0.9397180000000001</v>
+        <v>0</v>
       </c>
       <c r="BC51" t="n">
-        <v>1.638893</v>
+        <v>0</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.130501</v>
+        <v>0.18</v>
       </c>
       <c r="BE51" t="n">
-        <v>3.033233</v>
+        <v>0.06</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.054283</v>
+        <v>0.26</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ51" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BK51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BL51" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -10568,105 +9644,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.055131</v>
+        <v>0.48</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.42</v>
+        <v>0.52</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.52</v>
+        <v>109.59513</v>
       </c>
       <c r="AJ52" t="n">
-        <v>108.63642</v>
+        <v>5.3186</v>
       </c>
       <c r="AK52" t="n">
-        <v>109.59513</v>
+        <v>5.318</v>
       </c>
       <c r="AL52" t="n">
-        <v>5.3186</v>
+        <v>6852705</v>
       </c>
       <c r="AM52" t="n">
-        <v>5.318</v>
+        <v>2589817</v>
       </c>
       <c r="AN52" t="n">
-        <v>6852705</v>
+        <v>4.09</v>
       </c>
       <c r="AO52" t="n">
-        <v>2589817</v>
+        <v>2.77</v>
       </c>
       <c r="AP52" t="n">
-        <v>4262888</v>
+        <v>4.89</v>
       </c>
       <c r="AQ52" t="n">
-        <v>4.09</v>
+        <v>31.47</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.77</v>
+        <v>356582</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.89</v>
+        <v>-0.890309</v>
       </c>
       <c r="AT52" t="n">
-        <v>31.47</v>
+        <v>-1.986584</v>
       </c>
       <c r="AU52" t="n">
-        <v>356582</v>
+        <v>-1.986804</v>
       </c>
       <c r="AV52" t="n">
-        <v>-0.150542</v>
+        <v>1.155358</v>
       </c>
       <c r="AW52" t="n">
-        <v>-0.890309</v>
+        <v>1.710427</v>
       </c>
       <c r="AX52" t="n">
-        <v>-1.986584</v>
+        <v>1.657796</v>
       </c>
       <c r="AY52" t="n">
-        <v>-1.986804</v>
+        <v>5.172369</v>
       </c>
       <c r="AZ52" t="n">
-        <v>1.155358</v>
+        <v>2.828436</v>
       </c>
       <c r="BA52" t="n">
-        <v>1.710427</v>
+        <v>5.096104</v>
       </c>
       <c r="BB52" t="n">
-        <v>0.821088</v>
+        <v>0</v>
       </c>
       <c r="BC52" t="n">
-        <v>1.657796</v>
+        <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.172369</v>
+        <v>-0.05</v>
       </c>
       <c r="BE52" t="n">
-        <v>2.828436</v>
+        <v>-0.08</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.096104</v>
+        <v>-0.03</v>
       </c>
       <c r="BG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ52" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BK52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BM52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -10765,105 +9823,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.055131</v>
+        <v>0.09</v>
       </c>
       <c r="AG53" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>110.16346</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>5.3843</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>5.3837</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>2597630</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>357103</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0.518572</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.235287</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>1.235427</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>1.038729</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0.301682</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0.146109</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>4.680811</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0.924206</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>4.490243</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AH53" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>108.7159</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>110.16346</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>5.3843</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>5.3837</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>6923886</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2597630</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>4326256</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>32.04</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>357103</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0.073161</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0.518572</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1.235287</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1.235427</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>1.038729</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0.301682</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>1.486504</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>0.146109</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>4.680811</v>
-      </c>
       <c r="BE53" t="n">
-        <v>0.924206</v>
+        <v>0.05</v>
       </c>
       <c r="BF53" t="n">
-        <v>4.490243</v>
+        <v>0.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ53" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BK53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BL53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BM53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10962,105 +10002,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.055131</v>
+        <v>0.18</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.27</v>
+        <v>0.03</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03</v>
+        <v>106.90236</v>
       </c>
       <c r="AJ54" t="n">
-        <v>109.27405</v>
+        <v>5.3338</v>
       </c>
       <c r="AK54" t="n">
-        <v>106.90236</v>
+        <v>5.3332</v>
       </c>
       <c r="AL54" t="n">
-        <v>5.3338</v>
+        <v>7003273</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.3332</v>
+        <v>2616213</v>
       </c>
       <c r="AN54" t="n">
-        <v>7003273</v>
+        <v>4.23</v>
       </c>
       <c r="AO54" t="n">
-        <v>2616213</v>
+        <v>2.74</v>
       </c>
       <c r="AP54" t="n">
-        <v>4387061</v>
+        <v>5.12</v>
       </c>
       <c r="AQ54" t="n">
-        <v>4.23</v>
+        <v>32.32</v>
       </c>
       <c r="AR54" t="n">
-        <v>2.74</v>
+        <v>360578</v>
       </c>
       <c r="AS54" t="n">
-        <v>5.12</v>
+        <v>-2.960237</v>
       </c>
       <c r="AT54" t="n">
-        <v>32.32</v>
+        <v>-0.937912</v>
       </c>
       <c r="AU54" t="n">
-        <v>360578</v>
+        <v>-0.938017</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.513402</v>
+        <v>1.146567</v>
       </c>
       <c r="AW54" t="n">
-        <v>-2.960237</v>
+        <v>0.715383</v>
       </c>
       <c r="AX54" t="n">
-        <v>-0.937912</v>
+        <v>0.973109</v>
       </c>
       <c r="AY54" t="n">
-        <v>-0.938017</v>
+        <v>4.461836</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.146567</v>
+        <v>-0.101973</v>
       </c>
       <c r="BA54" t="n">
-        <v>0.715383</v>
+        <v>4.177803</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.405488</v>
+        <v>0</v>
       </c>
       <c r="BC54" t="n">
-        <v>0.973109</v>
+        <v>-0</v>
       </c>
       <c r="BD54" t="n">
-        <v>4.461836</v>
+        <v>0.05</v>
       </c>
       <c r="BE54" t="n">
-        <v>-0.101973</v>
+        <v>-0.08</v>
       </c>
       <c r="BF54" t="n">
-        <v>4.177803</v>
+        <v>0.13</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BI54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="BJ54" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BK54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BL54" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BM54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -11159,105 +10181,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.33</v>
+        <v>-0.01</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.01</v>
+        <v>0.21</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.21</v>
+        <v>107.17649</v>
       </c>
       <c r="AJ55" t="n">
-        <v>109.41762</v>
+        <v>5.5024</v>
       </c>
       <c r="AK55" t="n">
-        <v>107.17649</v>
+        <v>5.5018</v>
       </c>
       <c r="AL55" t="n">
-        <v>5.5024</v>
+        <v>7136436</v>
       </c>
       <c r="AM55" t="n">
-        <v>5.5018</v>
+        <v>2701146</v>
       </c>
       <c r="AN55" t="n">
-        <v>7136436</v>
+        <v>4.2</v>
       </c>
       <c r="AO55" t="n">
-        <v>2701146</v>
+        <v>2.68</v>
       </c>
       <c r="AP55" t="n">
-        <v>4435290</v>
+        <v>5.12</v>
       </c>
       <c r="AQ55" t="n">
-        <v>4.2</v>
+        <v>31.99</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.68</v>
+        <v>358234</v>
       </c>
       <c r="AS55" t="n">
-        <v>5.12</v>
+        <v>0.25643</v>
       </c>
       <c r="AT55" t="n">
-        <v>31.99</v>
+        <v>3.160973</v>
       </c>
       <c r="AU55" t="n">
-        <v>358234</v>
+        <v>3.161329</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.131385</v>
+        <v>1.90144</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.25643</v>
+        <v>3.24641</v>
       </c>
       <c r="AX55" t="n">
-        <v>3.160973</v>
+        <v>-0.650067</v>
       </c>
       <c r="AY55" t="n">
-        <v>3.161329</v>
+        <v>4.264385</v>
       </c>
       <c r="AZ55" t="n">
-        <v>1.90144</v>
+        <v>-1.042167</v>
       </c>
       <c r="BA55" t="n">
-        <v>3.24641</v>
+        <v>3.897866</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.099346</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>-0.650067</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>4.264385</v>
+        <v>-0.03</v>
       </c>
       <c r="BE55" t="n">
-        <v>-1.042167</v>
+        <v>-0.06</v>
       </c>
       <c r="BF55" t="n">
-        <v>3.897866</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ55" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BK55" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -11356,105 +10360,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF56" t="n">
-        <v>0.055131</v>
+        <v>0.33</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.39</v>
+        <v>102.36456</v>
       </c>
       <c r="AJ56" t="n">
-        <v>110.05486</v>
+        <v>5.2301</v>
       </c>
       <c r="AK56" t="n">
-        <v>102.36456</v>
+        <v>5.2295</v>
       </c>
       <c r="AL56" t="n">
-        <v>5.2301</v>
+        <v>7130500</v>
       </c>
       <c r="AM56" t="n">
-        <v>5.2295</v>
+        <v>2654052</v>
       </c>
       <c r="AN56" t="n">
-        <v>7130500</v>
+        <v>4.45</v>
       </c>
       <c r="AO56" t="n">
-        <v>2654052</v>
+        <v>2.87</v>
       </c>
       <c r="AP56" t="n">
-        <v>4476448</v>
+        <v>5.38</v>
       </c>
       <c r="AQ56" t="n">
-        <v>4.45</v>
+        <v>32.6</v>
       </c>
       <c r="AR56" t="n">
-        <v>2.87</v>
+        <v>364367</v>
       </c>
       <c r="AS56" t="n">
-        <v>5.38</v>
+        <v>-4.489725</v>
       </c>
       <c r="AT56" t="n">
-        <v>32.6</v>
+        <v>-4.94875</v>
       </c>
       <c r="AU56" t="n">
-        <v>364367</v>
+        <v>-4.949289</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.582392</v>
+        <v>-0.083179</v>
       </c>
       <c r="AW56" t="n">
-        <v>-4.489725</v>
+        <v>-1.743482</v>
       </c>
       <c r="AX56" t="n">
-        <v>-4.94875</v>
+        <v>1.712009</v>
       </c>
       <c r="AY56" t="n">
-        <v>-4.949289</v>
+        <v>4.441351</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.083179</v>
+        <v>-0.903999</v>
       </c>
       <c r="BA56" t="n">
-        <v>-1.743482</v>
+        <v>4.303068</v>
       </c>
       <c r="BB56" t="n">
-        <v>0.927966</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.712009</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>4.441351</v>
+        <v>0.25</v>
       </c>
       <c r="BE56" t="n">
-        <v>-0.903999</v>
+        <v>0.19</v>
       </c>
       <c r="BF56" t="n">
-        <v>4.303068</v>
+        <v>0.26</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ56" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BK56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BL56" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BM56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -11553,105 +10539,87 @@
         <v>0.055131</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.055131</v>
+        <v>0.7</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.5600000000000001</v>
+        <v>106.82125</v>
       </c>
       <c r="AJ57" t="n">
-        <v>110.65892</v>
+        <v>5.1495</v>
       </c>
       <c r="AK57" t="n">
-        <v>106.82125</v>
+        <v>5.1489</v>
       </c>
       <c r="AL57" t="n">
-        <v>5.1495</v>
+        <v>7156987</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.1489</v>
+        <v>2655931</v>
       </c>
       <c r="AN57" t="n">
-        <v>7156987</v>
+        <v>4.64</v>
       </c>
       <c r="AO57" t="n">
-        <v>2655931</v>
+        <v>3.07</v>
       </c>
       <c r="AP57" t="n">
-        <v>4501056</v>
+        <v>5.56</v>
       </c>
       <c r="AQ57" t="n">
-        <v>4.64</v>
+        <v>32.78</v>
       </c>
       <c r="AR57" t="n">
-        <v>3.07</v>
+        <v>371074</v>
       </c>
       <c r="AS57" t="n">
-        <v>5.56</v>
+        <v>4.353743</v>
       </c>
       <c r="AT57" t="n">
-        <v>32.78</v>
+        <v>-1.54108</v>
       </c>
       <c r="AU57" t="n">
-        <v>371074</v>
+        <v>-1.541256</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.548872</v>
+        <v>0.371461</v>
       </c>
       <c r="AW57" t="n">
-        <v>4.353743</v>
+        <v>0.070797</v>
       </c>
       <c r="AX57" t="n">
-        <v>-1.54108</v>
+        <v>1.840727</v>
       </c>
       <c r="AY57" t="n">
-        <v>-1.541256</v>
+        <v>3.812497</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.371461</v>
+        <v>-2.659212</v>
       </c>
       <c r="BA57" t="n">
-        <v>0.070797</v>
+        <v>3.357475</v>
       </c>
       <c r="BB57" t="n">
-        <v>0.549722</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.840727</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.812497</v>
+        <v>0.19</v>
       </c>
       <c r="BE57" t="n">
-        <v>-2.659212</v>
+        <v>0.2</v>
       </c>
       <c r="BF57" t="n">
-        <v>3.357475</v>
+        <v>0.18</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI57" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ57" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BK57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BL57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BM57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -11750,105 +10718,87 @@
         <v>0.054777</v>
       </c>
       <c r="AF58" t="n">
-        <v>0.054777</v>
+        <v>0.88</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.52</v>
+        <v>0.91</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.91</v>
+        <v>117.8089</v>
       </c>
       <c r="AJ58" t="n">
-        <v>110.51078</v>
+        <v>5.2194</v>
       </c>
       <c r="AK58" t="n">
-        <v>117.8089</v>
+        <v>5.2188</v>
       </c>
       <c r="AL58" t="n">
-        <v>5.2194</v>
+        <v>7237735</v>
       </c>
       <c r="AM58" t="n">
-        <v>5.2188</v>
+        <v>2686046</v>
       </c>
       <c r="AN58" t="n">
-        <v>7237735</v>
+        <v>4.52</v>
       </c>
       <c r="AO58" t="n">
-        <v>2686046</v>
+        <v>3.04</v>
       </c>
       <c r="AP58" t="n">
-        <v>4551689</v>
+        <v>5.4</v>
       </c>
       <c r="AQ58" t="n">
-        <v>4.52</v>
+        <v>32.99</v>
       </c>
       <c r="AR58" t="n">
-        <v>3.04</v>
+        <v>362002</v>
       </c>
       <c r="AS58" t="n">
-        <v>5.4</v>
+        <v>10.286015</v>
       </c>
       <c r="AT58" t="n">
-        <v>32.99</v>
+        <v>1.357413</v>
       </c>
       <c r="AU58" t="n">
-        <v>362002</v>
+        <v>1.357572</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.133871</v>
+        <v>1.12824</v>
       </c>
       <c r="AW58" t="n">
-        <v>10.286015</v>
+        <v>1.133877</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.357413</v>
+        <v>-2.444795</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.357572</v>
+        <v>4.142847</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.12824</v>
+        <v>-1.819225</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.133877</v>
+        <v>3.768807</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.124914</v>
+        <v>-0.25</v>
       </c>
       <c r="BC58" t="n">
-        <v>-2.444795</v>
+        <v>-0.000354</v>
       </c>
       <c r="BD58" t="n">
-        <v>4.142847</v>
+        <v>-0.12</v>
       </c>
       <c r="BE58" t="n">
-        <v>-1.819225</v>
+        <v>-0.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>3.768807</v>
+        <v>-0.16</v>
       </c>
       <c r="BG58" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH58" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="BI58" t="n">
-        <v>-0.000354</v>
-      </c>
-      <c r="BJ58" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BK58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BL58" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BM58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -11947,105 +10897,87 @@
         <v>0.054223</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.054223</v>
+        <v>0.67</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.67</v>
+        <v>2.73</v>
       </c>
       <c r="AH59" t="n">
-        <v>2.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.8100000000000001</v>
+        <v>113.99365</v>
       </c>
       <c r="AJ59" t="n">
-        <v>110.95732</v>
+        <v>4.9886</v>
       </c>
       <c r="AK59" t="n">
-        <v>113.99365</v>
+        <v>4.988</v>
       </c>
       <c r="AL59" t="n">
-        <v>4.9886</v>
+        <v>7258599</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.988</v>
+        <v>2684623</v>
       </c>
       <c r="AN59" t="n">
-        <v>7258599</v>
+        <v>4.63</v>
       </c>
       <c r="AO59" t="n">
-        <v>2684623</v>
+        <v>3.15</v>
       </c>
       <c r="AP59" t="n">
-        <v>4573976</v>
+        <v>5.51</v>
       </c>
       <c r="AQ59" t="n">
-        <v>4.63</v>
+        <v>33.51</v>
       </c>
       <c r="AR59" t="n">
-        <v>3.15</v>
+        <v>366913</v>
       </c>
       <c r="AS59" t="n">
-        <v>5.51</v>
+        <v>-3.238507</v>
       </c>
       <c r="AT59" t="n">
-        <v>33.51</v>
+        <v>-4.421964</v>
       </c>
       <c r="AU59" t="n">
-        <v>366913</v>
+        <v>-4.422473</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.404069</v>
+        <v>0.288267</v>
       </c>
       <c r="AW59" t="n">
-        <v>-3.238507</v>
+        <v>-0.052977</v>
       </c>
       <c r="AX59" t="n">
-        <v>-4.421964</v>
+        <v>1.356622</v>
       </c>
       <c r="AY59" t="n">
-        <v>-4.422473</v>
+        <v>4.39172</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.288267</v>
+        <v>0.619623</v>
       </c>
       <c r="BA59" t="n">
-        <v>-0.052977</v>
+        <v>4.109608</v>
       </c>
       <c r="BB59" t="n">
-        <v>0.489642</v>
+        <v>-0.25</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.356622</v>
+        <v>-0.000554</v>
       </c>
       <c r="BD59" t="n">
-        <v>4.39172</v>
+        <v>0.11</v>
       </c>
       <c r="BE59" t="n">
-        <v>0.619623</v>
+        <v>0.11</v>
       </c>
       <c r="BF59" t="n">
-        <v>4.109608</v>
+        <v>0.11</v>
       </c>
       <c r="BG59" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH59" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="BI59" t="n">
-        <v>-0.000554</v>
-      </c>
-      <c r="BJ59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BK59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BL59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -12144,105 +11076,87 @@
         <v>0.0534</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.0534</v>
+        <v>0.58</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.65</v>
+        <v>109.52993</v>
       </c>
       <c r="AJ60" t="n">
-        <v>111.03587</v>
+        <v>5.0569</v>
       </c>
       <c r="AK60" t="n">
-        <v>109.52993</v>
+        <v>5.0563</v>
       </c>
       <c r="AL60" t="n">
-        <v>5.0569</v>
+        <v>7299615</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.0563</v>
+        <v>2704550</v>
       </c>
       <c r="AN60" t="n">
-        <v>7299615</v>
+        <v>4.74</v>
       </c>
       <c r="AO60" t="n">
-        <v>2704550</v>
+        <v>3.24</v>
       </c>
       <c r="AP60" t="n">
-        <v>4595065</v>
+        <v>5.62</v>
       </c>
       <c r="AQ60" t="n">
-        <v>4.74</v>
+        <v>33.42</v>
       </c>
       <c r="AR60" t="n">
-        <v>3.24</v>
+        <v>371137</v>
       </c>
       <c r="AS60" t="n">
-        <v>5.62</v>
+        <v>-3.915762</v>
       </c>
       <c r="AT60" t="n">
-        <v>33.42</v>
+        <v>1.369122</v>
       </c>
       <c r="AU60" t="n">
-        <v>371137</v>
+        <v>1.369286</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.07079299999999999</v>
+        <v>0.565068</v>
       </c>
       <c r="AW60" t="n">
-        <v>-3.915762</v>
+        <v>0.742264</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.369122</v>
+        <v>1.151227</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.369286</v>
+        <v>4.724907</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.565068</v>
+        <v>1.964454</v>
       </c>
       <c r="BA60" t="n">
-        <v>0.742264</v>
+        <v>4.420848</v>
       </c>
       <c r="BB60" t="n">
-        <v>0.461065</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.151227</v>
+        <v>-0.0008229999999999999</v>
       </c>
       <c r="BD60" t="n">
-        <v>4.724907</v>
+        <v>0.11</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.964454</v>
+        <v>0.09</v>
       </c>
       <c r="BF60" t="n">
-        <v>4.420848</v>
+        <v>0.11</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH60" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="BI60" t="n">
-        <v>-0.0008229999999999999</v>
-      </c>
-      <c r="BJ60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BK60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BL60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BM60" t="n">
         <v>-0.09</v>
       </c>
     </row>
@@ -12341,71 +11255,61 @@
         <v>0.053028</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.053028</v>
+        <v>0.16</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.16</v>
+        <v>-0.5</v>
       </c>
       <c r="AH61" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
-      <c r="AJ61" t="inlineStr"/>
-      <c r="AK61" t="inlineStr"/>
-      <c r="AL61" t="n">
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AM61" t="n">
+      <c r="AK61" t="n">
         <v>5.176</v>
       </c>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
       <c r="AN61" t="inlineStr"/>
       <c r="AO61" t="inlineStr"/>
       <c r="AP61" t="inlineStr"/>
       <c r="AQ61" t="inlineStr"/>
-      <c r="AR61" t="inlineStr"/>
+      <c r="AR61" t="n">
+        <v>367558</v>
+      </c>
       <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="inlineStr"/>
+      <c r="AT61" t="n">
+        <v>2.367063</v>
+      </c>
       <c r="AU61" t="n">
-        <v>367558</v>
+        <v>2.367344</v>
       </c>
       <c r="AV61" t="inlineStr"/>
       <c r="AW61" t="inlineStr"/>
       <c r="AX61" t="n">
-        <v>2.367063</v>
+        <v>-0.964334</v>
       </c>
       <c r="AY61" t="n">
-        <v>2.367344</v>
-      </c>
-      <c r="AZ61" t="inlineStr"/>
-      <c r="BA61" t="inlineStr"/>
-      <c r="BB61" t="inlineStr"/>
+        <v>4.641328</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>3.177699</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>4.327084</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="BC61" t="n">
-        <v>-0.964334</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>4.641328</v>
-      </c>
-      <c r="BE61" t="n">
-        <v>3.177699</v>
-      </c>
-      <c r="BF61" t="n">
-        <v>4.327084</v>
-      </c>
-      <c r="BG61" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="BH61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BI61" t="n">
-        <v>-0.000372</v>
-      </c>
-      <c r="BJ61" t="inlineStr"/>
-      <c r="BK61" t="inlineStr"/>
-      <c r="BL61" t="inlineStr"/>
-      <c r="BM61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -12415,22 +11319,22 @@
         <v>175335</v>
       </c>
       <c r="C62" t="n">
-        <v>172.75</v>
+        <v>173.740005</v>
       </c>
       <c r="D62" t="n">
-        <v>106.699997</v>
+        <v>107.169998</v>
       </c>
       <c r="E62" t="n">
-        <v>426.859985</v>
+        <v>428.609985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1097</v>
+        <v>5.1259</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8091</v>
+        <v>5.8325</v>
       </c>
       <c r="H62" t="n">
-        <v>7413.180176</v>
+        <v>7428.779785</v>
       </c>
       <c r="I62" t="n">
         <v>24932.080078</v>
@@ -12439,40 +11343,40 @@
         <v>52210.078125</v>
       </c>
       <c r="K62" t="n">
-        <v>4026.600098</v>
+        <v>4092.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>81.860001</v>
+        <v>82.660004</v>
       </c>
       <c r="M62" t="n">
-        <v>87.160004</v>
+        <v>87.91999800000001</v>
       </c>
       <c r="N62" t="n">
-        <v>1208.5</v>
+        <v>1207.75</v>
       </c>
       <c r="O62" t="n">
-        <v>475.75</v>
+        <v>478.5</v>
       </c>
       <c r="P62" t="n">
         <v>1.924731</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1887</v>
+        <v>2.774329</v>
       </c>
       <c r="R62" t="n">
-        <v>-1.185411</v>
+        <v>-0.750144</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.017677</v>
+        <v>-1.615978</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.391157</v>
+        <v>-1.078532</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.826212</v>
+        <v>-1.430755</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.149161</v>
+        <v>-0.941148</v>
       </c>
       <c r="W62" t="n">
         <v>-4.889198</v>
@@ -12481,19 +11385,19 @@
         <v>-0.208568</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.091978</v>
+        <v>1.727609</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.784174</v>
+        <v>18.935257</v>
       </c>
       <c r="AA62" t="n">
-        <v>19.528258</v>
+        <v>20.570489</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.215805</v>
+        <v>8.148645999999999</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.263477</v>
+        <v>15.92974</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -12501,56 +11405,46 @@
       <c r="AE62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="AF62" t="n">
-        <v>0.052531</v>
-      </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="n">
-        <v>5.1005</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>5.0998</v>
-      </c>
+      <c r="AJ62" t="n">
+        <v>5.1177</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>5.1171</v>
+      </c>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr"/>
       <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AU62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>-1.137812</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>-1.137944</v>
+      </c>
       <c r="AV62" t="inlineStr"/>
       <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="n">
-        <v>-1.470077</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>-1.472179</v>
-      </c>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
-      <c r="BB62" t="inlineStr"/>
-      <c r="BC62" t="inlineStr"/>
+      <c r="BB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>-0.000497</v>
+      </c>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
       <c r="BF62" t="inlineStr"/>
-      <c r="BG62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH62" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="BI62" t="n">
-        <v>-0.000497</v>
-      </c>
-      <c r="BJ62" t="inlineStr"/>
-      <c r="BK62" t="inlineStr"/>
-      <c r="BL62" t="inlineStr"/>
-      <c r="BM62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG62"/>
+  <dimension ref="A1:BK62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,140 +578,160 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>bcb_sgs_cdi</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>bcb_sgs_ipca</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_ibc_br</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_saldo_credito_pf</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_ibc_br_sa</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_ibc_br</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_var_pct_saldo_credito_pf</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_cdi</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_dif_inadimplencia_pj</t>
-        </is>
-      </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -784,46 +804,50 @@
         <v>0.016137</v>
       </c>
       <c r="AF2" t="n">
+        <v>0.016137</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0.96</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.78</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>1.02</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
+        <v>96.31464</v>
+      </c>
+      <c r="AK2" t="n">
         <v>99.83978</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AL2" t="n">
         <v>5.1216</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AM2" t="n">
         <v>5.121</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AN2" t="n">
         <v>4271865</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AO2" t="n">
         <v>1833179</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AP2" t="n">
+        <v>2438686</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>2.36</v>
       </c>
-      <c r="AO2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AP2" t="n">
+      <c r="AR2" t="n">
         <v>2.94</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AS2" t="n">
         <v>20.26</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>355671</v>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
@@ -837,6 +861,10 @@
       <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -933,81 +961,93 @@
         <v>0.019413</v>
       </c>
       <c r="AF3" t="n">
+        <v>0.019413</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.87</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>0.66</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>0.88</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
+        <v>97.07568000000001</v>
+      </c>
+      <c r="AK3" t="n">
         <v>99.32829</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>5.1433</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>5.1427</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>4346060</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AO3" t="n">
         <v>1851006</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AP3" t="n">
+        <v>2495054</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>2.37</v>
       </c>
-      <c r="AO3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="AR3" t="n">
         <v>2.96</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AS3" t="n">
         <v>20.92</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>370395</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="AU3" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="AV3" t="n">
         <v>-0.512311</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="AW3" t="n">
         <v>0.423696</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AX3" t="n">
         <v>0.423745</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AY3" t="n">
         <v>1.736829</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AZ3" t="n">
         <v>0.972464</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BA3" t="n">
+        <v>2.311409</v>
+      </c>
+      <c r="BB3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="n">
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="n">
         <v>1</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BG3" t="n">
         <v>0.003276</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BH3" t="n">
+        <v>0.003276</v>
+      </c>
+      <c r="BI3" t="n">
         <v>0.01</v>
       </c>
-      <c r="BE3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>0.02</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1106,81 +1146,93 @@
         <v>0.021003</v>
       </c>
       <c r="AF4" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.16</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>-0.64</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>1.2</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
+        <v>96.95968999999999</v>
+      </c>
+      <c r="AK4" t="n">
         <v>97.24746</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>5.4394</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>5.4388</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>4441056</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
         <v>1894119</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
+        <v>2546936</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>2.34</v>
       </c>
-      <c r="AO4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="AR4" t="n">
         <v>3.01</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AS4" t="n">
         <v>21.42</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>368886</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="AU4" t="n">
+        <v>-0.119484</v>
+      </c>
+      <c r="AV4" t="n">
         <v>-2.094902</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="AW4" t="n">
         <v>5.757004</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AX4" t="n">
         <v>5.757676</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AY4" t="n">
         <v>2.185796</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AZ4" t="n">
         <v>2.329166</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BA4" t="n">
+        <v>2.079394</v>
+      </c>
+      <c r="BB4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="n">
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="n">
         <v>1</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BG4" t="n">
         <v>0.001591</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BH4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="BI4" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE4" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>0.05</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1279,81 +1331,93 @@
         <v>0.024244</v>
       </c>
       <c r="AF5" t="n">
+        <v>0.024244</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.25</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>0.64</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
+        <v>97.48142</v>
+      </c>
+      <c r="AK5" t="n">
         <v>96.62081999999999</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AL5" t="n">
         <v>5.643</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>5.6424</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>4511956</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
         <v>1910940</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AP5" t="n">
+        <v>2601017</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>2.33</v>
       </c>
-      <c r="AO5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AP5" t="n">
+      <c r="AR5" t="n">
         <v>2.99</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AS5" t="n">
         <v>22.89</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>367927</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AU5" t="n">
+        <v>0.53809</v>
+      </c>
+      <c r="AV5" t="n">
         <v>-0.644377</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AW5" t="n">
         <v>3.74306</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AX5" t="n">
         <v>3.743473</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AY5" t="n">
         <v>1.596467</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AZ5" t="n">
         <v>0.888065</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
+        <v>2.123375</v>
+      </c>
+      <c r="BB5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="n">
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="n">
         <v>1.5</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BG5" t="n">
         <v>0.00324</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BH5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="BI5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1452,81 +1516,93 @@
         <v>0.029256</v>
       </c>
       <c r="AF6" t="n">
+        <v>0.029256</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.95</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AH6" t="n">
         <v>0.02</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AI6" t="n">
         <v>0.84</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
+        <v>98.97262000000001</v>
+      </c>
+      <c r="AK6" t="n">
         <v>98.05768</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AL6" t="n">
         <v>5.6199</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>5.6193</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>4597507</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
         <v>1933111</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AP6" t="n">
+        <v>2664395</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>2.36</v>
       </c>
-      <c r="AO6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AR6" t="n">
         <v>3.01</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AS6" t="n">
         <v>23.91</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>367772</v>
       </c>
-      <c r="AS6" t="n">
+      <c r="AU6" t="n">
+        <v>1.529727</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1.487112</v>
       </c>
-      <c r="AT6" t="n">
+      <c r="AW6" t="n">
         <v>-0.409357</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AX6" t="n">
         <v>-0.4094</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AY6" t="n">
         <v>1.896096</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AZ6" t="n">
         <v>1.160214</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="BA6" t="n">
+        <v>2.436662</v>
+      </c>
+      <c r="BB6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="n">
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="n">
         <v>0</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BG6" t="n">
         <v>0.005012</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BH6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BI6" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BG6" t="n">
+      <c r="BK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1625,81 +1701,93 @@
         <v>0.033316</v>
       </c>
       <c r="AF7" t="n">
+        <v>0.033316</v>
+      </c>
+      <c r="AG7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AH7" t="n">
         <v>0.87</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AI7" t="n">
         <v>0.73</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
+        <v>99.35339</v>
+      </c>
+      <c r="AK7" t="n">
         <v>99.33126</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AL7" t="n">
         <v>5.5805</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>5.5799</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>4682852</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
         <v>1974391</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AP7" t="n">
+        <v>2708461</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>2.35</v>
       </c>
-      <c r="AO7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AR7" t="n">
         <v>3.05</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AS7" t="n">
         <v>24.21</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>362204</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="AU7" t="n">
+        <v>0.384723</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1.298807</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="AW7" t="n">
         <v>-0.70108</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AX7" t="n">
         <v>-0.701155</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AY7" t="n">
         <v>1.856332</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AZ7" t="n">
         <v>2.135418</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BA7" t="n">
+        <v>1.653884</v>
+      </c>
+      <c r="BB7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="n">
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BG7" t="n">
         <v>0.00406</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BH7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="BI7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BE7" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>0.04</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1798,81 +1886,93 @@
         <v>0.034749</v>
       </c>
       <c r="AF8" t="n">
+        <v>0.034749</v>
+      </c>
+      <c r="AG8" t="n">
         <v>0.54</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AH8" t="n">
         <v>1.82</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AI8" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
+        <v>97.34401</v>
+      </c>
+      <c r="AK8" t="n">
         <v>90.45032</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AL8" t="n">
         <v>5.3574</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>5.3568</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>4682131</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>1947035</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
+        <v>2735096</v>
+      </c>
+      <c r="AQ8" t="n">
         <v>2.51</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AR8" t="n">
         <v>3.26</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AS8" t="n">
         <v>25.23</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
         <v>358398</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="AU8" t="n">
+        <v>-2.022457</v>
+      </c>
+      <c r="AV8" t="n">
         <v>-8.94073</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="AW8" t="n">
         <v>-3.99785</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AX8" t="n">
         <v>-3.99828</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AY8" t="n">
         <v>-0.015397</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AZ8" t="n">
         <v>-1.385541</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BA8" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="BB8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="n">
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="n">
         <v>0</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BG8" t="n">
         <v>0.001433</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BH8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="BI8" t="n">
         <v>0.16</v>
       </c>
-      <c r="BE8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>0.21</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1971,81 +2071,93 @@
         <v>0.039598</v>
       </c>
       <c r="AF9" t="n">
+        <v>0.039598</v>
+      </c>
+      <c r="AG9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AI9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AJ9" t="n">
+        <v>98.43725000000001</v>
+      </c>
+      <c r="AK9" t="n">
         <v>95.72214</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
         <v>5.1394</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>5.1388</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>4727818</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
         <v>1971524</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
+        <v>2756295</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>2.57</v>
       </c>
-      <c r="AO9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="AR9" t="n">
         <v>3.38</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AS9" t="n">
         <v>25.63</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AT9" t="n">
         <v>357740</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="AU9" t="n">
+        <v>1.123069</v>
+      </c>
+      <c r="AV9" t="n">
         <v>5.828415</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="AW9" t="n">
         <v>-4.069138</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AX9" t="n">
         <v>-4.069594</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AY9" t="n">
         <v>0.975774</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AZ9" t="n">
         <v>1.257759</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BA9" t="n">
+        <v>0.775073</v>
+      </c>
+      <c r="BB9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="n">
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="n">
         <v>1.5</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BG9" t="n">
         <v>0.004849</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BH9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="BI9" t="n">
         <v>0.06</v>
       </c>
-      <c r="BE9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>0.12</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2144,81 +2256,93 @@
         <v>0.041954</v>
       </c>
       <c r="AF10" t="n">
+        <v>0.041954</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
         <v>1.74</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AI10" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
+        <v>99.55981</v>
+      </c>
+      <c r="AK10" t="n">
         <v>104.61484</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
         <v>4.7378</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AM10" t="n">
         <v>4.7372</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AN10" t="n">
         <v>4794583</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AO10" t="n">
         <v>1994119</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AP10" t="n">
+        <v>2800464</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>2.66</v>
       </c>
-      <c r="AO10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AR10" t="n">
         <v>3.45</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
         <v>26.54</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AT10" t="n">
         <v>353169</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AU10" t="n">
+        <v>1.140381</v>
+      </c>
+      <c r="AV10" t="n">
         <v>9.290118</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AW10" t="n">
         <v>-7.814142</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AX10" t="n">
         <v>-7.815054</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AY10" t="n">
         <v>1.412174</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AZ10" t="n">
         <v>1.146068</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BA10" t="n">
+        <v>1.602477</v>
+      </c>
+      <c r="BB10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="n">
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="n">
         <v>1</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BG10" t="n">
         <v>0.002356</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BH10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="BI10" t="n">
         <v>0.09</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2317,81 +2441,93 @@
         <v>0.043739</v>
       </c>
       <c r="AF11" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.06</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AH11" t="n">
         <v>1.41</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AI11" t="n">
         <v>1.04</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AJ11" t="n">
+        <v>99.51646</v>
+      </c>
+      <c r="AK11" t="n">
         <v>100.42352</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AL11" t="n">
         <v>4.9191</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AM11" t="n">
         <v>4.9185</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AN11" t="n">
         <v>4833732</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AO11" t="n">
         <v>2003312</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AP11" t="n">
+        <v>2830420</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>2.72</v>
       </c>
-      <c r="AO11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AR11" t="n">
         <v>3.54</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AS11" t="n">
         <v>27.46</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AT11" t="n">
         <v>345097</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AU11" t="n">
+        <v>-0.043542</v>
+      </c>
+      <c r="AV11" t="n">
         <v>-4.00643</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AW11" t="n">
         <v>3.826671</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AX11" t="n">
         <v>3.827155</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AY11" t="n">
         <v>0.816526</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AZ11" t="n">
         <v>0.461006</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BA11" t="n">
+        <v>1.06968</v>
+      </c>
+      <c r="BB11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="n">
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="n">
         <v>0</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BG11" t="n">
         <v>0.001785</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BH11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="BI11" t="n">
         <v>0.06</v>
       </c>
-      <c r="BE11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>0.09</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BK11" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -2490,81 +2626,93 @@
         <v>0.046796</v>
       </c>
       <c r="AF12" t="n">
+        <v>0.046796</v>
+      </c>
+      <c r="AG12" t="n">
         <v>0.47</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AI12" t="n">
         <v>0.45</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AJ12" t="n">
+        <v>99.67415</v>
+      </c>
+      <c r="AK12" t="n">
         <v>99.79777</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AL12" t="n">
         <v>4.7289</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AM12" t="n">
         <v>4.7283</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AN12" t="n">
         <v>4889397</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AO12" t="n">
         <v>2013726</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AP12" t="n">
+        <v>2875671</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>2.79</v>
       </c>
-      <c r="AO12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AP12" t="n">
+      <c r="AR12" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AS12" t="n">
         <v>27.42</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="AT12" t="n">
         <v>346415</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AU12" t="n">
+        <v>0.158456</v>
+      </c>
+      <c r="AV12" t="n">
         <v>-0.623111</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="AW12" t="n">
         <v>-3.866561</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AX12" t="n">
         <v>-3.867033</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AY12" t="n">
         <v>1.151595</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AZ12" t="n">
         <v>0.5198390000000001</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BA12" t="n">
+        <v>1.598738</v>
+      </c>
+      <c r="BB12" t="n">
         <v>0.381922</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="n">
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="n">
         <v>1</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BG12" t="n">
         <v>0.003057</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BH12" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="BI12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>0.11</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BK12" t="n">
         <v>-0.04</v>
       </c>
     </row>
@@ -2663,87 +2811,99 @@
         <v>0.048116</v>
       </c>
       <c r="AF13" t="n">
+        <v>0.048116</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AI13" t="n">
         <v>0.62</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AJ13" t="n">
+        <v>99.6343</v>
+      </c>
+      <c r="AK13" t="n">
         <v>99.53784</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AL13" t="n">
         <v>5.238</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AM13" t="n">
         <v>5.2374</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AN13" t="n">
         <v>4965603</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AO13" t="n">
         <v>2052569</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AP13" t="n">
+        <v>2913035</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>2.73</v>
       </c>
-      <c r="AO13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AR13" t="n">
         <v>3.57</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AS13" t="n">
         <v>27.88</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="AT13" t="n">
         <v>341958</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="AU13" t="n">
+        <v>-0.03998</v>
+      </c>
+      <c r="AV13" t="n">
         <v>-0.260457</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="AW13" t="n">
         <v>10.765717</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AX13" t="n">
         <v>10.767083</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AY13" t="n">
         <v>1.558597</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AZ13" t="n">
         <v>1.928912</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BA13" t="n">
+        <v>1.299314</v>
+      </c>
+      <c r="BB13" t="n">
         <v>-1.286607</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BC13" t="n">
         <v>11.88673</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BD13" t="n">
         <v>10.700862</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BE13" t="n">
         <v>11.919595</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BF13" t="n">
         <v>0.5</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BG13" t="n">
         <v>0.00132</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BH13" t="n">
+        <v>0.00132</v>
+      </c>
+      <c r="BI13" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BE13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BF13" t="n">
+      <c r="BJ13" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BK13" t="n">
         <v>0.46</v>
       </c>
     </row>
@@ -2842,87 +3002,99 @@
         <v>0.049037</v>
       </c>
       <c r="AF14" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG14" t="n">
         <v>-0.68</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AH14" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AI14" t="n">
         <v>-0.6</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AJ14" t="n">
+        <v>101.27684</v>
+      </c>
+      <c r="AK14" t="n">
         <v>103.95861</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AL14" t="n">
         <v>5.1884</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AM14" t="n">
         <v>5.1878</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AN14" t="n">
         <v>4999244</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AO14" t="n">
         <v>2047038</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AP14" t="n">
+        <v>2952207</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>2.84</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AR14" t="n">
         <v>3.71</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AS14" t="n">
         <v>29.24</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="AT14" t="n">
         <v>346403</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AU14" t="n">
+        <v>1.648569</v>
+      </c>
+      <c r="AV14" t="n">
         <v>4.441296</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="AW14" t="n">
         <v>-0.946926</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AX14" t="n">
         <v>-0.947035</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AY14" t="n">
         <v>0.677481</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AZ14" t="n">
         <v>-0.269467</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BA14" t="n">
+        <v>1.344714</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.299867</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BC14" t="n">
         <v>10.069235</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BD14" t="n">
         <v>10.074751</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BE14" t="n">
         <v>10.124804</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BF14" t="n">
         <v>0</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BG14" t="n">
         <v>0.0009210000000000001</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BH14" t="n">
+        <v>0.0009210000000000001</v>
+      </c>
+      <c r="BI14" t="n">
         <v>0.11</v>
       </c>
-      <c r="BE14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BF14" t="n">
+      <c r="BJ14" t="n">
         <v>0.14</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BK14" t="n">
         <v>1.36</v>
       </c>
     </row>
@@ -3021,87 +3193,99 @@
         <v>0.05056</v>
       </c>
       <c r="AF15" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="AG15" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AH15" t="n">
         <v>-0.7</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AI15" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AJ15" t="n">
+        <v>101.07328</v>
+      </c>
+      <c r="AK15" t="n">
         <v>104.56278</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AL15" t="n">
         <v>5.179</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AM15" t="n">
         <v>5.1784</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AN15" t="n">
         <v>5072711</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AO15" t="n">
         <v>2064183</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AP15" t="n">
+        <v>3008528</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AO15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AR15" t="n">
         <v>3.78</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AS15" t="n">
         <v>28.6</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="AT15" t="n">
         <v>339664</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="AU15" t="n">
+        <v>-0.200994</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0.581164</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="AW15" t="n">
         <v>-0.181173</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="AX15" t="n">
         <v>-0.181194</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AY15" t="n">
         <v>1.469562</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AZ15" t="n">
         <v>0.837552</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BA15" t="n">
+        <v>1.907759</v>
+      </c>
+      <c r="BB15" t="n">
         <v>-1.945422</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BC15" t="n">
         <v>8.727061000000001</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BD15" t="n">
         <v>8.58755</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BE15" t="n">
         <v>8.825751</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BF15" t="n">
         <v>0.5</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BG15" t="n">
         <v>0.001523</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BH15" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="BI15" t="n">
         <v>0.06</v>
       </c>
-      <c r="BE15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BF15" t="n">
+      <c r="BJ15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BK15" t="n">
         <v>-0.64</v>
       </c>
     </row>
@@ -3200,87 +3384,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF16" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG16" t="n">
         <v>-0.29</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AI16" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AJ16" t="n">
+        <v>101.17973</v>
+      </c>
+      <c r="AK16" t="n">
         <v>101.38087</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AL16" t="n">
         <v>5.4066</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AM16" t="n">
         <v>5.406</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AN16" t="n">
         <v>5164775</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AO16" t="n">
         <v>2109806</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AP16" t="n">
+        <v>3054969</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>2.92</v>
       </c>
-      <c r="AO16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AP16" t="n">
+      <c r="AR16" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AS16" t="n">
         <v>28.57</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="AT16" t="n">
         <v>327580</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="AU16" t="n">
+        <v>0.10532</v>
+      </c>
+      <c r="AV16" t="n">
         <v>-3.043062</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="AW16" t="n">
         <v>4.394671</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="AX16" t="n">
         <v>4.39518</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="AY16" t="n">
         <v>1.814888</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AZ16" t="n">
         <v>2.210221</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BA16" t="n">
+        <v>1.543645</v>
+      </c>
+      <c r="BB16" t="n">
         <v>-3.557633</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BC16" t="n">
         <v>7.168596</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BD16" t="n">
         <v>8.248760000000001</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BE16" t="n">
         <v>7.191214</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BF16" t="n">
         <v>0</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BG16" t="n">
         <v>0.000228</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BH16" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="BI16" t="n">
         <v>0.02</v>
       </c>
-      <c r="BE16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF16" t="n">
+      <c r="BJ16" t="n">
         <v>0.02</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BK16" t="n">
         <v>-0.03</v>
       </c>
     </row>
@@ -3379,87 +3575,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF17" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG17" t="n">
         <v>0.59</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
         <v>-0.97</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI17" t="n">
         <v>0.47</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ17" t="n">
+        <v>101.46342</v>
+      </c>
+      <c r="AK17" t="n">
         <v>100.20398</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AL17" t="n">
         <v>5.257</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AM17" t="n">
         <v>5.2564</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AN17" t="n">
         <v>5215990</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AO17" t="n">
         <v>2105856</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AP17" t="n">
+        <v>3110134</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>3.04</v>
       </c>
-      <c r="AO17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AP17" t="n">
+      <c r="AR17" t="n">
         <v>3.89</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AS17" t="n">
         <v>29.68</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="AT17" t="n">
         <v>325546</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AU17" t="n">
+        <v>0.280382</v>
+      </c>
+      <c r="AV17" t="n">
         <v>-1.16086</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="AW17" t="n">
         <v>-2.766988</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AX17" t="n">
         <v>-2.767296</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AY17" t="n">
         <v>0.991621</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AZ17" t="n">
         <v>-0.187221</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BA17" t="n">
+        <v>1.805747</v>
+      </c>
+      <c r="BB17" t="n">
         <v>-0.6209170000000001</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BC17" t="n">
         <v>6.470016</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BD17" t="n">
         <v>6.517038</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BE17" t="n">
         <v>6.460076</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BF17" t="n">
         <v>0</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BG17" t="n">
         <v>0</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
         <v>0.12</v>
       </c>
-      <c r="BE17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BF17" t="n">
+      <c r="BJ17" t="n">
         <v>0.09</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BK17" t="n">
         <v>1.11</v>
       </c>
     </row>
@@ -3558,87 +3766,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF18" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG18" t="n">
         <v>0.41</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AH18" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AI18" t="n">
         <v>0.38</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AJ18" t="n">
+        <v>100.66227</v>
+      </c>
+      <c r="AK18" t="n">
         <v>99.36927</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AL18" t="n">
         <v>5.2941</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AM18" t="n">
         <v>5.2935</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AN18" t="n">
         <v>5285657</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AO18" t="n">
         <v>2130312</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AP18" t="n">
+        <v>3155345</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>3.07</v>
       </c>
-      <c r="AO18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="AR18" t="n">
         <v>3.92</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AS18" t="n">
         <v>30.52</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="AT18" t="n">
         <v>331505</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="AU18" t="n">
+        <v>-0.789595</v>
+      </c>
+      <c r="AV18" t="n">
         <v>-0.8330109999999999</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="AW18" t="n">
         <v>0.705726</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AX18" t="n">
         <v>0.705806</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AY18" t="n">
         <v>1.335643</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AZ18" t="n">
         <v>1.161333</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BA18" t="n">
+        <v>1.453667</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.830463</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BC18" t="n">
         <v>5.900488</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BD18" t="n">
         <v>5.899363</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BE18" t="n">
         <v>5.974439</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BF18" t="n">
         <v>0</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BG18" t="n">
         <v>0</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI18" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE18" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BF18" t="n">
+      <c r="BJ18" t="n">
         <v>0.03</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BK18" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -3737,87 +3957,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF19" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG19" t="n">
         <v>0.62</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>0.45</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AI19" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AJ19" t="n">
+        <v>100.58196</v>
+      </c>
+      <c r="AK19" t="n">
         <v>99.97806</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AL19" t="n">
         <v>5.2177</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AM19" t="n">
         <v>5.2171</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AN19" t="n">
         <v>5366069</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AO19" t="n">
         <v>2178236</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AP19" t="n">
+        <v>3187833</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>3.07</v>
       </c>
-      <c r="AO19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="AR19" t="n">
         <v>3.94</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AS19" t="n">
         <v>29.64</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AT19" t="n">
         <v>324703</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="AU19" t="n">
+        <v>-0.07978200000000001</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0.612654</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="AW19" t="n">
         <v>-1.443116</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AX19" t="n">
         <v>-1.443279</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AY19" t="n">
         <v>1.521325</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AZ19" t="n">
         <v>2.249624</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BA19" t="n">
+        <v>1.029618</v>
+      </c>
+      <c r="BB19" t="n">
         <v>-2.051854</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BC19" t="n">
         <v>5.784842</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BD19" t="n">
         <v>5.458422</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BE19" t="n">
         <v>5.932356</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BF19" t="n">
         <v>0</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BG19" t="n">
         <v>-0</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BH19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI19" t="n">
         <v>0</v>
       </c>
-      <c r="BE19" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BF19" t="n">
+      <c r="BJ19" t="n">
         <v>0.02</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BK19" t="n">
         <v>-0.88</v>
       </c>
     </row>
@@ -3916,87 +4148,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF20" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG20" t="n">
         <v>0.53</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AH20" t="n">
         <v>0.21</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AI20" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AJ20" t="n">
+        <v>100.05178</v>
+      </c>
+      <c r="AK20" t="n">
         <v>93.79237000000001</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AL20" t="n">
         <v>5.0993</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AM20" t="n">
         <v>5.0987</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AN20" t="n">
         <v>5373231</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AO20" t="n">
         <v>2151399</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AP20" t="n">
+        <v>3221831</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>3.24</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AP20" t="n">
+      <c r="AR20" t="n">
         <v>4.11</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AS20" t="n">
         <v>30.54</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="AT20" t="n">
         <v>331122</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="AU20" t="n">
+        <v>-0.527112</v>
+      </c>
+      <c r="AV20" t="n">
         <v>-6.187047</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="AW20" t="n">
         <v>-2.269199</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="AX20" t="n">
         <v>-2.26946</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="AY20" t="n">
         <v>0.133468</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AZ20" t="n">
         <v>-1.232052</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BA20" t="n">
+        <v>1.066493</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.976883</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BC20" t="n">
         <v>5.77432</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BD20" t="n">
         <v>3.79089</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BE20" t="n">
         <v>5.711379</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BF20" t="n">
         <v>0</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BG20" t="n">
         <v>0</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
         <v>0.17</v>
       </c>
-      <c r="BE20" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BF20" t="n">
+      <c r="BJ20" t="n">
         <v>0.17</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BK20" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -4095,87 +4339,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF21" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG21" t="n">
         <v>0.84</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AH21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AI21" t="n">
         <v>0.77</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
+        <v>103.00964</v>
+      </c>
+      <c r="AK21" t="n">
         <v>98.75064999999999</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AL21" t="n">
         <v>5.2078</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AM21" t="n">
         <v>5.2072</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AN21" t="n">
         <v>5370950</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AO21" t="n">
         <v>2136105</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AP21" t="n">
+        <v>3234845</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>3.36</v>
       </c>
-      <c r="AO21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AR21" t="n">
         <v>4.16</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AS21" t="n">
         <v>30.48</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AT21" t="n">
         <v>328098</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AU21" t="n">
+        <v>2.956329</v>
+      </c>
+      <c r="AV21" t="n">
         <v>5.286443</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AW21" t="n">
         <v>2.127743</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AX21" t="n">
         <v>2.127993</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AY21" t="n">
         <v>-0.042451</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AZ21" t="n">
         <v>-0.710886</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BA21" t="n">
+        <v>0.403932</v>
+      </c>
+      <c r="BB21" t="n">
         <v>-0.913259</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BC21" t="n">
         <v>5.596302</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BD21" t="n">
         <v>1.864495</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BE21" t="n">
         <v>5.47065</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BF21" t="n">
         <v>0</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BG21" t="n">
         <v>0</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI21" t="n">
         <v>0.12</v>
       </c>
-      <c r="BE21" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BF21" t="n">
+      <c r="BJ21" t="n">
         <v>0.05</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BK21" t="n">
         <v>-0.06</v>
       </c>
     </row>
@@ -4274,87 +4530,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF22" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG22" t="n">
         <v>0.71</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AH22" t="n">
         <v>0.05</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AI22" t="n">
         <v>0.64</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AJ22" t="n">
+        <v>103.09341</v>
+      </c>
+      <c r="AK22" t="n">
         <v>110.62354</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AL22" t="n">
         <v>5.0804</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AM22" t="n">
         <v>5.0798</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AN22" t="n">
         <v>5424811</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AO22" t="n">
         <v>2154900</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AP22" t="n">
+        <v>3269910</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>3.35</v>
       </c>
-      <c r="AO22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AP22" t="n">
+      <c r="AR22" t="n">
         <v>4.11</v>
       </c>
-      <c r="AQ22" t="n">
+      <c r="AS22" t="n">
         <v>30.99</v>
       </c>
-      <c r="AR22" t="n">
+      <c r="AT22" t="n">
         <v>341158</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AU22" t="n">
+        <v>0.08132200000000001</v>
+      </c>
+      <c r="AV22" t="n">
         <v>12.023101</v>
       </c>
-      <c r="AT22" t="n">
+      <c r="AW22" t="n">
         <v>-2.446331</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AX22" t="n">
         <v>-2.446612</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AY22" t="n">
         <v>1.002821</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AZ22" t="n">
         <v>0.879872</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="BA22" t="n">
+        <v>1.083978</v>
+      </c>
+      <c r="BB22" t="n">
         <v>3.980518</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BC22" t="n">
         <v>4.650694</v>
       </c>
-      <c r="AZ22" t="n">
+      <c r="BD22" t="n">
         <v>0.172427</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BE22" t="n">
         <v>4.361088</v>
       </c>
-      <c r="BB22" t="n">
+      <c r="BF22" t="n">
         <v>0</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BG22" t="n">
         <v>0</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BE22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF22" t="n">
+      <c r="BJ22" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BK22" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4453,87 +4721,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF23" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG23" t="n">
         <v>0.61</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AH23" t="n">
         <v>-0.95</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AI23" t="n">
         <v>0.53</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AJ23" t="n">
+        <v>104.1626</v>
+      </c>
+      <c r="AK23" t="n">
         <v>104.34152</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AL23" t="n">
         <v>5.0007</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AM23" t="n">
         <v>5.0001</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AN23" t="n">
         <v>5426307</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AO23" t="n">
         <v>2145000</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AP23" t="n">
+        <v>3281308</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>3.54</v>
       </c>
-      <c r="AO23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="AR23" t="n">
         <v>4.26</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AS23" t="n">
         <v>31.62</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AT23" t="n">
         <v>345725</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AU23" t="n">
+        <v>1.037108</v>
+      </c>
+      <c r="AV23" t="n">
         <v>-5.678737</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AW23" t="n">
         <v>-1.568774</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AX23" t="n">
         <v>-1.568959</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AY23" t="n">
         <v>0.027577</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AZ23" t="n">
         <v>-0.459418</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="BA23" t="n">
+        <v>0.348572</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.338676</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BC23" t="n">
         <v>4.184706</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BD23" t="n">
         <v>-2.158772</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BE23" t="n">
         <v>3.834324</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BF23" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BG23" t="n">
         <v>0</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
         <v>0.19</v>
       </c>
-      <c r="BE23" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BF23" t="n">
+      <c r="BJ23" t="n">
         <v>0.15</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BK23" t="n">
         <v>0.63</v>
       </c>
     </row>
@@ -4632,87 +4912,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF24" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
         <v>-1.84</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AI24" t="n">
         <v>0.36</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AJ24" t="n">
+        <v>102.3642</v>
+      </c>
+      <c r="AK24" t="n">
         <v>102.66392</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AL24" t="n">
         <v>5.0959</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AM24" t="n">
         <v>5.0953</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AN24" t="n">
         <v>5453708</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AO24" t="n">
         <v>2145530</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AP24" t="n">
+        <v>3308178</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>3.65</v>
       </c>
-      <c r="AO24" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AP24" t="n">
+      <c r="AR24" t="n">
         <v>4.35</v>
       </c>
-      <c r="AQ24" t="n">
+      <c r="AS24" t="n">
         <v>31.63</v>
       </c>
-      <c r="AR24" t="n">
+      <c r="AT24" t="n">
         <v>343489</v>
       </c>
-      <c r="AS24" t="n">
+      <c r="AU24" t="n">
+        <v>-1.726531</v>
+      </c>
+      <c r="AV24" t="n">
         <v>-1.607797</v>
       </c>
-      <c r="AT24" t="n">
+      <c r="AW24" t="n">
         <v>1.903733</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AX24" t="n">
         <v>1.903962</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AY24" t="n">
         <v>0.504966</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AZ24" t="n">
         <v>0.024709</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="BA24" t="n">
+        <v>0.818881</v>
+      </c>
+      <c r="BB24" t="n">
         <v>-0.646757</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BC24" t="n">
         <v>3.935832</v>
       </c>
-      <c r="AZ24" t="n">
+      <c r="BD24" t="n">
         <v>-4.45588</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BE24" t="n">
         <v>3.741292</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BF24" t="n">
         <v>0</v>
       </c>
-      <c r="BC24" t="n">
+      <c r="BG24" t="n">
         <v>-0</v>
       </c>
-      <c r="BD24" t="n">
+      <c r="BH24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI24" t="n">
         <v>0.11</v>
       </c>
-      <c r="BE24" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="BF24" t="n">
+      <c r="BJ24" t="n">
         <v>0.09</v>
       </c>
-      <c r="BG24" t="n">
+      <c r="BK24" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4811,87 +5103,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF25" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG25" t="n">
         <v>-0.08</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AH25" t="n">
         <v>-1.93</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AI25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AJ25" t="n">
+        <v>102.50431</v>
+      </c>
+      <c r="AK25" t="n">
         <v>102.53174</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AL25" t="n">
         <v>4.8192</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AM25" t="n">
         <v>4.8186</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AN25" t="n">
         <v>5479459</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AO25" t="n">
         <v>2169613</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AP25" t="n">
+        <v>3309846</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>3.61</v>
       </c>
-      <c r="AO25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AR25" t="n">
         <v>4.25</v>
       </c>
-      <c r="AQ25" t="n">
+      <c r="AS25" t="n">
         <v>30.85</v>
       </c>
-      <c r="AR25" t="n">
+      <c r="AT25" t="n">
         <v>343620</v>
       </c>
-      <c r="AS25" t="n">
+      <c r="AU25" t="n">
+        <v>0.136874</v>
+      </c>
+      <c r="AV25" t="n">
         <v>-0.12875</v>
       </c>
-      <c r="AT25" t="n">
+      <c r="AW25" t="n">
         <v>-5.429855</v>
       </c>
-      <c r="AU25" t="n">
+      <c r="AX25" t="n">
         <v>-5.430495</v>
       </c>
-      <c r="AV25" t="n">
+      <c r="AY25" t="n">
         <v>0.472174</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AZ25" t="n">
         <v>1.122473</v>
       </c>
-      <c r="AX25" t="n">
+      <c r="BA25" t="n">
+        <v>0.050421</v>
+      </c>
+      <c r="BB25" t="n">
         <v>0.038138</v>
       </c>
-      <c r="AY25" t="n">
+      <c r="BC25" t="n">
         <v>3.161501</v>
       </c>
-      <c r="AZ25" t="n">
+      <c r="BD25" t="n">
         <v>-6.84947</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BE25" t="n">
         <v>2.998957</v>
       </c>
-      <c r="BB25" t="n">
+      <c r="BF25" t="n">
         <v>0</v>
       </c>
-      <c r="BC25" t="n">
+      <c r="BG25" t="n">
         <v>0</v>
       </c>
-      <c r="BD25" t="n">
+      <c r="BH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI25" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BE25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BF25" t="n">
+      <c r="BJ25" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BG25" t="n">
+      <c r="BK25" t="n">
         <v>-0.78</v>
       </c>
     </row>
@@ -4990,87 +5294,99 @@
         <v>0.050788</v>
       </c>
       <c r="AF26" t="n">
+        <v>0.050788</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.12</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AH26" t="n">
         <v>-0.72</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AI26" t="n">
         <v>-0.09</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AJ26" t="n">
+        <v>102.83357</v>
+      </c>
+      <c r="AK26" t="n">
         <v>105.47522</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AL26" t="n">
         <v>4.7415</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AM26" t="n">
         <v>4.7409</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
         <v>5484871</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AO26" t="n">
         <v>2153541</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AP26" t="n">
+        <v>3331330</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>3.63</v>
       </c>
-      <c r="AO26" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AR26" t="n">
         <v>4.22</v>
       </c>
-      <c r="AQ26" t="n">
+      <c r="AS26" t="n">
         <v>30.43</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>345476</v>
       </c>
-      <c r="AS26" t="n">
+      <c r="AU26" t="n">
+        <v>0.321216</v>
+      </c>
+      <c r="AV26" t="n">
         <v>2.870799</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="AW26" t="n">
         <v>-1.612301</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AX26" t="n">
         <v>-1.612502</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AY26" t="n">
         <v>0.098769</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AZ26" t="n">
         <v>-0.740777</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="BA26" t="n">
+        <v>0.6490939999999999</v>
+      </c>
+      <c r="BB26" t="n">
         <v>0.5401319999999999</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BC26" t="n">
         <v>3.992444</v>
       </c>
-      <c r="AZ26" t="n">
+      <c r="BD26" t="n">
         <v>-7.713954</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BE26" t="n">
         <v>3.527423</v>
       </c>
-      <c r="BB26" t="n">
+      <c r="BF26" t="n">
         <v>0</v>
       </c>
-      <c r="BC26" t="n">
+      <c r="BG26" t="n">
         <v>0</v>
       </c>
-      <c r="BD26" t="n">
+      <c r="BH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI26" t="n">
         <v>0.02</v>
       </c>
-      <c r="BE26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BF26" t="n">
+      <c r="BJ26" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BG26" t="n">
+      <c r="BK26" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5169,87 +5485,99 @@
         <v>0.049189</v>
       </c>
       <c r="AF27" t="n">
+        <v>0.049189</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.23</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AH27" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AI27" t="n">
         <v>0.2</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AJ27" t="n">
+        <v>102.45222</v>
+      </c>
+      <c r="AK27" t="n">
         <v>106.13139</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AL27" t="n">
         <v>4.9219</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AM27" t="n">
         <v>4.9213</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AN27" t="n">
         <v>5559063</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AO27" t="n">
         <v>2172658</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AP27" t="n">
+        <v>3386405</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>3.61</v>
       </c>
-      <c r="AO27" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AR27" t="n">
         <v>4.12</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AS27" t="n">
         <v>29.92</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>344177</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AU27" t="n">
+        <v>-0.370842</v>
+      </c>
+      <c r="AV27" t="n">
         <v>0.622108</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AW27" t="n">
         <v>3.804703</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AX27" t="n">
         <v>3.805185</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AY27" t="n">
         <v>1.352666</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AZ27" t="n">
         <v>0.887701</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="BA27" t="n">
+        <v>1.653244</v>
+      </c>
+      <c r="BB27" t="n">
         <v>-0.376003</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="BC27" t="n">
         <v>4.608216</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="BD27" t="n">
         <v>-7.193509</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BE27" t="n">
         <v>4.057054</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BF27" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BG27" t="n">
         <v>-0.001599</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BH27" t="n">
+        <v>-0.001599</v>
+      </c>
+      <c r="BI27" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BE27" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BF27" t="n">
+      <c r="BJ27" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BK27" t="n">
         <v>-0.51</v>
       </c>
     </row>
@@ -5348,87 +5676,99 @@
         <v>0.048422</v>
       </c>
       <c r="AF28" t="n">
+        <v>0.048422</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AH28" t="n">
         <v>0.37</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AI28" t="n">
         <v>0.11</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AJ28" t="n">
+        <v>102.57885</v>
+      </c>
+      <c r="AK28" t="n">
         <v>102.00419</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AL28" t="n">
         <v>5.0076</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AM28" t="n">
         <v>5.007</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AN28" t="n">
         <v>5625945</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AO28" t="n">
         <v>2215175</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AP28" t="n">
+        <v>3410769</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>3.54</v>
       </c>
-      <c r="AO28" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AP28" t="n">
+      <c r="AR28" t="n">
         <v>4</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="AS28" t="n">
         <v>29.66</v>
       </c>
-      <c r="AR28" t="n">
+      <c r="AT28" t="n">
         <v>340324</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AU28" t="n">
+        <v>0.123599</v>
+      </c>
+      <c r="AV28" t="n">
         <v>-3.888765</v>
       </c>
-      <c r="AT28" t="n">
+      <c r="AW28" t="n">
         <v>1.741198</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AX28" t="n">
         <v>1.74141</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AY28" t="n">
         <v>1.203116</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AZ28" t="n">
         <v>1.956912</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="BA28" t="n">
+        <v>0.719465</v>
+      </c>
+      <c r="BB28" t="n">
         <v>-1.119482</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BC28" t="n">
         <v>5.185235</v>
       </c>
-      <c r="AZ28" t="n">
+      <c r="BD28" t="n">
         <v>-5.956714</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BE28" t="n">
         <v>4.505936</v>
       </c>
-      <c r="BB28" t="n">
+      <c r="BF28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC28" t="n">
+      <c r="BG28" t="n">
         <v>-0.000768</v>
       </c>
-      <c r="BD28" t="n">
+      <c r="BH28" t="n">
+        <v>-0.000768</v>
+      </c>
+      <c r="BI28" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
+      <c r="BJ28" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BG28" t="n">
+      <c r="BK28" t="n">
         <v>-0.26</v>
       </c>
     </row>
@@ -5527,87 +5867,99 @@
         <v>0.047279</v>
       </c>
       <c r="AF29" t="n">
+        <v>0.047279</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AH29" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
         <v>0.12</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AJ29" t="n">
+        <v>102.87707</v>
+      </c>
+      <c r="AK29" t="n">
         <v>102.0744</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AL29" t="n">
         <v>5.0575</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AM29" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AN29" t="n">
         <v>5653808</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AO29" t="n">
         <v>2204808</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AP29" t="n">
+        <v>3449000</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>3.56</v>
       </c>
-      <c r="AO29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AP29" t="n">
+      <c r="AR29" t="n">
         <v>3.97</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AS29" t="n">
         <v>29.24</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AT29" t="n">
         <v>340247</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AU29" t="n">
+        <v>0.290723</v>
+      </c>
+      <c r="AV29" t="n">
         <v>0.068831</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AW29" t="n">
         <v>0.996485</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AX29" t="n">
         <v>0.996605</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AY29" t="n">
         <v>0.495259</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AZ29" t="n">
         <v>-0.467999</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="BA29" t="n">
+        <v>1.120891</v>
+      </c>
+      <c r="BB29" t="n">
         <v>-0.022625</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BC29" t="n">
         <v>4.819246</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="BD29" t="n">
         <v>-4.560737</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BE29" t="n">
         <v>4.141877</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BF29" t="n">
         <v>0</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BG29" t="n">
         <v>-0.001143</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BH29" t="n">
+        <v>-0.001143</v>
+      </c>
+      <c r="BI29" t="n">
         <v>0.02</v>
       </c>
-      <c r="BE29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BF29" t="n">
+      <c r="BJ29" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BG29" t="n">
+      <c r="BK29" t="n">
         <v>-0.42</v>
       </c>
     </row>
@@ -5706,87 +6058,99 @@
         <v>0.045601</v>
       </c>
       <c r="AF30" t="n">
+        <v>0.045601</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.28</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AH30" t="n">
         <v>0.59</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AI30" t="n">
         <v>0.1</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AJ30" t="n">
+        <v>103.528</v>
+      </c>
+      <c r="AK30" t="n">
         <v>101.86494</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AL30" t="n">
         <v>4.9355</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AM30" t="n">
         <v>4.9349</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AN30" t="n">
         <v>5711103</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AO30" t="n">
         <v>2220766</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AP30" t="n">
+        <v>3490337</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>3.53</v>
       </c>
-      <c r="AO30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AP30" t="n">
+      <c r="AR30" t="n">
         <v>3.88</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AS30" t="n">
         <v>29.01</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AT30" t="n">
         <v>348406</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AU30" t="n">
+        <v>0.632726</v>
+      </c>
+      <c r="AV30" t="n">
         <v>-0.205203</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AW30" t="n">
         <v>-2.412259</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AX30" t="n">
         <v>-2.412545</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AY30" t="n">
         <v>1.013388</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AZ30" t="n">
         <v>0.723782</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="BA30" t="n">
+        <v>1.198521</v>
+      </c>
+      <c r="BB30" t="n">
         <v>2.397964</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BC30" t="n">
         <v>4.683537</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="BD30" t="n">
         <v>-3.457004</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BE30" t="n">
         <v>3.851383</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BF30" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BG30" t="n">
         <v>-0.001678</v>
       </c>
-      <c r="BD30" t="n">
+      <c r="BH30" t="n">
+        <v>-0.001678</v>
+      </c>
+      <c r="BI30" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE30" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BF30" t="n">
+      <c r="BJ30" t="n">
         <v>-0.09</v>
       </c>
-      <c r="BG30" t="n">
+      <c r="BK30" t="n">
         <v>-0.23</v>
       </c>
     </row>
@@ -5885,87 +6249,99 @@
         <v>0.044537</v>
       </c>
       <c r="AF31" t="n">
+        <v>0.044537</v>
+      </c>
+      <c r="AG31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AH31" t="n">
         <v>0.74</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AI31" t="n">
         <v>0.55</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AJ31" t="n">
+        <v>104.8991</v>
+      </c>
+      <c r="AK31" t="n">
         <v>101.74606</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AL31" t="n">
         <v>4.8413</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AM31" t="n">
         <v>4.8407</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AN31" t="n">
         <v>5805157</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AO31" t="n">
         <v>2283485</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AP31" t="n">
+        <v>3521672</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>3.29</v>
       </c>
-      <c r="AO31" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AP31" t="n">
+      <c r="AR31" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AS31" t="n">
         <v>28.14</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AT31" t="n">
         <v>355034</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AU31" t="n">
+        <v>1.324376</v>
+      </c>
+      <c r="AV31" t="n">
         <v>-0.116704</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AW31" t="n">
         <v>-1.908621</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AX31" t="n">
         <v>-1.908853</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AY31" t="n">
         <v>1.646862</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AZ31" t="n">
         <v>2.824206</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="BA31" t="n">
+        <v>0.897764</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.902378</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BC31" t="n">
         <v>4.621114</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="BD31" t="n">
         <v>-3.178284</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BE31" t="n">
         <v>3.706988</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BF31" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BG31" t="n">
         <v>-0.001064</v>
       </c>
-      <c r="BD31" t="n">
+      <c r="BH31" t="n">
+        <v>-0.001064</v>
+      </c>
+      <c r="BI31" t="n">
         <v>-0.24</v>
       </c>
-      <c r="BE31" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="BF31" t="n">
+      <c r="BJ31" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BG31" t="n">
+      <c r="BK31" t="n">
         <v>-0.87</v>
       </c>
     </row>
@@ -6064,87 +6440,99 @@
         <v>0.043739</v>
       </c>
       <c r="AF32" t="n">
+        <v>0.043739</v>
+      </c>
+      <c r="AG32" t="n">
         <v>0.42</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AH32" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AI32" t="n">
         <v>0.57</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AJ32" t="n">
+        <v>104.53245</v>
+      </c>
+      <c r="AK32" t="n">
         <v>98.01879</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AL32" t="n">
         <v>4.9535</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AM32" t="n">
         <v>4.9529</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AN32" t="n">
         <v>5794707</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AO32" t="n">
         <v>2234362</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AP32" t="n">
+        <v>3560345</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>3.38</v>
       </c>
-      <c r="AO32" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AP32" t="n">
+      <c r="AR32" t="n">
         <v>3.76</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AS32" t="n">
         <v>28</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AT32" t="n">
         <v>355066</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AU32" t="n">
+        <v>-0.349526</v>
+      </c>
+      <c r="AV32" t="n">
         <v>-3.663306</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AW32" t="n">
         <v>2.317559</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AX32" t="n">
         <v>2.317847</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AY32" t="n">
         <v>-0.180012</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AZ32" t="n">
         <v>-2.151229</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="BA32" t="n">
+        <v>1.098143</v>
+      </c>
+      <c r="BB32" t="n">
         <v>0.009013</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BC32" t="n">
         <v>4.506637</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="BD32" t="n">
         <v>-3.31355</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BE32" t="n">
         <v>3.820543</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BF32" t="n">
         <v>0</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BG32" t="n">
         <v>-0.000798</v>
       </c>
-      <c r="BD32" t="n">
+      <c r="BH32" t="n">
+        <v>-0.000798</v>
+      </c>
+      <c r="BI32" t="n">
         <v>0.09</v>
       </c>
-      <c r="BE32" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BF32" t="n">
+      <c r="BJ32" t="n">
         <v>0.01</v>
       </c>
-      <c r="BG32" t="n">
+      <c r="BK32" t="n">
         <v>-0.14</v>
       </c>
     </row>
@@ -6243,87 +6631,99 @@
         <v>0.041957</v>
       </c>
       <c r="AF33" t="n">
+        <v>0.041957</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.83</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AH33" t="n">
         <v>-0.52</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AI33" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AJ33" t="n">
+        <v>104.75961</v>
+      </c>
+      <c r="AK33" t="n">
         <v>102.37988</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AL33" t="n">
         <v>4.9833</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AM33" t="n">
         <v>4.9827</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AN33" t="n">
         <v>5815954</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AO33" t="n">
         <v>2235302</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AP33" t="n">
+        <v>3580652</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>3.38</v>
       </c>
-      <c r="AO33" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="AR33" t="n">
         <v>3.76</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AS33" t="n">
         <v>27.85</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AT33" t="n">
         <v>352705</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AU33" t="n">
+        <v>0.217311</v>
+      </c>
+      <c r="AV33" t="n">
         <v>4.449239</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AW33" t="n">
         <v>0.601595</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AX33" t="n">
         <v>0.601668</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AY33" t="n">
         <v>0.366662</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AZ33" t="n">
         <v>0.04207</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="BA33" t="n">
+        <v>0.570366</v>
+      </c>
+      <c r="BB33" t="n">
         <v>-0.664947</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BC33" t="n">
         <v>4.496274</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="BD33" t="n">
         <v>-3.758575</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BE33" t="n">
         <v>3.861754</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BF33" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BG33" t="n">
         <v>-0.001782</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BH33" t="n">
+        <v>-0.001782</v>
+      </c>
+      <c r="BI33" t="n">
         <v>0</v>
       </c>
-      <c r="BE33" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BF33" t="n">
+      <c r="BJ33" t="n">
         <v>0</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BK33" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -6422,87 +6822,99 @@
         <v>0.04142</v>
       </c>
       <c r="AF34" t="n">
+        <v>0.04142</v>
+      </c>
+      <c r="AG34" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AH34" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
         <v>0.19</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AJ34" t="n">
+        <v>104.7097</v>
+      </c>
+      <c r="AK34" t="n">
         <v>109.58504</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AL34" t="n">
         <v>4.9962</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AM34" t="n">
         <v>4.9956</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AN34" t="n">
         <v>5899742</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AO34" t="n">
         <v>2285775</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AP34" t="n">
+        <v>3613967</v>
+      </c>
+      <c r="AQ34" t="n">
         <v>3.33</v>
       </c>
-      <c r="AO34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AP34" t="n">
+      <c r="AR34" t="n">
         <v>3.71</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AS34" t="n">
         <v>28.14</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AT34" t="n">
         <v>355008</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AU34" t="n">
+        <v>-0.047642</v>
+      </c>
+      <c r="AV34" t="n">
         <v>7.037672</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AW34" t="n">
         <v>0.258865</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AX34" t="n">
         <v>0.258896</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AY34" t="n">
         <v>1.440658</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AZ34" t="n">
         <v>2.257995</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="BA34" t="n">
+        <v>0.930417</v>
+      </c>
+      <c r="BB34" t="n">
         <v>0.652954</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="BC34" t="n">
         <v>3.925596</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="BD34" t="n">
         <v>-4.25878</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BE34" t="n">
         <v>3.397348</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BF34" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BG34" t="n">
         <v>-0.000537</v>
       </c>
-      <c r="BD34" t="n">
+      <c r="BH34" t="n">
+        <v>-0.000537</v>
+      </c>
+      <c r="BI34" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BE34" t="n">
+      <c r="BJ34" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BF34" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BG34" t="n">
+      <c r="BK34" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -6601,87 +7013,99 @@
         <v>0.040168</v>
       </c>
       <c r="AF35" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AH35" t="n">
         <v>0.31</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AI35" t="n">
         <v>0.37</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AJ35" t="n">
+        <v>104.75682</v>
+      </c>
+      <c r="AK35" t="n">
         <v>109.36335</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AL35" t="n">
         <v>5.1718</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AM35" t="n">
         <v>5.1712</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AN35" t="n">
         <v>5915538</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AO35" t="n">
         <v>2268879</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AP35" t="n">
+        <v>3646659</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>3.37</v>
       </c>
-      <c r="AO35" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AP35" t="n">
+      <c r="AR35" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AS35" t="n">
         <v>27.86</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
         <v>351599</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AU35" t="n">
+        <v>0.045001</v>
+      </c>
+      <c r="AV35" t="n">
         <v>-0.2023</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AW35" t="n">
         <v>3.514671</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AX35" t="n">
         <v>3.515093</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AY35" t="n">
         <v>0.267741</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AZ35" t="n">
         <v>-0.7391799999999999</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="BA35" t="n">
+        <v>0.904602</v>
+      </c>
+      <c r="BB35" t="n">
         <v>-0.96026</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="BC35" t="n">
         <v>3.688016</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="BD35" t="n">
         <v>-3.040871</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BE35" t="n">
         <v>3.232784</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BF35" t="n">
         <v>0</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BG35" t="n">
         <v>-0.001252</v>
       </c>
-      <c r="BD35" t="n">
+      <c r="BH35" t="n">
+        <v>-0.001252</v>
+      </c>
+      <c r="BI35" t="n">
         <v>0.04</v>
       </c>
-      <c r="BE35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BF35" t="n">
+      <c r="BJ35" t="n">
         <v>0.04</v>
       </c>
-      <c r="BG35" t="n">
+      <c r="BK35" t="n">
         <v>-0.28</v>
       </c>
     </row>
@@ -6780,87 +7204,99 @@
         <v>0.039484</v>
       </c>
       <c r="AF36" t="n">
+        <v>0.039484</v>
+      </c>
+      <c r="AG36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AH36" t="n">
         <v>0.89</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AI36" t="n">
         <v>0.46</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AJ36" t="n">
+        <v>105.70704</v>
+      </c>
+      <c r="AK36" t="n">
         <v>104.84682</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AL36" t="n">
         <v>5.2416</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AM36" t="n">
         <v>5.241</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AN36" t="n">
         <v>5953960</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AO36" t="n">
         <v>2278309</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AP36" t="n">
+        <v>3675652</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>3.43</v>
       </c>
-      <c r="AO36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP36" t="n">
+      <c r="AR36" t="n">
         <v>3.82</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AS36" t="n">
         <v>27.75</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AT36" t="n">
         <v>355560</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AU36" t="n">
+        <v>0.907072</v>
+      </c>
+      <c r="AV36" t="n">
         <v>-4.129839</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AW36" t="n">
         <v>1.349627</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AX36" t="n">
         <v>1.349783</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AY36" t="n">
         <v>0.64951</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AZ36" t="n">
         <v>0.415624</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="BA36" t="n">
+        <v>0.795057</v>
+      </c>
+      <c r="BB36" t="n">
         <v>1.126567</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BC36" t="n">
         <v>3.925952</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="BD36" t="n">
         <v>-0.344269</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BE36" t="n">
         <v>3.335647</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BF36" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BG36" t="n">
         <v>-0.000684</v>
       </c>
-      <c r="BD36" t="n">
+      <c r="BH36" t="n">
+        <v>-0.000684</v>
+      </c>
+      <c r="BI36" t="n">
         <v>0.06</v>
       </c>
-      <c r="BE36" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BF36" t="n">
+      <c r="BJ36" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG36" t="n">
+      <c r="BK36" t="n">
         <v>-0.11</v>
       </c>
     </row>
@@ -6959,87 +7395,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF37" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.21</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AH37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AI37" t="n">
         <v>0.25</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AJ37" t="n">
+        <v>106.57623</v>
+      </c>
+      <c r="AK37" t="n">
         <v>106.03093</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AL37" t="n">
         <v>5.5589</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AM37" t="n">
         <v>5.5583</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AN37" t="n">
         <v>6041898</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AO37" t="n">
         <v>2336858</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AP37" t="n">
+        <v>3705041</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>3.29</v>
       </c>
-      <c r="AO37" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AP37" t="n">
+      <c r="AR37" t="n">
         <v>3.71</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AS37" t="n">
         <v>27.81</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AT37" t="n">
         <v>357827</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AU37" t="n">
+        <v>0.822263</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1.129371</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AW37" t="n">
         <v>6.053495</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AX37" t="n">
         <v>6.054188</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AY37" t="n">
         <v>1.476967</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AZ37" t="n">
         <v>2.569845</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="BA37" t="n">
+        <v>0.799559</v>
+      </c>
+      <c r="BB37" t="n">
         <v>0.637586</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="BC37" t="n">
         <v>4.227578</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="BD37" t="n">
         <v>2.440035</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BE37" t="n">
         <v>3.697684</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BF37" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BG37" t="n">
         <v>-0.000214</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BH37" t="n">
+        <v>-0.000214</v>
+      </c>
+      <c r="BI37" t="n">
         <v>-0.14</v>
       </c>
-      <c r="BE37" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="BF37" t="n">
+      <c r="BJ37" t="n">
         <v>-0.11</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BK37" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -7138,87 +7586,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF38" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.38</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AH38" t="n">
         <v>0.61</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AI38" t="n">
         <v>0.26</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AJ38" t="n">
+        <v>106.88756</v>
+      </c>
+      <c r="AK38" t="n">
         <v>111.55002</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AL38" t="n">
         <v>5.6621</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AM38" t="n">
         <v>5.6615</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AN38" t="n">
         <v>6069205</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AO38" t="n">
         <v>2323362</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AP38" t="n">
+        <v>3745844</v>
+      </c>
+      <c r="AQ38" t="n">
         <v>3.3</v>
       </c>
-      <c r="AO38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AP38" t="n">
+      <c r="AR38" t="n">
         <v>3.78</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AS38" t="n">
         <v>27.74</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AT38" t="n">
         <v>363282</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AU38" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="AV38" t="n">
         <v>5.20517</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AW38" t="n">
         <v>1.856482</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AX38" t="n">
         <v>1.856683</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AY38" t="n">
         <v>0.451961</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AZ38" t="n">
         <v>-0.577528</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="BA38" t="n">
+        <v>1.101283</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.52448</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="BC38" t="n">
         <v>4.498245</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="BD38" t="n">
         <v>3.812368</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BE38" t="n">
         <v>4.060953</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BF38" t="n">
         <v>0</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BG38" t="n">
         <v>0</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" t="n">
         <v>0.01</v>
       </c>
-      <c r="BE38" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BF38" t="n">
+      <c r="BJ38" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG38" t="n">
+      <c r="BK38" t="n">
         <v>-0.07000000000000001</v>
       </c>
     </row>
@@ -7317,87 +7777,99 @@
         <v>0.03927</v>
       </c>
       <c r="AF39" t="n">
+        <v>0.03927</v>
+      </c>
+      <c r="AG39" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AH39" t="n">
         <v>0.29</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AI39" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AI39" t="n">
+      <c r="AJ39" t="n">
+        <v>107.14396</v>
+      </c>
+      <c r="AK39" t="n">
         <v>110.19363</v>
       </c>
-      <c r="AJ39" t="n">
+      <c r="AL39" t="n">
         <v>5.6562</v>
       </c>
-      <c r="AK39" t="n">
+      <c r="AM39" t="n">
         <v>5.6556</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AN39" t="n">
         <v>6135298</v>
       </c>
-      <c r="AM39" t="n">
+      <c r="AO39" t="n">
         <v>2344397</v>
       </c>
-      <c r="AN39" t="n">
+      <c r="AP39" t="n">
+        <v>3790900</v>
+      </c>
+      <c r="AQ39" t="n">
         <v>3.33</v>
       </c>
-      <c r="AO39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AP39" t="n">
+      <c r="AR39" t="n">
         <v>3.82</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AS39" t="n">
         <v>27.59</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>369214</v>
       </c>
-      <c r="AS39" t="n">
+      <c r="AU39" t="n">
+        <v>0.239878</v>
+      </c>
+      <c r="AV39" t="n">
         <v>-1.215948</v>
       </c>
-      <c r="AT39" t="n">
+      <c r="AW39" t="n">
         <v>-0.104202</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AX39" t="n">
         <v>-0.104213</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AY39" t="n">
         <v>1.088989</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AZ39" t="n">
         <v>0.905369</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="BA39" t="n">
+        <v>1.202826</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.632891</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="BC39" t="n">
         <v>4.237599</v>
       </c>
-      <c r="AZ39" t="n">
+      <c r="BD39" t="n">
         <v>4.259387</v>
       </c>
-      <c r="BA39" t="n">
+      <c r="BE39" t="n">
         <v>3.707852</v>
       </c>
-      <c r="BB39" t="n">
+      <c r="BF39" t="n">
         <v>0</v>
       </c>
-      <c r="BC39" t="n">
+      <c r="BG39" t="n">
         <v>0</v>
       </c>
-      <c r="BD39" t="n">
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE39" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BF39" t="n">
+      <c r="BJ39" t="n">
         <v>0.04</v>
       </c>
-      <c r="BG39" t="n">
+      <c r="BK39" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -7496,87 +7968,99 @@
         <v>0.039612</v>
       </c>
       <c r="AF40" t="n">
+        <v>0.039612</v>
+      </c>
+      <c r="AG40" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
         <v>0.62</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AI40" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI40" t="n">
+      <c r="AJ40" t="n">
+        <v>107.99916</v>
+      </c>
+      <c r="AK40" t="n">
         <v>107.28836</v>
       </c>
-      <c r="AJ40" t="n">
+      <c r="AL40" t="n">
         <v>5.4481</v>
       </c>
-      <c r="AK40" t="n">
+      <c r="AM40" t="n">
         <v>5.4475</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AN40" t="n">
         <v>6216528</v>
       </c>
-      <c r="AM40" t="n">
+      <c r="AO40" t="n">
         <v>2384828</v>
       </c>
-      <c r="AN40" t="n">
+      <c r="AP40" t="n">
+        <v>3831700</v>
+      </c>
+      <c r="AQ40" t="n">
         <v>3.34</v>
       </c>
-      <c r="AO40" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP40" t="n">
+      <c r="AR40" t="n">
         <v>3.83</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AS40" t="n">
         <v>27.49</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>372016</v>
       </c>
-      <c r="AS40" t="n">
+      <c r="AU40" t="n">
+        <v>0.7981780000000001</v>
+      </c>
+      <c r="AV40" t="n">
         <v>-2.636514</v>
       </c>
-      <c r="AT40" t="n">
+      <c r="AW40" t="n">
         <v>-3.679149</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AX40" t="n">
         <v>-3.679539</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AY40" t="n">
         <v>1.323978</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AZ40" t="n">
         <v>1.72458</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="BA40" t="n">
+        <v>1.076262</v>
+      </c>
+      <c r="BB40" t="n">
         <v>0.7589089999999999</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BC40" t="n">
         <v>4.42474</v>
       </c>
-      <c r="AZ40" t="n">
+      <c r="BD40" t="n">
         <v>4.519075</v>
       </c>
-      <c r="BA40" t="n">
+      <c r="BE40" t="n">
         <v>4.091149</v>
       </c>
-      <c r="BB40" t="n">
+      <c r="BF40" t="n">
         <v>0.25</v>
       </c>
-      <c r="BC40" t="n">
+      <c r="BG40" t="n">
         <v>0.000342</v>
       </c>
-      <c r="BD40" t="n">
+      <c r="BH40" t="n">
+        <v>0.000342</v>
+      </c>
+      <c r="BI40" t="n">
         <v>0.01</v>
       </c>
-      <c r="BE40" t="n">
+      <c r="BJ40" t="n">
         <v>0.01</v>
       </c>
-      <c r="BF40" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BG40" t="n">
+      <c r="BK40" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -7675,87 +8159,99 @@
         <v>0.040168</v>
       </c>
       <c r="AF41" t="n">
+        <v>0.040168</v>
+      </c>
+      <c r="AG41" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG41" t="n">
+      <c r="AH41" t="n">
         <v>1.52</v>
       </c>
-      <c r="AH41" t="n">
+      <c r="AI41" t="n">
         <v>0.61</v>
       </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
+        <v>108.15356</v>
+      </c>
+      <c r="AK41" t="n">
         <v>109.21678</v>
       </c>
-      <c r="AJ41" t="n">
+      <c r="AL41" t="n">
         <v>5.7779</v>
       </c>
-      <c r="AK41" t="n">
+      <c r="AM41" t="n">
         <v>5.7773</v>
       </c>
-      <c r="AL41" t="n">
+      <c r="AN41" t="n">
         <v>6275117</v>
       </c>
-      <c r="AM41" t="n">
+      <c r="AO41" t="n">
         <v>2397533</v>
       </c>
-      <c r="AN41" t="n">
+      <c r="AP41" t="n">
+        <v>3877584</v>
+      </c>
+      <c r="AQ41" t="n">
         <v>3.3</v>
       </c>
-      <c r="AO41" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AP41" t="n">
+      <c r="AR41" t="n">
         <v>3.79</v>
       </c>
-      <c r="AQ41" t="n">
+      <c r="AS41" t="n">
         <v>27.94</v>
       </c>
-      <c r="AR41" t="n">
+      <c r="AT41" t="n">
         <v>366096</v>
       </c>
-      <c r="AS41" t="n">
+      <c r="AU41" t="n">
+        <v>0.142964</v>
+      </c>
+      <c r="AV41" t="n">
         <v>1.797418</v>
       </c>
-      <c r="AT41" t="n">
+      <c r="AW41" t="n">
         <v>6.053487</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AX41" t="n">
         <v>6.054153</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AY41" t="n">
         <v>0.9424709999999999</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AZ41" t="n">
         <v>0.532743</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="BA41" t="n">
+        <v>1.197484</v>
+      </c>
+      <c r="BB41" t="n">
         <v>-1.591329</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="BC41" t="n">
         <v>4.758099</v>
       </c>
-      <c r="AZ41" t="n">
+      <c r="BD41" t="n">
         <v>5.579866</v>
       </c>
-      <c r="BA41" t="n">
+      <c r="BE41" t="n">
         <v>4.600584</v>
       </c>
-      <c r="BB41" t="n">
+      <c r="BF41" t="n">
         <v>0</v>
       </c>
-      <c r="BC41" t="n">
+      <c r="BG41" t="n">
         <v>0.000556</v>
       </c>
-      <c r="BD41" t="n">
+      <c r="BH41" t="n">
+        <v>0.000556</v>
+      </c>
+      <c r="BI41" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BE41" t="n">
+      <c r="BJ41" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF41" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="BG41" t="n">
+      <c r="BK41" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -7854,87 +8350,99 @@
         <v>0.04158</v>
       </c>
       <c r="AF42" t="n">
+        <v>0.04158</v>
+      </c>
+      <c r="AG42" t="n">
         <v>0.39</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AH42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH42" t="n">
+      <c r="AI42" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI42" t="n">
+      <c r="AJ42" t="n">
+        <v>107.98489</v>
+      </c>
+      <c r="AK42" t="n">
         <v>105.74688</v>
       </c>
-      <c r="AJ42" t="n">
+      <c r="AL42" t="n">
         <v>6.0535</v>
       </c>
-      <c r="AK42" t="n">
+      <c r="AM42" t="n">
         <v>6.0529</v>
       </c>
-      <c r="AL42" t="n">
+      <c r="AN42" t="n">
         <v>6365690</v>
       </c>
-      <c r="AM42" t="n">
+      <c r="AO42" t="n">
         <v>2436022</v>
       </c>
-      <c r="AN42" t="n">
+      <c r="AP42" t="n">
+        <v>3929668</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>3.27</v>
       </c>
-      <c r="AO42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AP42" t="n">
+      <c r="AR42" t="n">
         <v>3.75</v>
       </c>
-      <c r="AQ42" t="n">
+      <c r="AS42" t="n">
         <v>28.45</v>
       </c>
-      <c r="AR42" t="n">
+      <c r="AT42" t="n">
         <v>363003</v>
       </c>
-      <c r="AS42" t="n">
+      <c r="AU42" t="n">
+        <v>-0.155954</v>
+      </c>
+      <c r="AV42" t="n">
         <v>-3.177076</v>
       </c>
-      <c r="AT42" t="n">
+      <c r="AW42" t="n">
         <v>4.769899</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AX42" t="n">
         <v>4.770394</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AY42" t="n">
         <v>1.443368</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AZ42" t="n">
         <v>1.605359</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="BA42" t="n">
+        <v>1.343208</v>
+      </c>
+      <c r="BB42" t="n">
         <v>-0.8448600000000001</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="BC42" t="n">
         <v>4.873011</v>
       </c>
-      <c r="AZ42" t="n">
+      <c r="BD42" t="n">
         <v>6.325086</v>
       </c>
-      <c r="BA42" t="n">
+      <c r="BE42" t="n">
         <v>4.840925</v>
       </c>
-      <c r="BB42" t="n">
+      <c r="BF42" t="n">
         <v>0.5</v>
       </c>
-      <c r="BC42" t="n">
+      <c r="BG42" t="n">
         <v>0.001412</v>
       </c>
-      <c r="BD42" t="n">
+      <c r="BH42" t="n">
+        <v>0.001412</v>
+      </c>
+      <c r="BI42" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE42" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BF42" t="n">
+      <c r="BJ42" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BG42" t="n">
+      <c r="BK42" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -8033,87 +8541,99 @@
         <v>0.044158</v>
       </c>
       <c r="AF43" t="n">
+        <v>0.044158</v>
+      </c>
+      <c r="AG43" t="n">
         <v>0.52</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AH43" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AH43" t="n">
+      <c r="AI43" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI43" t="n">
+      <c r="AJ43" t="n">
+        <v>107.44467</v>
+      </c>
+      <c r="AK43" t="n">
         <v>104.2734</v>
       </c>
-      <c r="AJ43" t="n">
+      <c r="AL43" t="n">
         <v>6.1923</v>
       </c>
-      <c r="AK43" t="n">
+      <c r="AM43" t="n">
         <v>6.1917</v>
       </c>
-      <c r="AL43" t="n">
+      <c r="AN43" t="n">
         <v>6464602</v>
       </c>
-      <c r="AM43" t="n">
+      <c r="AO43" t="n">
         <v>2499177</v>
       </c>
-      <c r="AN43" t="n">
+      <c r="AP43" t="n">
+        <v>3965425</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>3.08</v>
       </c>
-      <c r="AO43" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AP43" t="n">
+      <c r="AR43" t="n">
         <v>3.63</v>
       </c>
-      <c r="AQ43" t="n">
+      <c r="AS43" t="n">
         <v>28.5</v>
       </c>
-      <c r="AR43" t="n">
+      <c r="AT43" t="n">
         <v>329730</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AU43" t="n">
+        <v>-0.500274</v>
+      </c>
+      <c r="AV43" t="n">
         <v>-1.393403</v>
       </c>
-      <c r="AT43" t="n">
+      <c r="AW43" t="n">
         <v>2.292888</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AX43" t="n">
         <v>2.293116</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AY43" t="n">
         <v>1.55383</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AZ43" t="n">
         <v>2.592546</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="BA43" t="n">
+        <v>0.909924</v>
+      </c>
+      <c r="BB43" t="n">
         <v>-9.166040000000001</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="BC43" t="n">
         <v>4.831296</v>
       </c>
-      <c r="AZ43" t="n">
+      <c r="BD43" t="n">
         <v>6.536174</v>
       </c>
-      <c r="BA43" t="n">
+      <c r="BE43" t="n">
         <v>4.767938</v>
       </c>
-      <c r="BB43" t="n">
+      <c r="BF43" t="n">
         <v>1</v>
       </c>
-      <c r="BC43" t="n">
+      <c r="BG43" t="n">
         <v>0.002578</v>
       </c>
-      <c r="BD43" t="n">
+      <c r="BH43" t="n">
+        <v>0.002578</v>
+      </c>
+      <c r="BI43" t="n">
         <v>-0.19</v>
       </c>
-      <c r="BE43" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BF43" t="n">
+      <c r="BJ43" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BG43" t="n">
+      <c r="BK43" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -8212,87 +8732,99 @@
         <v>0.045833</v>
       </c>
       <c r="AF44" t="n">
+        <v>0.045833</v>
+      </c>
+      <c r="AG44" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AH44" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH44" t="n">
+      <c r="AI44" t="n">
         <v>0</v>
       </c>
-      <c r="AI44" t="n">
+      <c r="AJ44" t="n">
+        <v>108.06979</v>
+      </c>
+      <c r="AK44" t="n">
         <v>101.23438</v>
       </c>
-      <c r="AJ44" t="n">
+      <c r="AL44" t="n">
         <v>5.8301</v>
       </c>
-      <c r="AK44" t="n">
+      <c r="AM44" t="n">
         <v>5.8295</v>
       </c>
-      <c r="AL44" t="n">
+      <c r="AN44" t="n">
         <v>6465016</v>
       </c>
-      <c r="AM44" t="n">
+      <c r="AO44" t="n">
         <v>2451957</v>
       </c>
-      <c r="AN44" t="n">
+      <c r="AP44" t="n">
+        <v>4013059</v>
+      </c>
+      <c r="AQ44" t="n">
         <v>3.34</v>
       </c>
-      <c r="AO44" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AP44" t="n">
+      <c r="AR44" t="n">
         <v>3.89</v>
       </c>
-      <c r="AQ44" t="n">
+      <c r="AS44" t="n">
         <v>29.88</v>
       </c>
-      <c r="AR44" t="n">
+      <c r="AT44" t="n">
         <v>328303</v>
       </c>
-      <c r="AS44" t="n">
+      <c r="AU44" t="n">
+        <v>0.581806</v>
+      </c>
+      <c r="AV44" t="n">
         <v>-2.914473</v>
       </c>
-      <c r="AT44" t="n">
+      <c r="AW44" t="n">
         <v>-5.8492</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AX44" t="n">
         <v>-5.849767</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AY44" t="n">
         <v>0.006404</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AZ44" t="n">
         <v>-1.889422</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="BA44" t="n">
+        <v>1.201233</v>
+      </c>
+      <c r="BB44" t="n">
         <v>-0.432778</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="BC44" t="n">
         <v>4.559874</v>
       </c>
-      <c r="AZ44" t="n">
+      <c r="BD44" t="n">
         <v>6.749097</v>
       </c>
-      <c r="BA44" t="n">
+      <c r="BE44" t="n">
         <v>4.174145</v>
       </c>
-      <c r="BB44" t="n">
+      <c r="BF44" t="n">
         <v>1</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="BG44" t="n">
         <v>0.001675</v>
       </c>
-      <c r="BD44" t="n">
+      <c r="BH44" t="n">
+        <v>0.001675</v>
+      </c>
+      <c r="BI44" t="n">
         <v>0.26</v>
       </c>
-      <c r="BE44" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BF44" t="n">
+      <c r="BJ44" t="n">
         <v>0.26</v>
       </c>
-      <c r="BG44" t="n">
+      <c r="BK44" t="n">
         <v>1.38</v>
       </c>
     </row>
@@ -8391,87 +8923,99 @@
         <v>0.049037</v>
       </c>
       <c r="AF45" t="n">
+        <v>0.049037</v>
+      </c>
+      <c r="AG45" t="n">
         <v>1.31</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AH45" t="n">
         <v>1.06</v>
       </c>
-      <c r="AH45" t="n">
+      <c r="AI45" t="n">
         <v>1.48</v>
       </c>
-      <c r="AI45" t="n">
+      <c r="AJ45" t="n">
+        <v>108.77346</v>
+      </c>
+      <c r="AK45" t="n">
         <v>107.07838</v>
       </c>
-      <c r="AJ45" t="n">
+      <c r="AL45" t="n">
         <v>5.8488</v>
       </c>
-      <c r="AK45" t="n">
+      <c r="AM45" t="n">
         <v>5.8482</v>
       </c>
-      <c r="AL45" t="n">
+      <c r="AN45" t="n">
         <v>6511444</v>
       </c>
-      <c r="AM45" t="n">
+      <c r="AO45" t="n">
         <v>2477151</v>
       </c>
-      <c r="AN45" t="n">
+      <c r="AP45" t="n">
+        <v>4034293</v>
+      </c>
+      <c r="AQ45" t="n">
         <v>3.41</v>
       </c>
-      <c r="AO45" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AP45" t="n">
+      <c r="AR45" t="n">
         <v>3.96</v>
       </c>
-      <c r="AQ45" t="n">
+      <c r="AS45" t="n">
         <v>30.53</v>
       </c>
-      <c r="AR45" t="n">
+      <c r="AT45" t="n">
         <v>332508</v>
       </c>
-      <c r="AS45" t="n">
+      <c r="AU45" t="n">
+        <v>0.651126</v>
+      </c>
+      <c r="AV45" t="n">
         <v>5.772742</v>
       </c>
-      <c r="AT45" t="n">
+      <c r="AW45" t="n">
         <v>0.320749</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AX45" t="n">
         <v>0.320782</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AY45" t="n">
         <v>0.7181419999999999</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AZ45" t="n">
         <v>1.027506</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="BA45" t="n">
+        <v>0.529123</v>
+      </c>
+      <c r="BB45" t="n">
         <v>1.280829</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="BC45" t="n">
         <v>5.05763</v>
       </c>
-      <c r="AZ45" t="n">
+      <c r="BD45" t="n">
         <v>8.444549</v>
       </c>
-      <c r="BA45" t="n">
+      <c r="BE45" t="n">
         <v>4.866504</v>
       </c>
-      <c r="BB45" t="n">
+      <c r="BF45" t="n">
         <v>0</v>
       </c>
-      <c r="BC45" t="n">
+      <c r="BG45" t="n">
         <v>0.003204</v>
       </c>
-      <c r="BD45" t="n">
+      <c r="BH45" t="n">
+        <v>0.003204</v>
+      </c>
+      <c r="BI45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BE45" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BF45" t="n">
+      <c r="BJ45" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG45" t="n">
+      <c r="BK45" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -8570,87 +9114,99 @@
         <v>0.050508</v>
       </c>
       <c r="AF46" t="n">
+        <v>0.050508</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AH46" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AH46" t="n">
+      <c r="AI46" t="n">
         <v>0.51</v>
       </c>
-      <c r="AI46" t="n">
+      <c r="AJ46" t="n">
+        <v>110.09056</v>
+      </c>
+      <c r="AK46" t="n">
         <v>114.05013</v>
       </c>
-      <c r="AJ46" t="n">
+      <c r="AL46" t="n">
         <v>5.7422</v>
       </c>
-      <c r="AK46" t="n">
+      <c r="AM46" t="n">
         <v>5.7416</v>
       </c>
-      <c r="AL46" t="n">
+      <c r="AN46" t="n">
         <v>6576464</v>
       </c>
-      <c r="AM46" t="n">
+      <c r="AO46" t="n">
         <v>2498262</v>
       </c>
-      <c r="AN46" t="n">
+      <c r="AP46" t="n">
+        <v>4078202</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>3.44</v>
       </c>
-      <c r="AO46" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AP46" t="n">
+      <c r="AR46" t="n">
         <v>4.03</v>
       </c>
-      <c r="AQ46" t="n">
+      <c r="AS46" t="n">
         <v>31.34</v>
       </c>
-      <c r="AR46" t="n">
+      <c r="AT46" t="n">
         <v>336157</v>
       </c>
-      <c r="AS46" t="n">
+      <c r="AU46" t="n">
+        <v>1.210865</v>
+      </c>
+      <c r="AV46" t="n">
         <v>6.510885</v>
       </c>
-      <c r="AT46" t="n">
+      <c r="AW46" t="n">
         <v>-1.822596</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AX46" t="n">
         <v>-1.822783</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AY46" t="n">
         <v>0.99855</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AZ46" t="n">
         <v>0.852229</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="BA46" t="n">
+        <v>1.088394</v>
+      </c>
+      <c r="BB46" t="n">
         <v>1.097417</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BC46" t="n">
         <v>5.47719</v>
       </c>
-      <c r="AZ46" t="n">
+      <c r="BD46" t="n">
         <v>8.586193</v>
       </c>
-      <c r="BA46" t="n">
+      <c r="BE46" t="n">
         <v>5.201441</v>
       </c>
-      <c r="BB46" t="n">
+      <c r="BF46" t="n">
         <v>1</v>
       </c>
-      <c r="BC46" t="n">
+      <c r="BG46" t="n">
         <v>0.001471</v>
       </c>
-      <c r="BD46" t="n">
+      <c r="BH46" t="n">
+        <v>0.001471</v>
+      </c>
+      <c r="BI46" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE46" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BF46" t="n">
+      <c r="BJ46" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="BG46" t="n">
+      <c r="BK46" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -8749,87 +9305,99 @@
         <v>0.052531</v>
       </c>
       <c r="AF47" t="n">
+        <v>0.052531</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.43</v>
       </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
         <v>0.24</v>
       </c>
-      <c r="AH47" t="n">
+      <c r="AI47" t="n">
         <v>0.48</v>
       </c>
-      <c r="AI47" t="n">
+      <c r="AJ47" t="n">
+        <v>109.72323</v>
+      </c>
+      <c r="AK47" t="n">
         <v>112.73813</v>
       </c>
-      <c r="AJ47" t="n">
+      <c r="AL47" t="n">
         <v>5.6608</v>
       </c>
-      <c r="AK47" t="n">
+      <c r="AM47" t="n">
         <v>5.6602</v>
       </c>
-      <c r="AL47" t="n">
+      <c r="AN47" t="n">
         <v>6623948</v>
       </c>
-      <c r="AM47" t="n">
+      <c r="AO47" t="n">
         <v>2512426</v>
       </c>
-      <c r="AN47" t="n">
+      <c r="AP47" t="n">
+        <v>4111522</v>
+      </c>
+      <c r="AQ47" t="n">
         <v>3.67</v>
       </c>
-      <c r="AO47" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AP47" t="n">
+      <c r="AR47" t="n">
         <v>4.25</v>
       </c>
-      <c r="AQ47" t="n">
+      <c r="AS47" t="n">
         <v>31.63</v>
       </c>
-      <c r="AR47" t="n">
+      <c r="AT47" t="n">
         <v>340789</v>
       </c>
-      <c r="AS47" t="n">
+      <c r="AU47" t="n">
+        <v>-0.333662</v>
+      </c>
+      <c r="AV47" t="n">
         <v>-1.150371</v>
       </c>
-      <c r="AT47" t="n">
+      <c r="AW47" t="n">
         <v>-1.417575</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AX47" t="n">
         <v>-1.417723</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AY47" t="n">
         <v>0.722029</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AZ47" t="n">
         <v>0.566954</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="BA47" t="n">
+        <v>0.8170269999999999</v>
+      </c>
+      <c r="BB47" t="n">
         <v>1.377928</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="BC47" t="n">
         <v>5.529729</v>
       </c>
-      <c r="AZ47" t="n">
+      <c r="BD47" t="n">
         <v>8.510418</v>
       </c>
-      <c r="BA47" t="n">
+      <c r="BE47" t="n">
         <v>5.316736</v>
       </c>
-      <c r="BB47" t="n">
+      <c r="BF47" t="n">
         <v>0</v>
       </c>
-      <c r="BC47" t="n">
+      <c r="BG47" t="n">
         <v>0.002023</v>
       </c>
-      <c r="BD47" t="n">
+      <c r="BH47" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="BI47" t="n">
         <v>0.23</v>
       </c>
-      <c r="BE47" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BF47" t="n">
+      <c r="BJ47" t="n">
         <v>0.22</v>
       </c>
-      <c r="BG47" t="n">
+      <c r="BK47" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -8928,87 +9496,99 @@
         <v>0.053936</v>
       </c>
       <c r="AF48" t="n">
+        <v>0.053936</v>
+      </c>
+      <c r="AG48" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AH48" t="n">
         <v>-0.49</v>
       </c>
-      <c r="AH48" t="n">
+      <c r="AI48" t="n">
         <v>0.35</v>
       </c>
-      <c r="AI48" t="n">
+      <c r="AJ48" t="n">
+        <v>109.00057</v>
+      </c>
+      <c r="AK48" t="n">
         <v>108.66481</v>
       </c>
-      <c r="AJ48" t="n">
+      <c r="AL48" t="n">
         <v>5.7087</v>
       </c>
-      <c r="AK48" t="n">
+      <c r="AM48" t="n">
         <v>5.7081</v>
       </c>
-      <c r="AL48" t="n">
+      <c r="AN48" t="n">
         <v>6666287</v>
       </c>
-      <c r="AM48" t="n">
+      <c r="AO48" t="n">
         <v>2532708</v>
       </c>
-      <c r="AN48" t="n">
+      <c r="AP48" t="n">
+        <v>4133579</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>3.72</v>
       </c>
-      <c r="AO48" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AP48" t="n">
+      <c r="AR48" t="n">
         <v>4.36</v>
       </c>
-      <c r="AQ48" t="n">
+      <c r="AS48" t="n">
         <v>31.7</v>
       </c>
-      <c r="AR48" t="n">
+      <c r="AT48" t="n">
         <v>341459</v>
       </c>
-      <c r="AS48" t="n">
+      <c r="AU48" t="n">
+        <v>-0.658621</v>
+      </c>
+      <c r="AV48" t="n">
         <v>-3.613081</v>
       </c>
-      <c r="AT48" t="n">
+      <c r="AW48" t="n">
         <v>0.84617</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AX48" t="n">
         <v>0.84626</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AY48" t="n">
         <v>0.639181</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AZ48" t="n">
         <v>0.807268</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="BA48" t="n">
+        <v>0.5364679999999999</v>
+      </c>
+      <c r="BB48" t="n">
         <v>0.196603</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BC48" t="n">
         <v>5.319636</v>
       </c>
-      <c r="AZ48" t="n">
+      <c r="BD48" t="n">
         <v>7.026183</v>
       </c>
-      <c r="BA48" t="n">
+      <c r="BE48" t="n">
         <v>5.201418</v>
       </c>
-      <c r="BB48" t="n">
+      <c r="BF48" t="n">
         <v>0.5</v>
       </c>
-      <c r="BC48" t="n">
+      <c r="BG48" t="n">
         <v>0.001405</v>
       </c>
-      <c r="BD48" t="n">
+      <c r="BH48" t="n">
+        <v>0.001405</v>
+      </c>
+      <c r="BI48" t="n">
         <v>0.05</v>
       </c>
-      <c r="BE48" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="BF48" t="n">
+      <c r="BJ48" t="n">
         <v>0.11</v>
       </c>
-      <c r="BG48" t="n">
+      <c r="BK48" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
@@ -9107,87 +9687,99 @@
         <v>0.054569</v>
       </c>
       <c r="AF49" t="n">
+        <v>0.054569</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.24</v>
       </c>
-      <c r="AG49" t="n">
+      <c r="AH49" t="n">
         <v>-1.67</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AI49" t="n">
         <v>0.23</v>
       </c>
-      <c r="AI49" t="n">
+      <c r="AJ49" t="n">
+        <v>108.76683</v>
+      </c>
+      <c r="AK49" t="n">
         <v>107.55639</v>
       </c>
-      <c r="AJ49" t="n">
+      <c r="AL49" t="n">
         <v>5.4571</v>
       </c>
-      <c r="AK49" t="n">
+      <c r="AM49" t="n">
         <v>5.4565</v>
       </c>
-      <c r="AL49" t="n">
+      <c r="AN49" t="n">
         <v>6703663</v>
       </c>
-      <c r="AM49" t="n">
+      <c r="AO49" t="n">
         <v>2547693</v>
       </c>
-      <c r="AN49" t="n">
+      <c r="AP49" t="n">
+        <v>4155970</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>3.75</v>
       </c>
-      <c r="AO49" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AP49" t="n">
+      <c r="AR49" t="n">
         <v>4.41</v>
       </c>
-      <c r="AQ49" t="n">
+      <c r="AS49" t="n">
         <v>31.85</v>
       </c>
-      <c r="AR49" t="n">
+      <c r="AT49" t="n">
         <v>344440</v>
       </c>
-      <c r="AS49" t="n">
+      <c r="AU49" t="n">
+        <v>-0.214439</v>
+      </c>
+      <c r="AV49" t="n">
         <v>-1.020036</v>
       </c>
-      <c r="AT49" t="n">
+      <c r="AW49" t="n">
         <v>-4.407308</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AX49" t="n">
         <v>-4.407771</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AY49" t="n">
         <v>0.5606719999999999</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AZ49" t="n">
         <v>0.591659</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="BA49" t="n">
+        <v>0.541686</v>
+      </c>
+      <c r="BB49" t="n">
         <v>0.873018</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="BC49" t="n">
         <v>5.351165</v>
       </c>
-      <c r="AZ49" t="n">
+      <c r="BD49" t="n">
         <v>4.393261</v>
       </c>
-      <c r="BA49" t="n">
+      <c r="BE49" t="n">
         <v>5.18043</v>
       </c>
-      <c r="BB49" t="n">
+      <c r="BF49" t="n">
         <v>0.25</v>
       </c>
-      <c r="BC49" t="n">
+      <c r="BG49" t="n">
         <v>0.000633</v>
       </c>
-      <c r="BD49" t="n">
+      <c r="BH49" t="n">
+        <v>0.000633</v>
+      </c>
+      <c r="BI49" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF49" t="n">
+      <c r="BJ49" t="n">
         <v>0.05</v>
       </c>
-      <c r="BG49" t="n">
+      <c r="BK49" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -9286,87 +9878,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF50" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG50" t="n">
         <v>0.26</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AH50" t="n">
         <v>-0.77</v>
       </c>
-      <c r="AH50" t="n">
+      <c r="AI50" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI50" t="n">
+      <c r="AJ50" t="n">
+        <v>108.27053</v>
+      </c>
+      <c r="AK50" t="n">
         <v>113.14433</v>
       </c>
-      <c r="AJ50" t="n">
+      <c r="AL50" t="n">
         <v>5.6021</v>
       </c>
-      <c r="AK50" t="n">
+      <c r="AM50" t="n">
         <v>5.6015</v>
       </c>
-      <c r="AL50" t="n">
+      <c r="AN50" t="n">
         <v>6733209</v>
       </c>
-      <c r="AM50" t="n">
+      <c r="AO50" t="n">
         <v>2544400</v>
       </c>
-      <c r="AN50" t="n">
+      <c r="AP50" t="n">
+        <v>4188808</v>
+      </c>
+      <c r="AQ50" t="n">
         <v>3.96</v>
       </c>
-      <c r="AO50" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AP50" t="n">
+      <c r="AR50" t="n">
         <v>4.66</v>
       </c>
-      <c r="AQ50" t="n">
+      <c r="AS50" t="n">
         <v>31.75</v>
       </c>
-      <c r="AR50" t="n">
+      <c r="AT50" t="n">
         <v>345111</v>
       </c>
-      <c r="AS50" t="n">
+      <c r="AU50" t="n">
+        <v>-0.456297</v>
+      </c>
+      <c r="AV50" t="n">
         <v>5.195358</v>
       </c>
-      <c r="AT50" t="n">
+      <c r="AW50" t="n">
         <v>2.657089</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AX50" t="n">
         <v>2.657381</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AY50" t="n">
         <v>0.440744</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AZ50" t="n">
         <v>-0.129254</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="BA50" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="BB50" t="n">
         <v>0.194809</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="BC50" t="n">
         <v>5.225222</v>
       </c>
-      <c r="AZ50" t="n">
+      <c r="BD50" t="n">
         <v>2.961368</v>
       </c>
-      <c r="BA50" t="n">
+      <c r="BE50" t="n">
         <v>5.127976</v>
       </c>
-      <c r="BB50" t="n">
+      <c r="BF50" t="n">
         <v>0</v>
       </c>
-      <c r="BC50" t="n">
+      <c r="BG50" t="n">
         <v>0.000562</v>
       </c>
-      <c r="BD50" t="n">
+      <c r="BH50" t="n">
+        <v>0.000562</v>
+      </c>
+      <c r="BI50" t="n">
         <v>0.21</v>
       </c>
-      <c r="BE50" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BF50" t="n">
+      <c r="BJ50" t="n">
         <v>0.25</v>
       </c>
-      <c r="BG50" t="n">
+      <c r="BK50" t="n">
         <v>-0.1</v>
       </c>
     </row>
@@ -9465,87 +10069,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF51" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG51" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AH51" t="n">
         <v>0.36</v>
       </c>
-      <c r="AH51" t="n">
+      <c r="AI51" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AI51" t="n">
+      <c r="AJ51" t="n">
+        <v>108.80021</v>
+      </c>
+      <c r="AK51" t="n">
         <v>110.57963</v>
       </c>
-      <c r="AJ51" t="n">
+      <c r="AL51" t="n">
         <v>5.4264</v>
       </c>
-      <c r="AK51" t="n">
+      <c r="AM51" t="n">
         <v>5.4258</v>
       </c>
-      <c r="AL51" t="n">
+      <c r="AN51" t="n">
         <v>6774436</v>
       </c>
-      <c r="AM51" t="n">
+      <c r="AO51" t="n">
         <v>2546265</v>
       </c>
-      <c r="AN51" t="n">
+      <c r="AP51" t="n">
+        <v>4228171</v>
+      </c>
+      <c r="AQ51" t="n">
         <v>4.14</v>
       </c>
-      <c r="AO51" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AP51" t="n">
+      <c r="AR51" t="n">
         <v>4.92</v>
       </c>
-      <c r="AQ51" t="n">
+      <c r="AS51" t="n">
         <v>31.87</v>
       </c>
-      <c r="AR51" t="n">
+      <c r="AT51" t="n">
         <v>350767</v>
       </c>
-      <c r="AS51" t="n">
+      <c r="AU51" t="n">
+        <v>0.489219</v>
+      </c>
+      <c r="AV51" t="n">
         <v>-2.266751</v>
       </c>
-      <c r="AT51" t="n">
+      <c r="AW51" t="n">
         <v>-3.136324</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AX51" t="n">
         <v>-3.13666</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AY51" t="n">
         <v>0.612293</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AZ51" t="n">
         <v>0.073298</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="BA51" t="n">
+        <v>0.9397180000000001</v>
+      </c>
+      <c r="BB51" t="n">
         <v>1.638893</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="BC51" t="n">
         <v>5.130501</v>
       </c>
-      <c r="AZ51" t="n">
+      <c r="BD51" t="n">
         <v>3.033233</v>
       </c>
-      <c r="BA51" t="n">
+      <c r="BE51" t="n">
         <v>5.054283</v>
       </c>
-      <c r="BB51" t="n">
+      <c r="BF51" t="n">
         <v>0</v>
       </c>
-      <c r="BC51" t="n">
+      <c r="BG51" t="n">
         <v>0</v>
       </c>
-      <c r="BD51" t="n">
+      <c r="BH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI51" t="n">
         <v>0.18</v>
       </c>
-      <c r="BE51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BF51" t="n">
+      <c r="BJ51" t="n">
         <v>0.26</v>
       </c>
-      <c r="BG51" t="n">
+      <c r="BK51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -9644,87 +10260,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF52" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG52" t="n">
         <v>0.48</v>
       </c>
-      <c r="AG52" t="n">
+      <c r="AH52" t="n">
         <v>0.42</v>
       </c>
-      <c r="AH52" t="n">
+      <c r="AI52" t="n">
         <v>0.52</v>
       </c>
-      <c r="AI52" t="n">
+      <c r="AJ52" t="n">
+        <v>108.63642</v>
+      </c>
+      <c r="AK52" t="n">
         <v>109.59513</v>
       </c>
-      <c r="AJ52" t="n">
+      <c r="AL52" t="n">
         <v>5.3186</v>
       </c>
-      <c r="AK52" t="n">
+      <c r="AM52" t="n">
         <v>5.318</v>
       </c>
-      <c r="AL52" t="n">
+      <c r="AN52" t="n">
         <v>6852705</v>
       </c>
-      <c r="AM52" t="n">
+      <c r="AO52" t="n">
         <v>2589817</v>
       </c>
-      <c r="AN52" t="n">
+      <c r="AP52" t="n">
+        <v>4262888</v>
+      </c>
+      <c r="AQ52" t="n">
         <v>4.09</v>
       </c>
-      <c r="AO52" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AP52" t="n">
+      <c r="AR52" t="n">
         <v>4.89</v>
       </c>
-      <c r="AQ52" t="n">
+      <c r="AS52" t="n">
         <v>31.47</v>
       </c>
-      <c r="AR52" t="n">
+      <c r="AT52" t="n">
         <v>356582</v>
       </c>
-      <c r="AS52" t="n">
+      <c r="AU52" t="n">
+        <v>-0.150542</v>
+      </c>
+      <c r="AV52" t="n">
         <v>-0.890309</v>
       </c>
-      <c r="AT52" t="n">
+      <c r="AW52" t="n">
         <v>-1.986584</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AX52" t="n">
         <v>-1.986804</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AY52" t="n">
         <v>1.155358</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AZ52" t="n">
         <v>1.710427</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="BA52" t="n">
+        <v>0.821088</v>
+      </c>
+      <c r="BB52" t="n">
         <v>1.657796</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="BC52" t="n">
         <v>5.172369</v>
       </c>
-      <c r="AZ52" t="n">
+      <c r="BD52" t="n">
         <v>2.828436</v>
       </c>
-      <c r="BA52" t="n">
+      <c r="BE52" t="n">
         <v>5.096104</v>
       </c>
-      <c r="BB52" t="n">
+      <c r="BF52" t="n">
         <v>0</v>
       </c>
-      <c r="BC52" t="n">
+      <c r="BG52" t="n">
         <v>0</v>
       </c>
-      <c r="BD52" t="n">
+      <c r="BH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI52" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BE52" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BF52" t="n">
+      <c r="BJ52" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BG52" t="n">
+      <c r="BK52" t="n">
         <v>-0.4</v>
       </c>
     </row>
@@ -9823,87 +10451,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF53" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG53" t="n">
         <v>0.09</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AH53" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AI53" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AJ53" t="n">
+        <v>108.7159</v>
+      </c>
+      <c r="AK53" t="n">
         <v>110.16346</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AL53" t="n">
         <v>5.3843</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AM53" t="n">
         <v>5.3837</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AN53" t="n">
         <v>6923886</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AO53" t="n">
         <v>2597630</v>
       </c>
-      <c r="AN53" t="n">
+      <c r="AP53" t="n">
+        <v>4326256</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>4.18</v>
       </c>
-      <c r="AO53" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AP53" t="n">
+      <c r="AR53" t="n">
         <v>4.99</v>
       </c>
-      <c r="AQ53" t="n">
+      <c r="AS53" t="n">
         <v>32.04</v>
       </c>
-      <c r="AR53" t="n">
+      <c r="AT53" t="n">
         <v>357103</v>
       </c>
-      <c r="AS53" t="n">
+      <c r="AU53" t="n">
+        <v>0.073161</v>
+      </c>
+      <c r="AV53" t="n">
         <v>0.518572</v>
       </c>
-      <c r="AT53" t="n">
+      <c r="AW53" t="n">
         <v>1.235287</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AX53" t="n">
         <v>1.235427</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AY53" t="n">
         <v>1.038729</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AZ53" t="n">
         <v>0.301682</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="BA53" t="n">
+        <v>1.486504</v>
+      </c>
+      <c r="BB53" t="n">
         <v>0.146109</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="BC53" t="n">
         <v>4.680811</v>
       </c>
-      <c r="AZ53" t="n">
+      <c r="BD53" t="n">
         <v>0.924206</v>
       </c>
-      <c r="BA53" t="n">
+      <c r="BE53" t="n">
         <v>4.490243</v>
       </c>
-      <c r="BB53" t="n">
+      <c r="BF53" t="n">
         <v>0</v>
       </c>
-      <c r="BC53" t="n">
+      <c r="BG53" t="n">
         <v>0</v>
       </c>
-      <c r="BD53" t="n">
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" t="n">
         <v>0.09</v>
       </c>
-      <c r="BE53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BF53" t="n">
+      <c r="BJ53" t="n">
         <v>0.1</v>
       </c>
-      <c r="BG53" t="n">
+      <c r="BK53" t="n">
         <v>0.57</v>
       </c>
     </row>
@@ -10002,87 +10642,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF54" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG54" t="n">
         <v>0.18</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AH54" t="n">
         <v>0.27</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AI54" t="n">
         <v>0.03</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AJ54" t="n">
+        <v>109.27405</v>
+      </c>
+      <c r="AK54" t="n">
         <v>106.90236</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AL54" t="n">
         <v>5.3338</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AM54" t="n">
         <v>5.3332</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AN54" t="n">
         <v>7003273</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AO54" t="n">
         <v>2616213</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AP54" t="n">
+        <v>4387061</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>4.23</v>
       </c>
-      <c r="AO54" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AP54" t="n">
+      <c r="AR54" t="n">
         <v>5.12</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AS54" t="n">
         <v>32.32</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AT54" t="n">
         <v>360578</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AU54" t="n">
+        <v>0.513402</v>
+      </c>
+      <c r="AV54" t="n">
         <v>-2.960237</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AW54" t="n">
         <v>-0.937912</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AX54" t="n">
         <v>-0.938017</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AY54" t="n">
         <v>1.146567</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AZ54" t="n">
         <v>0.715383</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="BA54" t="n">
+        <v>1.405488</v>
+      </c>
+      <c r="BB54" t="n">
         <v>0.973109</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="BC54" t="n">
         <v>4.461836</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="BD54" t="n">
         <v>-0.101973</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BE54" t="n">
         <v>4.177803</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BF54" t="n">
         <v>0</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BG54" t="n">
         <v>-0</v>
       </c>
-      <c r="BD54" t="n">
+      <c r="BH54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI54" t="n">
         <v>0.05</v>
       </c>
-      <c r="BE54" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="BF54" t="n">
+      <c r="BJ54" t="n">
         <v>0.13</v>
       </c>
-      <c r="BG54" t="n">
+      <c r="BK54" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -10181,87 +10833,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF55" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG55" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AH55" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AI55" t="n">
         <v>0.21</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AJ55" t="n">
+        <v>109.41762</v>
+      </c>
+      <c r="AK55" t="n">
         <v>107.17649</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AL55" t="n">
         <v>5.5024</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AM55" t="n">
         <v>5.5018</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AN55" t="n">
         <v>7136436</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AO55" t="n">
         <v>2701146</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AP55" t="n">
+        <v>4435290</v>
+      </c>
+      <c r="AQ55" t="n">
         <v>4.2</v>
       </c>
-      <c r="AO55" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AP55" t="n">
+      <c r="AR55" t="n">
         <v>5.12</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AS55" t="n">
         <v>31.99</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AT55" t="n">
         <v>358234</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AU55" t="n">
+        <v>0.131385</v>
+      </c>
+      <c r="AV55" t="n">
         <v>0.25643</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AW55" t="n">
         <v>3.160973</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AX55" t="n">
         <v>3.161329</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AY55" t="n">
         <v>1.90144</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AZ55" t="n">
         <v>3.24641</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="BA55" t="n">
+        <v>1.099346</v>
+      </c>
+      <c r="BB55" t="n">
         <v>-0.650067</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="BC55" t="n">
         <v>4.264385</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="BD55" t="n">
         <v>-1.042167</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BE55" t="n">
         <v>3.897866</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>-0.06</v>
       </c>
       <c r="BF55" t="n">
         <v>0</v>
       </c>
       <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK55" t="n">
         <v>-0.33</v>
       </c>
     </row>
@@ -10360,87 +11024,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF56" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG56" t="n">
         <v>0.33</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AH56" t="n">
         <v>0.41</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AI56" t="n">
         <v>0.39</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AJ56" t="n">
+        <v>110.05486</v>
+      </c>
+      <c r="AK56" t="n">
         <v>102.36456</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AL56" t="n">
         <v>5.2301</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AM56" t="n">
         <v>5.2295</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AN56" t="n">
         <v>7130500</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AO56" t="n">
         <v>2654052</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AP56" t="n">
+        <v>4476448</v>
+      </c>
+      <c r="AQ56" t="n">
         <v>4.45</v>
       </c>
-      <c r="AO56" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AP56" t="n">
+      <c r="AR56" t="n">
         <v>5.38</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AS56" t="n">
         <v>32.6</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AT56" t="n">
         <v>364367</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AU56" t="n">
+        <v>0.582392</v>
+      </c>
+      <c r="AV56" t="n">
         <v>-4.489725</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AW56" t="n">
         <v>-4.94875</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AX56" t="n">
         <v>-4.949289</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AY56" t="n">
         <v>-0.083179</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AZ56" t="n">
         <v>-1.743482</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="BA56" t="n">
+        <v>0.927966</v>
+      </c>
+      <c r="BB56" t="n">
         <v>1.712009</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="BC56" t="n">
         <v>4.441351</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="BD56" t="n">
         <v>-0.903999</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BE56" t="n">
         <v>4.303068</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BF56" t="n">
         <v>0</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BG56" t="n">
         <v>0</v>
       </c>
-      <c r="BD56" t="n">
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" t="n">
         <v>0.25</v>
       </c>
-      <c r="BE56" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="BF56" t="n">
+      <c r="BJ56" t="n">
         <v>0.26</v>
       </c>
-      <c r="BG56" t="n">
+      <c r="BK56" t="n">
         <v>0.61</v>
       </c>
     </row>
@@ -10539,87 +11215,99 @@
         <v>0.055131</v>
       </c>
       <c r="AF57" t="n">
+        <v>0.055131</v>
+      </c>
+      <c r="AG57" t="n">
         <v>0.7</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AH57" t="n">
         <v>-0.73</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AI57" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AJ57" t="n">
+        <v>110.65892</v>
+      </c>
+      <c r="AK57" t="n">
         <v>106.82125</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AL57" t="n">
         <v>5.1495</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AM57" t="n">
         <v>5.1489</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AN57" t="n">
         <v>7156987</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AO57" t="n">
         <v>2655931</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AP57" t="n">
+        <v>4501056</v>
+      </c>
+      <c r="AQ57" t="n">
         <v>4.64</v>
       </c>
-      <c r="AO57" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AP57" t="n">
+      <c r="AR57" t="n">
         <v>5.56</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AS57" t="n">
         <v>32.78</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AT57" t="n">
         <v>371074</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AU57" t="n">
+        <v>0.548872</v>
+      </c>
+      <c r="AV57" t="n">
         <v>4.353743</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AW57" t="n">
         <v>-1.54108</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AX57" t="n">
         <v>-1.541256</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AY57" t="n">
         <v>0.371461</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AZ57" t="n">
         <v>0.070797</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="BA57" t="n">
+        <v>0.549722</v>
+      </c>
+      <c r="BB57" t="n">
         <v>1.840727</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="BC57" t="n">
         <v>3.812497</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="BD57" t="n">
         <v>-2.659212</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BE57" t="n">
         <v>3.357475</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BF57" t="n">
         <v>0</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BG57" t="n">
         <v>0</v>
       </c>
-      <c r="BD57" t="n">
+      <c r="BH57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI57" t="n">
         <v>0.19</v>
       </c>
-      <c r="BE57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BF57" t="n">
+      <c r="BJ57" t="n">
         <v>0.18</v>
       </c>
-      <c r="BG57" t="n">
+      <c r="BK57" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -10718,87 +11406,99 @@
         <v>0.054777</v>
       </c>
       <c r="AF58" t="n">
+        <v>0.054777</v>
+      </c>
+      <c r="AG58" t="n">
         <v>0.88</v>
       </c>
-      <c r="AG58" t="n">
+      <c r="AH58" t="n">
         <v>0.52</v>
       </c>
-      <c r="AH58" t="n">
+      <c r="AI58" t="n">
         <v>0.91</v>
       </c>
-      <c r="AI58" t="n">
+      <c r="AJ58" t="n">
+        <v>110.51078</v>
+      </c>
+      <c r="AK58" t="n">
         <v>117.8089</v>
       </c>
-      <c r="AJ58" t="n">
+      <c r="AL58" t="n">
         <v>5.2194</v>
       </c>
-      <c r="AK58" t="n">
+      <c r="AM58" t="n">
         <v>5.2188</v>
       </c>
-      <c r="AL58" t="n">
-        <v>7237735</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>2686046</v>
-      </c>
       <c r="AN58" t="n">
-        <v>4.52</v>
+        <v>7240551</v>
       </c>
       <c r="AO58" t="n">
-        <v>3.04</v>
+        <v>2687537</v>
       </c>
       <c r="AP58" t="n">
+        <v>4553014</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AR58" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ58" t="n">
+      <c r="AS58" t="n">
         <v>32.99</v>
       </c>
-      <c r="AR58" t="n">
+      <c r="AT58" t="n">
         <v>362002</v>
       </c>
-      <c r="AS58" t="n">
+      <c r="AU58" t="n">
+        <v>-0.133871</v>
+      </c>
+      <c r="AV58" t="n">
         <v>10.286015</v>
       </c>
-      <c r="AT58" t="n">
+      <c r="AW58" t="n">
         <v>1.357413</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AX58" t="n">
         <v>1.357572</v>
       </c>
-      <c r="AV58" t="n">
-        <v>1.12824</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>1.133877</v>
-      </c>
-      <c r="AX58" t="n">
+      <c r="AY58" t="n">
+        <v>1.167586</v>
+      </c>
+      <c r="AZ58" t="n">
+        <v>1.190016</v>
+      </c>
+      <c r="BA58" t="n">
+        <v>1.154351</v>
+      </c>
+      <c r="BB58" t="n">
         <v>-2.444795</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="BC58" t="n">
         <v>4.142847</v>
       </c>
-      <c r="AZ58" t="n">
+      <c r="BD58" t="n">
         <v>-1.819225</v>
       </c>
-      <c r="BA58" t="n">
+      <c r="BE58" t="n">
         <v>3.768807</v>
       </c>
-      <c r="BB58" t="n">
+      <c r="BF58" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BC58" t="n">
+      <c r="BG58" t="n">
         <v>-0.000354</v>
       </c>
-      <c r="BD58" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="BE58" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BF58" t="n">
+      <c r="BH58" t="n">
+        <v>-0.000354</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="BJ58" t="n">
         <v>-0.16</v>
       </c>
-      <c r="BG58" t="n">
+      <c r="BK58" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -10897,87 +11597,99 @@
         <v>0.054223</v>
       </c>
       <c r="AF59" t="n">
+        <v>0.054223</v>
+      </c>
+      <c r="AG59" t="n">
         <v>0.67</v>
       </c>
-      <c r="AG59" t="n">
+      <c r="AH59" t="n">
         <v>2.73</v>
       </c>
-      <c r="AH59" t="n">
+      <c r="AI59" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI59" t="n">
+      <c r="AJ59" t="n">
+        <v>110.95732</v>
+      </c>
+      <c r="AK59" t="n">
         <v>113.99365</v>
       </c>
-      <c r="AJ59" t="n">
+      <c r="AL59" t="n">
         <v>4.9886</v>
       </c>
-      <c r="AK59" t="n">
+      <c r="AM59" t="n">
         <v>4.988</v>
       </c>
-      <c r="AL59" t="n">
-        <v>7258599</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>2684623</v>
-      </c>
       <c r="AN59" t="n">
-        <v>4.63</v>
+        <v>7259769</v>
       </c>
       <c r="AO59" t="n">
-        <v>3.15</v>
+        <v>2685400</v>
       </c>
       <c r="AP59" t="n">
+        <v>4574369</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AR59" t="n">
         <v>5.51</v>
       </c>
-      <c r="AQ59" t="n">
+      <c r="AS59" t="n">
         <v>33.51</v>
       </c>
-      <c r="AR59" t="n">
+      <c r="AT59" t="n">
         <v>366913</v>
       </c>
-      <c r="AS59" t="n">
+      <c r="AU59" t="n">
+        <v>0.404069</v>
+      </c>
+      <c r="AV59" t="n">
         <v>-3.238507</v>
       </c>
-      <c r="AT59" t="n">
+      <c r="AW59" t="n">
         <v>-4.421964</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AX59" t="n">
         <v>-4.422473</v>
       </c>
-      <c r="AV59" t="n">
-        <v>0.288267</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>-0.052977</v>
-      </c>
-      <c r="AX59" t="n">
+      <c r="AY59" t="n">
+        <v>0.265422</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>-0.079515</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>0.46903</v>
+      </c>
+      <c r="BB59" t="n">
         <v>1.356622</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="BC59" t="n">
         <v>4.39172</v>
       </c>
-      <c r="AZ59" t="n">
+      <c r="BD59" t="n">
         <v>0.619623</v>
       </c>
-      <c r="BA59" t="n">
+      <c r="BE59" t="n">
         <v>4.109608</v>
       </c>
-      <c r="BB59" t="n">
+      <c r="BF59" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BC59" t="n">
+      <c r="BG59" t="n">
         <v>-0.000554</v>
       </c>
-      <c r="BD59" t="n">
+      <c r="BH59" t="n">
+        <v>-0.000554</v>
+      </c>
+      <c r="BI59" t="n">
         <v>0.11</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BJ59" t="n">
         <v>0.11</v>
       </c>
-      <c r="BF59" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BG59" t="n">
+      <c r="BK59" t="n">
         <v>0.52</v>
       </c>
     </row>
@@ -11076,88 +11788,100 @@
         <v>0.0534</v>
       </c>
       <c r="AF60" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AG60" t="n">
         <v>0.58</v>
       </c>
-      <c r="AG60" t="n">
+      <c r="AH60" t="n">
         <v>0.84</v>
       </c>
-      <c r="AH60" t="n">
+      <c r="AI60" t="n">
         <v>0.65</v>
       </c>
-      <c r="AI60" t="n">
+      <c r="AJ60" t="n">
+        <v>111.03587</v>
+      </c>
+      <c r="AK60" t="n">
         <v>109.52993</v>
       </c>
-      <c r="AJ60" t="n">
+      <c r="AL60" t="n">
         <v>5.0569</v>
       </c>
-      <c r="AK60" t="n">
+      <c r="AM60" t="n">
         <v>5.0563</v>
       </c>
-      <c r="AL60" t="n">
-        <v>7299615</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>2704550</v>
-      </c>
       <c r="AN60" t="n">
+        <v>7303618</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>2707962</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>4595657</v>
+      </c>
+      <c r="AQ60" t="n">
         <v>4.74</v>
       </c>
-      <c r="AO60" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AP60" t="n">
+      <c r="AR60" t="n">
         <v>5.62</v>
       </c>
-      <c r="AQ60" t="n">
-        <v>33.42</v>
-      </c>
-      <c r="AR60" t="n">
+      <c r="AS60" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="AT60" t="n">
         <v>371137</v>
       </c>
-      <c r="AS60" t="n">
+      <c r="AU60" t="n">
+        <v>0.07079299999999999</v>
+      </c>
+      <c r="AV60" t="n">
         <v>-3.915762</v>
       </c>
-      <c r="AT60" t="n">
+      <c r="AW60" t="n">
         <v>1.369122</v>
       </c>
-      <c r="AU60" t="n">
+      <c r="AX60" t="n">
         <v>1.369286</v>
       </c>
-      <c r="AV60" t="n">
-        <v>0.565068</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0.742264</v>
-      </c>
-      <c r="AX60" t="n">
+      <c r="AY60" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0.8401729999999999</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0.465376</v>
+      </c>
+      <c r="BB60" t="n">
         <v>1.151227</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="BC60" t="n">
         <v>4.724907</v>
       </c>
-      <c r="AZ60" t="n">
+      <c r="BD60" t="n">
         <v>1.964454</v>
       </c>
-      <c r="BA60" t="n">
+      <c r="BE60" t="n">
         <v>4.420848</v>
       </c>
-      <c r="BB60" t="n">
+      <c r="BF60" t="n">
         <v>0</v>
       </c>
-      <c r="BC60" t="n">
+      <c r="BG60" t="n">
         <v>-0.0008229999999999999</v>
       </c>
-      <c r="BD60" t="n">
+      <c r="BH60" t="n">
+        <v>-0.0008229999999999999</v>
+      </c>
+      <c r="BI60" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BJ60" t="n">
         <v>0.11</v>
       </c>
-      <c r="BE60" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BG60" t="n">
-        <v>-0.09</v>
+      <c r="BK60" t="n">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="61">
@@ -11255,149 +11979,181 @@
         <v>0.053028</v>
       </c>
       <c r="AF61" t="n">
+        <v>0.053028</v>
+      </c>
+      <c r="AG61" t="n">
         <v>0.16</v>
       </c>
-      <c r="AG61" t="n">
+      <c r="AH61" t="n">
         <v>-0.5</v>
       </c>
-      <c r="AH61" t="n">
+      <c r="AI61" t="n">
         <v>0.14</v>
       </c>
-      <c r="AI61" t="inlineStr"/>
-      <c r="AJ61" t="n">
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="n">
         <v>5.1766</v>
       </c>
-      <c r="AK61" t="n">
+      <c r="AM61" t="n">
         <v>5.176</v>
       </c>
-      <c r="AL61" t="inlineStr"/>
-      <c r="AM61" t="inlineStr"/>
-      <c r="AN61" t="inlineStr"/>
-      <c r="AO61" t="inlineStr"/>
-      <c r="AP61" t="inlineStr"/>
-      <c r="AQ61" t="inlineStr"/>
+      <c r="AN61" t="n">
+        <v>7355800</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>2749001</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>4606799</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>4.68</v>
+      </c>
       <c r="AR61" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="AT61" t="n">
         <v>367558</v>
       </c>
-      <c r="AS61" t="inlineStr"/>
-      <c r="AT61" t="n">
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr"/>
+      <c r="AW61" t="n">
         <v>2.367063</v>
       </c>
-      <c r="AU61" t="n">
+      <c r="AX61" t="n">
         <v>2.367344</v>
       </c>
-      <c r="AV61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr"/>
-      <c r="AX61" t="n">
+      <c r="AY61" t="n">
+        <v>0.714468</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>1.515494</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0.242446</v>
+      </c>
+      <c r="BB61" t="n">
         <v>-0.964334</v>
       </c>
-      <c r="AY61" t="n">
+      <c r="BC61" t="n">
         <v>4.641328</v>
       </c>
-      <c r="AZ61" t="n">
+      <c r="BD61" t="n">
         <v>3.177699</v>
       </c>
-      <c r="BA61" t="n">
+      <c r="BE61" t="n">
         <v>4.327084</v>
       </c>
-      <c r="BB61" t="n">
+      <c r="BF61" t="n">
         <v>-0.25</v>
       </c>
-      <c r="BC61" t="n">
+      <c r="BG61" t="n">
         <v>-0.000372</v>
       </c>
-      <c r="BD61" t="inlineStr"/>
-      <c r="BE61" t="inlineStr"/>
-      <c r="BF61" t="inlineStr"/>
-      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="n">
+        <v>-0.000372</v>
+      </c>
+      <c r="BI61" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="BJ61" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK61" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B62" t="n">
-        <v>175335</v>
+        <v>173885</v>
       </c>
       <c r="C62" t="n">
-        <v>173.740005</v>
+        <v>170.550003</v>
       </c>
       <c r="D62" t="n">
-        <v>107.169998</v>
+        <v>105.099998</v>
       </c>
       <c r="E62" t="n">
-        <v>428.609985</v>
+        <v>421.559998</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1259</v>
+        <v>5.099</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8325</v>
+        <v>5.8475</v>
       </c>
       <c r="H62" t="n">
-        <v>7428.779785</v>
+        <v>7316.149902</v>
       </c>
       <c r="I62" t="n">
-        <v>24932.080078</v>
+        <v>24442.939453</v>
       </c>
       <c r="J62" t="n">
-        <v>52210.078125</v>
+        <v>51594.140625</v>
       </c>
       <c r="K62" t="n">
-        <v>4092.399902</v>
+        <v>4136.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>82.660004</v>
+        <v>83.41999800000001</v>
       </c>
       <c r="M62" t="n">
-        <v>87.91999800000001</v>
+        <v>89.889999</v>
       </c>
       <c r="N62" t="n">
-        <v>1207.75</v>
+        <v>1193.25</v>
       </c>
       <c r="O62" t="n">
-        <v>478.5</v>
+        <v>473.5</v>
       </c>
       <c r="P62" t="n">
-        <v>1.924731</v>
+        <v>1.081826</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.774329</v>
+        <v>0.887311</v>
       </c>
       <c r="R62" t="n">
-        <v>-0.750144</v>
+        <v>-2.667165</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.615978</v>
+        <v>-3.234247</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.078532</v>
+        <v>-1.597654</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.430755</v>
+        <v>-1.177257</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.941148</v>
+        <v>-2.443008</v>
       </c>
       <c r="W62" t="n">
-        <v>-4.889198</v>
+        <v>-6.755169</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.208568</v>
+        <v>-1.385837</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.727609</v>
+        <v>2.831289</v>
       </c>
       <c r="Z62" t="n">
-        <v>18.935257</v>
+        <v>20.028774</v>
       </c>
       <c r="AA62" t="n">
-        <v>20.570489</v>
+        <v>23.272081</v>
       </c>
       <c r="AB62" t="n">
-        <v>8.148645999999999</v>
+        <v>6.850235</v>
       </c>
       <c r="AC62" t="n">
-        <v>15.92974</v>
+        <v>14.718353</v>
       </c>
       <c r="AD62" t="n">
         <v>14.25</v>
@@ -11405,46 +12161,54 @@
       <c r="AE62" t="n">
         <v>0.052531</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
+      <c r="AF62" t="n">
+        <v>0.052531</v>
+      </c>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
       <c r="AI62" t="inlineStr"/>
-      <c r="AJ62" t="n">
-        <v>5.1177</v>
-      </c>
-      <c r="AK62" t="n">
-        <v>5.1171</v>
-      </c>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="n">
+        <v>5.1217</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>5.1211</v>
+      </c>
       <c r="AN62" t="inlineStr"/>
       <c r="AO62" t="inlineStr"/>
       <c r="AP62" t="inlineStr"/>
       <c r="AQ62" t="inlineStr"/>
       <c r="AR62" t="inlineStr"/>
       <c r="AS62" t="inlineStr"/>
-      <c r="AT62" t="n">
-        <v>-1.137812</v>
-      </c>
-      <c r="AU62" t="n">
-        <v>-1.137944</v>
-      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr"/>
-      <c r="AX62" t="inlineStr"/>
+      <c r="AW62" t="n">
+        <v>-1.060542</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>-1.060665</v>
+      </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="inlineStr"/>
-      <c r="BB62" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC62" t="n">
-        <v>-0.000497</v>
-      </c>
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
       <c r="BE62" t="inlineStr"/>
-      <c r="BF62" t="inlineStr"/>
-      <c r="BG62" t="inlineStr"/>
+      <c r="BF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG62" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="BH62" t="n">
+        <v>-0.000497</v>
+      </c>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/consolidada/base_conjuntura_mensal.xlsx
+++ b/data/final/consolidada/base_conjuntura_mensal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK62"/>
+  <dimension ref="A1:BI62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,140 +598,130 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>bcb_sgs_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_ibc_br</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
           <t>bcb_sgs_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>bcb_sgs_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>bcb_sgs_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_total</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>bcb_sgs_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bcb_sgs_juros_credito_total</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>bcb_sgs_reservas_internacionais</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_ibc_br_sa</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>bcb_sgs_var_pct_ibc_br</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_venda_usd</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_cambio_compra_usd</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_total</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pj</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_saldo_credito_pf</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>bcb_sgs_var_pct_reservas_internacionais</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>bcb_sgs_ipca_acum_12m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>bcb_sgs_igp_m_acum_12m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>bcb_sgs_inpc_acum_12m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_meta</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_selic_over</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_cdi</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_total</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>bcb_sgs_dif_inadimplencia_pj</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_inadimplencia_pf</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>bcb_sgs_dif_juros_credito_total</t>
         </is>
@@ -753,36 +743,16 @@
       <c r="E2" t="n">
         <v>250.350006</v>
       </c>
-      <c r="F2" t="n">
-        <v>5.0804</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6.0387</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4395.259766</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14672.679688</v>
-      </c>
-      <c r="J2" t="n">
-        <v>34935.46875</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1812.599976</v>
-      </c>
-      <c r="L2" t="n">
-        <v>73.949997</v>
-      </c>
-      <c r="M2" t="n">
-        <v>76.33000199999999</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1414.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>547</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -800,12 +770,8 @@
       <c r="AD2" t="n">
         <v>4.25</v>
       </c>
-      <c r="AE2" t="n">
-        <v>0.016137</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.016137</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>0.96</v>
       </c>
@@ -815,39 +781,33 @@
       <c r="AI2" t="n">
         <v>1.02</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>96.31464</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>99.83978</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>5.1216</v>
+        <v>4271865</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.121</v>
+        <v>1833179</v>
       </c>
       <c r="AN2" t="n">
-        <v>4271865</v>
+        <v>2438686</v>
       </c>
       <c r="AO2" t="n">
-        <v>1833179</v>
+        <v>2.36</v>
       </c>
       <c r="AP2" t="n">
-        <v>2438686</v>
+        <v>1.58</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.36</v>
+        <v>2.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.94</v>
+        <v>20.26</v>
       </c>
       <c r="AS2" t="n">
-        <v>20.26</v>
-      </c>
-      <c r="AT2" t="n">
         <v>355671</v>
       </c>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
@@ -863,8 +823,6 @@
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -924,36 +882,16 @@
       <c r="S3" t="n">
         <v>1.457956</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.017557</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.212177</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.899042</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.997638</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.217278</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.132408</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>-7.369841</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-4.375742</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>-8.199329000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-2.3766</v>
-      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>5.25</v>
       </c>
@@ -973,81 +911,67 @@
         <v>0.88</v>
       </c>
       <c r="AJ3" t="n">
-        <v>97.07568000000001</v>
+        <v>5.1433</v>
       </c>
       <c r="AK3" t="n">
-        <v>99.32829</v>
+        <v>5.1427</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.1433</v>
+        <v>4346060</v>
       </c>
       <c r="AM3" t="n">
-        <v>5.1427</v>
+        <v>1851006</v>
       </c>
       <c r="AN3" t="n">
-        <v>4346060</v>
+        <v>2495054</v>
       </c>
       <c r="AO3" t="n">
-        <v>1851006</v>
+        <v>2.37</v>
       </c>
       <c r="AP3" t="n">
-        <v>2495054</v>
+        <v>1.56</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.37</v>
+        <v>2.96</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.96</v>
+        <v>20.92</v>
       </c>
       <c r="AS3" t="n">
-        <v>20.92</v>
-      </c>
-      <c r="AT3" t="n">
         <v>370395</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0.79016</v>
-      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>-0.512311</v>
+        <v>1.736829</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.423696</v>
+        <v>0.972464</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.423745</v>
+        <v>2.311409</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.736829</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.972464</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.311409</v>
-      </c>
-      <c r="BB3" t="n">
         <v>4.139781</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="n">
+        <v>1</v>
+      </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.003276</v>
+        <v>-0.02</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.003276</v>
+        <v>0.02</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BK3" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1158,81 +1082,75 @@
         <v>1.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>96.95968999999999</v>
+        <v>5.4394</v>
       </c>
       <c r="AK4" t="n">
-        <v>97.24746</v>
+        <v>5.4388</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.4394</v>
+        <v>4441056</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.4388</v>
+        <v>1894119</v>
       </c>
       <c r="AN4" t="n">
-        <v>4441056</v>
+        <v>2546936</v>
       </c>
       <c r="AO4" t="n">
-        <v>1894119</v>
+        <v>2.34</v>
       </c>
       <c r="AP4" t="n">
-        <v>2546936</v>
+        <v>1.43</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.34</v>
+        <v>3.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.01</v>
+        <v>21.42</v>
       </c>
       <c r="AS4" t="n">
-        <v>21.42</v>
+        <v>368886</v>
       </c>
       <c r="AT4" t="n">
-        <v>368886</v>
+        <v>5.757004</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.119484</v>
+        <v>5.757676</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.094902</v>
+        <v>2.185796</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.757004</v>
+        <v>2.329166</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.757676</v>
+        <v>2.079394</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.185796</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.329166</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2.079394</v>
-      </c>
-      <c r="BB4" t="n">
         <v>-0.407403</v>
       </c>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.001591</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.001591</v>
+      </c>
       <c r="BF4" t="n">
-        <v>1</v>
+        <v>-0.03</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.001591</v>
+        <v>-0.13</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001591</v>
+        <v>0.05</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="BK4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1343,81 +1261,75 @@
         <v>1.16</v>
       </c>
       <c r="AJ5" t="n">
-        <v>97.48142</v>
+        <v>5.643</v>
       </c>
       <c r="AK5" t="n">
-        <v>96.62081999999999</v>
+        <v>5.6424</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.643</v>
+        <v>4511956</v>
       </c>
       <c r="AM5" t="n">
-        <v>5.6424</v>
+        <v>1910940</v>
       </c>
       <c r="AN5" t="n">
-        <v>4511956</v>
+        <v>2601017</v>
       </c>
       <c r="AO5" t="n">
-        <v>1910940</v>
+        <v>2.33</v>
       </c>
       <c r="AP5" t="n">
-        <v>2601017</v>
+        <v>1.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33</v>
+        <v>2.99</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.99</v>
+        <v>22.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>22.89</v>
+        <v>367927</v>
       </c>
       <c r="AT5" t="n">
-        <v>367927</v>
+        <v>3.74306</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.53809</v>
+        <v>3.743473</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.644377</v>
+        <v>1.596467</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.74306</v>
+        <v>0.888065</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.743473</v>
+        <v>2.123375</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.596467</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.888065</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>2.123375</v>
-      </c>
-      <c r="BB5" t="n">
         <v>-0.259972</v>
       </c>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.00324</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.00324</v>
+      </c>
       <c r="BF5" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.00324</v>
+        <v>0</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00324</v>
+        <v>-0.02</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BK5" t="n">
         <v>1.47</v>
       </c>
     </row>
@@ -1528,81 +1440,75 @@
         <v>0.84</v>
       </c>
       <c r="AJ6" t="n">
-        <v>98.97262000000001</v>
+        <v>5.6199</v>
       </c>
       <c r="AK6" t="n">
-        <v>98.05768</v>
+        <v>5.6193</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.6199</v>
+        <v>4597507</v>
       </c>
       <c r="AM6" t="n">
-        <v>5.6193</v>
+        <v>1933111</v>
       </c>
       <c r="AN6" t="n">
-        <v>4597507</v>
+        <v>2664395</v>
       </c>
       <c r="AO6" t="n">
-        <v>1933111</v>
+        <v>2.36</v>
       </c>
       <c r="AP6" t="n">
-        <v>2664395</v>
+        <v>1.46</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.01</v>
+        <v>23.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>23.91</v>
+        <v>367772</v>
       </c>
       <c r="AT6" t="n">
-        <v>367772</v>
+        <v>-0.409357</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.529727</v>
+        <v>-0.4094</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.487112</v>
+        <v>1.896096</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.409357</v>
+        <v>1.160214</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.4094</v>
+        <v>2.436662</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.896096</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1.160214</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.436662</v>
-      </c>
-      <c r="BB6" t="n">
         <v>-0.042128</v>
       </c>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.005012</v>
+      </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.005012</v>
+        <v>0.03</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.005012</v>
+        <v>0.02</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="BK6" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -1713,81 +1619,75 @@
         <v>0.73</v>
       </c>
       <c r="AJ7" t="n">
-        <v>99.35339</v>
+        <v>5.5805</v>
       </c>
       <c r="AK7" t="n">
-        <v>99.33126</v>
+        <v>5.5799</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.5805</v>
+        <v>4682852</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.5799</v>
+        <v>1974391</v>
       </c>
       <c r="AN7" t="n">
-        <v>4682852</v>
+        <v>2708461</v>
       </c>
       <c r="AO7" t="n">
-        <v>1974391</v>
+        <v>2.35</v>
       </c>
       <c r="AP7" t="n">
-        <v>2708461</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.05</v>
+        <v>24.21</v>
       </c>
       <c r="AS7" t="n">
-        <v>24.21</v>
+        <v>362204</v>
       </c>
       <c r="AT7" t="n">
-        <v>362204</v>
+        <v>-0.70108</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.384723</v>
+        <v>-0.701155</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.298807</v>
+        <v>1.856332</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.70108</v>
+        <v>2.135418</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.701155</v>
+        <v>1.653884</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.856332</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.135418</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.653884</v>
-      </c>
-      <c r="BB7" t="n">
         <v>-1.513981</v>
       </c>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.00406</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.00406</v>
+      </c>
       <c r="BF7" t="n">
-        <v>1.5</v>
+        <v>-0.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.00406</v>
+        <v>-0.06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.00406</v>
+        <v>0.04</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="BK7" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1898,81 +1798,75 @@
         <v>0.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>97.34401</v>
+        <v>5.3574</v>
       </c>
       <c r="AK8" t="n">
-        <v>90.45032</v>
+        <v>5.3568</v>
       </c>
       <c r="AL8" t="n">
-        <v>5.3574</v>
+        <v>4682131</v>
       </c>
       <c r="AM8" t="n">
-        <v>5.3568</v>
+        <v>1947035</v>
       </c>
       <c r="AN8" t="n">
-        <v>4682131</v>
+        <v>2735096</v>
       </c>
       <c r="AO8" t="n">
-        <v>1947035</v>
+        <v>2.51</v>
       </c>
       <c r="AP8" t="n">
-        <v>2735096</v>
+        <v>1.46</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.51</v>
+        <v>3.26</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.26</v>
+        <v>25.23</v>
       </c>
       <c r="AS8" t="n">
-        <v>25.23</v>
+        <v>358398</v>
       </c>
       <c r="AT8" t="n">
-        <v>358398</v>
+        <v>-3.99785</v>
       </c>
       <c r="AU8" t="n">
-        <v>-2.022457</v>
+        <v>-3.99828</v>
       </c>
       <c r="AV8" t="n">
-        <v>-8.94073</v>
+        <v>-0.015397</v>
       </c>
       <c r="AW8" t="n">
-        <v>-3.99785</v>
+        <v>-1.385541</v>
       </c>
       <c r="AX8" t="n">
-        <v>-3.99828</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.015397</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>-1.385541</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0.9834000000000001</v>
-      </c>
-      <c r="BB8" t="n">
         <v>-1.050789</v>
       </c>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.001433</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.001433</v>
+      </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001433</v>
+        <v>0.06</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001433</v>
+        <v>0.21</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="BK8" t="n">
         <v>1.02</v>
       </c>
     </row>
@@ -2083,81 +1977,75 @@
         <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>98.43725000000001</v>
+        <v>5.1394</v>
       </c>
       <c r="AK9" t="n">
-        <v>95.72214</v>
+        <v>5.1388</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.1394</v>
+        <v>4727818</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.1388</v>
+        <v>1971524</v>
       </c>
       <c r="AN9" t="n">
-        <v>4727818</v>
+        <v>2756295</v>
       </c>
       <c r="AO9" t="n">
-        <v>1971524</v>
+        <v>2.57</v>
       </c>
       <c r="AP9" t="n">
-        <v>2756295</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.57</v>
+        <v>3.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.38</v>
+        <v>25.63</v>
       </c>
       <c r="AS9" t="n">
-        <v>25.63</v>
+        <v>357740</v>
       </c>
       <c r="AT9" t="n">
-        <v>357740</v>
+        <v>-4.069138</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.123069</v>
+        <v>-4.069594</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.828415</v>
+        <v>0.975774</v>
       </c>
       <c r="AW9" t="n">
-        <v>-4.069138</v>
+        <v>1.257759</v>
       </c>
       <c r="AX9" t="n">
-        <v>-4.069594</v>
+        <v>0.775073</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.975774</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.257759</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.775073</v>
-      </c>
-      <c r="BB9" t="n">
         <v>-0.183595</v>
       </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.004849</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.004849</v>
+      </c>
       <c r="BF9" t="n">
-        <v>1.5</v>
+        <v>0.06</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.004849</v>
+        <v>-0.02</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.004849</v>
+        <v>0.12</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BK9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -2268,81 +2156,75 @@
         <v>1.71</v>
       </c>
       <c r="AJ10" t="n">
-        <v>99.55981</v>
+        <v>4.7378</v>
       </c>
       <c r="AK10" t="n">
-        <v>104.61484</v>
+        <v>4.7372</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.7378</v>
+        <v>4794583</v>
       </c>
       <c r="AM10" t="n">
-        <v>4.7372</v>
+        <v>1994119</v>
       </c>
       <c r="AN10" t="n">
-        <v>4794583</v>
+        <v>2800464</v>
       </c>
       <c r="AO10" t="n">
-        <v>1994119</v>
+        <v>2.66</v>
       </c>
       <c r="AP10" t="n">
-        <v>2800464</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.66</v>
+        <v>3.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.45</v>
+        <v>26.54</v>
       </c>
       <c r="AS10" t="n">
-        <v>26.54</v>
+        <v>353169</v>
       </c>
       <c r="AT10" t="n">
-        <v>353169</v>
+        <v>-7.814142</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.140381</v>
+        <v>-7.815054</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.290118</v>
+        <v>1.412174</v>
       </c>
       <c r="AW10" t="n">
-        <v>-7.814142</v>
+        <v>1.146068</v>
       </c>
       <c r="AX10" t="n">
-        <v>-7.815054</v>
+        <v>1.602477</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.412174</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.146068</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.602477</v>
-      </c>
-      <c r="BB10" t="n">
         <v>-1.277744</v>
       </c>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.002356</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.002356</v>
+      </c>
       <c r="BF10" t="n">
-        <v>1</v>
+        <v>0.09</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.002356</v>
+        <v>0.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.002356</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="BK10" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -2453,81 +2335,75 @@
         <v>1.04</v>
       </c>
       <c r="AJ11" t="n">
-        <v>99.51646</v>
+        <v>4.9191</v>
       </c>
       <c r="AK11" t="n">
-        <v>100.42352</v>
+        <v>4.9185</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.9191</v>
+        <v>4833732</v>
       </c>
       <c r="AM11" t="n">
-        <v>4.9185</v>
+        <v>2003312</v>
       </c>
       <c r="AN11" t="n">
-        <v>4833732</v>
+        <v>2830420</v>
       </c>
       <c r="AO11" t="n">
-        <v>2003312</v>
+        <v>2.72</v>
       </c>
       <c r="AP11" t="n">
-        <v>2830420</v>
+        <v>1.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.72</v>
+        <v>3.54</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.54</v>
+        <v>27.46</v>
       </c>
       <c r="AS11" t="n">
-        <v>27.46</v>
+        <v>345097</v>
       </c>
       <c r="AT11" t="n">
-        <v>345097</v>
+        <v>3.826671</v>
       </c>
       <c r="AU11" t="n">
-        <v>-0.043542</v>
+        <v>3.827155</v>
       </c>
       <c r="AV11" t="n">
-        <v>-4.00643</v>
+        <v>0.816526</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.826671</v>
+        <v>0.461006</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.827155</v>
+        <v>1.06968</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.816526</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.461006</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.06968</v>
-      </c>
-      <c r="BB11" t="n">
         <v>-2.285591</v>
       </c>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.001785</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.001785</v>
+      </c>
      